--- a/Design Files/Baseboard-v2.0/BOM/eSpark_BOM_Baseboard-v2.0.xlsx
+++ b/Design Files/Baseboard-v2.0/BOM/eSpark_BOM_Baseboard-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="488">
   <si>
     <t>Component list</t>
   </si>
@@ -357,18 +357,9 @@
     <t>68uF 50V SMD,D6.3xL7.7mm Aluminum Electrolytic Capacitors - SMD ROHS</t>
   </si>
   <si>
-    <t>CAP ALUM 220UF 20% 50V SMD</t>
-  </si>
-  <si>
-    <t>CAP ALUM 10uF 25V SMD</t>
-  </si>
-  <si>
     <t>47uF 6.3V 5Ω@100kHz ±10% CASE-A-3216 Tantalum Capacitors ROHS</t>
   </si>
   <si>
-    <t>330uF 16V ±20% SMD,D6.3xL7.7mm Aluminum Electrolytic Capacitors - SMD ROHS</t>
-  </si>
-  <si>
     <t>CAP TANT 100UF 20% 10V 1411</t>
   </si>
   <si>
@@ -429,15 +420,9 @@
     <t>1x2P 18A -40℃~+105℃ 250V Black 12~30 Straight pin 5.08mm 2.5 1 2 Plugin,P=5.08mm Screw terminal ROHS</t>
   </si>
   <si>
-    <t>CONN HEADER SMD R/A 11POS 1.25MM</t>
-  </si>
-  <si>
     <t>1x6P SH 1 1mm 6 SMD,P=1mm Wire To Board / Wire To Wire Connector ROHS</t>
   </si>
   <si>
-    <t>CONN U.FL RCPT STR 50 OHM SMD</t>
-  </si>
-  <si>
     <t>0.8mm mPCI-E Surface Mount 52 SMD,P=0.8mm Card Edge Connectors ROHS</t>
   </si>
   <si>
@@ -597,9 +582,6 @@
     <t>Case-A</t>
   </si>
   <si>
-    <t>GVT1C331M0607</t>
-  </si>
-  <si>
     <t>Case-B</t>
   </si>
   <si>
@@ -639,12 +621,6 @@
     <t>DB128L-5.08-2P-BK-S</t>
   </si>
   <si>
-    <t>53261-1171</t>
-  </si>
-  <si>
-    <t>U.FL-R-SMT-1(80)</t>
-  </si>
-  <si>
     <t>91304-99-052R2</t>
   </si>
   <si>
@@ -741,12 +717,6 @@
     <t>CC0402KRX7R9BB103</t>
   </si>
   <si>
-    <t>UCD1H221MNL1GS</t>
-  </si>
-  <si>
-    <t>RVT1E100M0405</t>
-  </si>
-  <si>
     <t>CA45-A-6.3V-47uF-K</t>
   </si>
   <si>
@@ -936,15 +906,9 @@
     <t>ROQANG</t>
   </si>
   <si>
-    <t>Nichicon</t>
-  </si>
-  <si>
     <t>CEC</t>
   </si>
   <si>
-    <t>Honor Elec</t>
-  </si>
-  <si>
     <t>Kyocera AVX</t>
   </si>
   <si>
@@ -999,9 +963,6 @@
     <t>BOOMELE</t>
   </si>
   <si>
-    <t>Hirose</t>
-  </si>
-  <si>
     <t>UMAX</t>
   </si>
   <si>
@@ -1077,18 +1038,9 @@
     <t>C5221836</t>
   </si>
   <si>
-    <t>C116211</t>
-  </si>
-  <si>
-    <t>C970655</t>
-  </si>
-  <si>
     <t>C129570</t>
   </si>
   <si>
-    <t>C2980164</t>
-  </si>
-  <si>
     <t>C7196</t>
   </si>
   <si>
@@ -1143,9 +1095,6 @@
     <t>C430601</t>
   </si>
   <si>
-    <t>C585957</t>
-  </si>
-  <si>
     <t>C404126</t>
   </si>
   <si>
@@ -1428,9 +1377,6 @@
     <t>--</t>
   </si>
   <si>
-    <t>C88374</t>
-  </si>
-  <si>
     <t>C705793</t>
   </si>
   <si>
@@ -1482,7 +1428,61 @@
     <t>chipsmall</t>
   </si>
   <si>
-    <t>Quote Required</t>
+    <t>CONN HEADER SMD 11POS 1.25MM</t>
+  </si>
+  <si>
+    <t>53398-1171</t>
+  </si>
+  <si>
+    <t>1 Inner bore SMA Board Edge Bend -55℃~+155℃ 50Ω Plugin RF Connectors / Coaxial Connectors ROHS</t>
+  </si>
+  <si>
+    <t>HJ-SMA508</t>
+  </si>
+  <si>
+    <t>HJ Tech</t>
+  </si>
+  <si>
+    <t>C1509209</t>
+  </si>
+  <si>
+    <t>CAP TANT 220UF 10% 10V 2917</t>
+  </si>
+  <si>
+    <t>Case-D</t>
+  </si>
+  <si>
+    <t>TAJD227K010RNJV</t>
+  </si>
+  <si>
+    <t>C8024</t>
+  </si>
+  <si>
+    <t>10uF 10V 8Ω@100kHz ±10% CASE-A-3216 Tantalum Capacitors ROHS</t>
+  </si>
+  <si>
+    <t>CA45-A-10V-10uF-K</t>
+  </si>
+  <si>
+    <t>CEC(Shenzhen Zhenhua XinYun Elec)</t>
+  </si>
+  <si>
+    <t>C128253</t>
+  </si>
+  <si>
+    <t>CAP TANT 330UF 20% 16V 2917</t>
+  </si>
+  <si>
+    <t>Case-E</t>
+  </si>
+  <si>
+    <t>TAJE337M016RNJ</t>
+  </si>
+  <si>
+    <t>C51599</t>
+  </si>
+  <si>
+    <t>C504827</t>
   </si>
 </sst>
 </file>
@@ -2153,38 +2153,6 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2219,6 +2187,38 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2596,15 +2596,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="68"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="80"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+      <c r="S1" s="81"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2654,7 +2654,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="69"/>
+      <c r="S3" s="82"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2679,7 +2679,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="70"/>
+      <c r="S4" s="83"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2704,7 +2704,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="70"/>
+      <c r="S5" s="83"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2725,7 +2725,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="70"/>
+      <c r="S6" s="83"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2746,7 +2746,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="70"/>
+      <c r="S7" s="83"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2767,7 +2767,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="70"/>
+      <c r="S8" s="83"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2784,46 +2784,46 @@
         <v>107</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="N9" s="30" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
       <c r="O9" s="30" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="R9" s="30" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="S9" s="30" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -2833,31 +2833,31 @@
         <v>1</v>
       </c>
       <c r="C10" s="53" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="D10" s="62" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="62" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="F10" s="62" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G10" s="62" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="H10" s="66" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="I10" s="66" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J10" s="66" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="K10" s="62" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L10" s="62">
         <v>1</v>
@@ -2867,19 +2867,19 @@
         <v>5</v>
       </c>
       <c r="N10" s="62" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="O10" s="62" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="P10" s="66" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="Q10" s="66" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="R10" s="63" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="S10" s="50"/>
     </row>
@@ -2899,22 +2899,22 @@
         <v>108</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J11" s="51" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -2927,7 +2927,7 @@
         <v>20</v>
       </c>
       <c r="O11" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P11" s="52">
         <v>2.01E-2</v>
@@ -2955,22 +2955,22 @@
         <v>109</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="L12" s="37">
         <v>25</v>
@@ -2983,7 +2983,7 @@
         <v>150</v>
       </c>
       <c r="O12" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P12" s="38">
         <v>1.0500000000000001E-2</v>
@@ -3011,22 +3011,22 @@
         <v>110</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="L13" s="51">
         <v>3</v>
@@ -3039,7 +3039,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P13" s="52">
         <v>8.9999999999999998E-4</v>
@@ -3067,22 +3067,22 @@
         <v>111</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="L14" s="37">
         <v>3</v>
@@ -3095,7 +3095,7 @@
         <v>20</v>
       </c>
       <c r="O14" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P14" s="38">
         <v>4.9099999999999998E-2</v>
@@ -3120,25 +3120,25 @@
         <v>33</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>112</v>
+        <v>475</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>240</v>
+        <v>477</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>352</v>
+        <v>478</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="L15" s="51">
         <v>2</v>
@@ -3148,22 +3148,22 @@
         <v>10</v>
       </c>
       <c r="N15" s="51">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O15" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P15" s="52">
-        <v>0.29670000000000002</v>
+        <v>0.27689999999999998</v>
       </c>
       <c r="Q15" s="52">
         <f t="shared" ref="Q15" si="6">P15*N15</f>
-        <v>4.4504999999999999</v>
+        <v>3.0458999999999996</v>
       </c>
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="46">
         <f>ROW(B16) - ROW($B$9)</f>
@@ -3176,25 +3176,25 @@
         <v>34</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>113</v>
+        <v>479</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>466</v>
+        <v>186</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>241</v>
+        <v>480</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>304</v>
+        <v>481</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>353</v>
+        <v>482</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="L16" s="37">
         <v>1</v>
@@ -3204,17 +3204,17 @@
         <v>5</v>
       </c>
       <c r="N16" s="37">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O16" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P16" s="38">
-        <v>2.7099999999999999E-2</v>
+        <v>7.0900000000000005E-2</v>
       </c>
       <c r="Q16" s="38">
         <f>P16*N16</f>
-        <v>0.54200000000000004</v>
+        <v>1.0635000000000001</v>
       </c>
       <c r="R16" s="37"/>
       <c r="S16" s="59"/>
@@ -3232,25 +3232,25 @@
         <v>35</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="L17" s="51">
         <v>1</v>
@@ -3263,7 +3263,7 @@
         <v>10</v>
       </c>
       <c r="O17" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P17" s="52">
         <v>6.3E-2</v>
@@ -3275,7 +3275,7 @@
       <c r="R17" s="51"/>
       <c r="S17" s="59"/>
     </row>
-    <row r="18" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="46">
         <f>ROW(B18) - ROW($B$9)</f>
@@ -3288,25 +3288,25 @@
         <v>36</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>115</v>
+        <v>483</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>192</v>
+        <v>485</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>355</v>
+        <v>486</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="L18" s="37">
         <v>1</v>
@@ -3316,17 +3316,17 @@
         <v>5</v>
       </c>
       <c r="N18" s="37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O18" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P18" s="38">
-        <v>6.7199999999999996E-2</v>
+        <v>1.7373000000000001</v>
       </c>
       <c r="Q18" s="38">
         <f>P18*N18</f>
-        <v>0.67199999999999993</v>
+        <v>10.4238</v>
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
@@ -3344,25 +3344,25 @@
         <v>37</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="H19" s="51" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="I19" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J19" s="51" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="L19" s="51">
         <v>1</v>
@@ -3375,7 +3375,7 @@
         <v>10</v>
       </c>
       <c r="O19" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P19" s="52">
         <v>0.26129999999999998</v>
@@ -3400,25 +3400,25 @@
         <v>38</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G20" s="62" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="L20" s="37">
         <v>4</v>
@@ -3431,7 +3431,7 @@
         <v>30</v>
       </c>
       <c r="O20" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P20" s="38">
         <v>4.2000000000000003E-2</v>
@@ -3456,25 +3456,25 @@
         <v>39</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H21" s="51" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J21" s="51" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="L21" s="51">
         <v>2</v>
@@ -3487,7 +3487,7 @@
         <v>50</v>
       </c>
       <c r="O21" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P21" s="52">
         <v>1.0800000000000001E-2</v>
@@ -3512,25 +3512,25 @@
         <v>40</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="L22" s="37">
         <v>2</v>
@@ -3543,7 +3543,7 @@
         <v>100</v>
       </c>
       <c r="O22" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P22" s="38">
         <v>1E-3</v>
@@ -3568,25 +3568,25 @@
         <v>41</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="H23" s="51" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I23" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="K23" s="51" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="L23" s="51">
         <v>3</v>
@@ -3599,7 +3599,7 @@
         <v>100</v>
       </c>
       <c r="O23" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P23" s="52">
         <v>3.8999999999999998E-3</v>
@@ -3624,25 +3624,25 @@
         <v>42</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J24" s="37" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="K24" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L24" s="37">
         <v>1</v>
@@ -3655,7 +3655,7 @@
         <v>10</v>
       </c>
       <c r="O24" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P24" s="38">
         <v>5.5599999999999997E-2</v>
@@ -3680,25 +3680,25 @@
         <v>43</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="H25" s="51" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="I25" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J25" s="51" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="K25" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L25" s="51">
         <v>1</v>
@@ -3711,7 +3711,7 @@
         <v>10</v>
       </c>
       <c r="O25" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P25" s="52">
         <v>4.4600000000000001E-2</v>
@@ -3736,25 +3736,25 @@
         <v>44</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="K26" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L26" s="37">
         <v>1</v>
@@ -3767,7 +3767,7 @@
         <v>6</v>
       </c>
       <c r="O26" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P26" s="38">
         <v>0.46939999999999998</v>
@@ -3792,25 +3792,25 @@
         <v>45</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J27" s="51" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="K27" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L27" s="51">
         <v>1</v>
@@ -3823,7 +3823,7 @@
         <v>10</v>
       </c>
       <c r="O27" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P27" s="52">
         <v>3.56E-2</v>
@@ -3848,25 +3848,25 @@
         <v>46</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="K28" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L28" s="37">
         <v>3</v>
@@ -3879,7 +3879,7 @@
         <v>20</v>
       </c>
       <c r="O28" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P28" s="38">
         <v>2.46E-2</v>
@@ -3904,25 +3904,25 @@
         <v>47</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="H29" s="51" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J29" s="51" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L29" s="51">
         <v>2</v>
@@ -3935,7 +3935,7 @@
         <v>20</v>
       </c>
       <c r="O29" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P29" s="52">
         <v>2.3400000000000001E-2</v>
@@ -3960,25 +3960,25 @@
         <v>48</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L30" s="37">
         <v>4</v>
@@ -3991,7 +3991,7 @@
         <v>25</v>
       </c>
       <c r="O30" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P30" s="38">
         <v>0.1351</v>
@@ -4016,25 +4016,25 @@
         <v>49</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="G31" s="51" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="H31" s="51" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J31" s="51" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L31" s="51">
         <v>4</v>
@@ -4047,7 +4047,7 @@
         <v>30</v>
       </c>
       <c r="O31" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P31" s="52">
         <v>4.7500000000000001E-2</v>
@@ -4072,25 +4072,25 @@
         <v>50</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J32" s="37" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="K32" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L32" s="37">
         <v>1</v>
@@ -4103,7 +4103,7 @@
         <v>10</v>
       </c>
       <c r="O32" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P32" s="38">
         <v>0.2286</v>
@@ -4128,25 +4128,25 @@
         <v>51</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="H33" s="51" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="K33" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L33" s="51">
         <v>1</v>
@@ -4159,7 +4159,7 @@
         <v>6</v>
       </c>
       <c r="O33" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P33" s="52">
         <v>1.1482000000000001</v>
@@ -4184,25 +4184,25 @@
         <v>52</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J34" s="37" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="K34" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L34" s="37">
         <v>4</v>
@@ -4215,7 +4215,7 @@
         <v>30</v>
       </c>
       <c r="O34" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P34" s="38">
         <v>5.6099999999999997E-2</v>
@@ -4240,25 +4240,25 @@
         <v>53</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F35" s="51" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G35" s="51" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="H35" s="51" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="I35" s="61" t="s">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="J35" s="51" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="K35" s="51" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="L35" s="51">
         <v>1</v>
@@ -4271,7 +4271,7 @@
         <v>10</v>
       </c>
       <c r="O35" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P35" s="52">
         <v>8.8300000000000003E-2</v>
@@ -4296,25 +4296,25 @@
         <v>54</v>
       </c>
       <c r="E36" s="37" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F36" s="51" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="K36" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L36" s="37">
         <v>8</v>
@@ -4327,7 +4327,7 @@
         <v>45</v>
       </c>
       <c r="O36" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P36" s="38">
         <v>0.2316</v>
@@ -4352,25 +4352,25 @@
         <v>55</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F37" s="51" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G37" s="51" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="H37" s="51" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="I37" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J37" s="51" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="K37" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L37" s="51">
         <v>1</v>
@@ -4383,7 +4383,7 @@
         <v>10</v>
       </c>
       <c r="O37" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P37" s="52">
         <v>0.21590000000000001</v>
@@ -4408,25 +4408,25 @@
         <v>56</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F38" s="51" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="K38" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L38" s="37">
         <v>4</v>
@@ -4439,7 +4439,7 @@
         <v>25</v>
       </c>
       <c r="O38" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P38" s="38">
         <v>0.17299999999999999</v>
@@ -4464,25 +4464,25 @@
         <v>57</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>136</v>
+        <v>469</v>
       </c>
       <c r="F39" s="51" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G39" s="51" t="s">
-        <v>206</v>
+        <v>470</v>
       </c>
       <c r="H39" s="51" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="I39" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J39" s="51" t="s">
-        <v>374</v>
+        <v>487</v>
       </c>
       <c r="K39" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L39" s="51">
         <v>1</v>
@@ -4492,17 +4492,17 @@
         <v>5</v>
       </c>
       <c r="N39" s="51">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O39" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P39" s="52">
-        <v>0.36749999999999999</v>
+        <v>0.3211</v>
       </c>
       <c r="Q39" s="52">
         <f t="shared" ref="Q39" si="30">P39*N39</f>
-        <v>2.2050000000000001</v>
+        <v>3.2109999999999999</v>
       </c>
       <c r="R39" s="51"/>
       <c r="S39" s="59"/>
@@ -4520,25 +4520,25 @@
         <v>58</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F40" s="51" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L40" s="37">
         <v>1</v>
@@ -4551,7 +4551,7 @@
         <v>12</v>
       </c>
       <c r="O40" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P40" s="38">
         <v>7.0400000000000004E-2</v>
@@ -4563,38 +4563,36 @@
       <c r="R40" s="37"/>
       <c r="S40" s="59"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" ht="36" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="47">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C41" s="54" t="s">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="D41" s="51" t="s">
         <v>59</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>138</v>
+        <v>471</v>
       </c>
       <c r="F41" s="51" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G41" s="51" t="s">
-        <v>207</v>
+        <v>472</v>
       </c>
       <c r="H41" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="I41" s="51" t="s">
-        <v>460</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="I41" s="51"/>
       <c r="J41" s="51" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="K41" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L41" s="51">
         <v>1</v>
@@ -4604,17 +4602,17 @@
         <v>5</v>
       </c>
       <c r="N41" s="51">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O41" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P41" s="52">
-        <v>7.9600000000000004E-2</v>
+        <v>0.91159999999999997</v>
       </c>
       <c r="Q41" s="52">
         <f t="shared" ref="Q41" si="32">P41*N41</f>
-        <v>0.79600000000000004</v>
+        <v>5.4695999999999998</v>
       </c>
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
@@ -4632,25 +4630,25 @@
         <v>60</v>
       </c>
       <c r="E42" s="37" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F42" s="51" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L42" s="37">
         <v>2</v>
@@ -4663,7 +4661,7 @@
         <v>11</v>
       </c>
       <c r="O42" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P42" s="38">
         <v>0.81459999999999999</v>
@@ -4688,25 +4686,25 @@
         <v>61</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F43" s="51" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G43" s="51" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="H43" s="51" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="I43" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J43" s="51" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="K43" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L43" s="51">
         <v>3</v>
@@ -4719,7 +4717,7 @@
         <v>16</v>
       </c>
       <c r="O43" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P43" s="52">
         <v>0.32619999999999999</v>
@@ -4744,25 +4742,25 @@
         <v>62</v>
       </c>
       <c r="E44" s="37" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F44" s="51" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J44" s="37" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="L44" s="37">
         <v>1</v>
@@ -4775,7 +4773,7 @@
         <v>10</v>
       </c>
       <c r="O44" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P44" s="38">
         <v>0.2137</v>
@@ -4800,25 +4798,25 @@
         <v>63</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F45" s="51" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G45" s="51" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="H45" s="51" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="I45" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J45" s="51" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="K45" s="51" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="L45" s="51">
         <v>1</v>
@@ -4831,7 +4829,7 @@
         <v>50</v>
       </c>
       <c r="O45" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P45" s="52">
         <v>8.3000000000000001E-3</v>
@@ -4856,25 +4854,25 @@
         <v>64</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L46" s="37">
         <v>2</v>
@@ -4887,7 +4885,7 @@
         <v>20</v>
       </c>
       <c r="O46" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P46" s="38">
         <v>5.7599999999999998E-2</v>
@@ -4912,25 +4910,25 @@
         <v>65</v>
       </c>
       <c r="E47" s="51" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F47" s="51" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="G47" s="51" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="H47" s="51" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="I47" s="61" t="s">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="J47" s="51" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="K47" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L47" s="51">
         <v>1</v>
@@ -4943,7 +4941,7 @@
         <v>10</v>
       </c>
       <c r="O47" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P47" s="52">
         <v>5.1499999999999997E-2</v>
@@ -4962,31 +4960,31 @@
         <v>39</v>
       </c>
       <c r="C48" s="53" t="s">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="D48" s="62" t="s">
         <v>66</v>
       </c>
       <c r="E48" s="62" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F48" s="62" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G48" s="62" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="H48" s="62" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="I48" s="62" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J48" s="62" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="K48" s="62" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L48" s="62">
         <v>10</v>
@@ -4996,19 +4994,19 @@
         <v>50</v>
       </c>
       <c r="N48" s="62" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="O48" s="62" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="P48" s="62" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="Q48" s="62" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="R48" s="63" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="S48" s="59"/>
     </row>
@@ -5019,29 +5017,29 @@
         <v>40</v>
       </c>
       <c r="C49" s="54" t="s">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="D49" s="51" t="s">
         <v>67</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F49" s="51" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="G49" s="51" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="H49" s="51" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="I49" s="51"/>
       <c r="J49" s="51" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="K49" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L49" s="51">
         <v>1</v>
@@ -5054,7 +5052,7 @@
         <v>20</v>
       </c>
       <c r="O49" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P49" s="52">
         <v>2.1000000000000001E-2</v>
@@ -5079,25 +5077,25 @@
         <v>68</v>
       </c>
       <c r="E50" s="37" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G50" s="62" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="I50" s="37" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="J50" s="37" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="K50" s="37" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="L50" s="37">
         <v>2</v>
@@ -5110,7 +5108,7 @@
         <v>20</v>
       </c>
       <c r="O50" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P50" s="38">
         <v>2.1700000000000001E-2</v>
@@ -5135,23 +5133,23 @@
         <v>69</v>
       </c>
       <c r="E51" s="51" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F51" s="51" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G51" s="51" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="H51" s="51" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="I51" s="51"/>
       <c r="J51" s="51" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="K51" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L51" s="51">
         <v>1</v>
@@ -5164,7 +5162,7 @@
         <v>10</v>
       </c>
       <c r="O51" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P51" s="52">
         <v>0.18260000000000001</v>
@@ -5189,23 +5187,23 @@
         <v>70</v>
       </c>
       <c r="E52" s="37" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F52" s="37" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="H52" s="37" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I52" s="37"/>
       <c r="J52" s="37" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="K52" s="37" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="L52" s="37">
         <v>1</v>
@@ -5218,7 +5216,7 @@
         <v>100</v>
       </c>
       <c r="O52" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P52" s="38">
         <v>2.5999999999999999E-3</v>
@@ -5243,23 +5241,23 @@
         <v>71</v>
       </c>
       <c r="E53" s="51" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F53" s="51" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G53" s="51" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="H53" s="51" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I53" s="51"/>
       <c r="J53" s="51" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="K53" s="51" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="L53" s="51">
         <v>25</v>
@@ -5272,7 +5270,7 @@
         <v>200</v>
       </c>
       <c r="O53" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P53" s="52">
         <v>8.9999999999999998E-4</v>
@@ -5297,25 +5295,25 @@
         <v>72</v>
       </c>
       <c r="E54" s="37" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F54" s="37" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G54" s="62" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="H54" s="37" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I54" s="37" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="J54" s="37" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="K54" s="37" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="L54" s="37">
         <v>7</v>
@@ -5328,7 +5326,7 @@
         <v>100</v>
       </c>
       <c r="O54" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P54" s="38">
         <v>8.9999999999999998E-4</v>
@@ -5353,25 +5351,25 @@
         <v>73</v>
       </c>
       <c r="E55" s="51" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F55" s="51" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="G55" s="51" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="H55" s="51" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="I55" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J55" s="51" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="K55" s="51" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="L55" s="51">
         <v>1</v>
@@ -5384,7 +5382,7 @@
         <v>100</v>
       </c>
       <c r="O55" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P55" s="52">
         <v>1E-3</v>
@@ -5409,25 +5407,25 @@
         <v>74</v>
       </c>
       <c r="E56" s="37" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F56" s="37" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="H56" s="37" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I56" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J56" s="37" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="K56" s="37" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="L56" s="37">
         <v>2</v>
@@ -5440,7 +5438,7 @@
         <v>100</v>
       </c>
       <c r="O56" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P56" s="38">
         <v>8.0000000000000004E-4</v>
@@ -5465,25 +5463,25 @@
         <v>75</v>
       </c>
       <c r="E57" s="51" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F57" s="51" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G57" s="62" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="H57" s="51" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I57" s="51" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="J57" s="51" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="K57" s="51" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="L57" s="51">
         <v>1</v>
@@ -5496,7 +5494,7 @@
         <v>100</v>
       </c>
       <c r="O57" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P57" s="52">
         <v>5.0000000000000001E-4</v>
@@ -5521,23 +5519,23 @@
         <v>76</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I58" s="37"/>
       <c r="J58" s="37" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="K58" s="37" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="L58" s="37">
         <v>2</v>
@@ -5550,7 +5548,7 @@
         <v>100</v>
       </c>
       <c r="O58" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P58" s="38">
         <v>6.9999999999999999E-4</v>
@@ -5575,23 +5573,23 @@
         <v>77</v>
       </c>
       <c r="E59" s="51" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F59" s="51" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G59" s="51" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="H59" s="51" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I59" s="51"/>
       <c r="J59" s="51" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="K59" s="51" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="L59" s="51">
         <v>22</v>
@@ -5604,7 +5602,7 @@
         <v>200</v>
       </c>
       <c r="O59" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P59" s="52">
         <v>6.9999999999999999E-4</v>
@@ -5629,23 +5627,23 @@
         <v>78</v>
       </c>
       <c r="E60" s="37" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I60" s="37"/>
       <c r="J60" s="37" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="K60" s="37" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="L60" s="37">
         <v>1</v>
@@ -5658,7 +5656,7 @@
         <v>100</v>
       </c>
       <c r="O60" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P60" s="38">
         <v>5.9999999999999995E-4</v>
@@ -5683,23 +5681,23 @@
         <v>79</v>
       </c>
       <c r="E61" s="37" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="H61" s="37" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I61" s="37"/>
       <c r="J61" s="37" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="K61" s="37" t="s">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="L61" s="37">
         <v>4</v>
@@ -5712,7 +5710,7 @@
         <v>100</v>
       </c>
       <c r="O61" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P61" s="38">
         <v>6.9999999999999999E-4</v>
@@ -5737,23 +5735,23 @@
         <v>80</v>
       </c>
       <c r="E62" s="51" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F62" s="51" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="G62" s="51" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="H62" s="51" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I62" s="51"/>
       <c r="J62" s="51" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="K62" s="51" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="L62" s="51">
         <v>1</v>
@@ -5766,7 +5764,7 @@
         <v>100</v>
       </c>
       <c r="O62" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P62" s="52">
         <v>1.1999999999999999E-3</v>
@@ -5791,23 +5789,23 @@
         <v>81</v>
       </c>
       <c r="E63" s="37" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="H63" s="37" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I63" s="37"/>
       <c r="J63" s="37" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="K63" s="37" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="L63" s="37">
         <v>1</v>
@@ -5820,7 +5818,7 @@
         <v>100</v>
       </c>
       <c r="O63" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P63" s="38">
         <v>2.5000000000000001E-3</v>
@@ -5845,23 +5843,23 @@
         <v>82</v>
       </c>
       <c r="E64" s="51" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F64" s="51" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="G64" s="51" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="H64" s="51" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I64" s="51"/>
       <c r="J64" s="51" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="K64" s="51" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="L64" s="51">
         <v>1</v>
@@ -5874,7 +5872,7 @@
         <v>20</v>
       </c>
       <c r="O64" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P64" s="52">
         <v>2.5999999999999999E-2</v>
@@ -5896,26 +5894,26 @@
         <v>21</v>
       </c>
       <c r="D65" s="51" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="E65" s="37" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="F65" s="37" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G65" s="37" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I65" s="37"/>
       <c r="J65" s="37" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="K65" s="37" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="L65" s="37">
         <v>10</v>
@@ -5928,7 +5926,7 @@
         <v>100</v>
       </c>
       <c r="O65" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P65" s="38">
         <v>6.9999999999999999E-4</v>
@@ -5953,25 +5951,25 @@
         <v>83</v>
       </c>
       <c r="E66" s="51" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F66" s="51" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G66" s="62" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="H66" s="51" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="I66" s="51" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="J66" s="51" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="K66" s="51" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="L66" s="51">
         <v>4</v>
@@ -5984,7 +5982,7 @@
         <v>100</v>
       </c>
       <c r="O66" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P66" s="52">
         <v>4.0000000000000002E-4</v>
@@ -6009,23 +6007,23 @@
         <v>84</v>
       </c>
       <c r="E67" s="37" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="G67" s="37" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="H67" s="37" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I67" s="37"/>
       <c r="J67" s="37" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="K67" s="37" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="L67" s="37">
         <v>1</v>
@@ -6038,7 +6036,7 @@
         <v>100</v>
       </c>
       <c r="O67" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P67" s="38">
         <v>1.1999999999999999E-3</v>
@@ -6063,23 +6061,23 @@
         <v>85</v>
       </c>
       <c r="E68" s="51" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F68" s="51" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G68" s="51" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="H68" s="51" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="I68" s="51"/>
       <c r="J68" s="51" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="K68" s="51" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="L68" s="51">
         <v>1</v>
@@ -6092,7 +6090,7 @@
         <v>10</v>
       </c>
       <c r="O68" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P68" s="52">
         <v>5.3600000000000002E-2</v>
@@ -6117,23 +6115,23 @@
         <v>86</v>
       </c>
       <c r="E69" s="37" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F69" s="37" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="G69" s="37" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="H69" s="37" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I69" s="37"/>
       <c r="J69" s="37" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="K69" s="37" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="L69" s="37">
         <v>2</v>
@@ -6146,7 +6144,7 @@
         <v>100</v>
       </c>
       <c r="O69" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P69" s="38">
         <v>1.1999999999999999E-3</v>
@@ -6171,23 +6169,23 @@
         <v>87</v>
       </c>
       <c r="E70" s="51" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F70" s="51" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G70" s="51" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="H70" s="51" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="I70" s="51"/>
       <c r="J70" s="51" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="K70" s="51" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="L70" s="51">
         <v>1</v>
@@ -6200,7 +6198,7 @@
         <v>100</v>
       </c>
       <c r="O70" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P70" s="52">
         <v>6.9999999999999999E-4</v>
@@ -6225,25 +6223,25 @@
         <v>88</v>
       </c>
       <c r="E71" s="64" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F71" s="65" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G71" s="64" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="H71" s="64" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="I71" s="64" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J71" s="64" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="K71" s="64" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L71" s="64">
         <v>2</v>
@@ -6253,19 +6251,19 @@
         <v>10</v>
       </c>
       <c r="N71" s="64" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="O71" s="64" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="P71" s="64" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="Q71" s="64" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="R71" s="63" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="S71" s="59"/>
     </row>
@@ -6282,25 +6280,25 @@
         <v>89</v>
       </c>
       <c r="E72" s="51" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="F72" s="51" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G72" s="51" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="H72" s="51" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="I72" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J72" s="51" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="K72" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L72" s="51">
         <v>1</v>
@@ -6313,7 +6311,7 @@
         <v>10</v>
       </c>
       <c r="O72" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P72" s="52">
         <v>0.1275</v>
@@ -6338,25 +6336,25 @@
         <v>90</v>
       </c>
       <c r="E73" s="37" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F73" s="37" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G73" s="37" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="H73" s="37" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="I73" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J73" s="37" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="K73" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L73" s="37">
         <v>1</v>
@@ -6369,7 +6367,7 @@
         <v>6</v>
       </c>
       <c r="O73" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P73" s="38">
         <v>0.82569999999999999</v>
@@ -6394,25 +6392,25 @@
         <v>91</v>
       </c>
       <c r="E74" s="51" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F74" s="51" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="G74" s="51" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="H74" s="51" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="I74" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J74" s="51" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="K74" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L74" s="51">
         <v>1</v>
@@ -6425,7 +6423,7 @@
         <v>6</v>
       </c>
       <c r="O74" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P74" s="52">
         <v>0.70009999999999994</v>
@@ -6450,25 +6448,25 @@
         <v>92</v>
       </c>
       <c r="E75" s="37" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F75" s="37" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="G75" s="37" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="H75" s="37" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="I75" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J75" s="37" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="K75" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L75" s="37">
         <v>1</v>
@@ -6481,7 +6479,7 @@
         <v>10</v>
       </c>
       <c r="O75" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P75" s="38">
         <v>0.32279999999999998</v>
@@ -6506,25 +6504,25 @@
         <v>93</v>
       </c>
       <c r="E76" s="51" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F76" s="51" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="G76" s="51" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="H76" s="51" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="I76" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J76" s="51" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="K76" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L76" s="51">
         <v>1</v>
@@ -6537,7 +6535,7 @@
         <v>6</v>
       </c>
       <c r="O76" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P76" s="52">
         <v>1.3062</v>
@@ -6562,23 +6560,23 @@
         <v>94</v>
       </c>
       <c r="E77" s="37" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F77" s="37" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="G77" s="37" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="H77" s="37" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="I77" s="37"/>
       <c r="J77" s="37" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="K77" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L77" s="37">
         <v>1</v>
@@ -6591,7 +6589,7 @@
         <v>6</v>
       </c>
       <c r="O77" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P77" s="38">
         <v>0.3644</v>
@@ -6603,117 +6601,117 @@
       <c r="R77" s="37"/>
       <c r="S77" s="59"/>
     </row>
-    <row r="78" spans="1:19" s="84" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="77"/>
-      <c r="B78" s="78">
+    <row r="78" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="67"/>
+      <c r="B78" s="68">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="C78" s="79" t="s">
+      <c r="C78" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="D78" s="80" t="s">
+      <c r="D78" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="E78" s="80" t="s">
-        <v>175</v>
-      </c>
-      <c r="F78" s="80" t="s">
-        <v>227</v>
-      </c>
-      <c r="G78" s="80" t="s">
-        <v>290</v>
-      </c>
-      <c r="H78" s="80" t="s">
-        <v>342</v>
-      </c>
-      <c r="I78" s="80" t="s">
-        <v>460</v>
-      </c>
-      <c r="J78" s="80" t="s">
-        <v>460</v>
-      </c>
-      <c r="K78" s="80" t="s">
-        <v>460</v>
-      </c>
-      <c r="L78" s="80">
+      <c r="E78" s="70" t="s">
+        <v>170</v>
+      </c>
+      <c r="F78" s="70" t="s">
+        <v>219</v>
+      </c>
+      <c r="G78" s="70" t="s">
+        <v>280</v>
+      </c>
+      <c r="H78" s="70" t="s">
+        <v>329</v>
+      </c>
+      <c r="I78" s="70" t="s">
+        <v>443</v>
+      </c>
+      <c r="J78" s="70" t="s">
+        <v>443</v>
+      </c>
+      <c r="K78" s="70" t="s">
+        <v>443</v>
+      </c>
+      <c r="L78" s="70">
         <v>1</v>
       </c>
-      <c r="M78" s="80">
+      <c r="M78" s="70">
         <f t="shared" ref="M78" si="67">L78*5</f>
         <v>5</v>
       </c>
-      <c r="N78" s="80">
+      <c r="N78" s="70">
         <v>6</v>
       </c>
-      <c r="O78" s="81" t="s">
-        <v>486</v>
-      </c>
-      <c r="P78" s="82">
+      <c r="O78" s="71" t="s">
+        <v>468</v>
+      </c>
+      <c r="P78" s="72">
         <v>2.5099999999999998</v>
       </c>
-      <c r="Q78" s="82">
+      <c r="Q78" s="72">
         <f t="shared" ref="Q78" si="68">P78*N78</f>
         <v>15.059999999999999</v>
       </c>
-      <c r="R78" s="80"/>
-      <c r="S78" s="83"/>
-    </row>
-    <row r="79" spans="1:19" s="84" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="77"/>
-      <c r="B79" s="85">
+      <c r="R78" s="70"/>
+      <c r="S78" s="73"/>
+    </row>
+    <row r="79" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="67"/>
+      <c r="B79" s="75">
         <f>ROW(B79) - ROW($B$9)</f>
         <v>70</v>
       </c>
-      <c r="C79" s="86" t="s">
+      <c r="C79" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="D79" s="87" t="s">
+      <c r="D79" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="E79" s="87" t="s">
-        <v>176</v>
-      </c>
-      <c r="F79" s="87" t="s">
-        <v>228</v>
-      </c>
-      <c r="G79" s="87" t="s">
-        <v>291</v>
-      </c>
-      <c r="H79" s="87" t="s">
-        <v>340</v>
-      </c>
-      <c r="I79" s="87" t="s">
-        <v>460</v>
-      </c>
-      <c r="J79" s="87" t="s">
-        <v>460</v>
-      </c>
-      <c r="K79" s="87" t="s">
-        <v>460</v>
-      </c>
-      <c r="L79" s="87">
+      <c r="E79" s="77" t="s">
+        <v>171</v>
+      </c>
+      <c r="F79" s="77" t="s">
+        <v>220</v>
+      </c>
+      <c r="G79" s="77" t="s">
+        <v>281</v>
+      </c>
+      <c r="H79" s="77" t="s">
+        <v>327</v>
+      </c>
+      <c r="I79" s="77" t="s">
+        <v>443</v>
+      </c>
+      <c r="J79" s="77" t="s">
+        <v>443</v>
+      </c>
+      <c r="K79" s="77" t="s">
+        <v>443</v>
+      </c>
+      <c r="L79" s="77">
         <v>1</v>
       </c>
-      <c r="M79" s="87">
+      <c r="M79" s="77">
         <f>L79*5</f>
         <v>5</v>
       </c>
-      <c r="N79" s="87">
+      <c r="N79" s="77">
         <v>6</v>
       </c>
-      <c r="O79" s="81" t="s">
-        <v>486</v>
-      </c>
-      <c r="P79" s="88">
+      <c r="O79" s="71" t="s">
+        <v>468</v>
+      </c>
+      <c r="P79" s="78">
         <v>3.4329999999999998</v>
       </c>
-      <c r="Q79" s="88">
+      <c r="Q79" s="78">
         <f>P79*N79</f>
         <v>20.597999999999999</v>
       </c>
-      <c r="R79" s="87"/>
-      <c r="S79" s="83"/>
+      <c r="R79" s="77"/>
+      <c r="S79" s="73"/>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
@@ -6728,23 +6726,23 @@
         <v>97</v>
       </c>
       <c r="E80" s="51" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F80" s="51" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="G80" s="51" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="H80" s="51" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="I80" s="51"/>
       <c r="J80" s="51" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="K80" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L80" s="51">
         <v>1</v>
@@ -6757,7 +6755,7 @@
         <v>6</v>
       </c>
       <c r="O80" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P80" s="52">
         <v>4.6247999999999996</v>
@@ -6769,61 +6767,61 @@
       <c r="R80" s="51"/>
       <c r="S80" s="59"/>
     </row>
-    <row r="81" spans="1:19" s="84" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="77"/>
-      <c r="B81" s="85">
+    <row r="81" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="67"/>
+      <c r="B81" s="75">
         <f>ROW(B81) - ROW($B$9)</f>
         <v>72</v>
       </c>
-      <c r="C81" s="86" t="s">
+      <c r="C81" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="D81" s="87" t="s">
+      <c r="D81" s="77" t="s">
         <v>98</v>
       </c>
-      <c r="E81" s="87" t="s">
-        <v>178</v>
-      </c>
-      <c r="F81" s="87" t="s">
-        <v>230</v>
-      </c>
-      <c r="G81" s="87" t="s">
-        <v>293</v>
-      </c>
-      <c r="H81" s="87" t="s">
-        <v>344</v>
-      </c>
-      <c r="I81" s="87" t="s">
-        <v>460</v>
-      </c>
-      <c r="J81" s="87" t="s">
-        <v>460</v>
-      </c>
-      <c r="K81" s="87" t="s">
-        <v>460</v>
-      </c>
-      <c r="L81" s="87">
+      <c r="E81" s="77" t="s">
+        <v>173</v>
+      </c>
+      <c r="F81" s="77" t="s">
+        <v>222</v>
+      </c>
+      <c r="G81" s="77" t="s">
+        <v>283</v>
+      </c>
+      <c r="H81" s="77" t="s">
+        <v>331</v>
+      </c>
+      <c r="I81" s="77" t="s">
+        <v>443</v>
+      </c>
+      <c r="J81" s="77" t="s">
+        <v>443</v>
+      </c>
+      <c r="K81" s="77" t="s">
+        <v>443</v>
+      </c>
+      <c r="L81" s="77">
         <v>1</v>
       </c>
-      <c r="M81" s="87">
+      <c r="M81" s="77">
         <f>L81*5</f>
         <v>5</v>
       </c>
-      <c r="N81" s="87">
+      <c r="N81" s="77">
         <v>6</v>
       </c>
-      <c r="O81" s="81" t="s">
-        <v>486</v>
-      </c>
-      <c r="P81" s="88"/>
-      <c r="Q81" s="88">
+      <c r="O81" s="71" t="s">
+        <v>468</v>
+      </c>
+      <c r="P81" s="78">
+        <v>7.9</v>
+      </c>
+      <c r="Q81" s="78">
         <f>P81*N81</f>
-        <v>0</v>
-      </c>
-      <c r="R81" s="89" t="s">
-        <v>487</v>
-      </c>
-      <c r="S81" s="83"/>
+        <v>47.400000000000006</v>
+      </c>
+      <c r="R81" s="79"/>
+      <c r="S81" s="73"/>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
@@ -6838,25 +6836,25 @@
         <v>99</v>
       </c>
       <c r="E82" s="51" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F82" s="51" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G82" s="51" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="H82" s="51" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="I82" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J82" s="51" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="K82" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L82" s="51">
         <v>3</v>
@@ -6869,7 +6867,7 @@
         <v>16</v>
       </c>
       <c r="O82" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P82" s="52">
         <v>1.7437</v>
@@ -6894,25 +6892,25 @@
         <v>100</v>
       </c>
       <c r="E83" s="37" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F83" s="37" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="G83" s="37" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="H83" s="37" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="I83" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J83" s="37" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="K83" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L83" s="37">
         <v>1</v>
@@ -6925,7 +6923,7 @@
         <v>10</v>
       </c>
       <c r="O83" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P83" s="38">
         <v>7.7799999999999994E-2</v>
@@ -6950,25 +6948,25 @@
         <v>101</v>
       </c>
       <c r="E84" s="51" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F84" s="51" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="G84" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="H84" s="51" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="I84" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J84" s="51" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="K84" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L84" s="51">
         <v>1</v>
@@ -6981,7 +6979,7 @@
         <v>6</v>
       </c>
       <c r="O84" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P84" s="52">
         <v>0.77800000000000002</v>
@@ -7006,25 +7004,25 @@
         <v>102</v>
       </c>
       <c r="E85" s="37" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F85" s="37" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G85" s="37" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="H85" s="37" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="I85" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J85" s="37" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="K85" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L85" s="37">
         <v>1</v>
@@ -7037,7 +7035,7 @@
         <v>6</v>
       </c>
       <c r="O85" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P85" s="38">
         <v>0.41049999999999998</v>
@@ -7062,25 +7060,25 @@
         <v>103</v>
       </c>
       <c r="E86" s="51" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F86" s="51" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="G86" s="51" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="H86" s="51" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="I86" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J86" s="51" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="K86" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L86" s="51">
         <v>1</v>
@@ -7093,7 +7091,7 @@
         <v>6</v>
       </c>
       <c r="O86" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P86" s="52">
         <v>1.1837</v>
@@ -7118,25 +7116,25 @@
         <v>104</v>
       </c>
       <c r="E87" s="37" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F87" s="37" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="G87" s="37" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="H87" s="37" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="I87" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J87" s="37" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="K87" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="L87" s="37">
         <v>1</v>
@@ -7149,7 +7147,7 @@
         <v>6</v>
       </c>
       <c r="O87" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P87" s="38">
         <v>1.2107000000000001</v>
@@ -7174,25 +7172,25 @@
         <v>105</v>
       </c>
       <c r="E88" s="51" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F88" s="51" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G88" s="51" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="H88" s="51" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="I88" s="51" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J88" s="51" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="K88" s="51" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="L88" s="51">
         <v>1</v>
@@ -7205,7 +7203,7 @@
         <v>10</v>
       </c>
       <c r="O88" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P88" s="52">
         <v>0.08</v>
@@ -7230,25 +7228,25 @@
         <v>106</v>
       </c>
       <c r="E89" s="37" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F89" s="51" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G89" s="37" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="H89" s="37" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="I89" s="37" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="J89" s="37" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="K89" s="37" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="L89" s="37">
         <v>1</v>
@@ -7261,7 +7259,7 @@
         <v>10</v>
       </c>
       <c r="O89" s="60" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="P89" s="38">
         <v>8.0699999999999994E-2</v>
@@ -7287,17 +7285,17 @@
       <c r="K90" s="45"/>
       <c r="L90" s="45"/>
       <c r="M90" s="45"/>
-      <c r="N90" s="75" t="s">
+      <c r="N90" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="O90" s="76"/>
-      <c r="P90" s="76"/>
+      <c r="O90" s="89"/>
+      <c r="P90" s="89"/>
       <c r="Q90" s="48">
         <f>SUM(Q10:Q89)</f>
-        <v>219.57099999999997</v>
-      </c>
-      <c r="R90" s="71"/>
-      <c r="S90" s="72"/>
+        <v>281.5193000000001</v>
+      </c>
+      <c r="R90" s="84"/>
+      <c r="S90" s="85"/>
     </row>
     <row r="91" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
@@ -7313,17 +7311,17 @@
       <c r="K91" s="10"/>
       <c r="L91" s="10"/>
       <c r="M91" s="10"/>
-      <c r="N91" s="75" t="s">
+      <c r="N91" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="O91" s="76"/>
-      <c r="P91" s="76"/>
+      <c r="O91" s="89"/>
+      <c r="P91" s="89"/>
       <c r="Q91" s="49">
         <f>Q90/5</f>
-        <v>43.914199999999994</v>
-      </c>
-      <c r="R91" s="73"/>
-      <c r="S91" s="74"/>
+        <v>56.303860000000022</v>
+      </c>
+      <c r="R91" s="86"/>
+      <c r="S91" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7338,79 +7336,79 @@
     <hyperlink ref="O12" r:id="rId2"/>
     <hyperlink ref="O13" r:id="rId3"/>
     <hyperlink ref="O14" r:id="rId4"/>
-    <hyperlink ref="O15" r:id="rId5"/>
-    <hyperlink ref="O16" r:id="rId6"/>
-    <hyperlink ref="O17" r:id="rId7"/>
-    <hyperlink ref="O18" r:id="rId8"/>
-    <hyperlink ref="O19" r:id="rId9"/>
-    <hyperlink ref="O22" r:id="rId10"/>
-    <hyperlink ref="O21" r:id="rId11"/>
-    <hyperlink ref="O23" r:id="rId12"/>
-    <hyperlink ref="O24" r:id="rId13"/>
-    <hyperlink ref="O25" r:id="rId14"/>
-    <hyperlink ref="O28" r:id="rId15"/>
-    <hyperlink ref="O29" r:id="rId16"/>
-    <hyperlink ref="O30" r:id="rId17"/>
-    <hyperlink ref="O31" r:id="rId18"/>
-    <hyperlink ref="O32" r:id="rId19"/>
-    <hyperlink ref="O33" r:id="rId20"/>
-    <hyperlink ref="O34" r:id="rId21"/>
-    <hyperlink ref="O35" r:id="rId22"/>
-    <hyperlink ref="O36" r:id="rId23"/>
-    <hyperlink ref="O37" r:id="rId24"/>
-    <hyperlink ref="O38" r:id="rId25"/>
-    <hyperlink ref="O39" r:id="rId26"/>
-    <hyperlink ref="O40" r:id="rId27"/>
-    <hyperlink ref="O41" r:id="rId28"/>
-    <hyperlink ref="O42" r:id="rId29"/>
-    <hyperlink ref="O43" r:id="rId30"/>
-    <hyperlink ref="O44" r:id="rId31"/>
-    <hyperlink ref="O45" r:id="rId32"/>
-    <hyperlink ref="O46" r:id="rId33"/>
-    <hyperlink ref="O47" r:id="rId34"/>
-    <hyperlink ref="O49" r:id="rId35"/>
-    <hyperlink ref="O51" r:id="rId36"/>
-    <hyperlink ref="O52" r:id="rId37"/>
-    <hyperlink ref="O53" r:id="rId38"/>
-    <hyperlink ref="O55" r:id="rId39"/>
-    <hyperlink ref="O56" r:id="rId40"/>
-    <hyperlink ref="O58" r:id="rId41"/>
-    <hyperlink ref="O59" r:id="rId42"/>
-    <hyperlink ref="O60" r:id="rId43"/>
-    <hyperlink ref="O61" r:id="rId44"/>
-    <hyperlink ref="O62" r:id="rId45"/>
-    <hyperlink ref="O63" r:id="rId46"/>
-    <hyperlink ref="O64" r:id="rId47"/>
-    <hyperlink ref="O65" r:id="rId48"/>
-    <hyperlink ref="O67" r:id="rId49"/>
-    <hyperlink ref="O68" r:id="rId50"/>
-    <hyperlink ref="O69" r:id="rId51"/>
-    <hyperlink ref="O70" r:id="rId52"/>
-    <hyperlink ref="O73" r:id="rId53"/>
-    <hyperlink ref="O74" r:id="rId54"/>
-    <hyperlink ref="O75" r:id="rId55"/>
-    <hyperlink ref="O76" r:id="rId56"/>
-    <hyperlink ref="O77" r:id="rId57"/>
-    <hyperlink ref="O80" r:id="rId58"/>
-    <hyperlink ref="O82" r:id="rId59"/>
-    <hyperlink ref="O83" r:id="rId60"/>
-    <hyperlink ref="O84" r:id="rId61"/>
-    <hyperlink ref="O85" r:id="rId62"/>
-    <hyperlink ref="O86" r:id="rId63"/>
-    <hyperlink ref="O87" r:id="rId64"/>
-    <hyperlink ref="O88" r:id="rId65"/>
-    <hyperlink ref="O89" r:id="rId66"/>
-    <hyperlink ref="O72" r:id="rId67"/>
-    <hyperlink ref="O20" r:id="rId68"/>
-    <hyperlink ref="O26" r:id="rId69"/>
-    <hyperlink ref="O27" r:id="rId70"/>
-    <hyperlink ref="O50" r:id="rId71"/>
-    <hyperlink ref="O54" r:id="rId72"/>
-    <hyperlink ref="O57" r:id="rId73"/>
-    <hyperlink ref="O66" r:id="rId74"/>
-    <hyperlink ref="O78" r:id="rId75"/>
-    <hyperlink ref="O79" r:id="rId76"/>
-    <hyperlink ref="O81" r:id="rId77"/>
+    <hyperlink ref="O17" r:id="rId5"/>
+    <hyperlink ref="O19" r:id="rId6"/>
+    <hyperlink ref="O22" r:id="rId7"/>
+    <hyperlink ref="O21" r:id="rId8"/>
+    <hyperlink ref="O23" r:id="rId9"/>
+    <hyperlink ref="O24" r:id="rId10"/>
+    <hyperlink ref="O25" r:id="rId11"/>
+    <hyperlink ref="O28" r:id="rId12"/>
+    <hyperlink ref="O29" r:id="rId13"/>
+    <hyperlink ref="O30" r:id="rId14"/>
+    <hyperlink ref="O31" r:id="rId15"/>
+    <hyperlink ref="O32" r:id="rId16"/>
+    <hyperlink ref="O33" r:id="rId17"/>
+    <hyperlink ref="O34" r:id="rId18"/>
+    <hyperlink ref="O35" r:id="rId19"/>
+    <hyperlink ref="O36" r:id="rId20"/>
+    <hyperlink ref="O37" r:id="rId21"/>
+    <hyperlink ref="O38" r:id="rId22"/>
+    <hyperlink ref="O40" r:id="rId23"/>
+    <hyperlink ref="O42" r:id="rId24"/>
+    <hyperlink ref="O43" r:id="rId25"/>
+    <hyperlink ref="O44" r:id="rId26"/>
+    <hyperlink ref="O45" r:id="rId27"/>
+    <hyperlink ref="O46" r:id="rId28"/>
+    <hyperlink ref="O47" r:id="rId29"/>
+    <hyperlink ref="O49" r:id="rId30"/>
+    <hyperlink ref="O51" r:id="rId31"/>
+    <hyperlink ref="O52" r:id="rId32"/>
+    <hyperlink ref="O53" r:id="rId33"/>
+    <hyperlink ref="O55" r:id="rId34"/>
+    <hyperlink ref="O56" r:id="rId35"/>
+    <hyperlink ref="O58" r:id="rId36"/>
+    <hyperlink ref="O59" r:id="rId37"/>
+    <hyperlink ref="O60" r:id="rId38"/>
+    <hyperlink ref="O61" r:id="rId39"/>
+    <hyperlink ref="O62" r:id="rId40"/>
+    <hyperlink ref="O63" r:id="rId41"/>
+    <hyperlink ref="O64" r:id="rId42"/>
+    <hyperlink ref="O65" r:id="rId43"/>
+    <hyperlink ref="O67" r:id="rId44"/>
+    <hyperlink ref="O68" r:id="rId45"/>
+    <hyperlink ref="O69" r:id="rId46"/>
+    <hyperlink ref="O70" r:id="rId47"/>
+    <hyperlink ref="O73" r:id="rId48"/>
+    <hyperlink ref="O74" r:id="rId49"/>
+    <hyperlink ref="O75" r:id="rId50"/>
+    <hyperlink ref="O76" r:id="rId51"/>
+    <hyperlink ref="O77" r:id="rId52"/>
+    <hyperlink ref="O80" r:id="rId53"/>
+    <hyperlink ref="O82" r:id="rId54"/>
+    <hyperlink ref="O83" r:id="rId55"/>
+    <hyperlink ref="O84" r:id="rId56"/>
+    <hyperlink ref="O85" r:id="rId57"/>
+    <hyperlink ref="O86" r:id="rId58"/>
+    <hyperlink ref="O87" r:id="rId59"/>
+    <hyperlink ref="O88" r:id="rId60"/>
+    <hyperlink ref="O89" r:id="rId61"/>
+    <hyperlink ref="O72" r:id="rId62"/>
+    <hyperlink ref="O20" r:id="rId63"/>
+    <hyperlink ref="O26" r:id="rId64"/>
+    <hyperlink ref="O27" r:id="rId65"/>
+    <hyperlink ref="O50" r:id="rId66"/>
+    <hyperlink ref="O54" r:id="rId67"/>
+    <hyperlink ref="O57" r:id="rId68"/>
+    <hyperlink ref="O66" r:id="rId69"/>
+    <hyperlink ref="O78" r:id="rId70"/>
+    <hyperlink ref="O79" r:id="rId71"/>
+    <hyperlink ref="O81" r:id="rId72"/>
+    <hyperlink ref="O15" r:id="rId73"/>
+    <hyperlink ref="O16" r:id="rId74"/>
+    <hyperlink ref="O18" r:id="rId75"/>
+    <hyperlink ref="O39" r:id="rId76"/>
+    <hyperlink ref="O41" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId78"/>

--- a/Design Files/Baseboard-v2.0/BOM/eSpark_BOM_Baseboard-v2.0.xlsx
+++ b/Design Files/Baseboard-v2.0/BOM/eSpark_BOM_Baseboard-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="495">
   <si>
     <t>Component list</t>
   </si>
@@ -234,9 +234,6 @@
     <t>R4</t>
   </si>
   <si>
-    <t>R5, R7, R10, R13, R34, R47, R48, R49, R50, R51, R52, R53, R54, R55, R56, R57, R58, R59, R60, R61, R62, R93, R94, R95, R96</t>
-  </si>
-  <si>
     <t>R6, R8, R79, R80, R81, R85, R86</t>
   </si>
   <si>
@@ -246,9 +243,6 @@
     <t>R11, R29</t>
   </si>
   <si>
-    <t>R12</t>
-  </si>
-  <si>
     <t>R14, R30</t>
   </si>
   <si>
@@ -426,9 +420,6 @@
     <t>0.8mm mPCI-E Surface Mount 52 SMD,P=0.8mm Card Edge Connectors ROHS</t>
   </si>
   <si>
-    <t>5V SPDT (1 Form C) 6 DIP,11x15.5mm Power Relays ROHS</t>
-  </si>
-  <si>
     <t>7A 10uH ±20% 10A SMD,10.3x10.5mm Power Inductors ROHS</t>
   </si>
   <si>
@@ -561,9 +552,6 @@
     <t>40MHz SMD Crystal Resonator 15pF SMD3225-4P Crystals ROHS</t>
   </si>
   <si>
-    <t>3.579545MHz 20pF ±20ppm ±30ppm HC-49S Crystals ROHS</t>
-  </si>
-  <si>
     <t>Footprint</t>
   </si>
   <si>
@@ -624,9 +612,6 @@
     <t>91304-99-052R2</t>
   </si>
   <si>
-    <t>BS4-5S-C20</t>
-  </si>
-  <si>
     <t>PSPMAA1040-100M-ANP</t>
   </si>
   <si>
@@ -702,9 +687,6 @@
     <t>SOP-8</t>
   </si>
   <si>
-    <t>X49SD3579545MSD2SC-1</t>
-  </si>
-  <si>
     <t>Manufacturer Part Number</t>
   </si>
   <si>
@@ -966,9 +948,6 @@
     <t>UMAX</t>
   </si>
   <si>
-    <t>NBC</t>
-  </si>
-  <si>
     <t>PROD Tech</t>
   </si>
   <si>
@@ -1098,9 +1077,6 @@
     <t>C404126</t>
   </si>
   <si>
-    <t>C396938</t>
-  </si>
-  <si>
     <t>C2983105</t>
   </si>
   <si>
@@ -1203,9 +1179,6 @@
     <t>C9010</t>
   </si>
   <si>
-    <t>C2195</t>
-  </si>
-  <si>
     <t>Antenna</t>
   </si>
   <si>
@@ -1422,9 +1395,6 @@
     <t>C25152</t>
   </si>
   <si>
-    <t>R63, R64, R65, R66, R67, R82, R83, R84, R88, R89</t>
-  </si>
-  <si>
     <t>chipsmall</t>
   </si>
   <si>
@@ -1483,6 +1453,57 @@
   </si>
   <si>
     <t>C504827</t>
+  </si>
+  <si>
+    <t>3.579545MHz 20pF ±30ppm HC-49S-SMD Crystals ROHS</t>
+  </si>
+  <si>
+    <t>HC-49S-SMD</t>
+  </si>
+  <si>
+    <t>TAXM3.579M2ILFBET2T</t>
+  </si>
+  <si>
+    <t>TAE</t>
+  </si>
+  <si>
+    <t>C362352</t>
+  </si>
+  <si>
+    <t>R5, R7, R13, R34, R47, R48, R54, R55, R93, R94, R95, R96</t>
+  </si>
+  <si>
+    <t>R12, R20</t>
+  </si>
+  <si>
+    <t>R21, R63, R64, R65, R66, R67, R82, R83, R84, R88, R89</t>
+  </si>
+  <si>
+    <t>Resistor Array</t>
+  </si>
+  <si>
+    <t>RN1, RN2, RN3, RN4, RN5</t>
+  </si>
+  <si>
+    <t>RES ARRAY 4 RES 10K OHM 1206</t>
+  </si>
+  <si>
+    <t>YC164-FR-0710KL</t>
+  </si>
+  <si>
+    <t>C110924</t>
+  </si>
+  <si>
+    <t>RELAY GEN PURPOSE SPDT 3A 5V</t>
+  </si>
+  <si>
+    <t>J102K1CS35VDC.20</t>
+  </si>
+  <si>
+    <t>CIT Relay &amp; Switch</t>
+  </si>
+  <si>
+    <t>Chipsmall</t>
   </si>
 </sst>
 </file>
@@ -2562,7 +2583,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S91"/>
+  <dimension ref="A1:S92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -2615,7 +2636,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2640,7 +2661,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2665,7 +2686,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2781,49 +2802,49 @@
         <v>27</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="N9" s="30" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="O9" s="30" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="R9" s="30" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="S9" s="30" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -2833,31 +2854,31 @@
         <v>1</v>
       </c>
       <c r="C10" s="53" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="D10" s="62" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="62" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="F10" s="62" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G10" s="62" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="H10" s="66" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="I10" s="66" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J10" s="66" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="K10" s="62" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L10" s="62">
         <v>1</v>
@@ -2867,26 +2888,26 @@
         <v>5</v>
       </c>
       <c r="N10" s="62" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="O10" s="62" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="P10" s="66" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="Q10" s="66" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="R10" s="63" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="S10" s="50"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B88" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B89" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
@@ -2896,25 +2917,25 @@
         <v>29</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J11" s="51" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -2927,7 +2948,7 @@
         <v>20</v>
       </c>
       <c r="O11" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P11" s="52">
         <v>2.01E-2</v>
@@ -2952,25 +2973,25 @@
         <v>30</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="L12" s="37">
         <v>25</v>
@@ -2983,7 +3004,7 @@
         <v>150</v>
       </c>
       <c r="O12" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P12" s="38">
         <v>1.0500000000000001E-2</v>
@@ -3008,25 +3029,25 @@
         <v>31</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="L13" s="51">
         <v>3</v>
@@ -3039,7 +3060,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P13" s="52">
         <v>8.9999999999999998E-4</v>
@@ -3064,25 +3085,25 @@
         <v>32</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="L14" s="37">
         <v>3</v>
@@ -3095,7 +3116,7 @@
         <v>20</v>
       </c>
       <c r="O14" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P14" s="38">
         <v>4.9099999999999998E-2</v>
@@ -3120,25 +3141,25 @@
         <v>33</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="L15" s="51">
         <v>2</v>
@@ -3151,7 +3172,7 @@
         <v>11</v>
       </c>
       <c r="O15" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P15" s="52">
         <v>0.27689999999999998</v>
@@ -3176,25 +3197,25 @@
         <v>34</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="L16" s="37">
         <v>1</v>
@@ -3207,7 +3228,7 @@
         <v>15</v>
       </c>
       <c r="O16" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P16" s="38">
         <v>7.0900000000000005E-2</v>
@@ -3232,25 +3253,25 @@
         <v>35</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="L17" s="51">
         <v>1</v>
@@ -3263,7 +3284,7 @@
         <v>10</v>
       </c>
       <c r="O17" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P17" s="52">
         <v>6.3E-2</v>
@@ -3288,25 +3309,25 @@
         <v>36</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="L18" s="37">
         <v>1</v>
@@ -3319,7 +3340,7 @@
         <v>6</v>
       </c>
       <c r="O18" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P18" s="38">
         <v>1.7373000000000001</v>
@@ -3344,25 +3365,25 @@
         <v>37</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="H19" s="51" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="I19" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J19" s="51" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="L19" s="51">
         <v>1</v>
@@ -3375,7 +3396,7 @@
         <v>10</v>
       </c>
       <c r="O19" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P19" s="52">
         <v>0.26129999999999998</v>
@@ -3400,25 +3421,25 @@
         <v>38</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G20" s="62" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="L20" s="37">
         <v>4</v>
@@ -3431,7 +3452,7 @@
         <v>30</v>
       </c>
       <c r="O20" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P20" s="38">
         <v>4.2000000000000003E-2</v>
@@ -3456,25 +3477,25 @@
         <v>39</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="H21" s="51" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J21" s="51" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="L21" s="51">
         <v>2</v>
@@ -3487,7 +3508,7 @@
         <v>50</v>
       </c>
       <c r="O21" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P21" s="52">
         <v>1.0800000000000001E-2</v>
@@ -3512,25 +3533,25 @@
         <v>40</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="L22" s="37">
         <v>2</v>
@@ -3543,7 +3564,7 @@
         <v>100</v>
       </c>
       <c r="O22" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P22" s="38">
         <v>1E-3</v>
@@ -3568,25 +3589,25 @@
         <v>41</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="H23" s="51" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I23" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="K23" s="51" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="L23" s="51">
         <v>3</v>
@@ -3599,7 +3620,7 @@
         <v>100</v>
       </c>
       <c r="O23" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P23" s="52">
         <v>3.8999999999999998E-3</v>
@@ -3624,25 +3645,25 @@
         <v>42</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J24" s="37" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="K24" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L24" s="37">
         <v>1</v>
@@ -3655,7 +3676,7 @@
         <v>10</v>
       </c>
       <c r="O24" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P24" s="38">
         <v>5.5599999999999997E-2</v>
@@ -3680,25 +3701,25 @@
         <v>43</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="H25" s="51" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="I25" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J25" s="51" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="K25" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L25" s="51">
         <v>1</v>
@@ -3711,7 +3732,7 @@
         <v>10</v>
       </c>
       <c r="O25" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P25" s="52">
         <v>4.4600000000000001E-2</v>
@@ -3736,25 +3757,25 @@
         <v>44</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="K26" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L26" s="37">
         <v>1</v>
@@ -3767,7 +3788,7 @@
         <v>6</v>
       </c>
       <c r="O26" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P26" s="38">
         <v>0.46939999999999998</v>
@@ -3792,25 +3813,25 @@
         <v>45</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J27" s="51" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="K27" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L27" s="51">
         <v>1</v>
@@ -3823,7 +3844,7 @@
         <v>10</v>
       </c>
       <c r="O27" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P27" s="52">
         <v>3.56E-2</v>
@@ -3848,25 +3869,25 @@
         <v>46</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="K28" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L28" s="37">
         <v>3</v>
@@ -3879,7 +3900,7 @@
         <v>20</v>
       </c>
       <c r="O28" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P28" s="38">
         <v>2.46E-2</v>
@@ -3904,25 +3925,25 @@
         <v>47</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H29" s="51" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J29" s="51" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L29" s="51">
         <v>2</v>
@@ -3935,7 +3956,7 @@
         <v>20</v>
       </c>
       <c r="O29" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P29" s="52">
         <v>2.3400000000000001E-2</v>
@@ -3960,25 +3981,25 @@
         <v>48</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L30" s="37">
         <v>4</v>
@@ -3991,7 +4012,7 @@
         <v>25</v>
       </c>
       <c r="O30" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P30" s="38">
         <v>0.1351</v>
@@ -4016,25 +4037,25 @@
         <v>49</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G31" s="51" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="H31" s="51" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J31" s="51" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L31" s="51">
         <v>4</v>
@@ -4047,7 +4068,7 @@
         <v>30</v>
       </c>
       <c r="O31" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P31" s="52">
         <v>4.7500000000000001E-2</v>
@@ -4072,25 +4093,25 @@
         <v>50</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J32" s="37" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="K32" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L32" s="37">
         <v>1</v>
@@ -4103,7 +4124,7 @@
         <v>10</v>
       </c>
       <c r="O32" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P32" s="38">
         <v>0.2286</v>
@@ -4128,25 +4149,25 @@
         <v>51</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="H33" s="51" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="K33" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L33" s="51">
         <v>1</v>
@@ -4159,7 +4180,7 @@
         <v>6</v>
       </c>
       <c r="O33" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P33" s="52">
         <v>1.1482000000000001</v>
@@ -4184,25 +4205,25 @@
         <v>52</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J34" s="37" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="K34" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L34" s="37">
         <v>4</v>
@@ -4215,7 +4236,7 @@
         <v>30</v>
       </c>
       <c r="O34" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P34" s="38">
         <v>5.6099999999999997E-2</v>
@@ -4240,25 +4261,25 @@
         <v>53</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F35" s="51" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G35" s="51" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="H35" s="51" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="I35" s="61" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="J35" s="51" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="K35" s="51" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="L35" s="51">
         <v>1</v>
@@ -4271,7 +4292,7 @@
         <v>10</v>
       </c>
       <c r="O35" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P35" s="52">
         <v>8.8300000000000003E-2</v>
@@ -4296,25 +4317,25 @@
         <v>54</v>
       </c>
       <c r="E36" s="37" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F36" s="51" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="K36" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L36" s="37">
         <v>8</v>
@@ -4327,7 +4348,7 @@
         <v>45</v>
       </c>
       <c r="O36" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P36" s="38">
         <v>0.2316</v>
@@ -4352,25 +4373,25 @@
         <v>55</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F37" s="51" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G37" s="51" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="H37" s="51" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="I37" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J37" s="51" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="K37" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L37" s="51">
         <v>1</v>
@@ -4383,7 +4404,7 @@
         <v>10</v>
       </c>
       <c r="O37" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P37" s="52">
         <v>0.21590000000000001</v>
@@ -4408,25 +4429,25 @@
         <v>56</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F38" s="51" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="K38" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L38" s="37">
         <v>4</v>
@@ -4439,7 +4460,7 @@
         <v>25</v>
       </c>
       <c r="O38" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P38" s="38">
         <v>0.17299999999999999</v>
@@ -4464,25 +4485,25 @@
         <v>57</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="F39" s="51" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G39" s="51" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="H39" s="51" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="I39" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J39" s="51" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="K39" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L39" s="51">
         <v>1</v>
@@ -4495,7 +4516,7 @@
         <v>10</v>
       </c>
       <c r="O39" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P39" s="52">
         <v>0.3211</v>
@@ -4520,25 +4541,25 @@
         <v>58</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F40" s="51" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L40" s="37">
         <v>1</v>
@@ -4551,7 +4572,7 @@
         <v>12</v>
       </c>
       <c r="O40" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P40" s="38">
         <v>7.0400000000000004E-2</v>
@@ -4570,29 +4591,29 @@
         <v>32</v>
       </c>
       <c r="C41" s="54" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="D41" s="51" t="s">
         <v>59</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="F41" s="51" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G41" s="51" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="H41" s="51" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="I41" s="51"/>
       <c r="J41" s="51" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="K41" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L41" s="51">
         <v>1</v>
@@ -4605,7 +4626,7 @@
         <v>6</v>
       </c>
       <c r="O41" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P41" s="52">
         <v>0.91159999999999997</v>
@@ -4630,25 +4651,25 @@
         <v>60</v>
       </c>
       <c r="E42" s="37" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F42" s="51" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L42" s="37">
         <v>2</v>
@@ -4661,7 +4682,7 @@
         <v>11</v>
       </c>
       <c r="O42" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P42" s="38">
         <v>0.81459999999999999</v>
@@ -4673,7 +4694,7 @@
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
     </row>
-    <row r="43" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="47">
         <f t="shared" si="0"/>
@@ -4686,25 +4707,25 @@
         <v>61</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>135</v>
+        <v>491</v>
       </c>
       <c r="F43" s="51" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G43" s="51" t="s">
-        <v>201</v>
+        <v>492</v>
       </c>
       <c r="H43" s="51" t="s">
-        <v>315</v>
+        <v>493</v>
       </c>
       <c r="I43" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J43" s="51" t="s">
-        <v>359</v>
+        <v>434</v>
       </c>
       <c r="K43" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L43" s="51">
         <v>3</v>
@@ -4717,14 +4738,14 @@
         <v>16</v>
       </c>
       <c r="O43" s="60" t="s">
-        <v>450</v>
+        <v>494</v>
       </c>
       <c r="P43" s="52">
-        <v>0.32619999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="Q43" s="52">
         <f t="shared" ref="Q43" si="34">P43*N43</f>
-        <v>5.2191999999999998</v>
+        <v>16.16</v>
       </c>
       <c r="R43" s="51"/>
       <c r="S43" s="59"/>
@@ -4742,25 +4763,25 @@
         <v>62</v>
       </c>
       <c r="E44" s="37" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F44" s="51" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J44" s="37" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="L44" s="37">
         <v>1</v>
@@ -4773,7 +4794,7 @@
         <v>10</v>
       </c>
       <c r="O44" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P44" s="38">
         <v>0.2137</v>
@@ -4798,25 +4819,25 @@
         <v>63</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F45" s="51" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G45" s="51" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="H45" s="51" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="I45" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J45" s="51" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="K45" s="51" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="L45" s="51">
         <v>1</v>
@@ -4829,7 +4850,7 @@
         <v>50</v>
       </c>
       <c r="O45" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P45" s="52">
         <v>8.3000000000000001E-3</v>
@@ -4854,25 +4875,25 @@
         <v>64</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L46" s="37">
         <v>2</v>
@@ -4885,7 +4906,7 @@
         <v>20</v>
       </c>
       <c r="O46" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P46" s="38">
         <v>5.7599999999999998E-2</v>
@@ -4910,25 +4931,25 @@
         <v>65</v>
       </c>
       <c r="E47" s="51" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F47" s="51" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G47" s="51" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="H47" s="51" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="I47" s="61" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="J47" s="51" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="K47" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L47" s="51">
         <v>1</v>
@@ -4941,7 +4962,7 @@
         <v>10</v>
       </c>
       <c r="O47" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P47" s="52">
         <v>5.1499999999999997E-2</v>
@@ -4960,31 +4981,31 @@
         <v>39</v>
       </c>
       <c r="C48" s="53" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="D48" s="62" t="s">
         <v>66</v>
       </c>
       <c r="E48" s="62" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F48" s="62" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G48" s="62" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="H48" s="62" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="I48" s="62" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J48" s="62" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="K48" s="62" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L48" s="62">
         <v>10</v>
@@ -4994,19 +5015,19 @@
         <v>50</v>
       </c>
       <c r="N48" s="62" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="O48" s="62" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="P48" s="62" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="Q48" s="62" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="R48" s="63" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="S48" s="59"/>
     </row>
@@ -5017,29 +5038,29 @@
         <v>40</v>
       </c>
       <c r="C49" s="54" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="D49" s="51" t="s">
         <v>67</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F49" s="51" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="G49" s="51" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="H49" s="51" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="I49" s="51"/>
       <c r="J49" s="51" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="K49" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L49" s="51">
         <v>1</v>
@@ -5052,7 +5073,7 @@
         <v>20</v>
       </c>
       <c r="O49" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P49" s="52">
         <v>2.1000000000000001E-2</v>
@@ -5077,25 +5098,25 @@
         <v>68</v>
       </c>
       <c r="E50" s="37" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G50" s="62" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="I50" s="37" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="J50" s="37" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="K50" s="37" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="L50" s="37">
         <v>2</v>
@@ -5108,7 +5129,7 @@
         <v>20</v>
       </c>
       <c r="O50" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P50" s="38">
         <v>2.1700000000000001E-2</v>
@@ -5133,23 +5154,23 @@
         <v>69</v>
       </c>
       <c r="E51" s="51" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F51" s="51" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="G51" s="51" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H51" s="51" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="I51" s="51"/>
       <c r="J51" s="51" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="K51" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="L51" s="51">
         <v>1</v>
@@ -5162,7 +5183,7 @@
         <v>10</v>
       </c>
       <c r="O51" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P51" s="52">
         <v>0.18260000000000001</v>
@@ -5187,23 +5208,23 @@
         <v>70</v>
       </c>
       <c r="E52" s="37" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F52" s="37" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="H52" s="37" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I52" s="37"/>
       <c r="J52" s="37" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="K52" s="37" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="L52" s="37">
         <v>1</v>
@@ -5216,7 +5237,7 @@
         <v>100</v>
       </c>
       <c r="O52" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P52" s="38">
         <v>2.5999999999999999E-3</v>
@@ -5228,7 +5249,7 @@
       <c r="R52" s="37"/>
       <c r="S52" s="59"/>
     </row>
-    <row r="53" spans="1:19" ht="48" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="47">
         <f t="shared" si="0"/>
@@ -5238,46 +5259,46 @@
         <v>21</v>
       </c>
       <c r="D53" s="51" t="s">
-        <v>71</v>
+        <v>483</v>
       </c>
       <c r="E53" s="51" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F53" s="51" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G53" s="51" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="H53" s="51" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I53" s="51"/>
       <c r="J53" s="51" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="K53" s="51" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="L53" s="51">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="M53" s="51">
         <f t="shared" ref="M53" si="43">L53*5</f>
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="N53" s="51">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O53" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P53" s="52">
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="Q53" s="52">
         <f t="shared" ref="Q53" si="44">P53*N53</f>
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="R53" s="51"/>
       <c r="S53" s="59"/>
@@ -5292,28 +5313,28 @@
         <v>21</v>
       </c>
       <c r="D54" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E54" s="37" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F54" s="37" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G54" s="62" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="H54" s="37" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I54" s="37" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="J54" s="37" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="K54" s="37" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="L54" s="37">
         <v>7</v>
@@ -5326,7 +5347,7 @@
         <v>100</v>
       </c>
       <c r="O54" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P54" s="38">
         <v>8.9999999999999998E-4</v>
@@ -5348,28 +5369,28 @@
         <v>21</v>
       </c>
       <c r="D55" s="51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E55" s="51" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F55" s="51" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G55" s="51" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="H55" s="51" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="I55" s="51" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J55" s="51" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="K55" s="51" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="L55" s="51">
         <v>1</v>
@@ -5382,7 +5403,7 @@
         <v>100</v>
       </c>
       <c r="O55" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P55" s="52">
         <v>1E-3</v>
@@ -5404,28 +5425,28 @@
         <v>21</v>
       </c>
       <c r="D56" s="37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E56" s="37" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F56" s="37" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="H56" s="37" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I56" s="37" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J56" s="37" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="K56" s="37" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="L56" s="37">
         <v>2</v>
@@ -5438,7 +5459,7 @@
         <v>100</v>
       </c>
       <c r="O56" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P56" s="38">
         <v>8.0000000000000004E-4</v>
@@ -5460,41 +5481,41 @@
         <v>21</v>
       </c>
       <c r="D57" s="51" t="s">
-        <v>75</v>
+        <v>484</v>
       </c>
       <c r="E57" s="51" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F57" s="51" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G57" s="62" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="H57" s="51" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I57" s="51" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="J57" s="51" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="K57" s="51" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="L57" s="51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M57" s="51">
         <f t="shared" ref="M57" si="47">L57*5</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N57" s="51">
         <v>100</v>
       </c>
       <c r="O57" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P57" s="52">
         <v>5.0000000000000001E-4</v>
@@ -5516,26 +5537,26 @@
         <v>21</v>
       </c>
       <c r="D58" s="37" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I58" s="37"/>
       <c r="J58" s="37" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="K58" s="37" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="L58" s="37">
         <v>2</v>
@@ -5548,7 +5569,7 @@
         <v>100</v>
       </c>
       <c r="O58" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P58" s="38">
         <v>6.9999999999999999E-4</v>
@@ -5570,26 +5591,26 @@
         <v>21</v>
       </c>
       <c r="D59" s="51" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E59" s="51" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F59" s="51" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G59" s="51" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="H59" s="51" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I59" s="51"/>
       <c r="J59" s="51" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="K59" s="51" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="L59" s="51">
         <v>22</v>
@@ -5602,7 +5623,7 @@
         <v>200</v>
       </c>
       <c r="O59" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P59" s="52">
         <v>6.9999999999999999E-4</v>
@@ -5624,26 +5645,26 @@
         <v>21</v>
       </c>
       <c r="D60" s="37" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E60" s="37" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I60" s="37"/>
       <c r="J60" s="37" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="K60" s="37" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="L60" s="37">
         <v>1</v>
@@ -5656,7 +5677,7 @@
         <v>100</v>
       </c>
       <c r="O60" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P60" s="38">
         <v>5.9999999999999995E-4</v>
@@ -5668,7 +5689,7 @@
       <c r="R60" s="37"/>
       <c r="S60" s="59"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="46">
         <f>ROW(B61) - ROW($B$9)</f>
@@ -5677,40 +5698,40 @@
       <c r="C61" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D61" s="37" t="s">
-        <v>79</v>
+      <c r="D61" s="51" t="s">
+        <v>485</v>
       </c>
       <c r="E61" s="37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H61" s="37" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I61" s="37"/>
       <c r="J61" s="37" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="K61" s="37" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="L61" s="37">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M61" s="37">
         <f>L61*5</f>
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="N61" s="37">
         <v>100</v>
       </c>
       <c r="O61" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P61" s="38">
         <v>6.9999999999999999E-4</v>
@@ -5724,218 +5745,218 @@
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
-      <c r="B62" s="47">
-        <f t="shared" si="0"/>
+      <c r="B62" s="46">
+        <f>ROW(B62) - ROW($B$9)</f>
         <v>53</v>
       </c>
-      <c r="C62" s="54" t="s">
+      <c r="C62" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D62" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="E62" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="F62" s="51" t="s">
-        <v>211</v>
-      </c>
-      <c r="G62" s="51" t="s">
-        <v>266</v>
-      </c>
-      <c r="H62" s="51" t="s">
-        <v>292</v>
-      </c>
-      <c r="I62" s="51"/>
-      <c r="J62" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="K62" s="51" t="s">
-        <v>423</v>
-      </c>
-      <c r="L62" s="51">
-        <v>1</v>
-      </c>
-      <c r="M62" s="51">
-        <f t="shared" ref="M62" si="51">L62*5</f>
-        <v>5</v>
-      </c>
-      <c r="N62" s="51">
+      <c r="D62" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="E62" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="F62" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="G62" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="H62" s="37" t="s">
+        <v>286</v>
+      </c>
+      <c r="I62" s="37"/>
+      <c r="J62" s="37" t="s">
+        <v>365</v>
+      </c>
+      <c r="K62" s="37" t="s">
+        <v>413</v>
+      </c>
+      <c r="L62" s="37">
+        <v>4</v>
+      </c>
+      <c r="M62" s="37">
+        <f>L62*5</f>
+        <v>20</v>
+      </c>
+      <c r="N62" s="37">
         <v>100</v>
       </c>
       <c r="O62" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P62" s="52">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="Q62" s="52">
-        <f t="shared" ref="Q62" si="52">P62*N62</f>
-        <v>0.12</v>
-      </c>
-      <c r="R62" s="51"/>
+        <v>441</v>
+      </c>
+      <c r="P62" s="38">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q62" s="38">
+        <f>P62*N62</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R62" s="37"/>
       <c r="S62" s="59"/>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
-      <c r="B63" s="46">
-        <f>ROW(B63) - ROW($B$9)</f>
+      <c r="B63" s="47">
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C63" s="53" t="s">
+      <c r="C63" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="D63" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="E63" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="F63" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="G63" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="H63" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="I63" s="37"/>
-      <c r="J63" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="K63" s="37" t="s">
-        <v>424</v>
-      </c>
-      <c r="L63" s="37">
+      <c r="D63" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="E63" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="F63" s="51" t="s">
+        <v>206</v>
+      </c>
+      <c r="G63" s="51" t="s">
+        <v>260</v>
+      </c>
+      <c r="H63" s="51" t="s">
+        <v>286</v>
+      </c>
+      <c r="I63" s="51"/>
+      <c r="J63" s="51" t="s">
+        <v>366</v>
+      </c>
+      <c r="K63" s="51" t="s">
+        <v>414</v>
+      </c>
+      <c r="L63" s="51">
         <v>1</v>
       </c>
-      <c r="M63" s="37">
-        <f>L63*5</f>
+      <c r="M63" s="51">
+        <f t="shared" ref="M63" si="51">L63*5</f>
         <v>5</v>
       </c>
-      <c r="N63" s="37">
+      <c r="N63" s="51">
         <v>100</v>
       </c>
       <c r="O63" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P63" s="38">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="Q63" s="38">
-        <f>P63*N63</f>
-        <v>0.25</v>
-      </c>
-      <c r="R63" s="37"/>
+        <v>441</v>
+      </c>
+      <c r="P63" s="52">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q63" s="52">
+        <f t="shared" ref="Q63" si="52">P63*N63</f>
+        <v>0.12</v>
+      </c>
+      <c r="R63" s="51"/>
       <c r="S63" s="59"/>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
-      <c r="B64" s="47">
-        <f t="shared" si="0"/>
+      <c r="B64" s="46">
+        <f>ROW(B64) - ROW($B$9)</f>
         <v>55</v>
       </c>
       <c r="C64" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="D64" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="E64" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="F64" s="51" t="s">
-        <v>211</v>
-      </c>
-      <c r="G64" s="51" t="s">
-        <v>268</v>
-      </c>
-      <c r="H64" s="51" t="s">
-        <v>292</v>
-      </c>
-      <c r="I64" s="51"/>
-      <c r="J64" s="51" t="s">
-        <v>452</v>
-      </c>
-      <c r="K64" s="51" t="s">
-        <v>425</v>
-      </c>
-      <c r="L64" s="51">
+      <c r="D64" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="E64" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="F64" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="G64" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="H64" s="37" t="s">
+        <v>286</v>
+      </c>
+      <c r="I64" s="37"/>
+      <c r="J64" s="37" t="s">
+        <v>367</v>
+      </c>
+      <c r="K64" s="37" t="s">
+        <v>415</v>
+      </c>
+      <c r="L64" s="37">
         <v>1</v>
       </c>
-      <c r="M64" s="51">
-        <f t="shared" ref="M64" si="53">L64*5</f>
+      <c r="M64" s="37">
+        <f>L64*5</f>
         <v>5</v>
       </c>
-      <c r="N64" s="51">
-        <v>20</v>
+      <c r="N64" s="37">
+        <v>100</v>
       </c>
       <c r="O64" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P64" s="52">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="Q64" s="52">
-        <f t="shared" ref="Q64" si="54">P64*N64</f>
-        <v>0.52</v>
-      </c>
-      <c r="R64" s="51"/>
+        <v>441</v>
+      </c>
+      <c r="P64" s="38">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="Q64" s="38">
+        <f>P64*N64</f>
+        <v>0.25</v>
+      </c>
+      <c r="R64" s="37"/>
       <c r="S64" s="59"/>
     </row>
-    <row r="65" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
-      <c r="B65" s="46">
-        <f>ROW(B65) - ROW($B$9)</f>
+      <c r="B65" s="47">
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="C65" s="53" t="s">
         <v>21</v>
       </c>
       <c r="D65" s="51" t="s">
-        <v>467</v>
-      </c>
-      <c r="E65" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="F65" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="G65" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="H65" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="I65" s="37"/>
-      <c r="J65" s="37" t="s">
-        <v>376</v>
-      </c>
-      <c r="K65" s="37" t="s">
-        <v>421</v>
-      </c>
-      <c r="L65" s="37">
-        <v>10</v>
-      </c>
-      <c r="M65" s="37">
-        <f>L65*5</f>
-        <v>50</v>
-      </c>
-      <c r="N65" s="37">
-        <v>100</v>
+        <v>80</v>
+      </c>
+      <c r="E65" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="F65" s="51" t="s">
+        <v>206</v>
+      </c>
+      <c r="G65" s="51" t="s">
+        <v>262</v>
+      </c>
+      <c r="H65" s="51" t="s">
+        <v>286</v>
+      </c>
+      <c r="I65" s="51"/>
+      <c r="J65" s="51" t="s">
+        <v>443</v>
+      </c>
+      <c r="K65" s="51" t="s">
+        <v>416</v>
+      </c>
+      <c r="L65" s="51">
+        <v>1</v>
+      </c>
+      <c r="M65" s="51">
+        <f t="shared" ref="M65" si="53">L65*5</f>
+        <v>5</v>
+      </c>
+      <c r="N65" s="51">
+        <v>20</v>
       </c>
       <c r="O65" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P65" s="38">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="Q65" s="38">
-        <f>P65*N65</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R65" s="37"/>
+        <v>441</v>
+      </c>
+      <c r="P65" s="52">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="Q65" s="52">
+        <f t="shared" ref="Q65" si="54">P65*N65</f>
+        <v>0.52</v>
+      </c>
+      <c r="R65" s="51"/>
       <c r="S65" s="59"/>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
@@ -5948,28 +5969,28 @@
         <v>21</v>
       </c>
       <c r="D66" s="51" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E66" s="51" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F66" s="51" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G66" s="62" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="H66" s="51" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="I66" s="51" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="J66" s="51" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="K66" s="51" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="L66" s="51">
         <v>4</v>
@@ -5982,7 +6003,7 @@
         <v>100</v>
       </c>
       <c r="O66" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P66" s="52">
         <v>4.0000000000000002E-4</v>
@@ -6004,26 +6025,26 @@
         <v>21</v>
       </c>
       <c r="D67" s="37" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E67" s="37" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G67" s="37" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="H67" s="37" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I67" s="37"/>
       <c r="J67" s="37" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="K67" s="37" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="L67" s="37">
         <v>1</v>
@@ -6036,7 +6057,7 @@
         <v>100</v>
       </c>
       <c r="O67" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P67" s="38">
         <v>1.1999999999999999E-3</v>
@@ -6058,26 +6079,26 @@
         <v>21</v>
       </c>
       <c r="D68" s="51" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E68" s="51" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F68" s="51" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G68" s="51" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="H68" s="51" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="I68" s="51"/>
       <c r="J68" s="51" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="K68" s="51" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="L68" s="51">
         <v>1</v>
@@ -6090,7 +6111,7 @@
         <v>10</v>
       </c>
       <c r="O68" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P68" s="52">
         <v>5.3600000000000002E-2</v>
@@ -6112,26 +6133,26 @@
         <v>21</v>
       </c>
       <c r="D69" s="37" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E69" s="37" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F69" s="37" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G69" s="37" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H69" s="37" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I69" s="37"/>
       <c r="J69" s="37" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="K69" s="37" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="L69" s="37">
         <v>2</v>
@@ -6144,7 +6165,7 @@
         <v>100</v>
       </c>
       <c r="O69" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P69" s="38">
         <v>1.1999999999999999E-3</v>
@@ -6166,45 +6187,45 @@
         <v>21</v>
       </c>
       <c r="D70" s="51" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E70" s="51" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F70" s="51" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G70" s="51" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="H70" s="51" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I70" s="51"/>
       <c r="J70" s="51" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="K70" s="51" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="L70" s="51">
         <v>1</v>
       </c>
       <c r="M70" s="51">
-        <f t="shared" ref="M70" si="59">L70*5</f>
+        <f t="shared" ref="M70:M71" si="59">L70*5</f>
         <v>5</v>
       </c>
       <c r="N70" s="51">
         <v>100</v>
       </c>
       <c r="O70" s="60" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="P70" s="52">
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="Q70" s="52">
-        <f t="shared" ref="Q70" si="60">P70*N70</f>
+        <f t="shared" ref="Q70:Q71" si="60">P70*N70</f>
         <v>6.9999999999999993E-2</v>
       </c>
       <c r="R70" s="51"/>
@@ -6212,1206 +6233,1261 @@
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
-      <c r="B71" s="46">
-        <f>ROW(B71) - ROW($B$9)</f>
+      <c r="B71" s="47">
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C71" s="53" t="s">
+      <c r="C71" s="54" t="s">
+        <v>486</v>
+      </c>
+      <c r="D71" s="51" t="s">
+        <v>487</v>
+      </c>
+      <c r="E71" s="51" t="s">
+        <v>488</v>
+      </c>
+      <c r="F71" s="51" t="s">
+        <v>440</v>
+      </c>
+      <c r="G71" s="51" t="s">
+        <v>489</v>
+      </c>
+      <c r="H71" s="51" t="s">
+        <v>286</v>
+      </c>
+      <c r="I71" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="J71" s="51" t="s">
+        <v>490</v>
+      </c>
+      <c r="K71" s="51" t="s">
+        <v>404</v>
+      </c>
+      <c r="L71" s="51">
+        <v>5</v>
+      </c>
+      <c r="M71" s="51">
+        <f t="shared" si="59"/>
+        <v>25</v>
+      </c>
+      <c r="N71" s="51">
+        <v>50</v>
+      </c>
+      <c r="O71" s="60" t="s">
+        <v>441</v>
+      </c>
+      <c r="P71" s="52">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="Q71" s="52">
+        <f t="shared" si="60"/>
+        <v>0.43499999999999994</v>
+      </c>
+      <c r="R71" s="51"/>
+      <c r="S71" s="59"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A72" s="1"/>
+      <c r="B72" s="46">
+        <f>ROW(B72) - ROW($B$9)</f>
+        <v>63</v>
+      </c>
+      <c r="C72" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="D71" s="64" t="s">
-        <v>88</v>
-      </c>
-      <c r="E71" s="64" t="s">
-        <v>163</v>
-      </c>
-      <c r="F71" s="65" t="s">
-        <v>449</v>
-      </c>
-      <c r="G71" s="64" t="s">
-        <v>212</v>
-      </c>
-      <c r="H71" s="64" t="s">
-        <v>443</v>
-      </c>
-      <c r="I71" s="64" t="s">
-        <v>443</v>
-      </c>
-      <c r="J71" s="64" t="s">
-        <v>443</v>
-      </c>
-      <c r="K71" s="64" t="s">
-        <v>443</v>
-      </c>
-      <c r="L71" s="64">
+      <c r="D72" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="E72" s="64" t="s">
+        <v>160</v>
+      </c>
+      <c r="F72" s="65" t="s">
+        <v>440</v>
+      </c>
+      <c r="G72" s="64" t="s">
+        <v>207</v>
+      </c>
+      <c r="H72" s="64" t="s">
+        <v>434</v>
+      </c>
+      <c r="I72" s="64" t="s">
+        <v>434</v>
+      </c>
+      <c r="J72" s="64" t="s">
+        <v>434</v>
+      </c>
+      <c r="K72" s="64" t="s">
+        <v>434</v>
+      </c>
+      <c r="L72" s="64">
         <v>2</v>
       </c>
-      <c r="M71" s="64">
-        <f>L71*5</f>
+      <c r="M72" s="64">
+        <f>L72*5</f>
         <v>10</v>
       </c>
-      <c r="N71" s="64" t="s">
-        <v>443</v>
-      </c>
-      <c r="O71" s="64" t="s">
-        <v>443</v>
-      </c>
-      <c r="P71" s="64" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q71" s="64" t="s">
-        <v>443</v>
-      </c>
-      <c r="R71" s="63" t="s">
-        <v>454</v>
-      </c>
-      <c r="S71" s="59"/>
-    </row>
-    <row r="72" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A72" s="1"/>
-      <c r="B72" s="47">
+      <c r="N72" s="64" t="s">
+        <v>434</v>
+      </c>
+      <c r="O72" s="64" t="s">
+        <v>434</v>
+      </c>
+      <c r="P72" s="64" t="s">
+        <v>434</v>
+      </c>
+      <c r="Q72" s="64" t="s">
+        <v>434</v>
+      </c>
+      <c r="R72" s="63" t="s">
+        <v>445</v>
+      </c>
+      <c r="S72" s="59"/>
+    </row>
+    <row r="73" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A73" s="1"/>
+      <c r="B73" s="47">
         <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-      <c r="C72" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="C73" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="D72" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="E72" s="51" t="s">
-        <v>164</v>
-      </c>
-      <c r="F72" s="51" t="s">
-        <v>449</v>
-      </c>
-      <c r="G72" s="51" t="s">
-        <v>213</v>
-      </c>
-      <c r="H72" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="I72" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="J72" s="51" t="s">
-        <v>453</v>
-      </c>
-      <c r="K72" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="L72" s="51">
+      <c r="D73" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="E73" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="F73" s="51" t="s">
+        <v>440</v>
+      </c>
+      <c r="G73" s="51" t="s">
+        <v>208</v>
+      </c>
+      <c r="H73" s="51" t="s">
+        <v>317</v>
+      </c>
+      <c r="I73" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="J73" s="51" t="s">
+        <v>444</v>
+      </c>
+      <c r="K73" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="L73" s="51">
         <v>1</v>
       </c>
-      <c r="M72" s="51">
-        <f t="shared" ref="M72" si="61">L72*5</f>
+      <c r="M73" s="51">
+        <f t="shared" ref="M73" si="61">L73*5</f>
         <v>5</v>
       </c>
-      <c r="N72" s="51">
+      <c r="N73" s="51">
         <v>10</v>
       </c>
-      <c r="O72" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P72" s="52">
+      <c r="O73" s="60" t="s">
+        <v>441</v>
+      </c>
+      <c r="P73" s="52">
         <v>0.1275</v>
       </c>
-      <c r="Q72" s="52">
-        <f t="shared" ref="Q72" si="62">P72*N72</f>
+      <c r="Q73" s="52">
+        <f t="shared" ref="Q73" si="62">P73*N73</f>
         <v>1.2749999999999999</v>
       </c>
-      <c r="R72" s="51"/>
-      <c r="S72" s="59"/>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A73" s="1"/>
-      <c r="B73" s="46">
-        <f>ROW(B73) - ROW($B$9)</f>
-        <v>64</v>
-      </c>
-      <c r="C73" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="D73" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E73" s="37" t="s">
-        <v>165</v>
-      </c>
-      <c r="F73" s="37" t="s">
-        <v>214</v>
-      </c>
-      <c r="G73" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="H73" s="37" t="s">
-        <v>325</v>
-      </c>
-      <c r="I73" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="J73" s="37" t="s">
-        <v>381</v>
-      </c>
-      <c r="K73" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="L73" s="37">
-        <v>1</v>
-      </c>
-      <c r="M73" s="37">
-        <f>L73*5</f>
-        <v>5</v>
-      </c>
-      <c r="N73" s="37">
-        <v>6</v>
-      </c>
-      <c r="O73" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P73" s="38">
-        <v>0.82569999999999999</v>
-      </c>
-      <c r="Q73" s="38">
-        <f>P73*N73</f>
-        <v>4.9542000000000002</v>
-      </c>
-      <c r="R73" s="37"/>
+      <c r="R73" s="51"/>
       <c r="S73" s="59"/>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
-      <c r="B74" s="47">
+      <c r="B74" s="46">
+        <f>ROW(B74) - ROW($B$9)</f>
+        <v>65</v>
+      </c>
+      <c r="C74" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D74" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E74" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="F74" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="G74" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="H74" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="I74" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="J74" s="37" t="s">
+        <v>373</v>
+      </c>
+      <c r="K74" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="L74" s="37">
+        <v>1</v>
+      </c>
+      <c r="M74" s="37">
+        <f>L74*5</f>
+        <v>5</v>
+      </c>
+      <c r="N74" s="37">
+        <v>6</v>
+      </c>
+      <c r="O74" s="60" t="s">
+        <v>441</v>
+      </c>
+      <c r="P74" s="38">
+        <v>0.82569999999999999</v>
+      </c>
+      <c r="Q74" s="38">
+        <f>P74*N74</f>
+        <v>4.9542000000000002</v>
+      </c>
+      <c r="R74" s="37"/>
+      <c r="S74" s="59"/>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A75" s="1"/>
+      <c r="B75" s="47">
         <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-      <c r="C74" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="C75" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="D74" s="51" t="s">
-        <v>91</v>
-      </c>
-      <c r="E74" s="51" t="s">
-        <v>166</v>
-      </c>
-      <c r="F74" s="51" t="s">
-        <v>215</v>
-      </c>
-      <c r="G74" s="51" t="s">
-        <v>276</v>
-      </c>
-      <c r="H74" s="51" t="s">
-        <v>325</v>
-      </c>
-      <c r="I74" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="J74" s="51" t="s">
-        <v>382</v>
-      </c>
-      <c r="K74" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="L74" s="51">
+      <c r="D75" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="E75" s="51" t="s">
+        <v>163</v>
+      </c>
+      <c r="F75" s="51" t="s">
+        <v>210</v>
+      </c>
+      <c r="G75" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="H75" s="51" t="s">
+        <v>318</v>
+      </c>
+      <c r="I75" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="J75" s="51" t="s">
+        <v>374</v>
+      </c>
+      <c r="K75" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="L75" s="51">
         <v>1</v>
       </c>
-      <c r="M74" s="51">
-        <f t="shared" ref="M74" si="63">L74*5</f>
+      <c r="M75" s="51">
+        <f t="shared" ref="M75" si="63">L75*5</f>
         <v>5</v>
       </c>
-      <c r="N74" s="51">
+      <c r="N75" s="51">
         <v>6</v>
       </c>
-      <c r="O74" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P74" s="52">
+      <c r="O75" s="60" t="s">
+        <v>441</v>
+      </c>
+      <c r="P75" s="52">
         <v>0.70009999999999994</v>
       </c>
-      <c r="Q74" s="52">
-        <f t="shared" ref="Q74" si="64">P74*N74</f>
+      <c r="Q75" s="52">
+        <f t="shared" ref="Q75" si="64">P75*N75</f>
         <v>4.2005999999999997</v>
       </c>
-      <c r="R74" s="51"/>
-      <c r="S74" s="59"/>
-    </row>
-    <row r="75" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A75" s="1"/>
-      <c r="B75" s="46">
-        <f>ROW(B75) - ROW($B$9)</f>
-        <v>66</v>
-      </c>
-      <c r="C75" s="53" t="s">
+      <c r="R75" s="51"/>
+      <c r="S75" s="59"/>
+    </row>
+    <row r="76" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+      <c r="A76" s="1"/>
+      <c r="B76" s="46">
+        <f>ROW(B76) - ROW($B$9)</f>
+        <v>67</v>
+      </c>
+      <c r="C76" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="D75" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E75" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="F75" s="37" t="s">
-        <v>216</v>
-      </c>
-      <c r="G75" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="H75" s="37" t="s">
-        <v>326</v>
-      </c>
-      <c r="I75" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="J75" s="37" t="s">
-        <v>383</v>
-      </c>
-      <c r="K75" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="L75" s="37">
+      <c r="D76" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E76" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="F76" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="G76" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="H76" s="37" t="s">
+        <v>319</v>
+      </c>
+      <c r="I76" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="J76" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="K76" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="L76" s="37">
         <v>1</v>
       </c>
-      <c r="M75" s="37">
-        <f>L75*5</f>
+      <c r="M76" s="37">
+        <f>L76*5</f>
         <v>5</v>
       </c>
-      <c r="N75" s="37">
+      <c r="N76" s="37">
         <v>10</v>
       </c>
-      <c r="O75" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P75" s="38">
+      <c r="O76" s="60" t="s">
+        <v>441</v>
+      </c>
+      <c r="P76" s="38">
         <v>0.32279999999999998</v>
       </c>
-      <c r="Q75" s="38">
-        <f>P75*N75</f>
+      <c r="Q76" s="38">
+        <f>P76*N76</f>
         <v>3.2279999999999998</v>
       </c>
-      <c r="R75" s="37"/>
-      <c r="S75" s="59"/>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A76" s="1"/>
-      <c r="B76" s="47">
-        <f t="shared" si="0"/>
-        <v>67</v>
-      </c>
-      <c r="C76" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="D76" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="E76" s="51" t="s">
-        <v>168</v>
-      </c>
-      <c r="F76" s="51" t="s">
-        <v>217</v>
-      </c>
-      <c r="G76" s="51" t="s">
-        <v>278</v>
-      </c>
-      <c r="H76" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="I76" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="J76" s="51" t="s">
-        <v>384</v>
-      </c>
-      <c r="K76" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="L76" s="51">
-        <v>1</v>
-      </c>
-      <c r="M76" s="51">
-        <f t="shared" ref="M76" si="65">L76*5</f>
-        <v>5</v>
-      </c>
-      <c r="N76" s="51">
-        <v>6</v>
-      </c>
-      <c r="O76" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P76" s="52">
-        <v>1.3062</v>
-      </c>
-      <c r="Q76" s="52">
-        <f t="shared" ref="Q76" si="66">P76*N76</f>
-        <v>7.8372000000000002</v>
-      </c>
-      <c r="R76" s="51"/>
+      <c r="R76" s="37"/>
       <c r="S76" s="59"/>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
-      <c r="B77" s="46">
-        <f>ROW(B77) - ROW($B$9)</f>
+      <c r="B77" s="47">
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C77" s="53" t="s">
+      <c r="C77" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="D77" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E77" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="F77" s="37" t="s">
-        <v>218</v>
-      </c>
-      <c r="G77" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="H77" s="37" t="s">
-        <v>328</v>
-      </c>
-      <c r="I77" s="37"/>
-      <c r="J77" s="37" t="s">
-        <v>385</v>
-      </c>
-      <c r="K77" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="L77" s="37">
+      <c r="D77" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="E77" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="F77" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="G77" s="51" t="s">
+        <v>272</v>
+      </c>
+      <c r="H77" s="51" t="s">
+        <v>320</v>
+      </c>
+      <c r="I77" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="J77" s="51" t="s">
+        <v>376</v>
+      </c>
+      <c r="K77" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="L77" s="51">
         <v>1</v>
       </c>
-      <c r="M77" s="37">
-        <f>L77*5</f>
+      <c r="M77" s="51">
+        <f t="shared" ref="M77" si="65">L77*5</f>
         <v>5</v>
       </c>
-      <c r="N77" s="37">
+      <c r="N77" s="51">
         <v>6</v>
       </c>
       <c r="O77" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P77" s="38">
+        <v>441</v>
+      </c>
+      <c r="P77" s="52">
+        <v>1.3062</v>
+      </c>
+      <c r="Q77" s="52">
+        <f t="shared" ref="Q77" si="66">P77*N77</f>
+        <v>7.8372000000000002</v>
+      </c>
+      <c r="R77" s="51"/>
+      <c r="S77" s="59"/>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A78" s="1"/>
+      <c r="B78" s="46">
+        <f>ROW(B78) - ROW($B$9)</f>
+        <v>69</v>
+      </c>
+      <c r="C78" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E78" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="F78" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="G78" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="H78" s="37" t="s">
+        <v>321</v>
+      </c>
+      <c r="I78" s="37"/>
+      <c r="J78" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="K78" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="L78" s="37">
+        <v>1</v>
+      </c>
+      <c r="M78" s="37">
+        <f>L78*5</f>
+        <v>5</v>
+      </c>
+      <c r="N78" s="37">
+        <v>6</v>
+      </c>
+      <c r="O78" s="60" t="s">
+        <v>441</v>
+      </c>
+      <c r="P78" s="38">
         <v>0.3644</v>
       </c>
-      <c r="Q77" s="38">
-        <f>P77*N77</f>
+      <c r="Q78" s="38">
+        <f>P78*N78</f>
         <v>2.1863999999999999</v>
       </c>
-      <c r="R77" s="37"/>
-      <c r="S77" s="59"/>
-    </row>
-    <row r="78" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="67"/>
-      <c r="B78" s="68">
-        <f t="shared" si="0"/>
-        <v>69</v>
-      </c>
-      <c r="C78" s="69" t="s">
-        <v>25</v>
-      </c>
-      <c r="D78" s="70" t="s">
-        <v>95</v>
-      </c>
-      <c r="E78" s="70" t="s">
-        <v>170</v>
-      </c>
-      <c r="F78" s="70" t="s">
-        <v>219</v>
-      </c>
-      <c r="G78" s="70" t="s">
-        <v>280</v>
-      </c>
-      <c r="H78" s="70" t="s">
-        <v>329</v>
-      </c>
-      <c r="I78" s="70" t="s">
-        <v>443</v>
-      </c>
-      <c r="J78" s="70" t="s">
-        <v>443</v>
-      </c>
-      <c r="K78" s="70" t="s">
-        <v>443</v>
-      </c>
-      <c r="L78" s="70">
-        <v>1</v>
-      </c>
-      <c r="M78" s="70">
-        <f t="shared" ref="M78" si="67">L78*5</f>
-        <v>5</v>
-      </c>
-      <c r="N78" s="70">
-        <v>6</v>
-      </c>
-      <c r="O78" s="71" t="s">
-        <v>468</v>
-      </c>
-      <c r="P78" s="72">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="Q78" s="72">
-        <f t="shared" ref="Q78" si="68">P78*N78</f>
-        <v>15.059999999999999</v>
-      </c>
-      <c r="R78" s="70"/>
-      <c r="S78" s="73"/>
+      <c r="R78" s="37"/>
+      <c r="S78" s="59"/>
     </row>
     <row r="79" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="67"/>
-      <c r="B79" s="75">
-        <f>ROW(B79) - ROW($B$9)</f>
+      <c r="B79" s="68">
+        <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C79" s="76" t="s">
+      <c r="C79" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="D79" s="77" t="s">
+      <c r="D79" s="70" t="s">
+        <v>93</v>
+      </c>
+      <c r="E79" s="70" t="s">
+        <v>167</v>
+      </c>
+      <c r="F79" s="70" t="s">
+        <v>214</v>
+      </c>
+      <c r="G79" s="70" t="s">
+        <v>274</v>
+      </c>
+      <c r="H79" s="70" t="s">
+        <v>322</v>
+      </c>
+      <c r="I79" s="70" t="s">
+        <v>434</v>
+      </c>
+      <c r="J79" s="70" t="s">
+        <v>434</v>
+      </c>
+      <c r="K79" s="70" t="s">
+        <v>434</v>
+      </c>
+      <c r="L79" s="70">
+        <v>1</v>
+      </c>
+      <c r="M79" s="70">
+        <f t="shared" ref="M79" si="67">L79*5</f>
+        <v>5</v>
+      </c>
+      <c r="N79" s="70">
+        <v>6</v>
+      </c>
+      <c r="O79" s="71" t="s">
+        <v>458</v>
+      </c>
+      <c r="P79" s="72">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="Q79" s="72">
+        <f t="shared" ref="Q79" si="68">P79*N79</f>
+        <v>15.059999999999999</v>
+      </c>
+      <c r="R79" s="70"/>
+      <c r="S79" s="73"/>
+    </row>
+    <row r="80" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="67"/>
+      <c r="B80" s="75">
+        <f>ROW(B80) - ROW($B$9)</f>
+        <v>71</v>
+      </c>
+      <c r="C80" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="D80" s="77" t="s">
+        <v>94</v>
+      </c>
+      <c r="E80" s="77" t="s">
+        <v>168</v>
+      </c>
+      <c r="F80" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="G80" s="77" t="s">
+        <v>275</v>
+      </c>
+      <c r="H80" s="77" t="s">
+        <v>320</v>
+      </c>
+      <c r="I80" s="77" t="s">
+        <v>434</v>
+      </c>
+      <c r="J80" s="77" t="s">
+        <v>434</v>
+      </c>
+      <c r="K80" s="77" t="s">
+        <v>434</v>
+      </c>
+      <c r="L80" s="77">
+        <v>1</v>
+      </c>
+      <c r="M80" s="77">
+        <f>L80*5</f>
+        <v>5</v>
+      </c>
+      <c r="N80" s="77">
+        <v>6</v>
+      </c>
+      <c r="O80" s="71" t="s">
+        <v>458</v>
+      </c>
+      <c r="P80" s="78">
+        <v>3.4329999999999998</v>
+      </c>
+      <c r="Q80" s="78">
+        <f>P80*N80</f>
+        <v>20.597999999999999</v>
+      </c>
+      <c r="R80" s="77"/>
+      <c r="S80" s="73"/>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A81" s="1"/>
+      <c r="B81" s="47">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="C81" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="D81" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="E81" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="F81" s="51" t="s">
+        <v>216</v>
+      </c>
+      <c r="G81" s="51" t="s">
+        <v>276</v>
+      </c>
+      <c r="H81" s="51" t="s">
+        <v>323</v>
+      </c>
+      <c r="I81" s="51"/>
+      <c r="J81" s="51" t="s">
+        <v>378</v>
+      </c>
+      <c r="K81" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="L81" s="51">
+        <v>1</v>
+      </c>
+      <c r="M81" s="51">
+        <f t="shared" ref="M81" si="69">L81*5</f>
+        <v>5</v>
+      </c>
+      <c r="N81" s="51">
+        <v>6</v>
+      </c>
+      <c r="O81" s="60" t="s">
+        <v>441</v>
+      </c>
+      <c r="P81" s="52">
+        <v>4.6247999999999996</v>
+      </c>
+      <c r="Q81" s="52">
+        <f t="shared" ref="Q81" si="70">P81*N81</f>
+        <v>27.748799999999996</v>
+      </c>
+      <c r="R81" s="51"/>
+      <c r="S81" s="59"/>
+    </row>
+    <row r="82" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="67"/>
+      <c r="B82" s="75">
+        <f>ROW(B82) - ROW($B$9)</f>
+        <v>73</v>
+      </c>
+      <c r="C82" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="D82" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="E79" s="77" t="s">
+      <c r="E82" s="77" t="s">
+        <v>170</v>
+      </c>
+      <c r="F82" s="77" t="s">
+        <v>217</v>
+      </c>
+      <c r="G82" s="77" t="s">
+        <v>277</v>
+      </c>
+      <c r="H82" s="77" t="s">
+        <v>324</v>
+      </c>
+      <c r="I82" s="77" t="s">
+        <v>434</v>
+      </c>
+      <c r="J82" s="77" t="s">
+        <v>434</v>
+      </c>
+      <c r="K82" s="77" t="s">
+        <v>434</v>
+      </c>
+      <c r="L82" s="77">
+        <v>1</v>
+      </c>
+      <c r="M82" s="77">
+        <f>L82*5</f>
+        <v>5</v>
+      </c>
+      <c r="N82" s="77">
+        <v>6</v>
+      </c>
+      <c r="O82" s="71" t="s">
+        <v>458</v>
+      </c>
+      <c r="P82" s="78">
+        <v>7.9</v>
+      </c>
+      <c r="Q82" s="78">
+        <f>P82*N82</f>
+        <v>47.400000000000006</v>
+      </c>
+      <c r="R82" s="79"/>
+      <c r="S82" s="73"/>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A83" s="1"/>
+      <c r="B83" s="47">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="C83" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="D83" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="E83" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="F79" s="77" t="s">
-        <v>220</v>
-      </c>
-      <c r="G79" s="77" t="s">
-        <v>281</v>
-      </c>
-      <c r="H79" s="77" t="s">
-        <v>327</v>
-      </c>
-      <c r="I79" s="77" t="s">
-        <v>443</v>
-      </c>
-      <c r="J79" s="77" t="s">
-        <v>443</v>
-      </c>
-      <c r="K79" s="77" t="s">
-        <v>443</v>
-      </c>
-      <c r="L79" s="77">
+      <c r="F83" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="G83" s="51" t="s">
+        <v>278</v>
+      </c>
+      <c r="H83" s="51" t="s">
+        <v>320</v>
+      </c>
+      <c r="I83" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="J83" s="51" t="s">
+        <v>379</v>
+      </c>
+      <c r="K83" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="L83" s="51">
+        <v>3</v>
+      </c>
+      <c r="M83" s="51">
+        <f t="shared" ref="M83" si="71">L83*5</f>
+        <v>15</v>
+      </c>
+      <c r="N83" s="51">
+        <v>16</v>
+      </c>
+      <c r="O83" s="60" t="s">
+        <v>441</v>
+      </c>
+      <c r="P83" s="52">
+        <v>1.7437</v>
+      </c>
+      <c r="Q83" s="52">
+        <f t="shared" ref="Q83" si="72">P83*N83</f>
+        <v>27.8992</v>
+      </c>
+      <c r="R83" s="51"/>
+      <c r="S83" s="59"/>
+    </row>
+    <row r="84" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="A84" s="1"/>
+      <c r="B84" s="46">
+        <f>ROW(B84) - ROW($B$9)</f>
+        <v>75</v>
+      </c>
+      <c r="C84" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D84" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E84" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="F84" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="G84" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="H84" s="37" t="s">
+        <v>325</v>
+      </c>
+      <c r="I84" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="J84" s="37" t="s">
+        <v>380</v>
+      </c>
+      <c r="K84" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="L84" s="37">
         <v>1</v>
       </c>
-      <c r="M79" s="77">
-        <f>L79*5</f>
+      <c r="M84" s="37">
+        <f>L84*5</f>
         <v>5</v>
       </c>
-      <c r="N79" s="77">
-        <v>6</v>
-      </c>
-      <c r="O79" s="71" t="s">
-        <v>468</v>
-      </c>
-      <c r="P79" s="78">
-        <v>3.4329999999999998</v>
-      </c>
-      <c r="Q79" s="78">
-        <f>P79*N79</f>
-        <v>20.597999999999999</v>
-      </c>
-      <c r="R79" s="77"/>
-      <c r="S79" s="73"/>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A80" s="1"/>
-      <c r="B80" s="47">
-        <f t="shared" si="0"/>
-        <v>71</v>
-      </c>
-      <c r="C80" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="D80" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="E80" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="F80" s="51" t="s">
-        <v>221</v>
-      </c>
-      <c r="G80" s="51" t="s">
-        <v>282</v>
-      </c>
-      <c r="H80" s="51" t="s">
-        <v>330</v>
-      </c>
-      <c r="I80" s="51"/>
-      <c r="J80" s="51" t="s">
-        <v>386</v>
-      </c>
-      <c r="K80" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="L80" s="51">
-        <v>1</v>
-      </c>
-      <c r="M80" s="51">
-        <f t="shared" ref="M80" si="69">L80*5</f>
-        <v>5</v>
-      </c>
-      <c r="N80" s="51">
-        <v>6</v>
-      </c>
-      <c r="O80" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P80" s="52">
-        <v>4.6247999999999996</v>
-      </c>
-      <c r="Q80" s="52">
-        <f t="shared" ref="Q80" si="70">P80*N80</f>
-        <v>27.748799999999996</v>
-      </c>
-      <c r="R80" s="51"/>
-      <c r="S80" s="59"/>
-    </row>
-    <row r="81" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="67"/>
-      <c r="B81" s="75">
-        <f>ROW(B81) - ROW($B$9)</f>
-        <v>72</v>
-      </c>
-      <c r="C81" s="76" t="s">
-        <v>25</v>
-      </c>
-      <c r="D81" s="77" t="s">
-        <v>98</v>
-      </c>
-      <c r="E81" s="77" t="s">
-        <v>173</v>
-      </c>
-      <c r="F81" s="77" t="s">
-        <v>222</v>
-      </c>
-      <c r="G81" s="77" t="s">
-        <v>283</v>
-      </c>
-      <c r="H81" s="77" t="s">
-        <v>331</v>
-      </c>
-      <c r="I81" s="77" t="s">
-        <v>443</v>
-      </c>
-      <c r="J81" s="77" t="s">
-        <v>443</v>
-      </c>
-      <c r="K81" s="77" t="s">
-        <v>443</v>
-      </c>
-      <c r="L81" s="77">
-        <v>1</v>
-      </c>
-      <c r="M81" s="77">
-        <f>L81*5</f>
-        <v>5</v>
-      </c>
-      <c r="N81" s="77">
-        <v>6</v>
-      </c>
-      <c r="O81" s="71" t="s">
-        <v>468</v>
-      </c>
-      <c r="P81" s="78">
-        <v>7.9</v>
-      </c>
-      <c r="Q81" s="78">
-        <f>P81*N81</f>
-        <v>47.400000000000006</v>
-      </c>
-      <c r="R81" s="79"/>
-      <c r="S81" s="73"/>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A82" s="1"/>
-      <c r="B82" s="47">
-        <f t="shared" si="0"/>
-        <v>73</v>
-      </c>
-      <c r="C82" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="D82" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="E82" s="51" t="s">
-        <v>174</v>
-      </c>
-      <c r="F82" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="G82" s="51" t="s">
-        <v>284</v>
-      </c>
-      <c r="H82" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="I82" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="J82" s="51" t="s">
-        <v>387</v>
-      </c>
-      <c r="K82" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="L82" s="51">
-        <v>3</v>
-      </c>
-      <c r="M82" s="51">
-        <f t="shared" ref="M82" si="71">L82*5</f>
-        <v>15</v>
-      </c>
-      <c r="N82" s="51">
-        <v>16</v>
-      </c>
-      <c r="O82" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P82" s="52">
-        <v>1.7437</v>
-      </c>
-      <c r="Q82" s="52">
-        <f t="shared" ref="Q82" si="72">P82*N82</f>
-        <v>27.8992</v>
-      </c>
-      <c r="R82" s="51"/>
-      <c r="S82" s="59"/>
-    </row>
-    <row r="83" spans="1:19" ht="60" x14ac:dyDescent="0.25">
-      <c r="A83" s="1"/>
-      <c r="B83" s="46">
-        <f>ROW(B83) - ROW($B$9)</f>
-        <v>74</v>
-      </c>
-      <c r="C83" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="D83" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="E83" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="F83" s="37" t="s">
-        <v>224</v>
-      </c>
-      <c r="G83" s="37" t="s">
-        <v>285</v>
-      </c>
-      <c r="H83" s="37" t="s">
-        <v>332</v>
-      </c>
-      <c r="I83" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="J83" s="37" t="s">
-        <v>388</v>
-      </c>
-      <c r="K83" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="L83" s="37">
-        <v>1</v>
-      </c>
-      <c r="M83" s="37">
-        <f>L83*5</f>
-        <v>5</v>
-      </c>
-      <c r="N83" s="37">
+      <c r="N84" s="37">
         <v>10</v>
       </c>
-      <c r="O83" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P83" s="38">
+      <c r="O84" s="60" t="s">
+        <v>441</v>
+      </c>
+      <c r="P84" s="38">
         <v>7.7799999999999994E-2</v>
       </c>
-      <c r="Q83" s="38">
-        <f>P83*N83</f>
+      <c r="Q84" s="38">
+        <f>P84*N84</f>
         <v>0.77799999999999991</v>
       </c>
-      <c r="R83" s="37"/>
-      <c r="S83" s="59"/>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A84" s="1"/>
-      <c r="B84" s="47">
-        <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="C84" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="D84" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="E84" s="51" t="s">
-        <v>176</v>
-      </c>
-      <c r="F84" s="51" t="s">
-        <v>225</v>
-      </c>
-      <c r="G84" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="H84" s="51" t="s">
-        <v>325</v>
-      </c>
-      <c r="I84" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="J84" s="51" t="s">
-        <v>389</v>
-      </c>
-      <c r="K84" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="L84" s="51">
-        <v>1</v>
-      </c>
-      <c r="M84" s="51">
-        <f t="shared" ref="M84" si="73">L84*5</f>
-        <v>5</v>
-      </c>
-      <c r="N84" s="51">
-        <v>6</v>
-      </c>
-      <c r="O84" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P84" s="52">
-        <v>0.77800000000000002</v>
-      </c>
-      <c r="Q84" s="52">
-        <f t="shared" ref="Q84" si="74">P84*N84</f>
-        <v>4.6680000000000001</v>
-      </c>
-      <c r="R84" s="51"/>
+      <c r="R84" s="37"/>
       <c r="S84" s="59"/>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
-      <c r="B85" s="46">
-        <f>ROW(B85) - ROW($B$9)</f>
+      <c r="B85" s="47">
+        <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="C85" s="53" t="s">
+      <c r="C85" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="D85" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="E85" s="37" t="s">
-        <v>177</v>
-      </c>
-      <c r="F85" s="37" t="s">
-        <v>226</v>
-      </c>
-      <c r="G85" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="H85" s="37" t="s">
-        <v>326</v>
-      </c>
-      <c r="I85" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="J85" s="37" t="s">
-        <v>390</v>
-      </c>
-      <c r="K85" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="L85" s="37">
+      <c r="D85" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="E85" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="F85" s="51" t="s">
+        <v>220</v>
+      </c>
+      <c r="G85" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="H85" s="51" t="s">
+        <v>318</v>
+      </c>
+      <c r="I85" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="J85" s="51" t="s">
+        <v>381</v>
+      </c>
+      <c r="K85" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="L85" s="51">
         <v>1</v>
       </c>
-      <c r="M85" s="37">
-        <f>L85*5</f>
+      <c r="M85" s="51">
+        <f t="shared" ref="M85" si="73">L85*5</f>
         <v>5</v>
       </c>
-      <c r="N85" s="37">
+      <c r="N85" s="51">
         <v>6</v>
       </c>
       <c r="O85" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P85" s="38">
-        <v>0.41049999999999998</v>
-      </c>
-      <c r="Q85" s="38">
-        <f>P85*N85</f>
-        <v>2.4630000000000001</v>
-      </c>
-      <c r="R85" s="37"/>
+        <v>441</v>
+      </c>
+      <c r="P85" s="52">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="Q85" s="52">
+        <f t="shared" ref="Q85" si="74">P85*N85</f>
+        <v>4.6680000000000001</v>
+      </c>
+      <c r="R85" s="51"/>
       <c r="S85" s="59"/>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
-      <c r="B86" s="47">
-        <f t="shared" si="0"/>
+      <c r="B86" s="46">
+        <f>ROW(B86) - ROW($B$9)</f>
         <v>77</v>
       </c>
-      <c r="C86" s="54" t="s">
+      <c r="C86" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="D86" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="E86" s="51" t="s">
-        <v>178</v>
-      </c>
-      <c r="F86" s="51" t="s">
-        <v>220</v>
-      </c>
-      <c r="G86" s="51" t="s">
-        <v>288</v>
-      </c>
-      <c r="H86" s="51" t="s">
-        <v>331</v>
-      </c>
-      <c r="I86" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="J86" s="51" t="s">
-        <v>391</v>
-      </c>
-      <c r="K86" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="L86" s="51">
+      <c r="D86" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="E86" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="F86" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="G86" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="H86" s="37" t="s">
+        <v>319</v>
+      </c>
+      <c r="I86" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="J86" s="37" t="s">
+        <v>382</v>
+      </c>
+      <c r="K86" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="L86" s="37">
         <v>1</v>
       </c>
-      <c r="M86" s="51">
-        <f t="shared" ref="M86" si="75">L86*5</f>
+      <c r="M86" s="37">
+        <f>L86*5</f>
         <v>5</v>
       </c>
-      <c r="N86" s="51">
+      <c r="N86" s="37">
         <v>6</v>
       </c>
       <c r="O86" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P86" s="52">
-        <v>1.1837</v>
-      </c>
-      <c r="Q86" s="52">
-        <f t="shared" ref="Q86" si="76">P86*N86</f>
-        <v>7.1021999999999998</v>
-      </c>
-      <c r="R86" s="51"/>
+        <v>441</v>
+      </c>
+      <c r="P86" s="38">
+        <v>0.41049999999999998</v>
+      </c>
+      <c r="Q86" s="38">
+        <f>P86*N86</f>
+        <v>2.4630000000000001</v>
+      </c>
+      <c r="R86" s="37"/>
       <c r="S86" s="59"/>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
-      <c r="B87" s="46">
-        <f>ROW(B87) - ROW($B$9)</f>
+      <c r="B87" s="47">
+        <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="C87" s="53" t="s">
+      <c r="C87" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="D87" s="37" t="s">
+      <c r="D87" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="E87" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="F87" s="51" t="s">
+        <v>215</v>
+      </c>
+      <c r="G87" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="H87" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="I87" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="J87" s="51" t="s">
+        <v>383</v>
+      </c>
+      <c r="K87" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="L87" s="51">
+        <v>1</v>
+      </c>
+      <c r="M87" s="51">
+        <f t="shared" ref="M87" si="75">L87*5</f>
+        <v>5</v>
+      </c>
+      <c r="N87" s="51">
+        <v>6</v>
+      </c>
+      <c r="O87" s="60" t="s">
+        <v>441</v>
+      </c>
+      <c r="P87" s="52">
+        <v>1.1837</v>
+      </c>
+      <c r="Q87" s="52">
+        <f t="shared" ref="Q87" si="76">P87*N87</f>
+        <v>7.1021999999999998</v>
+      </c>
+      <c r="R87" s="51"/>
+      <c r="S87" s="59"/>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A88" s="1"/>
+      <c r="B88" s="46">
+        <f>ROW(B88) - ROW($B$9)</f>
+        <v>79</v>
+      </c>
+      <c r="C88" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D88" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="E88" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="F88" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="G88" s="37" t="s">
+        <v>283</v>
+      </c>
+      <c r="H88" s="37" t="s">
+        <v>324</v>
+      </c>
+      <c r="I88" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="J88" s="37" t="s">
+        <v>384</v>
+      </c>
+      <c r="K88" s="37" t="s">
+        <v>434</v>
+      </c>
+      <c r="L88" s="37">
+        <v>1</v>
+      </c>
+      <c r="M88" s="37">
+        <f>L88*5</f>
+        <v>5</v>
+      </c>
+      <c r="N88" s="37">
+        <v>6</v>
+      </c>
+      <c r="O88" s="60" t="s">
+        <v>441</v>
+      </c>
+      <c r="P88" s="38">
+        <v>1.2107000000000001</v>
+      </c>
+      <c r="Q88" s="38">
+        <f>P88*N88</f>
+        <v>7.2642000000000007</v>
+      </c>
+      <c r="R88" s="37"/>
+      <c r="S88" s="59"/>
+    </row>
+    <row r="89" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+      <c r="A89" s="1"/>
+      <c r="B89" s="47">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="C89" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="D89" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="E89" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="F89" s="51" t="s">
+        <v>440</v>
+      </c>
+      <c r="G89" s="51" t="s">
+        <v>284</v>
+      </c>
+      <c r="H89" s="51" t="s">
+        <v>326</v>
+      </c>
+      <c r="I89" s="51" t="s">
+        <v>434</v>
+      </c>
+      <c r="J89" s="51" t="s">
+        <v>385</v>
+      </c>
+      <c r="K89" s="51" t="s">
+        <v>422</v>
+      </c>
+      <c r="L89" s="51">
+        <v>1</v>
+      </c>
+      <c r="M89" s="51">
+        <f t="shared" ref="M89" si="77">L89*5</f>
+        <v>5</v>
+      </c>
+      <c r="N89" s="51">
+        <v>10</v>
+      </c>
+      <c r="O89" s="60" t="s">
+        <v>441</v>
+      </c>
+      <c r="P89" s="52">
+        <v>0.08</v>
+      </c>
+      <c r="Q89" s="52">
+        <f t="shared" ref="Q89" si="78">P89*N89</f>
+        <v>0.8</v>
+      </c>
+      <c r="R89" s="51"/>
+      <c r="S89" s="59"/>
+    </row>
+    <row r="90" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="1"/>
+      <c r="B90" s="46">
+        <f>ROW(B90) - ROW($B$9)</f>
+        <v>81</v>
+      </c>
+      <c r="C90" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="D90" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="E87" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="F87" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="G87" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="H87" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="I87" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="J87" s="37" t="s">
-        <v>392</v>
-      </c>
-      <c r="K87" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="L87" s="37">
+      <c r="E90" s="37" t="s">
+        <v>478</v>
+      </c>
+      <c r="F90" s="37" t="s">
+        <v>479</v>
+      </c>
+      <c r="G90" s="37" t="s">
+        <v>480</v>
+      </c>
+      <c r="H90" s="37" t="s">
+        <v>481</v>
+      </c>
+      <c r="I90" s="37"/>
+      <c r="J90" s="37" t="s">
+        <v>482</v>
+      </c>
+      <c r="K90" s="37" t="s">
+        <v>423</v>
+      </c>
+      <c r="L90" s="37">
         <v>1</v>
       </c>
-      <c r="M87" s="37">
-        <f>L87*5</f>
+      <c r="M90" s="37">
+        <f>L90*5</f>
         <v>5</v>
       </c>
-      <c r="N87" s="37">
-        <v>6</v>
-      </c>
-      <c r="O87" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P87" s="38">
-        <v>1.2107000000000001</v>
-      </c>
-      <c r="Q87" s="38">
-        <f>P87*N87</f>
-        <v>7.2642000000000007</v>
-      </c>
-      <c r="R87" s="37"/>
-      <c r="S87" s="59"/>
-    </row>
-    <row r="88" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A88" s="1"/>
-      <c r="B88" s="47">
-        <f t="shared" si="0"/>
-        <v>79</v>
-      </c>
-      <c r="C88" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="D88" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="E88" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="F88" s="51" t="s">
-        <v>449</v>
-      </c>
-      <c r="G88" s="51" t="s">
-        <v>290</v>
-      </c>
-      <c r="H88" s="51" t="s">
-        <v>333</v>
-      </c>
-      <c r="I88" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="J88" s="51" t="s">
-        <v>393</v>
-      </c>
-      <c r="K88" s="51" t="s">
-        <v>431</v>
-      </c>
-      <c r="L88" s="51">
-        <v>1</v>
-      </c>
-      <c r="M88" s="51">
-        <f t="shared" ref="M88" si="77">L88*5</f>
-        <v>5</v>
-      </c>
-      <c r="N88" s="51">
+      <c r="N90" s="37">
         <v>10</v>
       </c>
-      <c r="O88" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P88" s="52">
-        <v>0.08</v>
-      </c>
-      <c r="Q88" s="52">
-        <f t="shared" ref="Q88" si="78">P88*N88</f>
-        <v>0.8</v>
-      </c>
-      <c r="R88" s="51"/>
-      <c r="S88" s="59"/>
-    </row>
-    <row r="89" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="1"/>
-      <c r="B89" s="46">
-        <f>ROW(B89) - ROW($B$9)</f>
-        <v>80</v>
-      </c>
-      <c r="C89" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="D89" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="E89" s="37" t="s">
-        <v>180</v>
-      </c>
-      <c r="F89" s="51" t="s">
-        <v>449</v>
-      </c>
-      <c r="G89" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="H89" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="I89" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="J89" s="37" t="s">
-        <v>394</v>
-      </c>
-      <c r="K89" s="37" t="s">
-        <v>432</v>
-      </c>
-      <c r="L89" s="37">
-        <v>1</v>
-      </c>
-      <c r="M89" s="37">
-        <f>L89*5</f>
-        <v>5</v>
-      </c>
-      <c r="N89" s="37">
-        <v>10</v>
-      </c>
-      <c r="O89" s="60" t="s">
-        <v>450</v>
-      </c>
-      <c r="P89" s="38">
-        <v>8.0699999999999994E-2</v>
-      </c>
-      <c r="Q89" s="38">
-        <f>P89*N89</f>
-        <v>0.80699999999999994</v>
-      </c>
-      <c r="R89" s="37"/>
-      <c r="S89" s="39"/>
-    </row>
-    <row r="90" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="1"/>
-      <c r="B90" s="40"/>
-      <c r="C90" s="41"/>
-      <c r="D90" s="42"/>
-      <c r="E90" s="43"/>
-      <c r="F90" s="44"/>
-      <c r="G90" s="45"/>
-      <c r="H90" s="44"/>
-      <c r="I90" s="45"/>
-      <c r="J90" s="44"/>
-      <c r="K90" s="45"/>
-      <c r="L90" s="45"/>
-      <c r="M90" s="45"/>
-      <c r="N90" s="88" t="s">
-        <v>5</v>
-      </c>
-      <c r="O90" s="89"/>
-      <c r="P90" s="89"/>
-      <c r="Q90" s="48">
-        <f>SUM(Q10:Q89)</f>
-        <v>281.5193000000001</v>
-      </c>
-      <c r="R90" s="84"/>
-      <c r="S90" s="85"/>
+      <c r="O90" s="60" t="s">
+        <v>441</v>
+      </c>
+      <c r="P90" s="38">
+        <v>0.1065</v>
+      </c>
+      <c r="Q90" s="38">
+        <f>P90*N90</f>
+        <v>1.0649999999999999</v>
+      </c>
+      <c r="R90" s="37"/>
+      <c r="S90" s="39"/>
     </row>
     <row r="91" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
-      <c r="B91" s="25"/>
-      <c r="C91" s="36"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="10"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="10"/>
-      <c r="H91" s="10"/>
-      <c r="I91" s="10"/>
-      <c r="J91" s="10"/>
-      <c r="K91" s="10"/>
-      <c r="L91" s="10"/>
-      <c r="M91" s="10"/>
+      <c r="B91" s="40"/>
+      <c r="C91" s="41"/>
+      <c r="D91" s="42"/>
+      <c r="E91" s="43"/>
+      <c r="F91" s="44"/>
+      <c r="G91" s="45"/>
+      <c r="H91" s="44"/>
+      <c r="I91" s="45"/>
+      <c r="J91" s="44"/>
+      <c r="K91" s="45"/>
+      <c r="L91" s="45"/>
+      <c r="M91" s="45"/>
       <c r="N91" s="88" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O91" s="89"/>
       <c r="P91" s="89"/>
-      <c r="Q91" s="49">
-        <f>Q90/5</f>
-        <v>56.303860000000022</v>
-      </c>
-      <c r="R91" s="86"/>
-      <c r="S91" s="87"/>
+      <c r="Q91" s="48">
+        <f>SUM(Q10:Q90)</f>
+        <v>293.06310000000008</v>
+      </c>
+      <c r="R91" s="84"/>
+      <c r="S91" s="85"/>
+    </row>
+    <row r="92" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="1"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="36"/>
+      <c r="D92" s="9"/>
+      <c r="E92" s="10"/>
+      <c r="F92" s="10"/>
+      <c r="G92" s="10"/>
+      <c r="H92" s="10"/>
+      <c r="I92" s="10"/>
+      <c r="J92" s="10"/>
+      <c r="K92" s="10"/>
+      <c r="L92" s="10"/>
+      <c r="M92" s="10"/>
+      <c r="N92" s="88" t="s">
+        <v>6</v>
+      </c>
+      <c r="O92" s="89"/>
+      <c r="P92" s="89"/>
+      <c r="Q92" s="49">
+        <f>Q91/5</f>
+        <v>58.612620000000014</v>
+      </c>
+      <c r="R92" s="86"/>
+      <c r="S92" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R90:S91"/>
-    <mergeCell ref="N90:P90"/>
+    <mergeCell ref="R91:S92"/>
     <mergeCell ref="N91:P91"/>
+    <mergeCell ref="N92:P92"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="O11" r:id="rId1"/>
-    <hyperlink ref="O12" r:id="rId2"/>
-    <hyperlink ref="O13" r:id="rId3"/>
-    <hyperlink ref="O14" r:id="rId4"/>
-    <hyperlink ref="O17" r:id="rId5"/>
-    <hyperlink ref="O19" r:id="rId6"/>
-    <hyperlink ref="O22" r:id="rId7"/>
-    <hyperlink ref="O21" r:id="rId8"/>
-    <hyperlink ref="O23" r:id="rId9"/>
-    <hyperlink ref="O24" r:id="rId10"/>
-    <hyperlink ref="O25" r:id="rId11"/>
-    <hyperlink ref="O28" r:id="rId12"/>
-    <hyperlink ref="O29" r:id="rId13"/>
-    <hyperlink ref="O30" r:id="rId14"/>
-    <hyperlink ref="O31" r:id="rId15"/>
-    <hyperlink ref="O32" r:id="rId16"/>
-    <hyperlink ref="O33" r:id="rId17"/>
-    <hyperlink ref="O34" r:id="rId18"/>
-    <hyperlink ref="O35" r:id="rId19"/>
-    <hyperlink ref="O36" r:id="rId20"/>
-    <hyperlink ref="O37" r:id="rId21"/>
-    <hyperlink ref="O38" r:id="rId22"/>
-    <hyperlink ref="O40" r:id="rId23"/>
-    <hyperlink ref="O42" r:id="rId24"/>
-    <hyperlink ref="O43" r:id="rId25"/>
-    <hyperlink ref="O44" r:id="rId26"/>
-    <hyperlink ref="O45" r:id="rId27"/>
-    <hyperlink ref="O46" r:id="rId28"/>
-    <hyperlink ref="O47" r:id="rId29"/>
-    <hyperlink ref="O49" r:id="rId30"/>
-    <hyperlink ref="O51" r:id="rId31"/>
-    <hyperlink ref="O52" r:id="rId32"/>
-    <hyperlink ref="O53" r:id="rId33"/>
-    <hyperlink ref="O55" r:id="rId34"/>
-    <hyperlink ref="O56" r:id="rId35"/>
-    <hyperlink ref="O58" r:id="rId36"/>
-    <hyperlink ref="O59" r:id="rId37"/>
-    <hyperlink ref="O60" r:id="rId38"/>
-    <hyperlink ref="O61" r:id="rId39"/>
-    <hyperlink ref="O62" r:id="rId40"/>
-    <hyperlink ref="O63" r:id="rId41"/>
-    <hyperlink ref="O64" r:id="rId42"/>
-    <hyperlink ref="O65" r:id="rId43"/>
-    <hyperlink ref="O67" r:id="rId44"/>
-    <hyperlink ref="O68" r:id="rId45"/>
-    <hyperlink ref="O69" r:id="rId46"/>
-    <hyperlink ref="O70" r:id="rId47"/>
-    <hyperlink ref="O73" r:id="rId48"/>
-    <hyperlink ref="O74" r:id="rId49"/>
-    <hyperlink ref="O75" r:id="rId50"/>
-    <hyperlink ref="O76" r:id="rId51"/>
-    <hyperlink ref="O77" r:id="rId52"/>
-    <hyperlink ref="O80" r:id="rId53"/>
-    <hyperlink ref="O82" r:id="rId54"/>
-    <hyperlink ref="O83" r:id="rId55"/>
-    <hyperlink ref="O84" r:id="rId56"/>
-    <hyperlink ref="O85" r:id="rId57"/>
-    <hyperlink ref="O86" r:id="rId58"/>
-    <hyperlink ref="O87" r:id="rId59"/>
-    <hyperlink ref="O88" r:id="rId60"/>
-    <hyperlink ref="O89" r:id="rId61"/>
-    <hyperlink ref="O72" r:id="rId62"/>
-    <hyperlink ref="O20" r:id="rId63"/>
-    <hyperlink ref="O26" r:id="rId64"/>
-    <hyperlink ref="O27" r:id="rId65"/>
-    <hyperlink ref="O50" r:id="rId66"/>
-    <hyperlink ref="O54" r:id="rId67"/>
-    <hyperlink ref="O57" r:id="rId68"/>
-    <hyperlink ref="O66" r:id="rId69"/>
-    <hyperlink ref="O78" r:id="rId70"/>
-    <hyperlink ref="O79" r:id="rId71"/>
-    <hyperlink ref="O81" r:id="rId72"/>
-    <hyperlink ref="O15" r:id="rId73"/>
-    <hyperlink ref="O16" r:id="rId74"/>
-    <hyperlink ref="O18" r:id="rId75"/>
-    <hyperlink ref="O39" r:id="rId76"/>
-    <hyperlink ref="O41" r:id="rId77"/>
+    <hyperlink ref="O43" r:id="rId1"/>
+    <hyperlink ref="O71" r:id="rId2"/>
+    <hyperlink ref="O90" r:id="rId3"/>
+    <hyperlink ref="O41" r:id="rId4"/>
+    <hyperlink ref="O39" r:id="rId5"/>
+    <hyperlink ref="O18" r:id="rId6"/>
+    <hyperlink ref="O16" r:id="rId7"/>
+    <hyperlink ref="O15" r:id="rId8"/>
+    <hyperlink ref="O82" r:id="rId9"/>
+    <hyperlink ref="O80" r:id="rId10"/>
+    <hyperlink ref="O79" r:id="rId11"/>
+    <hyperlink ref="O66" r:id="rId12"/>
+    <hyperlink ref="O57" r:id="rId13"/>
+    <hyperlink ref="O54" r:id="rId14"/>
+    <hyperlink ref="O50" r:id="rId15"/>
+    <hyperlink ref="O27" r:id="rId16"/>
+    <hyperlink ref="O26" r:id="rId17"/>
+    <hyperlink ref="O20" r:id="rId18"/>
+    <hyperlink ref="O73" r:id="rId19"/>
+    <hyperlink ref="O89" r:id="rId20"/>
+    <hyperlink ref="O88" r:id="rId21"/>
+    <hyperlink ref="O87" r:id="rId22"/>
+    <hyperlink ref="O86" r:id="rId23"/>
+    <hyperlink ref="O85" r:id="rId24"/>
+    <hyperlink ref="O84" r:id="rId25"/>
+    <hyperlink ref="O83" r:id="rId26"/>
+    <hyperlink ref="O81" r:id="rId27"/>
+    <hyperlink ref="O78" r:id="rId28"/>
+    <hyperlink ref="O77" r:id="rId29"/>
+    <hyperlink ref="O76" r:id="rId30"/>
+    <hyperlink ref="O75" r:id="rId31"/>
+    <hyperlink ref="O74" r:id="rId32"/>
+    <hyperlink ref="O70" r:id="rId33"/>
+    <hyperlink ref="O69" r:id="rId34"/>
+    <hyperlink ref="O68" r:id="rId35"/>
+    <hyperlink ref="O67" r:id="rId36"/>
+    <hyperlink ref="O61" r:id="rId37"/>
+    <hyperlink ref="O65" r:id="rId38"/>
+    <hyperlink ref="O64" r:id="rId39"/>
+    <hyperlink ref="O63" r:id="rId40"/>
+    <hyperlink ref="O62" r:id="rId41"/>
+    <hyperlink ref="O60" r:id="rId42"/>
+    <hyperlink ref="O59" r:id="rId43"/>
+    <hyperlink ref="O58" r:id="rId44"/>
+    <hyperlink ref="O56" r:id="rId45"/>
+    <hyperlink ref="O55" r:id="rId46"/>
+    <hyperlink ref="O53" r:id="rId47"/>
+    <hyperlink ref="O52" r:id="rId48"/>
+    <hyperlink ref="O51" r:id="rId49"/>
+    <hyperlink ref="O49" r:id="rId50"/>
+    <hyperlink ref="O47" r:id="rId51"/>
+    <hyperlink ref="O46" r:id="rId52"/>
+    <hyperlink ref="O45" r:id="rId53"/>
+    <hyperlink ref="O44" r:id="rId54"/>
+    <hyperlink ref="O42" r:id="rId55"/>
+    <hyperlink ref="O40" r:id="rId56"/>
+    <hyperlink ref="O38" r:id="rId57"/>
+    <hyperlink ref="O37" r:id="rId58"/>
+    <hyperlink ref="O36" r:id="rId59"/>
+    <hyperlink ref="O35" r:id="rId60"/>
+    <hyperlink ref="O34" r:id="rId61"/>
+    <hyperlink ref="O33" r:id="rId62"/>
+    <hyperlink ref="O32" r:id="rId63"/>
+    <hyperlink ref="O31" r:id="rId64"/>
+    <hyperlink ref="O30" r:id="rId65"/>
+    <hyperlink ref="O29" r:id="rId66"/>
+    <hyperlink ref="O28" r:id="rId67"/>
+    <hyperlink ref="O25" r:id="rId68"/>
+    <hyperlink ref="O24" r:id="rId69"/>
+    <hyperlink ref="O23" r:id="rId70"/>
+    <hyperlink ref="O21" r:id="rId71"/>
+    <hyperlink ref="O22" r:id="rId72"/>
+    <hyperlink ref="O19" r:id="rId73"/>
+    <hyperlink ref="O17" r:id="rId74"/>
+    <hyperlink ref="O14" r:id="rId75"/>
+    <hyperlink ref="O13" r:id="rId76"/>
+    <hyperlink ref="O12" r:id="rId77"/>
+    <hyperlink ref="O11" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId78"/>
-  <drawing r:id="rId79"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId79"/>
+  <drawing r:id="rId80"/>
 </worksheet>
 </file>
--- a/Design Files/Baseboard-v2.0/BOM/eSpark_BOM_Baseboard-v2.0.xlsx
+++ b/Design Files/Baseboard-v2.0/BOM/eSpark_BOM_Baseboard-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="501">
   <si>
     <t>Component list</t>
   </si>
@@ -66,9 +66,6 @@
     <t>USB Connector</t>
   </si>
   <si>
-    <t>Wire To Board Connector</t>
-  </si>
-  <si>
     <t>Connector</t>
   </si>
   <si>
@@ -219,9 +216,6 @@
     <t>LED2</t>
   </si>
   <si>
-    <t>P1, P2, P3, P4, P5, P6, P7, P8, P9, P10</t>
-  </si>
-  <si>
     <t>Q1</t>
   </si>
   <si>
@@ -234,9 +228,6 @@
     <t>R4</t>
   </si>
   <si>
-    <t>R6, R8, R79, R80, R81, R85, R86</t>
-  </si>
-  <si>
     <t>R9</t>
   </si>
   <si>
@@ -279,9 +270,6 @@
     <t>R92</t>
   </si>
   <si>
-    <t>SB1, SB2</t>
-  </si>
-  <si>
     <t>SW1</t>
   </si>
   <si>
@@ -939,9 +927,6 @@
     <t>Korean Hroparts Elec</t>
   </si>
   <si>
-    <t>Molex</t>
-  </si>
-  <si>
     <t>BOOMELE</t>
   </si>
   <si>
@@ -1398,12 +1383,6 @@
     <t>chipsmall</t>
   </si>
   <si>
-    <t>CONN HEADER SMD 11POS 1.25MM</t>
-  </si>
-  <si>
-    <t>53398-1171</t>
-  </si>
-  <si>
     <t>1 Inner bore SMA Board Edge Bend -55℃~+155℃ 50Ω Plugin RF Connectors / Coaxial Connectors ROHS</t>
   </si>
   <si>
@@ -1422,9 +1401,6 @@
     <t>Case-D</t>
   </si>
   <si>
-    <t>TAJD227K010RNJV</t>
-  </si>
-  <si>
     <t>C8024</t>
   </si>
   <si>
@@ -1452,9 +1428,6 @@
     <t>C51599</t>
   </si>
   <si>
-    <t>C504827</t>
-  </si>
-  <si>
     <t>3.579545MHz 20pF ±30ppm HC-49S-SMD Crystals ROHS</t>
   </si>
   <si>
@@ -1482,9 +1455,6 @@
     <t>Resistor Array</t>
   </si>
   <si>
-    <t>RN1, RN2, RN3, RN4, RN5</t>
-  </si>
-  <si>
     <t>RES ARRAY 4 RES 10K OHM 1206</t>
   </si>
   <si>
@@ -1504,6 +1474,54 @@
   </si>
   <si>
     <t>Chipsmall</t>
+  </si>
+  <si>
+    <t>P1, P2, P3, P4, P5, P6, P7, P8, P9</t>
+  </si>
+  <si>
+    <t>R6, R8, R10, R79, R80, R81, R85, R86</t>
+  </si>
+  <si>
+    <t>R22, R23, R24</t>
+  </si>
+  <si>
+    <t>RN1, RN2</t>
+  </si>
+  <si>
+    <t>SB1, SB2, SB3</t>
+  </si>
+  <si>
+    <t>TAJD227K010RNJ</t>
+  </si>
+  <si>
+    <t>F0503-ZV-18-20T-R</t>
+  </si>
+  <si>
+    <t>YC164-JR-07100KL</t>
+  </si>
+  <si>
+    <t>FPC Connector</t>
+  </si>
+  <si>
+    <t>Slide Lock 18P Contact, Vertical - One Side Brick nogging 0.5mm SMD,P=0.5mm FFC/FPC Connectors ROHS</t>
+  </si>
+  <si>
+    <t>XFCN</t>
+  </si>
+  <si>
+    <t>C481243</t>
+  </si>
+  <si>
+    <t>RES ARRAY 4 RES 100K OHM 1206</t>
+  </si>
+  <si>
+    <t>YC164-JR-070RL</t>
+  </si>
+  <si>
+    <t>C192933</t>
+  </si>
+  <si>
+    <t>DNP</t>
   </si>
 </sst>
 </file>
@@ -1515,7 +1533,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1696,6 +1714,20 @@
       <strike/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1992,7 +2024,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2174,40 +2206,22 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2583,7 +2597,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S92"/>
+  <dimension ref="A1:AA93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -2604,9 +2618,11 @@
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.140625" customWidth="1"/>
+    <col min="22" max="22" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -2617,17 +2633,17 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="80"/>
-      <c r="R1" s="80"/>
-      <c r="S1" s="81"/>
-    </row>
-    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="75"/>
+    </row>
+    <row r="2" spans="1:27" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="21"/>
       <c r="C2" s="31"/>
@@ -2636,7 +2652,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2652,7 +2668,7 @@
       <c r="R2" s="4"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="22"/>
       <c r="C3" s="32"/>
@@ -2661,7 +2677,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2675,9 +2691,9 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="82"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S3" s="76"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="22"/>
       <c r="C4" s="32"/>
@@ -2686,7 +2702,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2700,9 +2716,9 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="83"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S4" s="77"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="22"/>
       <c r="C5" s="32"/>
@@ -2725,9 +2741,9 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="83"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S5" s="77"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="23"/>
       <c r="C6" s="33"/>
@@ -2746,9 +2762,9 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="83"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="S6" s="77"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="24"/>
       <c r="C7" s="34"/>
@@ -2767,9 +2783,9 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="83"/>
-    </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S7" s="77"/>
+    </row>
+    <row r="8" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="27"/>
       <c r="C8" s="35"/>
@@ -2788,9 +2804,9 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="83"/>
-    </row>
-    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S8" s="77"/>
+    </row>
+    <row r="9" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="30" t="s">
         <v>4</v>
@@ -2799,86 +2815,90 @@
         <v>8</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>420</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>428</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>419</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>427</v>
+      </c>
+      <c r="N9" s="30" t="s">
+        <v>421</v>
+      </c>
+      <c r="O9" s="30" t="s">
+        <v>422</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>423</v>
+      </c>
+      <c r="Q9" s="30" t="s">
+        <v>424</v>
+      </c>
+      <c r="R9" s="30" t="s">
         <v>425</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>327</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>433</v>
-      </c>
-      <c r="L9" s="30" t="s">
-        <v>424</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>432</v>
-      </c>
-      <c r="N9" s="30" t="s">
+      <c r="S9" s="30" t="s">
         <v>426</v>
       </c>
-      <c r="O9" s="30" t="s">
-        <v>427</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>428</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>429</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>430</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U9" s="70"/>
+      <c r="V9" s="70"/>
+      <c r="W9" s="70"/>
+      <c r="X9" s="70"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
       <c r="C10" s="53" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="D10" s="62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" s="62" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="F10" s="62" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G10" s="62" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="H10" s="66" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="I10" s="66" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J10" s="66" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="K10" s="62" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L10" s="62">
         <v>1</v>
@@ -2888,54 +2908,58 @@
         <v>5</v>
       </c>
       <c r="N10" s="62" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="O10" s="62" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="P10" s="66" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="Q10" s="66" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="R10" s="63" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="S10" s="50"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U10" s="70"/>
+      <c r="V10" s="70"/>
+      <c r="W10" s="70"/>
+      <c r="X10" s="70"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="47">
-        <f t="shared" ref="B11:B89" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B90" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
       <c r="C11" s="54" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" s="51" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J11" s="51" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -2948,7 +2972,7 @@
         <v>20</v>
       </c>
       <c r="O11" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P11" s="52">
         <v>2.01E-2</v>
@@ -2959,9 +2983,16 @@
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
-    </row>
-    <row r="12" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
+      <c r="U11" s="70"/>
+      <c r="V11" s="70"/>
+      <c r="W11" s="70"/>
+      <c r="X11" s="70"/>
+      <c r="Y11" s="72"/>
+      <c r="Z11" s="72"/>
+      <c r="AA11" s="72"/>
+    </row>
+    <row r="12" spans="1:27" s="70" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A12" s="69"/>
       <c r="B12" s="46">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
@@ -2970,28 +3001,28 @@
         <v>9</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L12" s="37">
         <v>25</v>
@@ -3004,7 +3035,7 @@
         <v>150</v>
       </c>
       <c r="O12" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P12" s="38">
         <v>1.0500000000000001E-2</v>
@@ -3015,9 +3046,12 @@
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="59"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
+      <c r="Y12" s="72"/>
+      <c r="Z12" s="72"/>
+      <c r="AA12" s="72"/>
+    </row>
+    <row r="13" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="69"/>
       <c r="B13" s="47">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3026,28 +3060,28 @@
         <v>9</v>
       </c>
       <c r="D13" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="L13" s="51">
         <v>3</v>
@@ -3060,7 +3094,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P13" s="52">
         <v>8.9999999999999998E-4</v>
@@ -3071,9 +3105,12 @@
       </c>
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
-    </row>
-    <row r="14" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
+      <c r="Y13" s="72"/>
+      <c r="Z13" s="72"/>
+      <c r="AA13" s="72"/>
+    </row>
+    <row r="14" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A14" s="69"/>
       <c r="B14" s="46">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
@@ -3082,28 +3119,28 @@
         <v>9</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="L14" s="37">
         <v>3</v>
@@ -3116,7 +3153,7 @@
         <v>20</v>
       </c>
       <c r="O14" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P14" s="38">
         <v>4.9099999999999998E-2</v>
@@ -3127,9 +3164,12 @@
       </c>
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
+      <c r="Y14" s="72"/>
+      <c r="Z14" s="72"/>
+      <c r="AA14" s="72"/>
+    </row>
+    <row r="15" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="69"/>
       <c r="B15" s="47">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3138,28 +3178,28 @@
         <v>9</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="L15" s="51">
         <v>2</v>
@@ -3172,20 +3212,23 @@
         <v>11</v>
       </c>
       <c r="O15" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P15" s="52">
-        <v>0.27689999999999998</v>
+        <v>0.25940000000000002</v>
       </c>
       <c r="Q15" s="52">
         <f t="shared" ref="Q15" si="6">P15*N15</f>
-        <v>3.0458999999999996</v>
+        <v>2.8534000000000002</v>
       </c>
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
-    </row>
-    <row r="16" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
+      <c r="Y15" s="72"/>
+      <c r="Z15" s="72"/>
+      <c r="AA15" s="72"/>
+    </row>
+    <row r="16" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A16" s="69"/>
       <c r="B16" s="46">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
@@ -3194,28 +3237,28 @@
         <v>9</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="L16" s="37">
         <v>1</v>
@@ -3228,7 +3271,7 @@
         <v>15</v>
       </c>
       <c r="O16" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P16" s="38">
         <v>7.0900000000000005E-2</v>
@@ -3239,9 +3282,12 @@
       </c>
       <c r="R16" s="37"/>
       <c r="S16" s="59"/>
-    </row>
-    <row r="17" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
+      <c r="Y16" s="72"/>
+      <c r="Z16" s="72"/>
+      <c r="AA16" s="72"/>
+    </row>
+    <row r="17" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A17" s="69"/>
       <c r="B17" s="47">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3250,28 +3296,28 @@
         <v>9</v>
       </c>
       <c r="D17" s="51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="L17" s="51">
         <v>1</v>
@@ -3284,7 +3330,7 @@
         <v>10</v>
       </c>
       <c r="O17" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P17" s="52">
         <v>6.3E-2</v>
@@ -3295,9 +3341,12 @@
       </c>
       <c r="R17" s="51"/>
       <c r="S17" s="59"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
+      <c r="Y17" s="72"/>
+      <c r="Z17" s="72"/>
+      <c r="AA17" s="72"/>
+    </row>
+    <row r="18" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="69"/>
       <c r="B18" s="46">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
@@ -3306,28 +3355,28 @@
         <v>9</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="L18" s="37">
         <v>1</v>
@@ -3340,7 +3389,7 @@
         <v>6</v>
       </c>
       <c r="O18" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P18" s="38">
         <v>1.7373000000000001</v>
@@ -3351,9 +3400,12 @@
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
+      <c r="Y18" s="72"/>
+      <c r="Z18" s="72"/>
+      <c r="AA18" s="72"/>
+    </row>
+    <row r="19" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="69"/>
       <c r="B19" s="47">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3362,28 +3414,28 @@
         <v>9</v>
       </c>
       <c r="D19" s="51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="H19" s="51" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="I19" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J19" s="51" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="K19" s="51" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="L19" s="51">
         <v>1</v>
@@ -3396,7 +3448,7 @@
         <v>10</v>
       </c>
       <c r="O19" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P19" s="52">
         <v>0.26129999999999998</v>
@@ -3407,9 +3459,12 @@
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
+      <c r="Y19" s="72"/>
+      <c r="Z19" s="72"/>
+      <c r="AA19" s="72"/>
+    </row>
+    <row r="20" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="69"/>
       <c r="B20" s="46">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
@@ -3418,28 +3473,28 @@
         <v>9</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E20" s="37" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G20" s="62" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="L20" s="37">
         <v>4</v>
@@ -3452,7 +3507,7 @@
         <v>30</v>
       </c>
       <c r="O20" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P20" s="38">
         <v>4.2000000000000003E-2</v>
@@ -3463,9 +3518,12 @@
       </c>
       <c r="R20" s="37"/>
       <c r="S20" s="59"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
+      <c r="Y20" s="72"/>
+      <c r="Z20" s="72"/>
+      <c r="AA20" s="72"/>
+    </row>
+    <row r="21" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="69"/>
       <c r="B21" s="47">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -3474,28 +3532,28 @@
         <v>9</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="H21" s="51" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J21" s="51" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="L21" s="51">
         <v>2</v>
@@ -3508,7 +3566,7 @@
         <v>50</v>
       </c>
       <c r="O21" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P21" s="52">
         <v>1.0800000000000001E-2</v>
@@ -3519,9 +3577,12 @@
       </c>
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
+      <c r="Y21" s="72"/>
+      <c r="Z21" s="72"/>
+      <c r="AA21" s="72"/>
+    </row>
+    <row r="22" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="69"/>
       <c r="B22" s="46">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
@@ -3530,28 +3591,28 @@
         <v>9</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="L22" s="37">
         <v>2</v>
@@ -3564,7 +3625,7 @@
         <v>100</v>
       </c>
       <c r="O22" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P22" s="38">
         <v>1E-3</v>
@@ -3575,9 +3636,12 @@
       </c>
       <c r="R22" s="37"/>
       <c r="S22" s="59"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
+      <c r="Y22" s="72"/>
+      <c r="Z22" s="72"/>
+      <c r="AA22" s="72"/>
+    </row>
+    <row r="23" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="69"/>
       <c r="B23" s="47">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -3586,28 +3650,28 @@
         <v>9</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="H23" s="51" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I23" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="K23" s="51" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="L23" s="51">
         <v>3</v>
@@ -3620,7 +3684,7 @@
         <v>100</v>
       </c>
       <c r="O23" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P23" s="52">
         <v>3.8999999999999998E-3</v>
@@ -3631,9 +3695,12 @@
       </c>
       <c r="R23" s="51"/>
       <c r="S23" s="59"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
+      <c r="Y23" s="72"/>
+      <c r="Z23" s="72"/>
+      <c r="AA23" s="72"/>
+    </row>
+    <row r="24" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="69"/>
       <c r="B24" s="46">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
@@ -3642,28 +3709,28 @@
         <v>10</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J24" s="37" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="K24" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L24" s="37">
         <v>1</v>
@@ -3676,7 +3743,7 @@
         <v>10</v>
       </c>
       <c r="O24" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P24" s="38">
         <v>5.5599999999999997E-2</v>
@@ -3687,9 +3754,12 @@
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="59"/>
-    </row>
-    <row r="25" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
+      <c r="Y24" s="72"/>
+      <c r="Z24" s="72"/>
+      <c r="AA24" s="72"/>
+    </row>
+    <row r="25" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A25" s="69"/>
       <c r="B25" s="47">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -3698,28 +3768,28 @@
         <v>10</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H25" s="51" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I25" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J25" s="51" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="K25" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L25" s="51">
         <v>1</v>
@@ -3732,7 +3802,7 @@
         <v>10</v>
       </c>
       <c r="O25" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P25" s="52">
         <v>4.4600000000000001E-2</v>
@@ -3743,9 +3813,12 @@
       </c>
       <c r="R25" s="51"/>
       <c r="S25" s="59"/>
-    </row>
-    <row r="26" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
+      <c r="Y25" s="72"/>
+      <c r="Z25" s="72"/>
+      <c r="AA25" s="72"/>
+    </row>
+    <row r="26" spans="1:27" s="70" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A26" s="69"/>
       <c r="B26" s="46">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
@@ -3754,28 +3827,28 @@
         <v>10</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="K26" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L26" s="37">
         <v>1</v>
@@ -3788,7 +3861,7 @@
         <v>6</v>
       </c>
       <c r="O26" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P26" s="38">
         <v>0.46939999999999998</v>
@@ -3799,9 +3872,12 @@
       </c>
       <c r="R26" s="37"/>
       <c r="S26" s="59"/>
-    </row>
-    <row r="27" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
+      <c r="Y26" s="72"/>
+      <c r="Z26" s="72"/>
+      <c r="AA26" s="72"/>
+    </row>
+    <row r="27" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A27" s="69"/>
       <c r="B27" s="47">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -3810,28 +3886,28 @@
         <v>10</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J27" s="51" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="K27" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L27" s="51">
         <v>1</v>
@@ -3844,7 +3920,7 @@
         <v>10</v>
       </c>
       <c r="O27" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P27" s="52">
         <v>3.56E-2</v>
@@ -3855,9 +3931,12 @@
       </c>
       <c r="R27" s="51"/>
       <c r="S27" s="59"/>
-    </row>
-    <row r="28" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
+      <c r="Y27" s="72"/>
+      <c r="Z27" s="72"/>
+      <c r="AA27" s="72"/>
+    </row>
+    <row r="28" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A28" s="69"/>
       <c r="B28" s="46">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
@@ -3866,28 +3945,28 @@
         <v>10</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="K28" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L28" s="37">
         <v>3</v>
@@ -3900,7 +3979,7 @@
         <v>20</v>
       </c>
       <c r="O28" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P28" s="38">
         <v>2.46E-2</v>
@@ -3911,9 +3990,12 @@
       </c>
       <c r="R28" s="37"/>
       <c r="S28" s="59"/>
-    </row>
-    <row r="29" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
+      <c r="Y28" s="72"/>
+      <c r="Z28" s="72"/>
+      <c r="AA28" s="72"/>
+    </row>
+    <row r="29" spans="1:27" s="70" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A29" s="69"/>
       <c r="B29" s="47">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -3922,28 +4004,28 @@
         <v>10</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H29" s="51" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J29" s="51" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L29" s="51">
         <v>2</v>
@@ -3956,7 +4038,7 @@
         <v>20</v>
       </c>
       <c r="O29" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P29" s="52">
         <v>2.3400000000000001E-2</v>
@@ -3967,9 +4049,12 @@
       </c>
       <c r="R29" s="51"/>
       <c r="S29" s="59"/>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
+      <c r="Y29" s="72"/>
+      <c r="Z29" s="72"/>
+      <c r="AA29" s="72"/>
+    </row>
+    <row r="30" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="69"/>
       <c r="B30" s="46">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
@@ -3978,28 +4063,28 @@
         <v>10</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L30" s="37">
         <v>4</v>
@@ -4012,7 +4097,7 @@
         <v>25</v>
       </c>
       <c r="O30" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P30" s="38">
         <v>0.1351</v>
@@ -4023,9 +4108,12 @@
       </c>
       <c r="R30" s="37"/>
       <c r="S30" s="59"/>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
+      <c r="Y30" s="72"/>
+      <c r="Z30" s="72"/>
+      <c r="AA30" s="72"/>
+    </row>
+    <row r="31" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="69"/>
       <c r="B31" s="47">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -4034,28 +4122,28 @@
         <v>10</v>
       </c>
       <c r="D31" s="51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G31" s="51" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H31" s="51" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J31" s="51" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L31" s="51">
         <v>4</v>
@@ -4068,7 +4156,7 @@
         <v>30</v>
       </c>
       <c r="O31" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P31" s="52">
         <v>4.7500000000000001E-2</v>
@@ -4079,9 +4167,12 @@
       </c>
       <c r="R31" s="51"/>
       <c r="S31" s="59"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
+      <c r="Y31" s="72"/>
+      <c r="Z31" s="72"/>
+      <c r="AA31" s="72"/>
+    </row>
+    <row r="32" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="69"/>
       <c r="B32" s="46">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
@@ -4090,28 +4181,28 @@
         <v>11</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="I32" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J32" s="37" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="K32" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L32" s="37">
         <v>1</v>
@@ -4124,7 +4215,7 @@
         <v>10</v>
       </c>
       <c r="O32" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P32" s="38">
         <v>0.2286</v>
@@ -4135,9 +4226,12 @@
       </c>
       <c r="R32" s="37"/>
       <c r="S32" s="59"/>
-    </row>
-    <row r="33" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
+      <c r="Y32" s="72"/>
+      <c r="Z32" s="72"/>
+      <c r="AA32" s="72"/>
+    </row>
+    <row r="33" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A33" s="69"/>
       <c r="B33" s="47">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -4146,28 +4240,28 @@
         <v>11</v>
       </c>
       <c r="D33" s="51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E33" s="51" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F33" s="51" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G33" s="51" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H33" s="51" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="I33" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J33" s="51" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="K33" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L33" s="51">
         <v>1</v>
@@ -4180,7 +4274,7 @@
         <v>6</v>
       </c>
       <c r="O33" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P33" s="52">
         <v>1.1482000000000001</v>
@@ -4191,9 +4285,12 @@
       </c>
       <c r="R33" s="51"/>
       <c r="S33" s="59"/>
-    </row>
-    <row r="34" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
+      <c r="Y33" s="72"/>
+      <c r="Z33" s="72"/>
+      <c r="AA33" s="72"/>
+    </row>
+    <row r="34" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A34" s="69"/>
       <c r="B34" s="46">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
@@ -4202,28 +4299,28 @@
         <v>11</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E34" s="37" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J34" s="37" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="K34" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L34" s="37">
         <v>4</v>
@@ -4236,7 +4333,7 @@
         <v>30</v>
       </c>
       <c r="O34" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P34" s="38">
         <v>5.6099999999999997E-2</v>
@@ -4247,9 +4344,12 @@
       </c>
       <c r="R34" s="37"/>
       <c r="S34" s="59"/>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
+      <c r="Y34" s="72"/>
+      <c r="Z34" s="72"/>
+      <c r="AA34" s="72"/>
+    </row>
+    <row r="35" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="69"/>
       <c r="B35" s="47">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -4258,28 +4358,28 @@
         <v>12</v>
       </c>
       <c r="D35" s="51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F35" s="51" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G35" s="51" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="H35" s="51" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="I35" s="61" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="J35" s="51" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="K35" s="51" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="L35" s="51">
         <v>1</v>
@@ -4292,7 +4392,7 @@
         <v>10</v>
       </c>
       <c r="O35" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P35" s="52">
         <v>8.8300000000000003E-2</v>
@@ -4303,9 +4403,12 @@
       </c>
       <c r="R35" s="51"/>
       <c r="S35" s="59"/>
-    </row>
-    <row r="36" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
+      <c r="Y35" s="72"/>
+      <c r="Z35" s="72"/>
+      <c r="AA35" s="72"/>
+    </row>
+    <row r="36" spans="1:27" s="70" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A36" s="69"/>
       <c r="B36" s="46">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
@@ -4314,28 +4417,28 @@
         <v>13</v>
       </c>
       <c r="D36" s="37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E36" s="37" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F36" s="51" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="I36" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J36" s="37" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="K36" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L36" s="37">
         <v>8</v>
@@ -4348,7 +4451,7 @@
         <v>45</v>
       </c>
       <c r="O36" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P36" s="38">
         <v>0.2316</v>
@@ -4359,9 +4462,12 @@
       </c>
       <c r="R36" s="37"/>
       <c r="S36" s="59"/>
-    </row>
-    <row r="37" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
+      <c r="Y36" s="72"/>
+      <c r="Z36" s="72"/>
+      <c r="AA36" s="72"/>
+    </row>
+    <row r="37" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A37" s="69"/>
       <c r="B37" s="47">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -4370,28 +4476,28 @@
         <v>14</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F37" s="51" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G37" s="51" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H37" s="51" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I37" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J37" s="51" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="K37" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L37" s="51">
         <v>1</v>
@@ -4404,7 +4510,7 @@
         <v>10</v>
       </c>
       <c r="O37" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P37" s="52">
         <v>0.21590000000000001</v>
@@ -4415,9 +4521,12 @@
       </c>
       <c r="R37" s="51"/>
       <c r="S37" s="59"/>
-    </row>
-    <row r="38" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
+      <c r="Y37" s="72"/>
+      <c r="Z37" s="72"/>
+      <c r="AA37" s="72"/>
+    </row>
+    <row r="38" spans="1:27" s="70" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A38" s="69"/>
       <c r="B38" s="46">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
@@ -4426,28 +4535,28 @@
         <v>13</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F38" s="51" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="I38" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J38" s="37" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="K38" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L38" s="37">
         <v>4</v>
@@ -4460,7 +4569,7 @@
         <v>25</v>
       </c>
       <c r="O38" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P38" s="38">
         <v>0.17299999999999999</v>
@@ -4471,39 +4580,42 @@
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="59"/>
-    </row>
-    <row r="39" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
+      <c r="Y38" s="72"/>
+      <c r="Z38" s="72"/>
+      <c r="AA38" s="72"/>
+    </row>
+    <row r="39" spans="1:27" s="70" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A39" s="69"/>
       <c r="B39" s="47">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C39" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" s="51" t="s">
-        <v>57</v>
+        <v>493</v>
+      </c>
+      <c r="D39" s="68" t="s">
+        <v>56</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>459</v>
+        <v>494</v>
       </c>
       <c r="F39" s="51" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G39" s="51" t="s">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="H39" s="51" t="s">
-        <v>306</v>
+        <v>495</v>
       </c>
       <c r="I39" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J39" s="51" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="K39" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L39" s="51">
         <v>1</v>
@@ -4516,50 +4628,53 @@
         <v>10</v>
       </c>
       <c r="O39" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P39" s="52">
-        <v>0.3211</v>
+        <v>0.14860000000000001</v>
       </c>
       <c r="Q39" s="52">
         <f t="shared" ref="Q39" si="30">P39*N39</f>
-        <v>3.2109999999999999</v>
+        <v>1.4860000000000002</v>
       </c>
       <c r="R39" s="51"/>
       <c r="S39" s="59"/>
-    </row>
-    <row r="40" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
+      <c r="Y39" s="72"/>
+      <c r="Z39" s="72"/>
+      <c r="AA39" s="72"/>
+    </row>
+    <row r="40" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A40" s="69"/>
       <c r="B40" s="46">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
       <c r="C40" s="53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F40" s="51" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="I40" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J40" s="37" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="K40" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L40" s="37">
         <v>1</v>
@@ -4572,7 +4687,7 @@
         <v>12</v>
       </c>
       <c r="O40" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P40" s="38">
         <v>7.0400000000000004E-2</v>
@@ -4583,37 +4698,40 @@
       </c>
       <c r="R40" s="37"/>
       <c r="S40" s="59"/>
-    </row>
-    <row r="41" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
+      <c r="Y40" s="72"/>
+      <c r="Z40" s="72"/>
+      <c r="AA40" s="72"/>
+    </row>
+    <row r="41" spans="1:27" s="70" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A41" s="69"/>
       <c r="B41" s="47">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C41" s="54" t="s">
+        <v>430</v>
+      </c>
+      <c r="D41" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41" s="51" t="s">
+        <v>454</v>
+      </c>
+      <c r="F41" s="51" t="s">
         <v>435</v>
       </c>
-      <c r="D41" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="E41" s="51" t="s">
-        <v>461</v>
-      </c>
-      <c r="F41" s="51" t="s">
-        <v>440</v>
-      </c>
       <c r="G41" s="51" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="H41" s="51" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="I41" s="51"/>
       <c r="J41" s="51" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="K41" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L41" s="51">
         <v>1</v>
@@ -4626,7 +4744,7 @@
         <v>6</v>
       </c>
       <c r="O41" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P41" s="52">
         <v>0.91159999999999997</v>
@@ -4637,39 +4755,42 @@
       </c>
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
-    </row>
-    <row r="42" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
+      <c r="Y41" s="72"/>
+      <c r="Z41" s="72"/>
+      <c r="AA41" s="72"/>
+    </row>
+    <row r="42" spans="1:27" s="70" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A42" s="69"/>
       <c r="B42" s="46">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
       <c r="C42" s="53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D42" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E42" s="37" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F42" s="51" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H42" s="37" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J42" s="37" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="K42" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L42" s="37">
         <v>2</v>
@@ -4682,7 +4803,7 @@
         <v>11</v>
       </c>
       <c r="O42" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P42" s="38">
         <v>0.81459999999999999</v>
@@ -4693,39 +4814,42 @@
       </c>
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
-    </row>
-    <row r="43" spans="1:19" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
+      <c r="Y42" s="72"/>
+      <c r="Z42" s="72"/>
+      <c r="AA42" s="72"/>
+    </row>
+    <row r="43" spans="1:27" s="70" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="69"/>
       <c r="B43" s="47">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="C43" s="54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D43" s="51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="F43" s="51" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G43" s="51" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="H43" s="51" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="I43" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J43" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="K43" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L43" s="51">
         <v>3</v>
@@ -4738,7 +4862,7 @@
         <v>16</v>
       </c>
       <c r="O43" s="60" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="P43" s="52">
         <v>1.01</v>
@@ -4749,39 +4873,42 @@
       </c>
       <c r="R43" s="51"/>
       <c r="S43" s="59"/>
-    </row>
-    <row r="44" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
+      <c r="Y43" s="72"/>
+      <c r="Z43" s="72"/>
+      <c r="AA43" s="72"/>
+    </row>
+    <row r="44" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A44" s="69"/>
       <c r="B44" s="46">
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
       <c r="C44" s="53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D44" s="37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E44" s="37" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F44" s="51" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H44" s="37" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J44" s="37" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="K44" s="37" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="L44" s="37">
         <v>1</v>
@@ -4794,7 +4921,7 @@
         <v>10</v>
       </c>
       <c r="O44" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P44" s="38">
         <v>0.2137</v>
@@ -4805,39 +4932,42 @@
       </c>
       <c r="R44" s="37"/>
       <c r="S44" s="59"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
+      <c r="Y44" s="72"/>
+      <c r="Z44" s="72"/>
+      <c r="AA44" s="72"/>
+    </row>
+    <row r="45" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="69"/>
       <c r="B45" s="47">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="C45" s="53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D45" s="51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F45" s="51" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G45" s="51" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H45" s="51" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="I45" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J45" s="51" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="K45" s="51" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="L45" s="51">
         <v>1</v>
@@ -4850,7 +4980,7 @@
         <v>50</v>
       </c>
       <c r="O45" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P45" s="52">
         <v>8.3000000000000001E-3</v>
@@ -4861,39 +4991,42 @@
       </c>
       <c r="R45" s="51"/>
       <c r="S45" s="59"/>
-    </row>
-    <row r="46" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
+      <c r="Y45" s="72"/>
+      <c r="Z45" s="72"/>
+      <c r="AA45" s="72"/>
+    </row>
+    <row r="46" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A46" s="69"/>
       <c r="B46" s="46">
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
       <c r="C46" s="53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L46" s="37">
         <v>2</v>
@@ -4906,7 +5039,7 @@
         <v>20</v>
       </c>
       <c r="O46" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P46" s="38">
         <v>5.7599999999999998E-2</v>
@@ -4917,39 +5050,42 @@
       </c>
       <c r="R46" s="37"/>
       <c r="S46" s="59"/>
-    </row>
-    <row r="47" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
+      <c r="Y46" s="72"/>
+      <c r="Z46" s="72"/>
+      <c r="AA46" s="72"/>
+    </row>
+    <row r="47" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A47" s="69"/>
       <c r="B47" s="47">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="C47" s="54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D47" s="51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E47" s="51" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F47" s="51" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G47" s="51" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H47" s="51" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="I47" s="61" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="J47" s="51" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="K47" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L47" s="51">
         <v>1</v>
@@ -4962,7 +5098,7 @@
         <v>10</v>
       </c>
       <c r="O47" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P47" s="52">
         <v>5.1499999999999997E-2</v>
@@ -4973,94 +5109,100 @@
       </c>
       <c r="R47" s="51"/>
       <c r="S47" s="59"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
+      <c r="Y47" s="72"/>
+      <c r="Z47" s="72"/>
+      <c r="AA47" s="72"/>
+    </row>
+    <row r="48" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="69"/>
       <c r="B48" s="46">
         <f>ROW(B48) - ROW($B$9)</f>
         <v>39</v>
       </c>
       <c r="C48" s="53" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="D48" s="62" t="s">
-        <v>66</v>
+        <v>485</v>
       </c>
       <c r="E48" s="62" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F48" s="62" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G48" s="62" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H48" s="62" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="I48" s="62" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J48" s="62" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="K48" s="62" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L48" s="62">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M48" s="62">
         <f>L48*5</f>
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N48" s="62" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="O48" s="62" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="P48" s="62" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="Q48" s="62" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="R48" s="63" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="S48" s="59"/>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
+      <c r="Y48" s="71"/>
+      <c r="Z48" s="71"/>
+      <c r="AA48" s="71"/>
+    </row>
+    <row r="49" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="69"/>
       <c r="B49" s="47">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="C49" s="54" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="D49" s="51" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E49" s="51" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F49" s="51" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G49" s="51" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H49" s="51" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="I49" s="51"/>
       <c r="J49" s="51" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K49" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="L49" s="51">
         <v>1</v>
@@ -5073,7 +5215,7 @@
         <v>20</v>
       </c>
       <c r="O49" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P49" s="52">
         <v>2.1000000000000001E-2</v>
@@ -5084,39 +5226,42 @@
       </c>
       <c r="R49" s="51"/>
       <c r="S49" s="59"/>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
+      <c r="Y49"/>
+      <c r="Z49"/>
+      <c r="AA49"/>
+    </row>
+    <row r="50" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="69"/>
       <c r="B50" s="46">
         <f>ROW(B50) - ROW($B$9)</f>
         <v>41</v>
       </c>
       <c r="C50" s="53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D50" s="37" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E50" s="37" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G50" s="62" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H50" s="37" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="I50" s="37" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="J50" s="37" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="K50" s="37" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="L50" s="37">
         <v>2</v>
@@ -5129,7 +5274,7 @@
         <v>20</v>
       </c>
       <c r="O50" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P50" s="38">
         <v>2.1700000000000001E-2</v>
@@ -5140,37 +5285,42 @@
       </c>
       <c r="R50" s="37"/>
       <c r="S50" s="59"/>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
+      <c r="Y50"/>
+      <c r="Z50"/>
+      <c r="AA50"/>
+    </row>
+    <row r="51" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="69"/>
       <c r="B51" s="47">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="C51" s="54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D51" s="51" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E51" s="51" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F51" s="51" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G51" s="51" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H51" s="51" t="s">
-        <v>314</v>
-      </c>
-      <c r="I51" s="51"/>
+        <v>309</v>
+      </c>
+      <c r="I51" s="51" t="s">
+        <v>429</v>
+      </c>
       <c r="J51" s="51" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="K51" s="51" t="s">
-        <v>434</v>
+        <v>500</v>
       </c>
       <c r="L51" s="51">
         <v>1</v>
@@ -5183,48 +5333,54 @@
         <v>10</v>
       </c>
       <c r="O51" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P51" s="52">
-        <v>0.18260000000000001</v>
-      </c>
-      <c r="Q51" s="52">
-        <f t="shared" ref="Q51" si="42">P51*N51</f>
-        <v>1.8260000000000001</v>
-      </c>
-      <c r="R51" s="51"/>
+        <v>436</v>
+      </c>
+      <c r="P51" s="52" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q51" s="52" t="s">
+        <v>429</v>
+      </c>
+      <c r="R51" s="63" t="s">
+        <v>440</v>
+      </c>
       <c r="S51" s="59"/>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
+      <c r="Y51"/>
+      <c r="Z51"/>
+      <c r="AA51"/>
+    </row>
+    <row r="52" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="69"/>
       <c r="B52" s="46">
         <f>ROW(B52) - ROW($B$9)</f>
         <v>43</v>
       </c>
       <c r="C52" s="53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D52" s="37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E52" s="37" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F52" s="37" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G52" s="37" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="H52" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="I52" s="37"/>
+        <v>282</v>
+      </c>
+      <c r="I52" s="37" t="s">
+        <v>429</v>
+      </c>
       <c r="J52" s="37" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="K52" s="37" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="L52" s="37">
         <v>1</v>
@@ -5237,7 +5393,7 @@
         <v>100</v>
       </c>
       <c r="O52" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P52" s="38">
         <v>2.5999999999999999E-3</v>
@@ -5248,106 +5404,114 @@
       </c>
       <c r="R52" s="37"/>
       <c r="S52" s="59"/>
-    </row>
-    <row r="53" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A53" s="1"/>
+      <c r="Y52"/>
+      <c r="Z52"/>
+      <c r="AA52"/>
+    </row>
+    <row r="53" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A53" s="69"/>
       <c r="B53" s="47">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="C53" s="54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D53" s="51" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="E53" s="51" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F53" s="51" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G53" s="51" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H53" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="I53" s="51"/>
+        <v>282</v>
+      </c>
+      <c r="I53" s="37" t="s">
+        <v>429</v>
+      </c>
       <c r="J53" s="51" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="K53" s="51" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="L53" s="51">
         <v>12</v>
       </c>
       <c r="M53" s="51">
-        <f t="shared" ref="M53" si="43">L53*5</f>
+        <f t="shared" ref="M53" si="42">L53*5</f>
         <v>60</v>
       </c>
       <c r="N53" s="51">
         <v>100</v>
       </c>
       <c r="O53" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P53" s="52">
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="Q53" s="52">
-        <f t="shared" ref="Q53" si="44">P53*N53</f>
+        <f t="shared" ref="Q53" si="43">P53*N53</f>
         <v>0.09</v>
       </c>
       <c r="R53" s="51"/>
       <c r="S53" s="59"/>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A54" s="1"/>
+      <c r="Y53"/>
+      <c r="Z53"/>
+      <c r="AA53"/>
+    </row>
+    <row r="54" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A54" s="69"/>
       <c r="B54" s="46">
         <f>ROW(B54) - ROW($B$9)</f>
         <v>45</v>
       </c>
       <c r="C54" s="54" t="s">
-        <v>21</v>
-      </c>
-      <c r="D54" s="37" t="s">
-        <v>71</v>
+        <v>20</v>
+      </c>
+      <c r="D54" s="67" t="s">
+        <v>486</v>
       </c>
       <c r="E54" s="37" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F54" s="37" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G54" s="62" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H54" s="37" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I54" s="37" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="J54" s="37" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="K54" s="37" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="L54" s="37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M54" s="37">
         <f>L54*5</f>
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N54" s="37">
         <v>100</v>
       </c>
       <c r="O54" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P54" s="38">
         <v>8.9999999999999998E-4</v>
@@ -5358,95 +5522,101 @@
       </c>
       <c r="R54" s="37"/>
       <c r="S54" s="59"/>
-    </row>
-    <row r="55" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A55" s="1"/>
+      <c r="Y54"/>
+      <c r="Z54"/>
+      <c r="AA54"/>
+    </row>
+    <row r="55" spans="1:27" s="70" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A55" s="69"/>
       <c r="B55" s="47">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="C55" s="54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D55" s="51" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E55" s="51" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F55" s="51" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G55" s="51" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H55" s="51" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="I55" s="51" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J55" s="51" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="K55" s="51" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="L55" s="51">
         <v>1</v>
       </c>
       <c r="M55" s="51">
-        <f t="shared" ref="M55" si="45">L55*5</f>
+        <f t="shared" ref="M55" si="44">L55*5</f>
         <v>5</v>
       </c>
       <c r="N55" s="51">
         <v>100</v>
       </c>
       <c r="O55" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P55" s="52">
         <v>1E-3</v>
       </c>
       <c r="Q55" s="52">
-        <f t="shared" ref="Q55" si="46">P55*N55</f>
+        <f t="shared" ref="Q55" si="45">P55*N55</f>
         <v>0.1</v>
       </c>
       <c r="R55" s="51"/>
       <c r="S55" s="59"/>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A56" s="1"/>
+      <c r="Y55"/>
+      <c r="Z55"/>
+      <c r="AA55"/>
+    </row>
+    <row r="56" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="69"/>
       <c r="B56" s="46">
         <f>ROW(B56) - ROW($B$9)</f>
         <v>47</v>
       </c>
       <c r="C56" s="54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D56" s="37" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E56" s="37" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F56" s="37" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G56" s="37" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="H56" s="37" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I56" s="37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="J56" s="37" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="K56" s="37" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="L56" s="37">
         <v>2</v>
@@ -5459,7 +5629,7 @@
         <v>100</v>
       </c>
       <c r="O56" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P56" s="38">
         <v>8.0000000000000004E-4</v>
@@ -5470,93 +5640,101 @@
       </c>
       <c r="R56" s="37"/>
       <c r="S56" s="59"/>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A57" s="1"/>
+      <c r="Y56"/>
+      <c r="Z56"/>
+      <c r="AA56"/>
+    </row>
+    <row r="57" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="69"/>
       <c r="B57" s="47">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="C57" s="54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D57" s="51" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="E57" s="51" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F57" s="51" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G57" s="62" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H57" s="51" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I57" s="51" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="J57" s="51" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="K57" s="51" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="L57" s="51">
         <v>2</v>
       </c>
       <c r="M57" s="51">
-        <f t="shared" ref="M57" si="47">L57*5</f>
+        <f t="shared" ref="M57" si="46">L57*5</f>
         <v>10</v>
       </c>
       <c r="N57" s="51">
         <v>100</v>
       </c>
       <c r="O57" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P57" s="52">
         <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q57" s="52">
-        <f t="shared" ref="Q57" si="48">P57*N57</f>
+        <f t="shared" ref="Q57" si="47">P57*N57</f>
         <v>0.05</v>
       </c>
       <c r="R57" s="51"/>
       <c r="S57" s="59"/>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A58" s="1"/>
+      <c r="Y57"/>
+      <c r="Z57"/>
+      <c r="AA57"/>
+    </row>
+    <row r="58" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="69"/>
       <c r="B58" s="46">
         <f>ROW(B58) - ROW($B$9)</f>
         <v>49</v>
       </c>
       <c r="C58" s="53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D58" s="37" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="H58" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="I58" s="37"/>
+        <v>282</v>
+      </c>
+      <c r="I58" s="37" t="s">
+        <v>429</v>
+      </c>
       <c r="J58" s="37" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="K58" s="37" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="L58" s="37">
         <v>2</v>
@@ -5569,7 +5747,7 @@
         <v>100</v>
       </c>
       <c r="O58" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P58" s="38">
         <v>6.9999999999999999E-4</v>
@@ -5580,91 +5758,101 @@
       </c>
       <c r="R58" s="37"/>
       <c r="S58" s="59"/>
-    </row>
-    <row r="59" spans="1:19" ht="48" x14ac:dyDescent="0.25">
-      <c r="A59" s="1"/>
+      <c r="Y58"/>
+      <c r="Z58"/>
+      <c r="AA58"/>
+    </row>
+    <row r="59" spans="1:27" s="70" customFormat="1" ht="48" x14ac:dyDescent="0.25">
+      <c r="A59" s="69"/>
       <c r="B59" s="47">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="C59" s="54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D59" s="51" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E59" s="51" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F59" s="51" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G59" s="51" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H59" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="I59" s="51"/>
+        <v>282</v>
+      </c>
+      <c r="I59" s="51" t="s">
+        <v>429</v>
+      </c>
       <c r="J59" s="51" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="K59" s="51" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="L59" s="51">
         <v>22</v>
       </c>
       <c r="M59" s="51">
-        <f t="shared" ref="M59" si="49">L59*5</f>
+        <f t="shared" ref="M59" si="48">L59*5</f>
         <v>110</v>
       </c>
       <c r="N59" s="51">
         <v>200</v>
       </c>
       <c r="O59" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P59" s="52">
         <v>6.9999999999999999E-4</v>
       </c>
       <c r="Q59" s="52">
-        <f t="shared" ref="Q59" si="50">P59*N59</f>
+        <f t="shared" ref="Q59" si="49">P59*N59</f>
         <v>0.13999999999999999</v>
       </c>
       <c r="R59" s="51"/>
       <c r="S59" s="59"/>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A60" s="1"/>
+      <c r="Y59"/>
+      <c r="Z59"/>
+      <c r="AA59"/>
+    </row>
+    <row r="60" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="69"/>
       <c r="B60" s="46">
         <f>ROW(B60) - ROW($B$9)</f>
         <v>51</v>
       </c>
       <c r="C60" s="54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D60" s="37" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E60" s="37" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G60" s="37" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="H60" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="I60" s="37"/>
+        <v>282</v>
+      </c>
+      <c r="I60" s="37" t="s">
+        <v>429</v>
+      </c>
       <c r="J60" s="37" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="K60" s="37" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="L60" s="37">
         <v>1</v>
@@ -5677,7 +5865,7 @@
         <v>100</v>
       </c>
       <c r="O60" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P60" s="38">
         <v>5.9999999999999995E-4</v>
@@ -5688,37 +5876,42 @@
       </c>
       <c r="R60" s="37"/>
       <c r="S60" s="59"/>
-    </row>
-    <row r="61" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A61" s="1"/>
+      <c r="Y60"/>
+      <c r="Z60"/>
+      <c r="AA60"/>
+    </row>
+    <row r="61" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A61" s="69"/>
       <c r="B61" s="46">
         <f>ROW(B61) - ROW($B$9)</f>
         <v>52</v>
       </c>
       <c r="C61" s="53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D61" s="51" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="E61" s="37" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="H61" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="I61" s="37"/>
+        <v>282</v>
+      </c>
+      <c r="I61" s="37" t="s">
+        <v>429</v>
+      </c>
       <c r="J61" s="37" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="K61" s="37" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="L61" s="37">
         <v>11</v>
@@ -5731,7 +5924,7 @@
         <v>100</v>
       </c>
       <c r="O61" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P61" s="38">
         <v>6.9999999999999999E-4</v>
@@ -5742,1752 +5935,1921 @@
       </c>
       <c r="R61" s="37"/>
       <c r="S61" s="59"/>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Y61"/>
+      <c r="Z61"/>
+      <c r="AA61"/>
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="46">
         <f>ROW(B62) - ROW($B$9)</f>
         <v>53</v>
       </c>
-      <c r="C62" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="D62" s="37" t="s">
-        <v>77</v>
+      <c r="C62" s="54" t="s">
+        <v>477</v>
+      </c>
+      <c r="D62" s="67" t="s">
+        <v>487</v>
       </c>
       <c r="E62" s="37" t="s">
-        <v>150</v>
+        <v>497</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>203</v>
+        <v>498</v>
       </c>
       <c r="G62" s="37" t="s">
-        <v>259</v>
+        <v>492</v>
       </c>
       <c r="H62" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="I62" s="37"/>
+        <v>282</v>
+      </c>
+      <c r="I62" s="37" t="s">
+        <v>429</v>
+      </c>
       <c r="J62" s="37" t="s">
-        <v>365</v>
+        <v>499</v>
       </c>
       <c r="K62" s="37" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="L62" s="37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M62" s="37">
         <f>L62*5</f>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N62" s="37">
         <v>100</v>
       </c>
-      <c r="O62" s="60" t="s">
-        <v>441</v>
+      <c r="O62" s="73" t="s">
+        <v>436</v>
       </c>
       <c r="P62" s="38">
-        <v>6.9999999999999999E-4</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="Q62" s="38">
         <f>P62*N62</f>
-        <v>6.9999999999999993E-2</v>
+        <v>0.69</v>
       </c>
       <c r="R62" s="37"/>
       <c r="S62" s="59"/>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A63" s="1"/>
-      <c r="B63" s="47">
+      <c r="U62" s="70"/>
+      <c r="V62" s="70"/>
+      <c r="W62" s="70"/>
+      <c r="X62" s="70"/>
+    </row>
+    <row r="63" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="69"/>
+      <c r="B63" s="46">
+        <f>ROW(B63) - ROW($B$9)</f>
+        <v>54</v>
+      </c>
+      <c r="C63" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="E63" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="F63" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="G63" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="H63" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="I63" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="J63" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="K63" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="L63" s="37">
+        <v>4</v>
+      </c>
+      <c r="M63" s="37">
+        <f>L63*5</f>
+        <v>20</v>
+      </c>
+      <c r="N63" s="37">
+        <v>100</v>
+      </c>
+      <c r="O63" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P63" s="38">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q63" s="38">
+        <f>P63*N63</f>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="R63" s="37"/>
+      <c r="S63" s="59"/>
+      <c r="Y63"/>
+      <c r="Z63"/>
+      <c r="AA63"/>
+    </row>
+    <row r="64" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="69"/>
+      <c r="B64" s="47">
         <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="C63" s="54" t="s">
-        <v>21</v>
-      </c>
-      <c r="D63" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="E63" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="F63" s="51" t="s">
-        <v>206</v>
-      </c>
-      <c r="G63" s="51" t="s">
-        <v>260</v>
-      </c>
-      <c r="H63" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="I63" s="51"/>
-      <c r="J63" s="51" t="s">
-        <v>366</v>
-      </c>
-      <c r="K63" s="51" t="s">
-        <v>414</v>
-      </c>
-      <c r="L63" s="51">
+        <v>55</v>
+      </c>
+      <c r="C64" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="E64" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="F64" s="51" t="s">
+        <v>202</v>
+      </c>
+      <c r="G64" s="51" t="s">
+        <v>256</v>
+      </c>
+      <c r="H64" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="I64" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="J64" s="51" t="s">
+        <v>361</v>
+      </c>
+      <c r="K64" s="51" t="s">
+        <v>409</v>
+      </c>
+      <c r="L64" s="51">
         <v>1</v>
       </c>
-      <c r="M63" s="51">
-        <f t="shared" ref="M63" si="51">L63*5</f>
+      <c r="M64" s="51">
+        <f t="shared" ref="M64" si="50">L64*5</f>
         <v>5</v>
       </c>
-      <c r="N63" s="51">
+      <c r="N64" s="51">
         <v>100</v>
       </c>
-      <c r="O63" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P63" s="52">
+      <c r="O64" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P64" s="52">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q63" s="52">
-        <f t="shared" ref="Q63" si="52">P63*N63</f>
+      <c r="Q64" s="52">
+        <f t="shared" ref="Q64" si="51">P64*N64</f>
         <v>0.12</v>
       </c>
-      <c r="R63" s="51"/>
-      <c r="S63" s="59"/>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A64" s="1"/>
-      <c r="B64" s="46">
-        <f>ROW(B64) - ROW($B$9)</f>
-        <v>55</v>
-      </c>
-      <c r="C64" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="D64" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="E64" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="F64" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="G64" s="37" t="s">
-        <v>261</v>
-      </c>
-      <c r="H64" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="I64" s="37"/>
-      <c r="J64" s="37" t="s">
-        <v>367</v>
-      </c>
-      <c r="K64" s="37" t="s">
-        <v>415</v>
-      </c>
-      <c r="L64" s="37">
+      <c r="R64" s="51"/>
+      <c r="S64" s="59"/>
+      <c r="Y64"/>
+      <c r="Z64"/>
+      <c r="AA64"/>
+    </row>
+    <row r="65" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="69"/>
+      <c r="B65" s="46">
+        <f>ROW(B65) - ROW($B$9)</f>
+        <v>56</v>
+      </c>
+      <c r="C65" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="E65" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="F65" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="G65" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="H65" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="I65" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="J65" s="37" t="s">
+        <v>362</v>
+      </c>
+      <c r="K65" s="37" t="s">
+        <v>410</v>
+      </c>
+      <c r="L65" s="37">
         <v>1</v>
       </c>
-      <c r="M64" s="37">
-        <f>L64*5</f>
+      <c r="M65" s="37">
+        <f>L65*5</f>
         <v>5</v>
       </c>
-      <c r="N64" s="37">
+      <c r="N65" s="37">
         <v>100</v>
       </c>
-      <c r="O64" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P64" s="38">
+      <c r="O65" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P65" s="38">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="Q64" s="38">
-        <f>P64*N64</f>
+      <c r="Q65" s="38">
+        <f>P65*N65</f>
         <v>0.25</v>
       </c>
-      <c r="R64" s="37"/>
-      <c r="S64" s="59"/>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A65" s="1"/>
-      <c r="B65" s="47">
-        <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-      <c r="C65" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="D65" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="E65" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="F65" s="51" t="s">
-        <v>206</v>
-      </c>
-      <c r="G65" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="H65" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="I65" s="51"/>
-      <c r="J65" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="K65" s="51" t="s">
-        <v>416</v>
-      </c>
-      <c r="L65" s="51">
-        <v>1</v>
-      </c>
-      <c r="M65" s="51">
-        <f t="shared" ref="M65" si="53">L65*5</f>
-        <v>5</v>
-      </c>
-      <c r="N65" s="51">
-        <v>20</v>
-      </c>
-      <c r="O65" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P65" s="52">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="Q65" s="52">
-        <f t="shared" ref="Q65" si="54">P65*N65</f>
-        <v>0.52</v>
-      </c>
-      <c r="R65" s="51"/>
+      <c r="R65" s="37"/>
       <c r="S65" s="59"/>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A66" s="1"/>
+      <c r="Y65"/>
+      <c r="Z65"/>
+      <c r="AA65"/>
+    </row>
+    <row r="66" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="69"/>
       <c r="B66" s="47">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="C66" s="53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D66" s="51" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E66" s="51" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F66" s="51" t="s">
-        <v>203</v>
-      </c>
-      <c r="G66" s="62" t="s">
-        <v>264</v>
+        <v>202</v>
+      </c>
+      <c r="G66" s="51" t="s">
+        <v>258</v>
       </c>
       <c r="H66" s="51" t="s">
-        <v>316</v>
+        <v>282</v>
       </c>
       <c r="I66" s="51" t="s">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="J66" s="51" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="K66" s="51" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="L66" s="51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M66" s="51">
-        <f t="shared" ref="M66" si="55">L66*5</f>
+        <f t="shared" ref="M66" si="52">L66*5</f>
+        <v>5</v>
+      </c>
+      <c r="N66" s="51">
         <v>20</v>
       </c>
-      <c r="N66" s="51">
-        <v>100</v>
-      </c>
       <c r="O66" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P66" s="52">
-        <v>4.0000000000000002E-4</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="Q66" s="52">
-        <f t="shared" ref="Q66" si="56">P66*N66</f>
-        <v>0.04</v>
+        <f t="shared" ref="Q66" si="53">P66*N66</f>
+        <v>0.52</v>
       </c>
       <c r="R66" s="51"/>
       <c r="S66" s="59"/>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A67" s="1"/>
-      <c r="B67" s="46">
-        <f>ROW(B67) - ROW($B$9)</f>
+      <c r="Y66"/>
+      <c r="Z66"/>
+      <c r="AA66"/>
+    </row>
+    <row r="67" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="69"/>
+      <c r="B67" s="47">
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="C67" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="D67" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="E67" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="F67" s="37" t="s">
-        <v>206</v>
-      </c>
-      <c r="G67" s="37" t="s">
-        <v>265</v>
-      </c>
-      <c r="H67" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="I67" s="37"/>
-      <c r="J67" s="37" t="s">
-        <v>369</v>
-      </c>
-      <c r="K67" s="37" t="s">
-        <v>418</v>
-      </c>
-      <c r="L67" s="37">
+        <v>20</v>
+      </c>
+      <c r="D67" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="E67" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="F67" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="G67" s="62" t="s">
+        <v>260</v>
+      </c>
+      <c r="H67" s="51" t="s">
+        <v>311</v>
+      </c>
+      <c r="I67" s="51" t="s">
+        <v>451</v>
+      </c>
+      <c r="J67" s="51" t="s">
+        <v>452</v>
+      </c>
+      <c r="K67" s="51" t="s">
+        <v>412</v>
+      </c>
+      <c r="L67" s="51">
+        <v>4</v>
+      </c>
+      <c r="M67" s="51">
+        <f t="shared" ref="M67" si="54">L67*5</f>
+        <v>20</v>
+      </c>
+      <c r="N67" s="51">
+        <v>100</v>
+      </c>
+      <c r="O67" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P67" s="52">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="Q67" s="52">
+        <f t="shared" ref="Q67" si="55">P67*N67</f>
+        <v>0.04</v>
+      </c>
+      <c r="R67" s="51"/>
+      <c r="S67" s="59"/>
+      <c r="Y67"/>
+      <c r="Z67"/>
+      <c r="AA67"/>
+    </row>
+    <row r="68" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="69"/>
+      <c r="B68" s="46">
+        <f>ROW(B68) - ROW($B$9)</f>
+        <v>59</v>
+      </c>
+      <c r="C68" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="E68" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="F68" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="G68" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="H68" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="I68" s="37"/>
+      <c r="J68" s="37" t="s">
+        <v>364</v>
+      </c>
+      <c r="K68" s="37" t="s">
+        <v>413</v>
+      </c>
+      <c r="L68" s="37">
         <v>1</v>
       </c>
-      <c r="M67" s="37">
-        <f>L67*5</f>
+      <c r="M68" s="37">
+        <f>L68*5</f>
         <v>5</v>
       </c>
-      <c r="N67" s="37">
+      <c r="N68" s="37">
         <v>100</v>
       </c>
-      <c r="O67" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P67" s="38">
+      <c r="O68" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P68" s="38">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q67" s="38">
-        <f>P67*N67</f>
+      <c r="Q68" s="38">
+        <f>P68*N68</f>
         <v>0.12</v>
       </c>
-      <c r="R67" s="37"/>
-      <c r="S67" s="59"/>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A68" s="1"/>
-      <c r="B68" s="47">
+      <c r="R68" s="37"/>
+      <c r="S68" s="59"/>
+      <c r="Y68"/>
+      <c r="Z68"/>
+      <c r="AA68"/>
+    </row>
+    <row r="69" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="69"/>
+      <c r="B69" s="47">
         <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-      <c r="C68" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="D68" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="E68" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="F68" s="51" t="s">
-        <v>203</v>
-      </c>
-      <c r="G68" s="51" t="s">
-        <v>266</v>
-      </c>
-      <c r="H68" s="51" t="s">
-        <v>313</v>
-      </c>
-      <c r="I68" s="51"/>
-      <c r="J68" s="51" t="s">
-        <v>370</v>
-      </c>
-      <c r="K68" s="51" t="s">
-        <v>419</v>
-      </c>
-      <c r="L68" s="51">
+        <v>60</v>
+      </c>
+      <c r="C69" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D69" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="E69" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="F69" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="G69" s="51" t="s">
+        <v>262</v>
+      </c>
+      <c r="H69" s="51" t="s">
+        <v>308</v>
+      </c>
+      <c r="I69" s="51"/>
+      <c r="J69" s="51" t="s">
+        <v>365</v>
+      </c>
+      <c r="K69" s="51" t="s">
+        <v>414</v>
+      </c>
+      <c r="L69" s="51">
         <v>1</v>
       </c>
-      <c r="M68" s="51">
-        <f t="shared" ref="M68" si="57">L68*5</f>
+      <c r="M69" s="51">
+        <f t="shared" ref="M69" si="56">L69*5</f>
         <v>5</v>
       </c>
-      <c r="N68" s="51">
+      <c r="N69" s="51">
         <v>10</v>
       </c>
-      <c r="O68" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P68" s="52">
+      <c r="O69" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P69" s="52">
         <v>5.3600000000000002E-2</v>
       </c>
-      <c r="Q68" s="52">
-        <f t="shared" ref="Q68" si="58">P68*N68</f>
+      <c r="Q69" s="52">
+        <f t="shared" ref="Q69" si="57">P69*N69</f>
         <v>0.53600000000000003</v>
       </c>
-      <c r="R68" s="51"/>
-      <c r="S68" s="59"/>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A69" s="1"/>
-      <c r="B69" s="46">
-        <f>ROW(B69) - ROW($B$9)</f>
-        <v>60</v>
-      </c>
-      <c r="C69" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="D69" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="E69" s="37" t="s">
-        <v>158</v>
-      </c>
-      <c r="F69" s="37" t="s">
-        <v>206</v>
-      </c>
-      <c r="G69" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="H69" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="I69" s="37"/>
-      <c r="J69" s="37" t="s">
-        <v>371</v>
-      </c>
-      <c r="K69" s="37" t="s">
-        <v>420</v>
-      </c>
-      <c r="L69" s="37">
+      <c r="R69" s="51"/>
+      <c r="S69" s="59"/>
+      <c r="Y69"/>
+      <c r="Z69"/>
+      <c r="AA69"/>
+    </row>
+    <row r="70" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="69"/>
+      <c r="B70" s="46">
+        <f>ROW(B70) - ROW($B$9)</f>
+        <v>61</v>
+      </c>
+      <c r="C70" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D70" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="E70" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="F70" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="G70" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="H70" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="I70" s="37"/>
+      <c r="J70" s="37" t="s">
+        <v>366</v>
+      </c>
+      <c r="K70" s="37" t="s">
+        <v>415</v>
+      </c>
+      <c r="L70" s="37">
         <v>2</v>
       </c>
-      <c r="M69" s="37">
-        <f>L69*5</f>
+      <c r="M70" s="37">
+        <f>L70*5</f>
         <v>10</v>
       </c>
-      <c r="N69" s="37">
+      <c r="N70" s="37">
         <v>100</v>
       </c>
-      <c r="O69" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P69" s="38">
+      <c r="O70" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P70" s="38">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q69" s="38">
-        <f>P69*N69</f>
+      <c r="Q70" s="38">
+        <f>P70*N70</f>
         <v>0.12</v>
       </c>
-      <c r="R69" s="37"/>
-      <c r="S69" s="59"/>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A70" s="1"/>
-      <c r="B70" s="47">
-        <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-      <c r="C70" s="54" t="s">
-        <v>21</v>
-      </c>
-      <c r="D70" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="E70" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="F70" s="51" t="s">
-        <v>203</v>
-      </c>
-      <c r="G70" s="51" t="s">
-        <v>268</v>
-      </c>
-      <c r="H70" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="I70" s="51"/>
-      <c r="J70" s="51" t="s">
-        <v>372</v>
-      </c>
-      <c r="K70" s="51" t="s">
-        <v>421</v>
-      </c>
-      <c r="L70" s="51">
-        <v>1</v>
-      </c>
-      <c r="M70" s="51">
-        <f t="shared" ref="M70:M71" si="59">L70*5</f>
-        <v>5</v>
-      </c>
-      <c r="N70" s="51">
-        <v>100</v>
-      </c>
-      <c r="O70" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P70" s="52">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="Q70" s="52">
-        <f t="shared" ref="Q70:Q71" si="60">P70*N70</f>
-        <v>6.9999999999999993E-2</v>
-      </c>
-      <c r="R70" s="51"/>
+      <c r="R70" s="37"/>
       <c r="S70" s="59"/>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A71" s="1"/>
+      <c r="Y70"/>
+      <c r="Z70"/>
+      <c r="AA70"/>
+    </row>
+    <row r="71" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="69"/>
       <c r="B71" s="47">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="C71" s="54" t="s">
-        <v>486</v>
+        <v>20</v>
       </c>
       <c r="D71" s="51" t="s">
-        <v>487</v>
+        <v>82</v>
       </c>
       <c r="E71" s="51" t="s">
-        <v>488</v>
+        <v>155</v>
       </c>
       <c r="F71" s="51" t="s">
-        <v>440</v>
+        <v>199</v>
       </c>
       <c r="G71" s="51" t="s">
-        <v>489</v>
+        <v>264</v>
       </c>
       <c r="H71" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="I71" s="51" t="s">
-        <v>434</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="I71" s="51"/>
       <c r="J71" s="51" t="s">
-        <v>490</v>
+        <v>367</v>
       </c>
       <c r="K71" s="51" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="L71" s="51">
+        <v>1</v>
+      </c>
+      <c r="M71" s="51">
+        <f t="shared" ref="M71:M72" si="58">L71*5</f>
         <v>5</v>
       </c>
-      <c r="M71" s="51">
-        <f t="shared" si="59"/>
-        <v>25</v>
-      </c>
       <c r="N71" s="51">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O71" s="60" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P71" s="52">
-        <v>8.6999999999999994E-3</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="Q71" s="52">
-        <f t="shared" si="60"/>
-        <v>0.43499999999999994</v>
+        <f t="shared" ref="Q71:Q72" si="59">P71*N71</f>
+        <v>6.9999999999999993E-2</v>
       </c>
       <c r="R71" s="51"/>
       <c r="S71" s="59"/>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A72" s="1"/>
-      <c r="B72" s="46">
-        <f>ROW(B72) - ROW($B$9)</f>
+      <c r="Y71"/>
+      <c r="Z71"/>
+      <c r="AA71"/>
+    </row>
+    <row r="72" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="69"/>
+      <c r="B72" s="47">
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="C72" s="53" t="s">
+      <c r="C72" s="54" t="s">
+        <v>477</v>
+      </c>
+      <c r="D72" s="67" t="s">
+        <v>488</v>
+      </c>
+      <c r="E72" s="51" t="s">
+        <v>478</v>
+      </c>
+      <c r="F72" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="G72" s="51" t="s">
+        <v>479</v>
+      </c>
+      <c r="H72" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="I72" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="J72" s="51" t="s">
+        <v>480</v>
+      </c>
+      <c r="K72" s="51" t="s">
+        <v>399</v>
+      </c>
+      <c r="L72" s="51">
+        <v>2</v>
+      </c>
+      <c r="M72" s="51">
+        <f t="shared" si="58"/>
+        <v>10</v>
+      </c>
+      <c r="N72" s="51">
+        <v>50</v>
+      </c>
+      <c r="O72" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P72" s="52">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="Q72" s="52">
+        <f t="shared" si="59"/>
+        <v>0.43499999999999994</v>
+      </c>
+      <c r="R72" s="51"/>
+      <c r="S72" s="59"/>
+      <c r="Y72"/>
+      <c r="Z72"/>
+      <c r="AA72"/>
+    </row>
+    <row r="73" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="69"/>
+      <c r="B73" s="46">
+        <f>ROW(B73) - ROW($B$9)</f>
+        <v>64</v>
+      </c>
+      <c r="C73" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="D73" s="64" t="s">
+        <v>489</v>
+      </c>
+      <c r="E73" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="F73" s="65" t="s">
+        <v>435</v>
+      </c>
+      <c r="G73" s="64" t="s">
+        <v>203</v>
+      </c>
+      <c r="H73" s="64" t="s">
+        <v>429</v>
+      </c>
+      <c r="I73" s="64" t="s">
+        <v>429</v>
+      </c>
+      <c r="J73" s="64" t="s">
+        <v>429</v>
+      </c>
+      <c r="K73" s="64" t="s">
+        <v>429</v>
+      </c>
+      <c r="L73" s="64">
+        <v>3</v>
+      </c>
+      <c r="M73" s="64">
+        <f>L73*5</f>
+        <v>15</v>
+      </c>
+      <c r="N73" s="64" t="s">
+        <v>429</v>
+      </c>
+      <c r="O73" s="64" t="s">
+        <v>429</v>
+      </c>
+      <c r="P73" s="64" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q73" s="64" t="s">
+        <v>429</v>
+      </c>
+      <c r="R73" s="63" t="s">
+        <v>440</v>
+      </c>
+      <c r="S73" s="59"/>
+      <c r="Y73"/>
+      <c r="Z73"/>
+      <c r="AA73"/>
+    </row>
+    <row r="74" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A74" s="69"/>
+      <c r="B74" s="47">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="C74" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="D72" s="64" t="s">
+      <c r="D74" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="E74" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="F74" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="G74" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="H74" s="51" t="s">
+        <v>312</v>
+      </c>
+      <c r="I74" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="J74" s="51" t="s">
+        <v>439</v>
+      </c>
+      <c r="K74" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="L74" s="51">
+        <v>1</v>
+      </c>
+      <c r="M74" s="51">
+        <f t="shared" ref="M74" si="60">L74*5</f>
+        <v>5</v>
+      </c>
+      <c r="N74" s="51">
+        <v>10</v>
+      </c>
+      <c r="O74" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P74" s="52">
+        <v>0.1275</v>
+      </c>
+      <c r="Q74" s="52">
+        <f t="shared" ref="Q74" si="61">P74*N74</f>
+        <v>1.2749999999999999</v>
+      </c>
+      <c r="R74" s="51"/>
+      <c r="S74" s="59"/>
+      <c r="Y74"/>
+      <c r="Z74"/>
+      <c r="AA74"/>
+    </row>
+    <row r="75" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="69"/>
+      <c r="B75" s="46">
+        <f>ROW(B75) - ROW($B$9)</f>
+        <v>66</v>
+      </c>
+      <c r="C75" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D75" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="E75" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="F75" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="G75" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="H75" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="I75" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="J75" s="37" t="s">
+        <v>368</v>
+      </c>
+      <c r="K75" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="L75" s="37">
+        <v>1</v>
+      </c>
+      <c r="M75" s="37">
+        <f>L75*5</f>
+        <v>5</v>
+      </c>
+      <c r="N75" s="37">
+        <v>6</v>
+      </c>
+      <c r="O75" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P75" s="38">
+        <v>0.82569999999999999</v>
+      </c>
+      <c r="Q75" s="38">
+        <f>P75*N75</f>
+        <v>4.9542000000000002</v>
+      </c>
+      <c r="R75" s="37"/>
+      <c r="S75" s="59"/>
+      <c r="Y75"/>
+      <c r="Z75"/>
+      <c r="AA75"/>
+    </row>
+    <row r="76" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="69"/>
+      <c r="B76" s="47">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="C76" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D76" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="E76" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="F76" s="51" t="s">
+        <v>206</v>
+      </c>
+      <c r="G76" s="51" t="s">
+        <v>266</v>
+      </c>
+      <c r="H76" s="51" t="s">
+        <v>313</v>
+      </c>
+      <c r="I76" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="J76" s="51" t="s">
+        <v>369</v>
+      </c>
+      <c r="K76" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="L76" s="51">
+        <v>1</v>
+      </c>
+      <c r="M76" s="51">
+        <f t="shared" ref="M76" si="62">L76*5</f>
+        <v>5</v>
+      </c>
+      <c r="N76" s="51">
+        <v>6</v>
+      </c>
+      <c r="O76" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P76" s="52">
+        <v>0.70009999999999994</v>
+      </c>
+      <c r="Q76" s="52">
+        <f t="shared" ref="Q76" si="63">P76*N76</f>
+        <v>4.2005999999999997</v>
+      </c>
+      <c r="R76" s="51"/>
+      <c r="S76" s="59"/>
+      <c r="Y76"/>
+      <c r="Z76"/>
+      <c r="AA76"/>
+    </row>
+    <row r="77" spans="1:27" s="70" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+      <c r="A77" s="69"/>
+      <c r="B77" s="46">
+        <f>ROW(B77) - ROW($B$9)</f>
+        <v>68</v>
+      </c>
+      <c r="C77" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D77" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="E72" s="64" t="s">
+      <c r="E77" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="F72" s="65" t="s">
-        <v>440</v>
-      </c>
-      <c r="G72" s="64" t="s">
+      <c r="F77" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="H72" s="64" t="s">
-        <v>434</v>
-      </c>
-      <c r="I72" s="64" t="s">
-        <v>434</v>
-      </c>
-      <c r="J72" s="64" t="s">
-        <v>434</v>
-      </c>
-      <c r="K72" s="64" t="s">
-        <v>434</v>
-      </c>
-      <c r="L72" s="64">
-        <v>2</v>
-      </c>
-      <c r="M72" s="64">
-        <f>L72*5</f>
+      <c r="G77" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="H77" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="I77" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="J77" s="37" t="s">
+        <v>370</v>
+      </c>
+      <c r="K77" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="L77" s="37">
+        <v>1</v>
+      </c>
+      <c r="M77" s="37">
+        <f>L77*5</f>
+        <v>5</v>
+      </c>
+      <c r="N77" s="37">
         <v>10</v>
       </c>
-      <c r="N72" s="64" t="s">
-        <v>434</v>
-      </c>
-      <c r="O72" s="64" t="s">
-        <v>434</v>
-      </c>
-      <c r="P72" s="64" t="s">
-        <v>434</v>
-      </c>
-      <c r="Q72" s="64" t="s">
-        <v>434</v>
-      </c>
-      <c r="R72" s="63" t="s">
-        <v>445</v>
-      </c>
-      <c r="S72" s="59"/>
-    </row>
-    <row r="73" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A73" s="1"/>
-      <c r="B73" s="47">
+      <c r="O77" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P77" s="38">
+        <v>0.32279999999999998</v>
+      </c>
+      <c r="Q77" s="38">
+        <f>P77*N77</f>
+        <v>3.2279999999999998</v>
+      </c>
+      <c r="R77" s="37"/>
+      <c r="S77" s="59"/>
+      <c r="Y77"/>
+      <c r="Z77"/>
+      <c r="AA77"/>
+    </row>
+    <row r="78" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="69"/>
+      <c r="B78" s="47">
         <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="C73" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="C78" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="D73" s="51" t="s">
+      <c r="D78" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="E73" s="51" t="s">
+      <c r="E78" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="F73" s="51" t="s">
-        <v>440</v>
-      </c>
-      <c r="G73" s="51" t="s">
+      <c r="F78" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="H73" s="51" t="s">
+      <c r="G78" s="51" t="s">
+        <v>268</v>
+      </c>
+      <c r="H78" s="51" t="s">
+        <v>315</v>
+      </c>
+      <c r="I78" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="J78" s="51" t="s">
+        <v>371</v>
+      </c>
+      <c r="K78" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="L78" s="51">
+        <v>1</v>
+      </c>
+      <c r="M78" s="51">
+        <f t="shared" ref="M78" si="64">L78*5</f>
+        <v>5</v>
+      </c>
+      <c r="N78" s="51">
+        <v>6</v>
+      </c>
+      <c r="O78" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P78" s="52">
+        <v>1.3062</v>
+      </c>
+      <c r="Q78" s="52">
+        <f t="shared" ref="Q78" si="65">P78*N78</f>
+        <v>7.8372000000000002</v>
+      </c>
+      <c r="R78" s="51"/>
+      <c r="S78" s="59"/>
+      <c r="Y78"/>
+      <c r="Z78"/>
+      <c r="AA78"/>
+    </row>
+    <row r="79" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="69"/>
+      <c r="B79" s="46">
+        <f>ROW(B79) - ROW($B$9)</f>
+        <v>70</v>
+      </c>
+      <c r="C79" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D79" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E79" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="F79" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="G79" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="H79" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="I79" s="37"/>
+      <c r="J79" s="37" t="s">
+        <v>372</v>
+      </c>
+      <c r="K79" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="L79" s="37">
+        <v>1</v>
+      </c>
+      <c r="M79" s="37">
+        <f>L79*5</f>
+        <v>5</v>
+      </c>
+      <c r="N79" s="37">
+        <v>6</v>
+      </c>
+      <c r="O79" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P79" s="38">
+        <v>0.3644</v>
+      </c>
+      <c r="Q79" s="38">
+        <f>P79*N79</f>
+        <v>2.1863999999999999</v>
+      </c>
+      <c r="R79" s="37"/>
+      <c r="S79" s="59"/>
+      <c r="Y79"/>
+      <c r="Z79"/>
+      <c r="AA79"/>
+    </row>
+    <row r="80" spans="1:27" s="70" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A80" s="69"/>
+      <c r="B80" s="47">
+        <f t="shared" si="0"/>
+        <v>71</v>
+      </c>
+      <c r="C80" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D80" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="E80" s="51" t="s">
+        <v>163</v>
+      </c>
+      <c r="F80" s="51" t="s">
+        <v>210</v>
+      </c>
+      <c r="G80" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="H80" s="51" t="s">
         <v>317</v>
       </c>
-      <c r="I73" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="J73" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="K73" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="L73" s="51">
+      <c r="I80" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="J80" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="K80" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="L80" s="51">
         <v>1</v>
       </c>
-      <c r="M73" s="51">
-        <f t="shared" ref="M73" si="61">L73*5</f>
+      <c r="M80" s="51">
+        <f t="shared" ref="M80" si="66">L80*5</f>
         <v>5</v>
       </c>
-      <c r="N73" s="51">
+      <c r="N80" s="51">
+        <v>6</v>
+      </c>
+      <c r="O80" s="60" t="s">
+        <v>453</v>
+      </c>
+      <c r="P80" s="52">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="Q80" s="52">
+        <f t="shared" ref="Q80" si="67">P80*N80</f>
+        <v>15.059999999999999</v>
+      </c>
+      <c r="R80" s="51"/>
+      <c r="S80" s="59"/>
+      <c r="Y80"/>
+      <c r="Z80"/>
+      <c r="AA80"/>
+    </row>
+    <row r="81" spans="1:27" s="70" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A81" s="69"/>
+      <c r="B81" s="46">
+        <f>ROW(B81) - ROW($B$9)</f>
+        <v>72</v>
+      </c>
+      <c r="C81" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D81" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E81" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="F81" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="G81" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="H81" s="37" t="s">
+        <v>315</v>
+      </c>
+      <c r="I81" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="J81" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="K81" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="L81" s="37">
+        <v>1</v>
+      </c>
+      <c r="M81" s="37">
+        <f>L81*5</f>
+        <v>5</v>
+      </c>
+      <c r="N81" s="37">
+        <v>6</v>
+      </c>
+      <c r="O81" s="60" t="s">
+        <v>453</v>
+      </c>
+      <c r="P81" s="38">
+        <v>3.4329999999999998</v>
+      </c>
+      <c r="Q81" s="38">
+        <f>P81*N81</f>
+        <v>20.597999999999999</v>
+      </c>
+      <c r="R81" s="37"/>
+      <c r="S81" s="59"/>
+      <c r="Y81"/>
+      <c r="Z81"/>
+      <c r="AA81"/>
+    </row>
+    <row r="82" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="69"/>
+      <c r="B82" s="47">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+      <c r="C82" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D82" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="E82" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="F82" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="G82" s="51" t="s">
+        <v>272</v>
+      </c>
+      <c r="H82" s="51" t="s">
+        <v>318</v>
+      </c>
+      <c r="I82" s="51"/>
+      <c r="J82" s="51" t="s">
+        <v>373</v>
+      </c>
+      <c r="K82" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="L82" s="51">
+        <v>1</v>
+      </c>
+      <c r="M82" s="51">
+        <f t="shared" ref="M82" si="68">L82*5</f>
+        <v>5</v>
+      </c>
+      <c r="N82" s="51">
+        <v>6</v>
+      </c>
+      <c r="O82" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P82" s="52">
+        <v>4.6247999999999996</v>
+      </c>
+      <c r="Q82" s="52">
+        <f t="shared" ref="Q82" si="69">P82*N82</f>
+        <v>27.748799999999996</v>
+      </c>
+      <c r="R82" s="51"/>
+      <c r="S82" s="59"/>
+      <c r="Y82"/>
+      <c r="Z82"/>
+      <c r="AA82"/>
+    </row>
+    <row r="83" spans="1:27" s="70" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A83" s="69"/>
+      <c r="B83" s="46">
+        <f>ROW(B83) - ROW($B$9)</f>
+        <v>74</v>
+      </c>
+      <c r="C83" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D83" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E83" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="F83" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="G83" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="H83" s="37" t="s">
+        <v>319</v>
+      </c>
+      <c r="I83" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="J83" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="K83" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="L83" s="37">
+        <v>1</v>
+      </c>
+      <c r="M83" s="37">
+        <f>L83*5</f>
+        <v>5</v>
+      </c>
+      <c r="N83" s="37">
+        <v>6</v>
+      </c>
+      <c r="O83" s="60" t="s">
+        <v>453</v>
+      </c>
+      <c r="P83" s="38">
+        <v>7.9</v>
+      </c>
+      <c r="Q83" s="38">
+        <f>P83*N83</f>
+        <v>47.400000000000006</v>
+      </c>
+      <c r="R83" s="63"/>
+      <c r="S83" s="59"/>
+      <c r="Y83"/>
+      <c r="Z83"/>
+      <c r="AA83"/>
+    </row>
+    <row r="84" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="69"/>
+      <c r="B84" s="47">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="C84" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D84" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="E84" s="51" t="s">
+        <v>167</v>
+      </c>
+      <c r="F84" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="G84" s="51" t="s">
+        <v>274</v>
+      </c>
+      <c r="H84" s="51" t="s">
+        <v>315</v>
+      </c>
+      <c r="I84" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="J84" s="51" t="s">
+        <v>374</v>
+      </c>
+      <c r="K84" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="L84" s="51">
+        <v>3</v>
+      </c>
+      <c r="M84" s="51">
+        <f t="shared" ref="M84" si="70">L84*5</f>
+        <v>15</v>
+      </c>
+      <c r="N84" s="51">
+        <v>16</v>
+      </c>
+      <c r="O84" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P84" s="52">
+        <v>1.7437</v>
+      </c>
+      <c r="Q84" s="52">
+        <f t="shared" ref="Q84" si="71">P84*N84</f>
+        <v>27.8992</v>
+      </c>
+      <c r="R84" s="51"/>
+      <c r="S84" s="59"/>
+      <c r="Y84"/>
+      <c r="Z84"/>
+      <c r="AA84"/>
+    </row>
+    <row r="85" spans="1:27" s="70" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A85" s="69"/>
+      <c r="B85" s="46">
+        <f>ROW(B85) - ROW($B$9)</f>
+        <v>76</v>
+      </c>
+      <c r="C85" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D85" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="E85" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="F85" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="G85" s="37" t="s">
+        <v>275</v>
+      </c>
+      <c r="H85" s="37" t="s">
+        <v>320</v>
+      </c>
+      <c r="I85" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="J85" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="K85" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="L85" s="37">
+        <v>1</v>
+      </c>
+      <c r="M85" s="37">
+        <f>L85*5</f>
+        <v>5</v>
+      </c>
+      <c r="N85" s="37">
         <v>10</v>
       </c>
-      <c r="O73" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P73" s="52">
-        <v>0.1275</v>
-      </c>
-      <c r="Q73" s="52">
-        <f t="shared" ref="Q73" si="62">P73*N73</f>
-        <v>1.2749999999999999</v>
-      </c>
-      <c r="R73" s="51"/>
-      <c r="S73" s="59"/>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A74" s="1"/>
-      <c r="B74" s="46">
-        <f>ROW(B74) - ROW($B$9)</f>
-        <v>65</v>
-      </c>
-      <c r="C74" s="53" t="s">
+      <c r="O85" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P85" s="38">
+        <v>7.7799999999999994E-2</v>
+      </c>
+      <c r="Q85" s="38">
+        <f>P85*N85</f>
+        <v>0.77799999999999991</v>
+      </c>
+      <c r="R85" s="37"/>
+      <c r="S85" s="59"/>
+      <c r="Y85"/>
+      <c r="Z85"/>
+      <c r="AA85"/>
+    </row>
+    <row r="86" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="69"/>
+      <c r="B86" s="47">
+        <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="C86" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D86" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="E86" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="F86" s="51" t="s">
+        <v>216</v>
+      </c>
+      <c r="G86" s="51" t="s">
+        <v>276</v>
+      </c>
+      <c r="H86" s="51" t="s">
+        <v>313</v>
+      </c>
+      <c r="I86" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="J86" s="51" t="s">
+        <v>376</v>
+      </c>
+      <c r="K86" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="L86" s="51">
+        <v>1</v>
+      </c>
+      <c r="M86" s="51">
+        <f t="shared" ref="M86" si="72">L86*5</f>
+        <v>5</v>
+      </c>
+      <c r="N86" s="51">
+        <v>6</v>
+      </c>
+      <c r="O86" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P86" s="52">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="Q86" s="52">
+        <f t="shared" ref="Q86" si="73">P86*N86</f>
+        <v>4.6680000000000001</v>
+      </c>
+      <c r="R86" s="51"/>
+      <c r="S86" s="59"/>
+      <c r="Y86"/>
+      <c r="Z86"/>
+      <c r="AA86"/>
+    </row>
+    <row r="87" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="69"/>
+      <c r="B87" s="46">
+        <f>ROW(B87) - ROW($B$9)</f>
+        <v>78</v>
+      </c>
+      <c r="C87" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D87" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E87" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="F87" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="G87" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="H87" s="37" t="s">
+        <v>314</v>
+      </c>
+      <c r="I87" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="J87" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="K87" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="L87" s="37">
+        <v>1</v>
+      </c>
+      <c r="M87" s="37">
+        <f>L87*5</f>
+        <v>5</v>
+      </c>
+      <c r="N87" s="37">
+        <v>6</v>
+      </c>
+      <c r="O87" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P87" s="38">
+        <v>0.41049999999999998</v>
+      </c>
+      <c r="Q87" s="38">
+        <f>P87*N87</f>
+        <v>2.4630000000000001</v>
+      </c>
+      <c r="R87" s="37"/>
+      <c r="S87" s="59"/>
+      <c r="Y87"/>
+      <c r="Z87"/>
+      <c r="AA87"/>
+    </row>
+    <row r="88" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="69"/>
+      <c r="B88" s="47">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+      <c r="C88" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D88" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="E88" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="F88" s="51" t="s">
+        <v>211</v>
+      </c>
+      <c r="G88" s="51" t="s">
+        <v>278</v>
+      </c>
+      <c r="H88" s="51" t="s">
+        <v>319</v>
+      </c>
+      <c r="I88" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="J88" s="51" t="s">
+        <v>378</v>
+      </c>
+      <c r="K88" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="L88" s="51">
+        <v>1</v>
+      </c>
+      <c r="M88" s="51">
+        <f t="shared" ref="M88" si="74">L88*5</f>
+        <v>5</v>
+      </c>
+      <c r="N88" s="51">
+        <v>6</v>
+      </c>
+      <c r="O88" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P88" s="52">
+        <v>1.1837</v>
+      </c>
+      <c r="Q88" s="52">
+        <f t="shared" ref="Q88" si="75">P88*N88</f>
+        <v>7.1021999999999998</v>
+      </c>
+      <c r="R88" s="51"/>
+      <c r="S88" s="59"/>
+      <c r="Y88"/>
+      <c r="Z88"/>
+      <c r="AA88"/>
+    </row>
+    <row r="89" spans="1:27" s="70" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="69"/>
+      <c r="B89" s="46">
+        <f>ROW(B89) - ROW($B$9)</f>
+        <v>80</v>
+      </c>
+      <c r="C89" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D89" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E89" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="F89" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="G89" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="H89" s="37" t="s">
+        <v>319</v>
+      </c>
+      <c r="I89" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="J89" s="37" t="s">
+        <v>379</v>
+      </c>
+      <c r="K89" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="L89" s="37">
+        <v>1</v>
+      </c>
+      <c r="M89" s="37">
+        <f>L89*5</f>
+        <v>5</v>
+      </c>
+      <c r="N89" s="37">
+        <v>6</v>
+      </c>
+      <c r="O89" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P89" s="38">
+        <v>1.2107000000000001</v>
+      </c>
+      <c r="Q89" s="38">
+        <f>P89*N89</f>
+        <v>7.2642000000000007</v>
+      </c>
+      <c r="R89" s="37"/>
+      <c r="S89" s="59"/>
+      <c r="Y89"/>
+      <c r="Z89"/>
+      <c r="AA89"/>
+    </row>
+    <row r="90" spans="1:27" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A90" s="69"/>
+      <c r="B90" s="47">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="C90" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="D74" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="E74" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="F74" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="G74" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="H74" s="37" t="s">
-        <v>318</v>
-      </c>
-      <c r="I74" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="J74" s="37" t="s">
-        <v>373</v>
-      </c>
-      <c r="K74" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="L74" s="37">
+      <c r="D90" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="E90" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="F90" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="G90" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="H90" s="51" t="s">
+        <v>321</v>
+      </c>
+      <c r="I90" s="51" t="s">
+        <v>429</v>
+      </c>
+      <c r="J90" s="51" t="s">
+        <v>380</v>
+      </c>
+      <c r="K90" s="51" t="s">
+        <v>417</v>
+      </c>
+      <c r="L90" s="51">
         <v>1</v>
       </c>
-      <c r="M74" s="37">
-        <f>L74*5</f>
+      <c r="M90" s="51">
+        <f t="shared" ref="M90" si="76">L90*5</f>
         <v>5</v>
       </c>
-      <c r="N74" s="37">
+      <c r="N90" s="51">
+        <v>10</v>
+      </c>
+      <c r="O90" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P90" s="52">
+        <v>0.08</v>
+      </c>
+      <c r="Q90" s="52">
+        <f t="shared" ref="Q90" si="77">P90*N90</f>
+        <v>0.8</v>
+      </c>
+      <c r="R90" s="51"/>
+      <c r="S90" s="59"/>
+      <c r="Y90"/>
+      <c r="Z90"/>
+      <c r="AA90"/>
+    </row>
+    <row r="91" spans="1:27" s="70" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="69"/>
+      <c r="B91" s="46">
+        <f>ROW(B91) - ROW($B$9)</f>
+        <v>82</v>
+      </c>
+      <c r="C91" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D91" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="E91" s="37" t="s">
+        <v>469</v>
+      </c>
+      <c r="F91" s="37" t="s">
+        <v>470</v>
+      </c>
+      <c r="G91" s="37" t="s">
+        <v>471</v>
+      </c>
+      <c r="H91" s="37" t="s">
+        <v>472</v>
+      </c>
+      <c r="I91" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="J91" s="37" t="s">
+        <v>473</v>
+      </c>
+      <c r="K91" s="37" t="s">
+        <v>418</v>
+      </c>
+      <c r="L91" s="37">
+        <v>1</v>
+      </c>
+      <c r="M91" s="37">
+        <f>L91*5</f>
+        <v>5</v>
+      </c>
+      <c r="N91" s="37">
+        <v>10</v>
+      </c>
+      <c r="O91" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P91" s="38">
+        <v>0.1065</v>
+      </c>
+      <c r="Q91" s="38">
+        <f>P91*N91</f>
+        <v>1.0649999999999999</v>
+      </c>
+      <c r="R91" s="37"/>
+      <c r="S91" s="39"/>
+      <c r="Y91"/>
+      <c r="Z91"/>
+      <c r="AA91"/>
+    </row>
+    <row r="92" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="1"/>
+      <c r="B92" s="40"/>
+      <c r="C92" s="41"/>
+      <c r="D92" s="42"/>
+      <c r="E92" s="43"/>
+      <c r="F92" s="44"/>
+      <c r="G92" s="45"/>
+      <c r="H92" s="44"/>
+      <c r="I92" s="45"/>
+      <c r="J92" s="44"/>
+      <c r="K92" s="45"/>
+      <c r="L92" s="45"/>
+      <c r="M92" s="45"/>
+      <c r="N92" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="O92" s="83"/>
+      <c r="P92" s="83"/>
+      <c r="Q92" s="48">
+        <f>SUM(Q10:Q91)</f>
+        <v>290.00960000000003</v>
+      </c>
+      <c r="R92" s="78"/>
+      <c r="S92" s="79"/>
+      <c r="U92" s="70"/>
+      <c r="V92" s="70"/>
+      <c r="W92" s="70"/>
+      <c r="X92" s="70"/>
+    </row>
+    <row r="93" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="1"/>
+      <c r="B93" s="25"/>
+      <c r="C93" s="36"/>
+      <c r="D93" s="9"/>
+      <c r="E93" s="10"/>
+      <c r="F93" s="10"/>
+      <c r="G93" s="10"/>
+      <c r="H93" s="10"/>
+      <c r="I93" s="10"/>
+      <c r="J93" s="10"/>
+      <c r="K93" s="10"/>
+      <c r="L93" s="10"/>
+      <c r="M93" s="10"/>
+      <c r="N93" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="O74" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P74" s="38">
-        <v>0.82569999999999999</v>
-      </c>
-      <c r="Q74" s="38">
-        <f>P74*N74</f>
-        <v>4.9542000000000002</v>
-      </c>
-      <c r="R74" s="37"/>
-      <c r="S74" s="59"/>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A75" s="1"/>
-      <c r="B75" s="47">
-        <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-      <c r="C75" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="D75" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="E75" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="F75" s="51" t="s">
-        <v>210</v>
-      </c>
-      <c r="G75" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="H75" s="51" t="s">
-        <v>318</v>
-      </c>
-      <c r="I75" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="J75" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="K75" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="L75" s="51">
-        <v>1</v>
-      </c>
-      <c r="M75" s="51">
-        <f t="shared" ref="M75" si="63">L75*5</f>
-        <v>5</v>
-      </c>
-      <c r="N75" s="51">
-        <v>6</v>
-      </c>
-      <c r="O75" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P75" s="52">
-        <v>0.70009999999999994</v>
-      </c>
-      <c r="Q75" s="52">
-        <f t="shared" ref="Q75" si="64">P75*N75</f>
-        <v>4.2005999999999997</v>
-      </c>
-      <c r="R75" s="51"/>
-      <c r="S75" s="59"/>
-    </row>
-    <row r="76" spans="1:19" ht="36" x14ac:dyDescent="0.25">
-      <c r="A76" s="1"/>
-      <c r="B76" s="46">
-        <f>ROW(B76) - ROW($B$9)</f>
-        <v>67</v>
-      </c>
-      <c r="C76" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="D76" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="E76" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="F76" s="37" t="s">
-        <v>211</v>
-      </c>
-      <c r="G76" s="37" t="s">
-        <v>271</v>
-      </c>
-      <c r="H76" s="37" t="s">
-        <v>319</v>
-      </c>
-      <c r="I76" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="J76" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="K76" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="L76" s="37">
-        <v>1</v>
-      </c>
-      <c r="M76" s="37">
-        <f>L76*5</f>
-        <v>5</v>
-      </c>
-      <c r="N76" s="37">
-        <v>10</v>
-      </c>
-      <c r="O76" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P76" s="38">
-        <v>0.32279999999999998</v>
-      </c>
-      <c r="Q76" s="38">
-        <f>P76*N76</f>
-        <v>3.2279999999999998</v>
-      </c>
-      <c r="R76" s="37"/>
-      <c r="S76" s="59"/>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A77" s="1"/>
-      <c r="B77" s="47">
-        <f t="shared" si="0"/>
-        <v>68</v>
-      </c>
-      <c r="C77" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="D77" s="51" t="s">
-        <v>91</v>
-      </c>
-      <c r="E77" s="51" t="s">
-        <v>165</v>
-      </c>
-      <c r="F77" s="51" t="s">
-        <v>212</v>
-      </c>
-      <c r="G77" s="51" t="s">
-        <v>272</v>
-      </c>
-      <c r="H77" s="51" t="s">
-        <v>320</v>
-      </c>
-      <c r="I77" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="J77" s="51" t="s">
-        <v>376</v>
-      </c>
-      <c r="K77" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="L77" s="51">
-        <v>1</v>
-      </c>
-      <c r="M77" s="51">
-        <f t="shared" ref="M77" si="65">L77*5</f>
-        <v>5</v>
-      </c>
-      <c r="N77" s="51">
-        <v>6</v>
-      </c>
-      <c r="O77" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P77" s="52">
-        <v>1.3062</v>
-      </c>
-      <c r="Q77" s="52">
-        <f t="shared" ref="Q77" si="66">P77*N77</f>
-        <v>7.8372000000000002</v>
-      </c>
-      <c r="R77" s="51"/>
-      <c r="S77" s="59"/>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" s="1"/>
-      <c r="B78" s="46">
-        <f>ROW(B78) - ROW($B$9)</f>
-        <v>69</v>
-      </c>
-      <c r="C78" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="D78" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E78" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="F78" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="G78" s="37" t="s">
-        <v>273</v>
-      </c>
-      <c r="H78" s="37" t="s">
-        <v>321</v>
-      </c>
-      <c r="I78" s="37"/>
-      <c r="J78" s="37" t="s">
-        <v>377</v>
-      </c>
-      <c r="K78" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="L78" s="37">
-        <v>1</v>
-      </c>
-      <c r="M78" s="37">
-        <f>L78*5</f>
-        <v>5</v>
-      </c>
-      <c r="N78" s="37">
-        <v>6</v>
-      </c>
-      <c r="O78" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P78" s="38">
-        <v>0.3644</v>
-      </c>
-      <c r="Q78" s="38">
-        <f>P78*N78</f>
-        <v>2.1863999999999999</v>
-      </c>
-      <c r="R78" s="37"/>
-      <c r="S78" s="59"/>
-    </row>
-    <row r="79" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="67"/>
-      <c r="B79" s="68">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-      <c r="C79" s="69" t="s">
-        <v>25</v>
-      </c>
-      <c r="D79" s="70" t="s">
-        <v>93</v>
-      </c>
-      <c r="E79" s="70" t="s">
-        <v>167</v>
-      </c>
-      <c r="F79" s="70" t="s">
-        <v>214</v>
-      </c>
-      <c r="G79" s="70" t="s">
-        <v>274</v>
-      </c>
-      <c r="H79" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="I79" s="70" t="s">
-        <v>434</v>
-      </c>
-      <c r="J79" s="70" t="s">
-        <v>434</v>
-      </c>
-      <c r="K79" s="70" t="s">
-        <v>434</v>
-      </c>
-      <c r="L79" s="70">
-        <v>1</v>
-      </c>
-      <c r="M79" s="70">
-        <f t="shared" ref="M79" si="67">L79*5</f>
-        <v>5</v>
-      </c>
-      <c r="N79" s="70">
-        <v>6</v>
-      </c>
-      <c r="O79" s="71" t="s">
-        <v>458</v>
-      </c>
-      <c r="P79" s="72">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="Q79" s="72">
-        <f t="shared" ref="Q79" si="68">P79*N79</f>
-        <v>15.059999999999999</v>
-      </c>
-      <c r="R79" s="70"/>
-      <c r="S79" s="73"/>
-    </row>
-    <row r="80" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="67"/>
-      <c r="B80" s="75">
-        <f>ROW(B80) - ROW($B$9)</f>
-        <v>71</v>
-      </c>
-      <c r="C80" s="76" t="s">
-        <v>25</v>
-      </c>
-      <c r="D80" s="77" t="s">
-        <v>94</v>
-      </c>
-      <c r="E80" s="77" t="s">
-        <v>168</v>
-      </c>
-      <c r="F80" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="G80" s="77" t="s">
-        <v>275</v>
-      </c>
-      <c r="H80" s="77" t="s">
-        <v>320</v>
-      </c>
-      <c r="I80" s="77" t="s">
-        <v>434</v>
-      </c>
-      <c r="J80" s="77" t="s">
-        <v>434</v>
-      </c>
-      <c r="K80" s="77" t="s">
-        <v>434</v>
-      </c>
-      <c r="L80" s="77">
-        <v>1</v>
-      </c>
-      <c r="M80" s="77">
-        <f>L80*5</f>
-        <v>5</v>
-      </c>
-      <c r="N80" s="77">
-        <v>6</v>
-      </c>
-      <c r="O80" s="71" t="s">
-        <v>458</v>
-      </c>
-      <c r="P80" s="78">
-        <v>3.4329999999999998</v>
-      </c>
-      <c r="Q80" s="78">
-        <f>P80*N80</f>
-        <v>20.597999999999999</v>
-      </c>
-      <c r="R80" s="77"/>
-      <c r="S80" s="73"/>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A81" s="1"/>
-      <c r="B81" s="47">
-        <f t="shared" si="0"/>
-        <v>72</v>
-      </c>
-      <c r="C81" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="D81" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="E81" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="F81" s="51" t="s">
-        <v>216</v>
-      </c>
-      <c r="G81" s="51" t="s">
-        <v>276</v>
-      </c>
-      <c r="H81" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="I81" s="51"/>
-      <c r="J81" s="51" t="s">
-        <v>378</v>
-      </c>
-      <c r="K81" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="L81" s="51">
-        <v>1</v>
-      </c>
-      <c r="M81" s="51">
-        <f t="shared" ref="M81" si="69">L81*5</f>
-        <v>5</v>
-      </c>
-      <c r="N81" s="51">
-        <v>6</v>
-      </c>
-      <c r="O81" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P81" s="52">
-        <v>4.6247999999999996</v>
-      </c>
-      <c r="Q81" s="52">
-        <f t="shared" ref="Q81" si="70">P81*N81</f>
-        <v>27.748799999999996</v>
-      </c>
-      <c r="R81" s="51"/>
-      <c r="S81" s="59"/>
-    </row>
-    <row r="82" spans="1:19" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="67"/>
-      <c r="B82" s="75">
-        <f>ROW(B82) - ROW($B$9)</f>
-        <v>73</v>
-      </c>
-      <c r="C82" s="76" t="s">
-        <v>25</v>
-      </c>
-      <c r="D82" s="77" t="s">
-        <v>96</v>
-      </c>
-      <c r="E82" s="77" t="s">
-        <v>170</v>
-      </c>
-      <c r="F82" s="77" t="s">
-        <v>217</v>
-      </c>
-      <c r="G82" s="77" t="s">
-        <v>277</v>
-      </c>
-      <c r="H82" s="77" t="s">
-        <v>324</v>
-      </c>
-      <c r="I82" s="77" t="s">
-        <v>434</v>
-      </c>
-      <c r="J82" s="77" t="s">
-        <v>434</v>
-      </c>
-      <c r="K82" s="77" t="s">
-        <v>434</v>
-      </c>
-      <c r="L82" s="77">
-        <v>1</v>
-      </c>
-      <c r="M82" s="77">
-        <f>L82*5</f>
-        <v>5</v>
-      </c>
-      <c r="N82" s="77">
-        <v>6</v>
-      </c>
-      <c r="O82" s="71" t="s">
-        <v>458</v>
-      </c>
-      <c r="P82" s="78">
-        <v>7.9</v>
-      </c>
-      <c r="Q82" s="78">
-        <f>P82*N82</f>
-        <v>47.400000000000006</v>
-      </c>
-      <c r="R82" s="79"/>
-      <c r="S82" s="73"/>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A83" s="1"/>
-      <c r="B83" s="47">
-        <f t="shared" si="0"/>
-        <v>74</v>
-      </c>
-      <c r="C83" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="D83" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="E83" s="51" t="s">
-        <v>171</v>
-      </c>
-      <c r="F83" s="51" t="s">
-        <v>218</v>
-      </c>
-      <c r="G83" s="51" t="s">
-        <v>278</v>
-      </c>
-      <c r="H83" s="51" t="s">
-        <v>320</v>
-      </c>
-      <c r="I83" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="J83" s="51" t="s">
-        <v>379</v>
-      </c>
-      <c r="K83" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="L83" s="51">
-        <v>3</v>
-      </c>
-      <c r="M83" s="51">
-        <f t="shared" ref="M83" si="71">L83*5</f>
-        <v>15</v>
-      </c>
-      <c r="N83" s="51">
-        <v>16</v>
-      </c>
-      <c r="O83" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P83" s="52">
-        <v>1.7437</v>
-      </c>
-      <c r="Q83" s="52">
-        <f t="shared" ref="Q83" si="72">P83*N83</f>
-        <v>27.8992</v>
-      </c>
-      <c r="R83" s="51"/>
-      <c r="S83" s="59"/>
-    </row>
-    <row r="84" spans="1:19" ht="60" x14ac:dyDescent="0.25">
-      <c r="A84" s="1"/>
-      <c r="B84" s="46">
-        <f>ROW(B84) - ROW($B$9)</f>
-        <v>75</v>
-      </c>
-      <c r="C84" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="D84" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="E84" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="F84" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="G84" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="H84" s="37" t="s">
-        <v>325</v>
-      </c>
-      <c r="I84" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="J84" s="37" t="s">
-        <v>380</v>
-      </c>
-      <c r="K84" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="L84" s="37">
-        <v>1</v>
-      </c>
-      <c r="M84" s="37">
-        <f>L84*5</f>
-        <v>5</v>
-      </c>
-      <c r="N84" s="37">
-        <v>10</v>
-      </c>
-      <c r="O84" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P84" s="38">
-        <v>7.7799999999999994E-2</v>
-      </c>
-      <c r="Q84" s="38">
-        <f>P84*N84</f>
-        <v>0.77799999999999991</v>
-      </c>
-      <c r="R84" s="37"/>
-      <c r="S84" s="59"/>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A85" s="1"/>
-      <c r="B85" s="47">
-        <f t="shared" si="0"/>
-        <v>76</v>
-      </c>
-      <c r="C85" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="D85" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="E85" s="51" t="s">
-        <v>173</v>
-      </c>
-      <c r="F85" s="51" t="s">
-        <v>220</v>
-      </c>
-      <c r="G85" s="51" t="s">
-        <v>280</v>
-      </c>
-      <c r="H85" s="51" t="s">
-        <v>318</v>
-      </c>
-      <c r="I85" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="J85" s="51" t="s">
-        <v>381</v>
-      </c>
-      <c r="K85" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="L85" s="51">
-        <v>1</v>
-      </c>
-      <c r="M85" s="51">
-        <f t="shared" ref="M85" si="73">L85*5</f>
-        <v>5</v>
-      </c>
-      <c r="N85" s="51">
-        <v>6</v>
-      </c>
-      <c r="O85" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P85" s="52">
-        <v>0.77800000000000002</v>
-      </c>
-      <c r="Q85" s="52">
-        <f t="shared" ref="Q85" si="74">P85*N85</f>
-        <v>4.6680000000000001</v>
-      </c>
-      <c r="R85" s="51"/>
-      <c r="S85" s="59"/>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A86" s="1"/>
-      <c r="B86" s="46">
-        <f>ROW(B86) - ROW($B$9)</f>
-        <v>77</v>
-      </c>
-      <c r="C86" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="D86" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="E86" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="F86" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="G86" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="H86" s="37" t="s">
-        <v>319</v>
-      </c>
-      <c r="I86" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="J86" s="37" t="s">
-        <v>382</v>
-      </c>
-      <c r="K86" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="L86" s="37">
-        <v>1</v>
-      </c>
-      <c r="M86" s="37">
-        <f>L86*5</f>
-        <v>5</v>
-      </c>
-      <c r="N86" s="37">
-        <v>6</v>
-      </c>
-      <c r="O86" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P86" s="38">
-        <v>0.41049999999999998</v>
-      </c>
-      <c r="Q86" s="38">
-        <f>P86*N86</f>
-        <v>2.4630000000000001</v>
-      </c>
-      <c r="R86" s="37"/>
-      <c r="S86" s="59"/>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A87" s="1"/>
-      <c r="B87" s="47">
-        <f t="shared" si="0"/>
-        <v>78</v>
-      </c>
-      <c r="C87" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="D87" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="E87" s="51" t="s">
-        <v>175</v>
-      </c>
-      <c r="F87" s="51" t="s">
-        <v>215</v>
-      </c>
-      <c r="G87" s="51" t="s">
-        <v>282</v>
-      </c>
-      <c r="H87" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="I87" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="J87" s="51" t="s">
-        <v>383</v>
-      </c>
-      <c r="K87" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="L87" s="51">
-        <v>1</v>
-      </c>
-      <c r="M87" s="51">
-        <f t="shared" ref="M87" si="75">L87*5</f>
-        <v>5</v>
-      </c>
-      <c r="N87" s="51">
-        <v>6</v>
-      </c>
-      <c r="O87" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P87" s="52">
-        <v>1.1837</v>
-      </c>
-      <c r="Q87" s="52">
-        <f t="shared" ref="Q87" si="76">P87*N87</f>
-        <v>7.1021999999999998</v>
-      </c>
-      <c r="R87" s="51"/>
-      <c r="S87" s="59"/>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A88" s="1"/>
-      <c r="B88" s="46">
-        <f>ROW(B88) - ROW($B$9)</f>
-        <v>79</v>
-      </c>
-      <c r="C88" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="D88" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="E88" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="F88" s="37" t="s">
-        <v>215</v>
-      </c>
-      <c r="G88" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="H88" s="37" t="s">
-        <v>324</v>
-      </c>
-      <c r="I88" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="J88" s="37" t="s">
-        <v>384</v>
-      </c>
-      <c r="K88" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="L88" s="37">
-        <v>1</v>
-      </c>
-      <c r="M88" s="37">
-        <f>L88*5</f>
-        <v>5</v>
-      </c>
-      <c r="N88" s="37">
-        <v>6</v>
-      </c>
-      <c r="O88" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P88" s="38">
-        <v>1.2107000000000001</v>
-      </c>
-      <c r="Q88" s="38">
-        <f>P88*N88</f>
-        <v>7.2642000000000007</v>
-      </c>
-      <c r="R88" s="37"/>
-      <c r="S88" s="59"/>
-    </row>
-    <row r="89" spans="1:19" ht="24" x14ac:dyDescent="0.25">
-      <c r="A89" s="1"/>
-      <c r="B89" s="47">
-        <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-      <c r="C89" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="D89" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="E89" s="51" t="s">
-        <v>176</v>
-      </c>
-      <c r="F89" s="51" t="s">
-        <v>440</v>
-      </c>
-      <c r="G89" s="51" t="s">
-        <v>284</v>
-      </c>
-      <c r="H89" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="I89" s="51" t="s">
-        <v>434</v>
-      </c>
-      <c r="J89" s="51" t="s">
-        <v>385</v>
-      </c>
-      <c r="K89" s="51" t="s">
-        <v>422</v>
-      </c>
-      <c r="L89" s="51">
-        <v>1</v>
-      </c>
-      <c r="M89" s="51">
-        <f t="shared" ref="M89" si="77">L89*5</f>
-        <v>5</v>
-      </c>
-      <c r="N89" s="51">
-        <v>10</v>
-      </c>
-      <c r="O89" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P89" s="52">
-        <v>0.08</v>
-      </c>
-      <c r="Q89" s="52">
-        <f t="shared" ref="Q89" si="78">P89*N89</f>
-        <v>0.8</v>
-      </c>
-      <c r="R89" s="51"/>
-      <c r="S89" s="59"/>
-    </row>
-    <row r="90" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="1"/>
-      <c r="B90" s="46">
-        <f>ROW(B90) - ROW($B$9)</f>
-        <v>81</v>
-      </c>
-      <c r="C90" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="D90" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="E90" s="37" t="s">
-        <v>478</v>
-      </c>
-      <c r="F90" s="37" t="s">
-        <v>479</v>
-      </c>
-      <c r="G90" s="37" t="s">
-        <v>480</v>
-      </c>
-      <c r="H90" s="37" t="s">
-        <v>481</v>
-      </c>
-      <c r="I90" s="37"/>
-      <c r="J90" s="37" t="s">
-        <v>482</v>
-      </c>
-      <c r="K90" s="37" t="s">
-        <v>423</v>
-      </c>
-      <c r="L90" s="37">
-        <v>1</v>
-      </c>
-      <c r="M90" s="37">
-        <f>L90*5</f>
-        <v>5</v>
-      </c>
-      <c r="N90" s="37">
-        <v>10</v>
-      </c>
-      <c r="O90" s="60" t="s">
-        <v>441</v>
-      </c>
-      <c r="P90" s="38">
-        <v>0.1065</v>
-      </c>
-      <c r="Q90" s="38">
-        <f>P90*N90</f>
-        <v>1.0649999999999999</v>
-      </c>
-      <c r="R90" s="37"/>
-      <c r="S90" s="39"/>
-    </row>
-    <row r="91" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="1"/>
-      <c r="B91" s="40"/>
-      <c r="C91" s="41"/>
-      <c r="D91" s="42"/>
-      <c r="E91" s="43"/>
-      <c r="F91" s="44"/>
-      <c r="G91" s="45"/>
-      <c r="H91" s="44"/>
-      <c r="I91" s="45"/>
-      <c r="J91" s="44"/>
-      <c r="K91" s="45"/>
-      <c r="L91" s="45"/>
-      <c r="M91" s="45"/>
-      <c r="N91" s="88" t="s">
-        <v>5</v>
-      </c>
-      <c r="O91" s="89"/>
-      <c r="P91" s="89"/>
-      <c r="Q91" s="48">
-        <f>SUM(Q10:Q90)</f>
-        <v>293.06310000000008</v>
-      </c>
-      <c r="R91" s="84"/>
-      <c r="S91" s="85"/>
-    </row>
-    <row r="92" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="1"/>
-      <c r="B92" s="25"/>
-      <c r="C92" s="36"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="10"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="10"/>
-      <c r="H92" s="10"/>
-      <c r="I92" s="10"/>
-      <c r="J92" s="10"/>
-      <c r="K92" s="10"/>
-      <c r="L92" s="10"/>
-      <c r="M92" s="10"/>
-      <c r="N92" s="88" t="s">
-        <v>6</v>
-      </c>
-      <c r="O92" s="89"/>
-      <c r="P92" s="89"/>
-      <c r="Q92" s="49">
-        <f>Q91/5</f>
-        <v>58.612620000000014</v>
-      </c>
-      <c r="R92" s="86"/>
-      <c r="S92" s="87"/>
+      <c r="O93" s="83"/>
+      <c r="P93" s="83"/>
+      <c r="Q93" s="49">
+        <f>Q92/5</f>
+        <v>58.001920000000005</v>
+      </c>
+      <c r="R93" s="80"/>
+      <c r="S93" s="81"/>
+      <c r="U93" s="70"/>
+      <c r="V93" s="70"/>
+      <c r="W93" s="70"/>
+      <c r="X93" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R91:S92"/>
-    <mergeCell ref="N91:P91"/>
+    <mergeCell ref="R92:S93"/>
     <mergeCell ref="N92:P92"/>
+    <mergeCell ref="N93:P93"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O43" r:id="rId1"/>
-    <hyperlink ref="O71" r:id="rId2"/>
-    <hyperlink ref="O90" r:id="rId3"/>
+    <hyperlink ref="O72" r:id="rId2"/>
+    <hyperlink ref="O91" r:id="rId3"/>
     <hyperlink ref="O41" r:id="rId4"/>
-    <hyperlink ref="O39" r:id="rId5"/>
-    <hyperlink ref="O18" r:id="rId6"/>
-    <hyperlink ref="O16" r:id="rId7"/>
-    <hyperlink ref="O15" r:id="rId8"/>
-    <hyperlink ref="O82" r:id="rId9"/>
-    <hyperlink ref="O80" r:id="rId10"/>
-    <hyperlink ref="O79" r:id="rId11"/>
-    <hyperlink ref="O66" r:id="rId12"/>
-    <hyperlink ref="O57" r:id="rId13"/>
-    <hyperlink ref="O54" r:id="rId14"/>
-    <hyperlink ref="O50" r:id="rId15"/>
-    <hyperlink ref="O27" r:id="rId16"/>
-    <hyperlink ref="O26" r:id="rId17"/>
-    <hyperlink ref="O20" r:id="rId18"/>
-    <hyperlink ref="O73" r:id="rId19"/>
-    <hyperlink ref="O89" r:id="rId20"/>
-    <hyperlink ref="O88" r:id="rId21"/>
-    <hyperlink ref="O87" r:id="rId22"/>
-    <hyperlink ref="O86" r:id="rId23"/>
-    <hyperlink ref="O85" r:id="rId24"/>
-    <hyperlink ref="O84" r:id="rId25"/>
-    <hyperlink ref="O83" r:id="rId26"/>
-    <hyperlink ref="O81" r:id="rId27"/>
-    <hyperlink ref="O78" r:id="rId28"/>
-    <hyperlink ref="O77" r:id="rId29"/>
-    <hyperlink ref="O76" r:id="rId30"/>
-    <hyperlink ref="O75" r:id="rId31"/>
-    <hyperlink ref="O74" r:id="rId32"/>
-    <hyperlink ref="O70" r:id="rId33"/>
-    <hyperlink ref="O69" r:id="rId34"/>
-    <hyperlink ref="O68" r:id="rId35"/>
-    <hyperlink ref="O67" r:id="rId36"/>
-    <hyperlink ref="O61" r:id="rId37"/>
-    <hyperlink ref="O65" r:id="rId38"/>
-    <hyperlink ref="O64" r:id="rId39"/>
-    <hyperlink ref="O63" r:id="rId40"/>
-    <hyperlink ref="O62" r:id="rId41"/>
-    <hyperlink ref="O60" r:id="rId42"/>
-    <hyperlink ref="O59" r:id="rId43"/>
-    <hyperlink ref="O58" r:id="rId44"/>
-    <hyperlink ref="O56" r:id="rId45"/>
-    <hyperlink ref="O55" r:id="rId46"/>
-    <hyperlink ref="O53" r:id="rId47"/>
-    <hyperlink ref="O52" r:id="rId48"/>
-    <hyperlink ref="O51" r:id="rId49"/>
-    <hyperlink ref="O49" r:id="rId50"/>
-    <hyperlink ref="O47" r:id="rId51"/>
-    <hyperlink ref="O46" r:id="rId52"/>
-    <hyperlink ref="O45" r:id="rId53"/>
-    <hyperlink ref="O44" r:id="rId54"/>
-    <hyperlink ref="O42" r:id="rId55"/>
-    <hyperlink ref="O40" r:id="rId56"/>
-    <hyperlink ref="O38" r:id="rId57"/>
-    <hyperlink ref="O37" r:id="rId58"/>
-    <hyperlink ref="O36" r:id="rId59"/>
-    <hyperlink ref="O35" r:id="rId60"/>
-    <hyperlink ref="O34" r:id="rId61"/>
-    <hyperlink ref="O33" r:id="rId62"/>
-    <hyperlink ref="O32" r:id="rId63"/>
-    <hyperlink ref="O31" r:id="rId64"/>
-    <hyperlink ref="O30" r:id="rId65"/>
-    <hyperlink ref="O29" r:id="rId66"/>
-    <hyperlink ref="O28" r:id="rId67"/>
-    <hyperlink ref="O25" r:id="rId68"/>
-    <hyperlink ref="O24" r:id="rId69"/>
-    <hyperlink ref="O23" r:id="rId70"/>
-    <hyperlink ref="O21" r:id="rId71"/>
-    <hyperlink ref="O22" r:id="rId72"/>
-    <hyperlink ref="O19" r:id="rId73"/>
-    <hyperlink ref="O17" r:id="rId74"/>
-    <hyperlink ref="O14" r:id="rId75"/>
-    <hyperlink ref="O13" r:id="rId76"/>
-    <hyperlink ref="O12" r:id="rId77"/>
-    <hyperlink ref="O11" r:id="rId78"/>
+    <hyperlink ref="O18" r:id="rId5"/>
+    <hyperlink ref="O16" r:id="rId6"/>
+    <hyperlink ref="O83" r:id="rId7"/>
+    <hyperlink ref="O81" r:id="rId8"/>
+    <hyperlink ref="O80" r:id="rId9"/>
+    <hyperlink ref="O67" r:id="rId10"/>
+    <hyperlink ref="O57" r:id="rId11"/>
+    <hyperlink ref="O54" r:id="rId12"/>
+    <hyperlink ref="O50" r:id="rId13"/>
+    <hyperlink ref="O27" r:id="rId14"/>
+    <hyperlink ref="O26" r:id="rId15"/>
+    <hyperlink ref="O20" r:id="rId16"/>
+    <hyperlink ref="O74" r:id="rId17"/>
+    <hyperlink ref="O90" r:id="rId18"/>
+    <hyperlink ref="O89" r:id="rId19"/>
+    <hyperlink ref="O88" r:id="rId20"/>
+    <hyperlink ref="O87" r:id="rId21"/>
+    <hyperlink ref="O86" r:id="rId22"/>
+    <hyperlink ref="O85" r:id="rId23"/>
+    <hyperlink ref="O84" r:id="rId24"/>
+    <hyperlink ref="O82" r:id="rId25"/>
+    <hyperlink ref="O79" r:id="rId26"/>
+    <hyperlink ref="O78" r:id="rId27"/>
+    <hyperlink ref="O77" r:id="rId28"/>
+    <hyperlink ref="O76" r:id="rId29"/>
+    <hyperlink ref="O75" r:id="rId30"/>
+    <hyperlink ref="O71" r:id="rId31"/>
+    <hyperlink ref="O70" r:id="rId32"/>
+    <hyperlink ref="O69" r:id="rId33"/>
+    <hyperlink ref="O68" r:id="rId34"/>
+    <hyperlink ref="O61" r:id="rId35"/>
+    <hyperlink ref="O66" r:id="rId36"/>
+    <hyperlink ref="O65" r:id="rId37"/>
+    <hyperlink ref="O64" r:id="rId38"/>
+    <hyperlink ref="O63" r:id="rId39"/>
+    <hyperlink ref="O60" r:id="rId40"/>
+    <hyperlink ref="O59" r:id="rId41"/>
+    <hyperlink ref="O58" r:id="rId42"/>
+    <hyperlink ref="O56" r:id="rId43"/>
+    <hyperlink ref="O55" r:id="rId44"/>
+    <hyperlink ref="O53" r:id="rId45"/>
+    <hyperlink ref="O52" r:id="rId46"/>
+    <hyperlink ref="O51" r:id="rId47"/>
+    <hyperlink ref="O49" r:id="rId48"/>
+    <hyperlink ref="O47" r:id="rId49"/>
+    <hyperlink ref="O46" r:id="rId50"/>
+    <hyperlink ref="O45" r:id="rId51"/>
+    <hyperlink ref="O44" r:id="rId52"/>
+    <hyperlink ref="O42" r:id="rId53"/>
+    <hyperlink ref="O40" r:id="rId54"/>
+    <hyperlink ref="O38" r:id="rId55"/>
+    <hyperlink ref="O37" r:id="rId56"/>
+    <hyperlink ref="O36" r:id="rId57"/>
+    <hyperlink ref="O35" r:id="rId58"/>
+    <hyperlink ref="O34" r:id="rId59"/>
+    <hyperlink ref="O33" r:id="rId60"/>
+    <hyperlink ref="O32" r:id="rId61"/>
+    <hyperlink ref="O31" r:id="rId62"/>
+    <hyperlink ref="O30" r:id="rId63"/>
+    <hyperlink ref="O29" r:id="rId64"/>
+    <hyperlink ref="O28" r:id="rId65"/>
+    <hyperlink ref="O25" r:id="rId66"/>
+    <hyperlink ref="O24" r:id="rId67"/>
+    <hyperlink ref="O23" r:id="rId68"/>
+    <hyperlink ref="O21" r:id="rId69"/>
+    <hyperlink ref="O22" r:id="rId70"/>
+    <hyperlink ref="O19" r:id="rId71"/>
+    <hyperlink ref="O17" r:id="rId72"/>
+    <hyperlink ref="O14" r:id="rId73"/>
+    <hyperlink ref="O13" r:id="rId74"/>
+    <hyperlink ref="O12" r:id="rId75"/>
+    <hyperlink ref="O11" r:id="rId76"/>
+    <hyperlink ref="O15" r:id="rId77"/>
+    <hyperlink ref="O39" r:id="rId78"/>
+    <hyperlink ref="O62" r:id="rId79"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId79"/>
-  <drawing r:id="rId80"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId80"/>
+  <drawing r:id="rId81"/>
 </worksheet>
 </file>
--- a/Design Files/Baseboard-v2.0/BOM/eSpark_BOM_Baseboard-v2.0.xlsx
+++ b/Design Files/Baseboard-v2.0/BOM/eSpark_BOM_Baseboard-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="504">
   <si>
     <t>Component list</t>
   </si>
@@ -1522,6 +1522,15 @@
   </si>
   <si>
     <t>DNP</t>
+  </si>
+  <si>
+    <t>peripheral</t>
+  </si>
+  <si>
+    <t>RF2111027</t>
+  </si>
+  <si>
+    <t>C2936948</t>
   </si>
 </sst>
 </file>
@@ -2597,7 +2606,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA93"/>
+  <dimension ref="A1:AA94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -7699,73 +7708,132 @@
       <c r="Z91"/>
       <c r="AA91"/>
     </row>
-    <row r="92" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="1"/>
-      <c r="B92" s="40"/>
-      <c r="C92" s="41"/>
-      <c r="D92" s="42"/>
-      <c r="E92" s="43"/>
-      <c r="F92" s="44"/>
-      <c r="G92" s="45"/>
-      <c r="H92" s="44"/>
-      <c r="I92" s="45"/>
-      <c r="J92" s="44"/>
-      <c r="K92" s="45"/>
-      <c r="L92" s="45"/>
-      <c r="M92" s="45"/>
-      <c r="N92" s="82" t="s">
+    <row r="92" spans="1:27" s="70" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="69"/>
+      <c r="B92" s="46">
+        <f>ROW(B92) - ROW($B$9)</f>
+        <v>83</v>
+      </c>
+      <c r="C92" s="53" t="s">
+        <v>501</v>
+      </c>
+      <c r="D92" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="E92" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="F92" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="G92" s="37" t="s">
+        <v>502</v>
+      </c>
+      <c r="H92" s="37" t="s">
+        <v>456</v>
+      </c>
+      <c r="I92" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="J92" s="37" t="s">
+        <v>503</v>
+      </c>
+      <c r="K92" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="L92" s="37">
+        <v>1</v>
+      </c>
+      <c r="M92" s="37">
+        <f>L92*5</f>
         <v>5</v>
       </c>
-      <c r="O92" s="83"/>
-      <c r="P92" s="83"/>
-      <c r="Q92" s="48">
-        <f>SUM(Q10:Q91)</f>
-        <v>290.00960000000003</v>
-      </c>
-      <c r="R92" s="78"/>
-      <c r="S92" s="79"/>
-      <c r="U92" s="70"/>
-      <c r="V92" s="70"/>
-      <c r="W92" s="70"/>
-      <c r="X92" s="70"/>
+      <c r="N92" s="37">
+        <v>5</v>
+      </c>
+      <c r="O92" s="60" t="s">
+        <v>436</v>
+      </c>
+      <c r="P92" s="38">
+        <v>1.3777999999999999</v>
+      </c>
+      <c r="Q92" s="38">
+        <f>P92*N92</f>
+        <v>6.8889999999999993</v>
+      </c>
+      <c r="R92" s="37"/>
+      <c r="S92" s="39"/>
+      <c r="Y92"/>
+      <c r="Z92"/>
+      <c r="AA92"/>
     </row>
     <row r="93" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
-      <c r="B93" s="25"/>
-      <c r="C93" s="36"/>
-      <c r="D93" s="9"/>
-      <c r="E93" s="10"/>
-      <c r="F93" s="10"/>
-      <c r="G93" s="10"/>
-      <c r="H93" s="10"/>
-      <c r="I93" s="10"/>
-      <c r="J93" s="10"/>
-      <c r="K93" s="10"/>
-      <c r="L93" s="10"/>
-      <c r="M93" s="10"/>
+      <c r="B93" s="40"/>
+      <c r="C93" s="41"/>
+      <c r="D93" s="42"/>
+      <c r="E93" s="43"/>
+      <c r="F93" s="44"/>
+      <c r="G93" s="45"/>
+      <c r="H93" s="44"/>
+      <c r="I93" s="45"/>
+      <c r="J93" s="44"/>
+      <c r="K93" s="45"/>
+      <c r="L93" s="45"/>
+      <c r="M93" s="45"/>
       <c r="N93" s="82" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O93" s="83"/>
       <c r="P93" s="83"/>
-      <c r="Q93" s="49">
-        <f>Q92/5</f>
-        <v>58.001920000000005</v>
-      </c>
-      <c r="R93" s="80"/>
-      <c r="S93" s="81"/>
+      <c r="Q93" s="48">
+        <f>SUM(Q10:Q92)</f>
+        <v>296.89860000000004</v>
+      </c>
+      <c r="R93" s="78"/>
+      <c r="S93" s="79"/>
       <c r="U93" s="70"/>
       <c r="V93" s="70"/>
       <c r="W93" s="70"/>
       <c r="X93" s="70"/>
     </row>
+    <row r="94" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="1"/>
+      <c r="B94" s="25"/>
+      <c r="C94" s="36"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="10"/>
+      <c r="F94" s="10"/>
+      <c r="G94" s="10"/>
+      <c r="H94" s="10"/>
+      <c r="I94" s="10"/>
+      <c r="J94" s="10"/>
+      <c r="K94" s="10"/>
+      <c r="L94" s="10"/>
+      <c r="M94" s="10"/>
+      <c r="N94" s="82" t="s">
+        <v>6</v>
+      </c>
+      <c r="O94" s="83"/>
+      <c r="P94" s="83"/>
+      <c r="Q94" s="49">
+        <f>Q93/5</f>
+        <v>59.379720000000006</v>
+      </c>
+      <c r="R94" s="80"/>
+      <c r="S94" s="81"/>
+      <c r="U94" s="70"/>
+      <c r="V94" s="70"/>
+      <c r="W94" s="70"/>
+      <c r="X94" s="70"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R92:S93"/>
-    <mergeCell ref="N92:P92"/>
+    <mergeCell ref="R93:S94"/>
     <mergeCell ref="N93:P93"/>
+    <mergeCell ref="N94:P94"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O43" r:id="rId1"/>
@@ -7847,9 +7915,10 @@
     <hyperlink ref="O15" r:id="rId77"/>
     <hyperlink ref="O39" r:id="rId78"/>
     <hyperlink ref="O62" r:id="rId79"/>
+    <hyperlink ref="O92" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId80"/>
-  <drawing r:id="rId81"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId81"/>
+  <drawing r:id="rId82"/>
 </worksheet>
 </file>
--- a/Design Files/Baseboard-v2.0/BOM/eSpark_BOM_Baseboard-v2.0.xlsx
+++ b/Design Files/Baseboard-v2.0/BOM/eSpark_BOM_Baseboard-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="506">
   <si>
     <t>Component list</t>
   </si>
@@ -1527,10 +1527,16 @@
     <t>peripheral</t>
   </si>
   <si>
-    <t>RF2111027</t>
-  </si>
-  <si>
-    <t>C2936948</t>
+    <t>BAT WIRELESS</t>
+  </si>
+  <si>
+    <t>BW2.4JWX195-13KJ</t>
+  </si>
+  <si>
+    <t>C497018</t>
+  </si>
+  <si>
+    <t>1.8 8dBi Vertical 50W - Antennas ROHS</t>
   </si>
 </sst>
 </file>
@@ -2033,7 +2039,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2264,6 +2270,26 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -7708,64 +7734,61 @@
       <c r="Z91"/>
       <c r="AA91"/>
     </row>
-    <row r="92" spans="1:27" s="70" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="69"/>
-      <c r="B92" s="46">
+    <row r="92" spans="1:27" s="91" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="84"/>
+      <c r="B92" s="85">
         <f>ROW(B92) - ROW($B$9)</f>
         <v>83</v>
       </c>
-      <c r="C92" s="53" t="s">
+      <c r="C92" s="86" t="s">
         <v>501</v>
       </c>
-      <c r="D92" s="37" t="s">
-        <v>429</v>
-      </c>
-      <c r="E92" s="37" t="s">
-        <v>429</v>
-      </c>
-      <c r="F92" s="37" t="s">
-        <v>429</v>
-      </c>
-      <c r="G92" s="37" t="s">
+      <c r="D92" s="87" t="s">
+        <v>429</v>
+      </c>
+      <c r="E92" s="87" t="s">
+        <v>505</v>
+      </c>
+      <c r="F92" s="87" t="s">
+        <v>429</v>
+      </c>
+      <c r="G92" s="87" t="s">
+        <v>503</v>
+      </c>
+      <c r="H92" s="87" t="s">
         <v>502</v>
       </c>
-      <c r="H92" s="37" t="s">
-        <v>456</v>
-      </c>
-      <c r="I92" s="37" t="s">
-        <v>429</v>
-      </c>
-      <c r="J92" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="K92" s="37" t="s">
-        <v>429</v>
-      </c>
-      <c r="L92" s="37">
+      <c r="I92" s="87" t="s">
+        <v>429</v>
+      </c>
+      <c r="J92" s="87" t="s">
+        <v>504</v>
+      </c>
+      <c r="K92" s="87" t="s">
+        <v>429</v>
+      </c>
+      <c r="L92" s="87">
         <v>1</v>
       </c>
-      <c r="M92" s="37">
+      <c r="M92" s="87">
         <f>L92*5</f>
         <v>5</v>
       </c>
-      <c r="N92" s="37">
+      <c r="N92" s="87">
         <v>5</v>
       </c>
-      <c r="O92" s="60" t="s">
+      <c r="O92" s="88" t="s">
         <v>436</v>
       </c>
-      <c r="P92" s="38">
-        <v>1.3777999999999999</v>
-      </c>
-      <c r="Q92" s="38">
+      <c r="P92" s="89">
+        <v>1.1609</v>
+      </c>
+      <c r="Q92" s="89">
         <f>P92*N92</f>
-        <v>6.8889999999999993</v>
-      </c>
-      <c r="R92" s="37"/>
-      <c r="S92" s="39"/>
-      <c r="Y92"/>
-      <c r="Z92"/>
-      <c r="AA92"/>
+        <v>5.8045</v>
+      </c>
+      <c r="R92" s="87"/>
+      <c r="S92" s="90"/>
     </row>
     <row r="93" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
@@ -7788,7 +7811,7 @@
       <c r="P93" s="83"/>
       <c r="Q93" s="48">
         <f>SUM(Q10:Q92)</f>
-        <v>296.89860000000004</v>
+        <v>295.81410000000005</v>
       </c>
       <c r="R93" s="78"/>
       <c r="S93" s="79"/>
@@ -7818,7 +7841,7 @@
       <c r="P94" s="83"/>
       <c r="Q94" s="49">
         <f>Q93/5</f>
-        <v>59.379720000000006</v>
+        <v>59.162820000000011</v>
       </c>
       <c r="R94" s="80"/>
       <c r="S94" s="81"/>

--- a/Design Files/Baseboard-v2.0/BOM/eSpark_BOM_Baseboard-v2.0.xlsx
+++ b/Design Files/Baseboard-v2.0/BOM/eSpark_BOM_Baseboard-v2.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="506">
   <si>
     <t>Component list</t>
   </si>
@@ -1311,9 +1311,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>UFL Connector</t>
-  </si>
-  <si>
     <t>Test Point</t>
   </si>
   <si>
@@ -1383,18 +1380,9 @@
     <t>chipsmall</t>
   </si>
   <si>
-    <t>1 Inner bore SMA Board Edge Bend -55℃~+155℃ 50Ω Plugin RF Connectors / Coaxial Connectors ROHS</t>
-  </si>
-  <si>
-    <t>HJ-SMA508</t>
-  </si>
-  <si>
     <t>HJ Tech</t>
   </si>
   <si>
-    <t>C1509209</t>
-  </si>
-  <si>
     <t>CAP TANT 220UF 10% 10V 2917</t>
   </si>
   <si>
@@ -1537,6 +1525,18 @@
   </si>
   <si>
     <t>1.8 8dBi Vertical 50W - Antennas ROHS</t>
+  </si>
+  <si>
+    <t>SMA Connector</t>
+  </si>
+  <si>
+    <t>1 Inner bore SMA Board Edge Bend 11mm 5.35mm Plugin RF Connectors / Coaxial Connectors ROHS</t>
+  </si>
+  <si>
+    <t>HJ-SMA175</t>
+  </si>
+  <si>
+    <t>C1509213</t>
   </si>
 </sst>
 </file>
@@ -2238,6 +2238,26 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2270,26 +2290,6 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2668,15 +2668,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="75"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="82"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="82"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="83"/>
     </row>
     <row r="2" spans="1:27" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -2726,7 +2726,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="76"/>
+      <c r="S3" s="84"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="57" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -2751,7 +2751,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="77"/>
+      <c r="S4" s="85"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2776,7 +2776,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="77"/>
+      <c r="S5" s="85"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2797,7 +2797,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="77"/>
+      <c r="S6" s="85"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2818,7 +2818,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="77"/>
+      <c r="S7" s="85"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2839,7 +2839,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="77"/>
+      <c r="S8" s="85"/>
     </row>
     <row r="9" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2955,7 +2955,7 @@
         <v>429</v>
       </c>
       <c r="R10" s="63" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="S10" s="50"/>
       <c r="U10" s="70"/>
@@ -3007,7 +3007,7 @@
         <v>20</v>
       </c>
       <c r="O11" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P11" s="52">
         <v>2.01E-2</v>
@@ -3070,7 +3070,7 @@
         <v>150</v>
       </c>
       <c r="O12" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P12" s="38">
         <v>1.0500000000000001E-2</v>
@@ -3129,7 +3129,7 @@
         <v>100</v>
       </c>
       <c r="O13" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P13" s="52">
         <v>8.9999999999999998E-4</v>
@@ -3160,7 +3160,7 @@
         <v>105</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G14" s="37" t="s">
         <v>177</v>
@@ -3188,7 +3188,7 @@
         <v>20</v>
       </c>
       <c r="O14" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P14" s="38">
         <v>4.9099999999999998E-2</v>
@@ -3216,13 +3216,13 @@
         <v>32</v>
       </c>
       <c r="E15" s="51" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="H15" s="51" t="s">
         <v>286</v>
@@ -3231,7 +3231,7 @@
         <v>429</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="K15" s="51" t="s">
         <v>386</v>
@@ -3247,7 +3247,7 @@
         <v>11</v>
       </c>
       <c r="O15" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P15" s="52">
         <v>0.25940000000000002</v>
@@ -3275,22 +3275,22 @@
         <v>33</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="F16" s="37" t="s">
         <v>178</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="I16" s="37" t="s">
         <v>429</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="K16" s="37" t="s">
         <v>387</v>
@@ -3306,7 +3306,7 @@
         <v>15</v>
       </c>
       <c r="O16" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P16" s="38">
         <v>7.0900000000000005E-2</v>
@@ -3365,7 +3365,7 @@
         <v>10</v>
       </c>
       <c r="O17" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P17" s="52">
         <v>6.3E-2</v>
@@ -3393,13 +3393,13 @@
         <v>35</v>
       </c>
       <c r="E18" s="37" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="H18" s="37" t="s">
         <v>286</v>
@@ -3408,7 +3408,7 @@
         <v>429</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="K18" s="37" t="s">
         <v>389</v>
@@ -3424,7 +3424,7 @@
         <v>6</v>
       </c>
       <c r="O18" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P18" s="38">
         <v>1.7373000000000001</v>
@@ -3483,7 +3483,7 @@
         <v>10</v>
       </c>
       <c r="O19" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P19" s="52">
         <v>0.26129999999999998</v>
@@ -3523,10 +3523,10 @@
         <v>287</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K20" s="37" t="s">
         <v>391</v>
@@ -3542,7 +3542,7 @@
         <v>30</v>
       </c>
       <c r="O20" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P20" s="38">
         <v>4.2000000000000003E-2</v>
@@ -3601,7 +3601,7 @@
         <v>50</v>
       </c>
       <c r="O21" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P21" s="52">
         <v>1.0800000000000001E-2</v>
@@ -3660,7 +3660,7 @@
         <v>100</v>
       </c>
       <c r="O22" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P22" s="38">
         <v>1E-3</v>
@@ -3719,7 +3719,7 @@
         <v>100</v>
       </c>
       <c r="O23" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P23" s="52">
         <v>3.8999999999999998E-3</v>
@@ -3778,7 +3778,7 @@
         <v>10</v>
       </c>
       <c r="O24" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P24" s="38">
         <v>5.5599999999999997E-2</v>
@@ -3837,7 +3837,7 @@
         <v>10</v>
       </c>
       <c r="O25" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P25" s="52">
         <v>4.4600000000000001E-2</v>
@@ -3896,7 +3896,7 @@
         <v>6</v>
       </c>
       <c r="O26" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P26" s="38">
         <v>0.46939999999999998</v>
@@ -3930,7 +3930,7 @@
         <v>184</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H27" s="51" t="s">
         <v>292</v>
@@ -3939,7 +3939,7 @@
         <v>429</v>
       </c>
       <c r="J27" s="51" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K27" s="51" t="s">
         <v>429</v>
@@ -3955,7 +3955,7 @@
         <v>10</v>
       </c>
       <c r="O27" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P27" s="52">
         <v>3.56E-2</v>
@@ -4014,7 +4014,7 @@
         <v>20</v>
       </c>
       <c r="O28" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P28" s="38">
         <v>2.46E-2</v>
@@ -4073,7 +4073,7 @@
         <v>20</v>
       </c>
       <c r="O29" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P29" s="52">
         <v>2.3400000000000001E-2</v>
@@ -4132,7 +4132,7 @@
         <v>25</v>
       </c>
       <c r="O30" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P30" s="38">
         <v>0.1351</v>
@@ -4191,7 +4191,7 @@
         <v>30</v>
       </c>
       <c r="O31" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P31" s="52">
         <v>4.7500000000000001E-2</v>
@@ -4250,7 +4250,7 @@
         <v>10</v>
       </c>
       <c r="O32" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P32" s="38">
         <v>0.2286</v>
@@ -4309,7 +4309,7 @@
         <v>6</v>
       </c>
       <c r="O33" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P33" s="52">
         <v>1.1482000000000001</v>
@@ -4368,7 +4368,7 @@
         <v>30</v>
       </c>
       <c r="O34" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P34" s="38">
         <v>5.6099999999999997E-2</v>
@@ -4408,7 +4408,7 @@
         <v>283</v>
       </c>
       <c r="I35" s="61" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J35" s="51" t="s">
         <v>342</v>
@@ -4427,7 +4427,7 @@
         <v>10</v>
       </c>
       <c r="O35" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P35" s="52">
         <v>8.8300000000000003E-2</v>
@@ -4458,7 +4458,7 @@
         <v>124</v>
       </c>
       <c r="F36" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G36" s="37" t="s">
         <v>190</v>
@@ -4486,7 +4486,7 @@
         <v>45</v>
       </c>
       <c r="O36" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P36" s="38">
         <v>0.2316</v>
@@ -4517,7 +4517,7 @@
         <v>125</v>
       </c>
       <c r="F37" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G37" s="51" t="s">
         <v>239</v>
@@ -4545,7 +4545,7 @@
         <v>10</v>
       </c>
       <c r="O37" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P37" s="52">
         <v>0.21590000000000001</v>
@@ -4576,7 +4576,7 @@
         <v>126</v>
       </c>
       <c r="F38" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G38" s="37" t="s">
         <v>191</v>
@@ -4604,7 +4604,7 @@
         <v>25</v>
       </c>
       <c r="O38" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P38" s="38">
         <v>0.17299999999999999</v>
@@ -4626,28 +4626,28 @@
         <v>30</v>
       </c>
       <c r="C39" s="54" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D39" s="68" t="s">
         <v>56</v>
       </c>
       <c r="E39" s="51" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="F39" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G39" s="51" t="s">
+        <v>487</v>
+      </c>
+      <c r="H39" s="51" t="s">
         <v>491</v>
       </c>
-      <c r="H39" s="51" t="s">
-        <v>495</v>
-      </c>
       <c r="I39" s="51" t="s">
         <v>429</v>
       </c>
       <c r="J39" s="51" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="K39" s="51" t="s">
         <v>429</v>
@@ -4663,7 +4663,7 @@
         <v>10</v>
       </c>
       <c r="O39" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P39" s="52">
         <v>0.14860000000000001</v>
@@ -4694,7 +4694,7 @@
         <v>127</v>
       </c>
       <c r="F40" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G40" s="37" t="s">
         <v>240</v>
@@ -4722,7 +4722,7 @@
         <v>12</v>
       </c>
       <c r="O40" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P40" s="38">
         <v>7.0400000000000004E-2</v>
@@ -4744,30 +4744,28 @@
         <v>32</v>
       </c>
       <c r="C41" s="54" t="s">
-        <v>430</v>
+        <v>502</v>
       </c>
       <c r="D41" s="51" t="s">
         <v>58</v>
       </c>
       <c r="E41" s="51" t="s">
-        <v>454</v>
+        <v>503</v>
       </c>
       <c r="F41" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G41" s="51" t="s">
-        <v>455</v>
+        <v>504</v>
       </c>
       <c r="H41" s="51" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I41" s="51"/>
       <c r="J41" s="51" t="s">
-        <v>457</v>
-      </c>
-      <c r="K41" s="51" t="s">
-        <v>429</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="K41" s="51"/>
       <c r="L41" s="51">
         <v>1</v>
       </c>
@@ -4775,18 +4773,12 @@
         <f t="shared" ref="M41" si="31">L41*5</f>
         <v>5</v>
       </c>
-      <c r="N41" s="51">
-        <v>6</v>
-      </c>
-      <c r="O41" s="60" t="s">
-        <v>436</v>
-      </c>
-      <c r="P41" s="52">
-        <v>0.91159999999999997</v>
-      </c>
+      <c r="N41" s="51"/>
+      <c r="O41" s="51"/>
+      <c r="P41" s="52"/>
       <c r="Q41" s="52">
         <f t="shared" ref="Q41" si="32">P41*N41</f>
-        <v>5.4695999999999998</v>
+        <v>0</v>
       </c>
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
@@ -4810,7 +4802,7 @@
         <v>128</v>
       </c>
       <c r="F42" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G42" s="37" t="s">
         <v>192</v>
@@ -4838,7 +4830,7 @@
         <v>11</v>
       </c>
       <c r="O42" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P42" s="38">
         <v>0.81459999999999999</v>
@@ -4866,16 +4858,16 @@
         <v>60</v>
       </c>
       <c r="E43" s="51" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="F43" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G43" s="51" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="H43" s="51" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="I43" s="51" t="s">
         <v>429</v>
@@ -4897,7 +4889,7 @@
         <v>16</v>
       </c>
       <c r="O43" s="60" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="P43" s="52">
         <v>1.01</v>
@@ -4928,7 +4920,7 @@
         <v>129</v>
       </c>
       <c r="F44" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G44" s="37" t="s">
         <v>193</v>
@@ -4956,7 +4948,7 @@
         <v>10</v>
       </c>
       <c r="O44" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P44" s="38">
         <v>0.2137</v>
@@ -5015,7 +5007,7 @@
         <v>50</v>
       </c>
       <c r="O45" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P45" s="52">
         <v>8.3000000000000001E-3</v>
@@ -5074,7 +5066,7 @@
         <v>20</v>
       </c>
       <c r="O46" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P46" s="38">
         <v>5.7599999999999998E-2</v>
@@ -5114,7 +5106,7 @@
         <v>306</v>
       </c>
       <c r="I47" s="61" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J47" s="51" t="s">
         <v>350</v>
@@ -5133,7 +5125,7 @@
         <v>10</v>
       </c>
       <c r="O47" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P47" s="52">
         <v>5.1499999999999997E-2</v>
@@ -5155,16 +5147,16 @@
         <v>39</v>
       </c>
       <c r="C48" s="53" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D48" s="62" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E48" s="62" t="s">
         <v>133</v>
       </c>
       <c r="F48" s="62" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G48" s="62" t="s">
         <v>197</v>
@@ -5201,7 +5193,7 @@
         <v>429</v>
       </c>
       <c r="R48" s="63" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="S48" s="59"/>
       <c r="Y48" s="71"/>
@@ -5215,7 +5207,7 @@
         <v>40</v>
       </c>
       <c r="C49" s="54" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D49" s="51" t="s">
         <v>65</v>
@@ -5250,7 +5242,7 @@
         <v>20</v>
       </c>
       <c r="O49" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P49" s="52">
         <v>2.1000000000000001E-2</v>
@@ -5290,10 +5282,10 @@
         <v>308</v>
       </c>
       <c r="I50" s="37" t="s">
+        <v>444</v>
+      </c>
+      <c r="J50" s="37" t="s">
         <v>445</v>
-      </c>
-      <c r="J50" s="37" t="s">
-        <v>446</v>
       </c>
       <c r="K50" s="37" t="s">
         <v>397</v>
@@ -5309,7 +5301,7 @@
         <v>20</v>
       </c>
       <c r="O50" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P50" s="38">
         <v>2.1700000000000001E-2</v>
@@ -5340,7 +5332,7 @@
         <v>136</v>
       </c>
       <c r="F51" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G51" s="51" t="s">
         <v>200</v>
@@ -5355,7 +5347,7 @@
         <v>352</v>
       </c>
       <c r="K51" s="51" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="L51" s="51">
         <v>1</v>
@@ -5368,7 +5360,7 @@
         <v>10</v>
       </c>
       <c r="O51" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P51" s="52" t="s">
         <v>429</v>
@@ -5377,7 +5369,7 @@
         <v>429</v>
       </c>
       <c r="R51" s="63" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="S51" s="59"/>
       <c r="Y51"/>
@@ -5428,7 +5420,7 @@
         <v>100</v>
       </c>
       <c r="O52" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P52" s="38">
         <v>2.5999999999999999E-3</v>
@@ -5453,7 +5445,7 @@
         <v>20</v>
       </c>
       <c r="D53" s="51" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E53" s="51" t="s">
         <v>138</v>
@@ -5487,7 +5479,7 @@
         <v>100</v>
       </c>
       <c r="O53" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P53" s="52">
         <v>8.9999999999999998E-4</v>
@@ -5512,7 +5504,7 @@
         <v>20</v>
       </c>
       <c r="D54" s="67" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="E54" s="37" t="s">
         <v>139</v>
@@ -5527,10 +5519,10 @@
         <v>282</v>
       </c>
       <c r="I54" s="37" t="s">
+        <v>446</v>
+      </c>
+      <c r="J54" s="37" t="s">
         <v>447</v>
-      </c>
-      <c r="J54" s="37" t="s">
-        <v>448</v>
       </c>
       <c r="K54" s="37" t="s">
         <v>400</v>
@@ -5546,7 +5538,7 @@
         <v>100</v>
       </c>
       <c r="O54" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P54" s="38">
         <v>8.9999999999999998E-4</v>
@@ -5605,7 +5597,7 @@
         <v>100</v>
       </c>
       <c r="O55" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P55" s="52">
         <v>1E-3</v>
@@ -5664,7 +5656,7 @@
         <v>100</v>
       </c>
       <c r="O56" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P56" s="38">
         <v>8.0000000000000004E-4</v>
@@ -5689,7 +5681,7 @@
         <v>20</v>
       </c>
       <c r="D57" s="51" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="E57" s="51" t="s">
         <v>142</v>
@@ -5704,10 +5696,10 @@
         <v>282</v>
       </c>
       <c r="I57" s="51" t="s">
+        <v>448</v>
+      </c>
+      <c r="J57" s="51" t="s">
         <v>449</v>
-      </c>
-      <c r="J57" s="51" t="s">
-        <v>450</v>
       </c>
       <c r="K57" s="51" t="s">
         <v>403</v>
@@ -5723,7 +5715,7 @@
         <v>100</v>
       </c>
       <c r="O57" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P57" s="52">
         <v>5.0000000000000001E-4</v>
@@ -5782,7 +5774,7 @@
         <v>100</v>
       </c>
       <c r="O58" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P58" s="38">
         <v>6.9999999999999999E-4</v>
@@ -5841,7 +5833,7 @@
         <v>200</v>
       </c>
       <c r="O59" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P59" s="52">
         <v>6.9999999999999999E-4</v>
@@ -5900,7 +5892,7 @@
         <v>100</v>
       </c>
       <c r="O60" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P60" s="38">
         <v>5.9999999999999995E-4</v>
@@ -5925,7 +5917,7 @@
         <v>20</v>
       </c>
       <c r="D61" s="51" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E61" s="37" t="s">
         <v>150</v>
@@ -5959,7 +5951,7 @@
         <v>100</v>
       </c>
       <c r="O61" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P61" s="38">
         <v>6.9999999999999999E-4</v>
@@ -5981,19 +5973,19 @@
         <v>53</v>
       </c>
       <c r="C62" s="54" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D62" s="67" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E62" s="37" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G62" s="37" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="H62" s="37" t="s">
         <v>282</v>
@@ -6002,7 +5994,7 @@
         <v>429</v>
       </c>
       <c r="J62" s="37" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="K62" s="37" t="s">
         <v>402</v>
@@ -6018,7 +6010,7 @@
         <v>100</v>
       </c>
       <c r="O62" s="73" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P62" s="38">
         <v>6.8999999999999999E-3</v>
@@ -6078,7 +6070,7 @@
         <v>100</v>
       </c>
       <c r="O63" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P63" s="38">
         <v>6.9999999999999999E-4</v>
@@ -6137,7 +6129,7 @@
         <v>100</v>
       </c>
       <c r="O64" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P64" s="52">
         <v>1.1999999999999999E-3</v>
@@ -6196,7 +6188,7 @@
         <v>100</v>
       </c>
       <c r="O65" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P65" s="38">
         <v>2.5000000000000001E-3</v>
@@ -6239,7 +6231,7 @@
         <v>429</v>
       </c>
       <c r="J66" s="51" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K66" s="51" t="s">
         <v>411</v>
@@ -6255,7 +6247,7 @@
         <v>20</v>
       </c>
       <c r="O66" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P66" s="52">
         <v>2.5999999999999999E-2</v>
@@ -6295,10 +6287,10 @@
         <v>311</v>
       </c>
       <c r="I67" s="51" t="s">
+        <v>450</v>
+      </c>
+      <c r="J67" s="51" t="s">
         <v>451</v>
-      </c>
-      <c r="J67" s="51" t="s">
-        <v>452</v>
       </c>
       <c r="K67" s="51" t="s">
         <v>412</v>
@@ -6314,7 +6306,7 @@
         <v>100</v>
       </c>
       <c r="O67" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P67" s="52">
         <v>4.0000000000000002E-4</v>
@@ -6371,7 +6363,7 @@
         <v>100</v>
       </c>
       <c r="O68" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P68" s="38">
         <v>1.1999999999999999E-3</v>
@@ -6428,7 +6420,7 @@
         <v>10</v>
       </c>
       <c r="O69" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P69" s="52">
         <v>5.3600000000000002E-2</v>
@@ -6485,7 +6477,7 @@
         <v>100</v>
       </c>
       <c r="O70" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P70" s="38">
         <v>1.1999999999999999E-3</v>
@@ -6542,7 +6534,7 @@
         <v>100</v>
       </c>
       <c r="O71" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P71" s="52">
         <v>6.9999999999999999E-4</v>
@@ -6564,19 +6556,19 @@
         <v>63</v>
       </c>
       <c r="C72" s="54" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D72" s="67" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E72" s="51" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="F72" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G72" s="51" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="H72" s="51" t="s">
         <v>282</v>
@@ -6585,7 +6577,7 @@
         <v>429</v>
       </c>
       <c r="J72" s="51" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="K72" s="51" t="s">
         <v>399</v>
@@ -6601,7 +6593,7 @@
         <v>50</v>
       </c>
       <c r="O72" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P72" s="52">
         <v>8.6999999999999994E-3</v>
@@ -6626,13 +6618,13 @@
         <v>22</v>
       </c>
       <c r="D73" s="64" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="E73" s="64" t="s">
         <v>156</v>
       </c>
       <c r="F73" s="65" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G73" s="64" t="s">
         <v>203</v>
@@ -6669,7 +6661,7 @@
         <v>429</v>
       </c>
       <c r="R73" s="63" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="S73" s="59"/>
       <c r="Y73"/>
@@ -6692,7 +6684,7 @@
         <v>157</v>
       </c>
       <c r="F74" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G74" s="51" t="s">
         <v>204</v>
@@ -6704,7 +6696,7 @@
         <v>429</v>
       </c>
       <c r="J74" s="51" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K74" s="51" t="s">
         <v>429</v>
@@ -6720,7 +6712,7 @@
         <v>10</v>
       </c>
       <c r="O74" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P74" s="52">
         <v>0.1275</v>
@@ -6779,7 +6771,7 @@
         <v>6</v>
       </c>
       <c r="O75" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P75" s="38">
         <v>0.82569999999999999</v>
@@ -6838,7 +6830,7 @@
         <v>6</v>
       </c>
       <c r="O76" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P76" s="52">
         <v>0.70009999999999994</v>
@@ -6897,7 +6889,7 @@
         <v>10</v>
       </c>
       <c r="O77" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P77" s="38">
         <v>0.32279999999999998</v>
@@ -6956,7 +6948,7 @@
         <v>6</v>
       </c>
       <c r="O78" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P78" s="52">
         <v>1.3062</v>
@@ -7013,7 +7005,7 @@
         <v>6</v>
       </c>
       <c r="O79" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P79" s="38">
         <v>0.3644</v>
@@ -7072,7 +7064,7 @@
         <v>6</v>
       </c>
       <c r="O80" s="60" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P80" s="52">
         <v>2.5099999999999998</v>
@@ -7131,7 +7123,7 @@
         <v>6</v>
       </c>
       <c r="O81" s="60" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P81" s="38">
         <v>3.4329999999999998</v>
@@ -7188,7 +7180,7 @@
         <v>6</v>
       </c>
       <c r="O82" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P82" s="52">
         <v>4.6247999999999996</v>
@@ -7247,7 +7239,7 @@
         <v>6</v>
       </c>
       <c r="O83" s="60" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P83" s="38">
         <v>7.9</v>
@@ -7306,7 +7298,7 @@
         <v>16</v>
       </c>
       <c r="O84" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P84" s="52">
         <v>1.7437</v>
@@ -7365,7 +7357,7 @@
         <v>10</v>
       </c>
       <c r="O85" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P85" s="38">
         <v>7.7799999999999994E-2</v>
@@ -7424,7 +7416,7 @@
         <v>6</v>
       </c>
       <c r="O86" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P86" s="52">
         <v>0.77800000000000002</v>
@@ -7483,7 +7475,7 @@
         <v>6</v>
       </c>
       <c r="O87" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P87" s="38">
         <v>0.41049999999999998</v>
@@ -7542,7 +7534,7 @@
         <v>6</v>
       </c>
       <c r="O88" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P88" s="52">
         <v>1.1837</v>
@@ -7601,7 +7593,7 @@
         <v>6</v>
       </c>
       <c r="O89" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P89" s="38">
         <v>1.2107000000000001</v>
@@ -7632,7 +7624,7 @@
         <v>172</v>
       </c>
       <c r="F90" s="51" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G90" s="51" t="s">
         <v>280</v>
@@ -7660,7 +7652,7 @@
         <v>10</v>
       </c>
       <c r="O90" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P90" s="52">
         <v>0.08</v>
@@ -7688,22 +7680,22 @@
         <v>100</v>
       </c>
       <c r="E91" s="37" t="s">
+        <v>465</v>
+      </c>
+      <c r="F91" s="37" t="s">
+        <v>466</v>
+      </c>
+      <c r="G91" s="37" t="s">
+        <v>467</v>
+      </c>
+      <c r="H91" s="37" t="s">
+        <v>468</v>
+      </c>
+      <c r="I91" s="37" t="s">
+        <v>429</v>
+      </c>
+      <c r="J91" s="37" t="s">
         <v>469</v>
-      </c>
-      <c r="F91" s="37" t="s">
-        <v>470</v>
-      </c>
-      <c r="G91" s="37" t="s">
-        <v>471</v>
-      </c>
-      <c r="H91" s="37" t="s">
-        <v>472</v>
-      </c>
-      <c r="I91" s="37" t="s">
-        <v>429</v>
-      </c>
-      <c r="J91" s="37" t="s">
-        <v>473</v>
       </c>
       <c r="K91" s="37" t="s">
         <v>418</v>
@@ -7719,7 +7711,7 @@
         <v>10</v>
       </c>
       <c r="O91" s="60" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P91" s="38">
         <v>0.1065</v>
@@ -7734,61 +7726,61 @@
       <c r="Z91"/>
       <c r="AA91"/>
     </row>
-    <row r="92" spans="1:27" s="91" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="84"/>
-      <c r="B92" s="85">
+    <row r="92" spans="1:27" s="81" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="74"/>
+      <c r="B92" s="75">
         <f>ROW(B92) - ROW($B$9)</f>
         <v>83</v>
       </c>
-      <c r="C92" s="86" t="s">
+      <c r="C92" s="76" t="s">
+        <v>497</v>
+      </c>
+      <c r="D92" s="77" t="s">
+        <v>429</v>
+      </c>
+      <c r="E92" s="77" t="s">
         <v>501</v>
       </c>
-      <c r="D92" s="87" t="s">
-        <v>429</v>
-      </c>
-      <c r="E92" s="87" t="s">
-        <v>505</v>
-      </c>
-      <c r="F92" s="87" t="s">
-        <v>429</v>
-      </c>
-      <c r="G92" s="87" t="s">
-        <v>503</v>
-      </c>
-      <c r="H92" s="87" t="s">
-        <v>502</v>
-      </c>
-      <c r="I92" s="87" t="s">
-        <v>429</v>
-      </c>
-      <c r="J92" s="87" t="s">
-        <v>504</v>
-      </c>
-      <c r="K92" s="87" t="s">
-        <v>429</v>
-      </c>
-      <c r="L92" s="87">
+      <c r="F92" s="77" t="s">
+        <v>429</v>
+      </c>
+      <c r="G92" s="77" t="s">
+        <v>499</v>
+      </c>
+      <c r="H92" s="77" t="s">
+        <v>498</v>
+      </c>
+      <c r="I92" s="77" t="s">
+        <v>429</v>
+      </c>
+      <c r="J92" s="77" t="s">
+        <v>500</v>
+      </c>
+      <c r="K92" s="77" t="s">
+        <v>429</v>
+      </c>
+      <c r="L92" s="77">
         <v>1</v>
       </c>
-      <c r="M92" s="87">
+      <c r="M92" s="77">
         <f>L92*5</f>
         <v>5</v>
       </c>
-      <c r="N92" s="87">
+      <c r="N92" s="77">
         <v>5</v>
       </c>
-      <c r="O92" s="88" t="s">
-        <v>436</v>
-      </c>
-      <c r="P92" s="89">
+      <c r="O92" s="78" t="s">
+        <v>435</v>
+      </c>
+      <c r="P92" s="79">
         <v>1.1609</v>
       </c>
-      <c r="Q92" s="89">
+      <c r="Q92" s="79">
         <f>P92*N92</f>
         <v>5.8045</v>
       </c>
-      <c r="R92" s="87"/>
-      <c r="S92" s="90"/>
+      <c r="R92" s="77"/>
+      <c r="S92" s="80"/>
     </row>
     <row r="93" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
@@ -7804,17 +7796,17 @@
       <c r="K93" s="45"/>
       <c r="L93" s="45"/>
       <c r="M93" s="45"/>
-      <c r="N93" s="82" t="s">
+      <c r="N93" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="O93" s="83"/>
-      <c r="P93" s="83"/>
+      <c r="O93" s="91"/>
+      <c r="P93" s="91"/>
       <c r="Q93" s="48">
         <f>SUM(Q10:Q92)</f>
-        <v>295.81410000000005</v>
-      </c>
-      <c r="R93" s="78"/>
-      <c r="S93" s="79"/>
+        <v>290.3445000000001</v>
+      </c>
+      <c r="R93" s="86"/>
+      <c r="S93" s="87"/>
       <c r="U93" s="70"/>
       <c r="V93" s="70"/>
       <c r="W93" s="70"/>
@@ -7834,17 +7826,17 @@
       <c r="K94" s="10"/>
       <c r="L94" s="10"/>
       <c r="M94" s="10"/>
-      <c r="N94" s="82" t="s">
+      <c r="N94" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="O94" s="83"/>
-      <c r="P94" s="83"/>
+      <c r="O94" s="91"/>
+      <c r="P94" s="91"/>
       <c r="Q94" s="49">
         <f>Q93/5</f>
-        <v>59.162820000000011</v>
-      </c>
-      <c r="R94" s="80"/>
-      <c r="S94" s="81"/>
+        <v>58.068900000000021</v>
+      </c>
+      <c r="R94" s="88"/>
+      <c r="S94" s="89"/>
       <c r="U94" s="70"/>
       <c r="V94" s="70"/>
       <c r="W94" s="70"/>
@@ -7862,7 +7854,7 @@
     <hyperlink ref="O43" r:id="rId1"/>
     <hyperlink ref="O72" r:id="rId2"/>
     <hyperlink ref="O91" r:id="rId3"/>
-    <hyperlink ref="O41" r:id="rId4"/>
+    <hyperlink ref="O41" r:id="rId4" display="LCSC"/>
     <hyperlink ref="O18" r:id="rId5"/>
     <hyperlink ref="O16" r:id="rId6"/>
     <hyperlink ref="O83" r:id="rId7"/>

--- a/Design Files/Baseboard-v2.0/BOM/eSpark_BOM_Baseboard-v2.0.xlsx
+++ b/Design Files/Baseboard-v2.0/BOM/eSpark_BOM_Baseboard-v2.0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5182" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5194" uniqueCount="527">
   <si>
     <t>Component list</t>
   </si>
@@ -2107,7 +2107,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2326,6 +2326,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2358,25 +2379,10 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3027,15 +3033,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="83"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="89"/>
+      <c r="Q1" s="89"/>
+      <c r="R1" s="89"/>
+      <c r="S1" s="90"/>
     </row>
     <row r="2" spans="1:27" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -3085,7 +3091,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="84"/>
+      <c r="S3" s="91"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -3110,7 +3116,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="85"/>
+      <c r="S4" s="92"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -3135,7 +3141,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="85"/>
+      <c r="S5" s="92"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -3156,7 +3162,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="85"/>
+      <c r="S6" s="92"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -3177,7 +3183,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="85"/>
+      <c r="S7" s="92"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -3198,7 +3204,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="85"/>
+      <c r="S8" s="92"/>
     </row>
     <row r="9" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -8155,17 +8161,17 @@
       <c r="K93" s="45"/>
       <c r="L93" s="45"/>
       <c r="M93" s="45"/>
-      <c r="N93" s="90" t="s">
+      <c r="N93" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="O93" s="91"/>
-      <c r="P93" s="91"/>
+      <c r="O93" s="98"/>
+      <c r="P93" s="98"/>
       <c r="Q93" s="48">
         <f>SUM(Q10:Q92)</f>
         <v>290.3445000000001</v>
       </c>
-      <c r="R93" s="86"/>
-      <c r="S93" s="87"/>
+      <c r="R93" s="93"/>
+      <c r="S93" s="94"/>
       <c r="U93" s="70"/>
       <c r="V93" s="70"/>
       <c r="W93" s="70"/>
@@ -8185,17 +8191,17 @@
       <c r="K94" s="10"/>
       <c r="L94" s="10"/>
       <c r="M94" s="10"/>
-      <c r="N94" s="90" t="s">
+      <c r="N94" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="O94" s="91"/>
-      <c r="P94" s="91"/>
+      <c r="O94" s="98"/>
+      <c r="P94" s="98"/>
       <c r="Q94" s="49">
         <f>Q93/5</f>
         <v>58.068900000000021</v>
       </c>
-      <c r="R94" s="88"/>
-      <c r="S94" s="89"/>
+      <c r="R94" s="95"/>
+      <c r="S94" s="96"/>
       <c r="U94" s="70"/>
       <c r="V94" s="70"/>
       <c r="W94" s="70"/>
@@ -8333,15 +8339,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="83"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="89"/>
+      <c r="Q1" s="89"/>
+      <c r="R1" s="89"/>
+      <c r="S1" s="90"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -8391,7 +8397,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="84"/>
+      <c r="S3" s="91"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -8416,7 +8422,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="85"/>
+      <c r="S4" s="92"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -8441,7 +8447,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="85"/>
+      <c r="S5" s="92"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -8462,7 +8468,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="85"/>
+      <c r="S6" s="92"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -8483,7 +8489,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="85"/>
+      <c r="S7" s="92"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -8504,7 +8510,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="85"/>
+      <c r="S8" s="92"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -8618,7 +8624,7 @@
       <c r="R10" s="63" t="s">
         <v>439</v>
       </c>
-      <c r="S10" s="92"/>
+      <c r="S10" s="82"/>
     </row>
     <row r="11" spans="1:19" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="69"/>
@@ -9832,7 +9838,7 @@
       <c r="L32" s="77">
         <v>1</v>
       </c>
-      <c r="M32" s="93">
+      <c r="M32" s="83">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
@@ -9850,7 +9856,7 @@
         <v>5.7149999999999999</v>
       </c>
       <c r="R32" s="77"/>
-      <c r="S32" s="94"/>
+      <c r="S32" s="84"/>
     </row>
     <row r="33" spans="1:19" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A33" s="69"/>
@@ -12032,59 +12038,59 @@
     </row>
     <row r="72" spans="1:19" s="81" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="74"/>
-      <c r="B72" s="95">
+      <c r="B72" s="85">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="C72" s="96" t="s">
+      <c r="C72" s="86" t="s">
         <v>473</v>
       </c>
-      <c r="D72" s="93" t="s">
+      <c r="D72" s="83" t="s">
         <v>484</v>
       </c>
-      <c r="E72" s="97" t="s">
+      <c r="E72" s="87" t="s">
         <v>474</v>
       </c>
-      <c r="F72" s="97" t="s">
+      <c r="F72" s="87" t="s">
         <v>434</v>
       </c>
-      <c r="G72" s="97" t="s">
+      <c r="G72" s="87" t="s">
         <v>475</v>
       </c>
-      <c r="H72" s="97" t="s">
+      <c r="H72" s="87" t="s">
         <v>282</v>
       </c>
-      <c r="I72" s="97" t="s">
-        <v>429</v>
-      </c>
-      <c r="J72" s="97" t="s">
+      <c r="I72" s="87" t="s">
+        <v>429</v>
+      </c>
+      <c r="J72" s="87" t="s">
         <v>476</v>
       </c>
-      <c r="K72" s="97" t="s">
+      <c r="K72" s="87" t="s">
         <v>399</v>
       </c>
-      <c r="L72" s="97">
+      <c r="L72" s="87">
         <v>2</v>
       </c>
-      <c r="M72" s="93">
+      <c r="M72" s="83">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="N72" s="97">
+      <c r="N72" s="87">
         <v>50</v>
       </c>
       <c r="O72" s="78" t="s">
         <v>435</v>
       </c>
-      <c r="P72" s="98">
+      <c r="P72" s="88">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="Q72" s="98">
+      <c r="Q72" s="88">
         <f t="shared" si="29"/>
         <v>0.43499999999999994</v>
       </c>
-      <c r="R72" s="97"/>
-      <c r="S72" s="94"/>
+      <c r="R72" s="87"/>
+      <c r="S72" s="84"/>
     </row>
     <row r="73" spans="1:19" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A73" s="69"/>
@@ -12908,17 +12914,17 @@
         <v>20</v>
       </c>
       <c r="N87" s="37">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="O87" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P87" s="38">
-        <v>0.41049999999999998</v>
+        <v>0.33119999999999999</v>
       </c>
       <c r="Q87" s="38">
         <f>P87*N87</f>
-        <v>2.4630000000000001</v>
+        <v>8.2799999999999994</v>
       </c>
       <c r="R87" s="37"/>
       <c r="S87" s="59"/>
@@ -12964,17 +12970,17 @@
         <v>20</v>
       </c>
       <c r="N88" s="51">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="O88" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P88" s="52">
-        <v>1.1837</v>
+        <v>1.0347</v>
       </c>
       <c r="Q88" s="52">
         <f t="shared" ref="Q88" si="38">P88*N88</f>
-        <v>7.1021999999999998</v>
+        <v>21.7287</v>
       </c>
       <c r="R88" s="51"/>
       <c r="S88" s="59"/>
@@ -13020,17 +13026,17 @@
         <v>20</v>
       </c>
       <c r="N89" s="37">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="O89" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P89" s="38">
-        <v>1.2107000000000001</v>
+        <v>1.0676000000000001</v>
       </c>
       <c r="Q89" s="38">
         <f>P89*N89</f>
-        <v>7.2642000000000007</v>
+        <v>22.419600000000003</v>
       </c>
       <c r="R89" s="37"/>
       <c r="S89" s="59"/>
@@ -13076,17 +13082,17 @@
         <v>20</v>
       </c>
       <c r="N90" s="51">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="O90" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P90" s="52">
-        <v>0.08</v>
+        <v>8.0699999999999994E-2</v>
       </c>
       <c r="Q90" s="52">
         <f t="shared" ref="Q90" si="39">P90*N90</f>
-        <v>0.8</v>
+        <v>2.0175000000000001</v>
       </c>
       <c r="R90" s="51"/>
       <c r="S90" s="59"/>
@@ -13132,17 +13138,17 @@
         <v>20</v>
       </c>
       <c r="N91" s="37">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="O91" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P91" s="38">
-        <v>0.1065</v>
+        <v>9.4600000000000004E-2</v>
       </c>
       <c r="Q91" s="38">
         <f>P91*N91</f>
-        <v>1.0649999999999999</v>
+        <v>2.3650000000000002</v>
       </c>
       <c r="R91" s="37"/>
       <c r="S91" s="39"/>
@@ -13188,17 +13194,17 @@
         <v>20</v>
       </c>
       <c r="N92" s="37">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="O92" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P92" s="38">
-        <v>1.1609</v>
+        <v>1.0323</v>
       </c>
       <c r="Q92" s="38">
         <f>P92*N92</f>
-        <v>5.8045</v>
+        <v>20.646000000000001</v>
       </c>
       <c r="R92" s="37"/>
       <c r="S92" s="39"/>
@@ -13217,17 +13223,17 @@
       <c r="K93" s="45"/>
       <c r="L93" s="45"/>
       <c r="M93" s="45"/>
-      <c r="N93" s="90" t="s">
+      <c r="N93" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="O93" s="91"/>
-      <c r="P93" s="91"/>
+      <c r="O93" s="98"/>
+      <c r="P93" s="98"/>
       <c r="Q93" s="48">
         <f>SUM(Q10:Q92)</f>
-        <v>868.12909999999999</v>
-      </c>
-      <c r="R93" s="86"/>
-      <c r="S93" s="87"/>
+        <v>921.0870000000001</v>
+      </c>
+      <c r="R93" s="93"/>
+      <c r="S93" s="94"/>
     </row>
     <row r="94" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
@@ -13243,17 +13249,17 @@
       <c r="K94" s="10"/>
       <c r="L94" s="10"/>
       <c r="M94" s="10"/>
-      <c r="N94" s="90" t="s">
+      <c r="N94" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="O94" s="91"/>
-      <c r="P94" s="91"/>
+      <c r="O94" s="98"/>
+      <c r="P94" s="98"/>
       <c r="Q94" s="49">
         <f>Q93/20</f>
-        <v>43.406455000000001</v>
-      </c>
-      <c r="R94" s="88"/>
-      <c r="S94" s="89"/>
+        <v>46.054350000000007</v>
+      </c>
+      <c r="R94" s="95"/>
+      <c r="S94" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -13357,7 +13363,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.5703125" customWidth="1"/>
@@ -13386,15 +13392,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="83"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="89"/>
+      <c r="Q1" s="89"/>
+      <c r="R1" s="89"/>
+      <c r="S1" s="90"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -13444,7 +13450,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="84"/>
+      <c r="S3" s="91"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -13469,7 +13475,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="85"/>
+      <c r="S4" s="92"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -13494,7 +13500,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="85"/>
+      <c r="S5" s="92"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -13515,7 +13521,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="85"/>
+      <c r="S6" s="92"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -13536,7 +13542,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="85"/>
+      <c r="S7" s="92"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -13557,7 +13563,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="85"/>
+      <c r="S8" s="92"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -13671,7 +13677,7 @@
       <c r="R10" s="63" t="s">
         <v>439</v>
       </c>
-      <c r="S10" s="92"/>
+      <c r="S10" s="82"/>
     </row>
     <row r="11" spans="1:19" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="69"/>
@@ -13714,7 +13720,7 @@
         <v>50</v>
       </c>
       <c r="N11" s="51">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="O11" s="60" t="s">
         <v>435</v>
@@ -13724,7 +13730,7 @@
       </c>
       <c r="Q11" s="52">
         <f t="shared" ref="Q11" si="1">P11*N11</f>
-        <v>0.40200000000000002</v>
+        <v>1.206</v>
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
@@ -13770,17 +13776,17 @@
         <v>1250</v>
       </c>
       <c r="N12" s="37">
-        <v>150</v>
+        <v>1300</v>
       </c>
       <c r="O12" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P12" s="38">
-        <v>1.0500000000000001E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="Q12" s="38">
         <f>P12*N12</f>
-        <v>1.5750000000000002</v>
+        <v>11.7</v>
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="59"/>
@@ -13826,7 +13832,7 @@
         <v>150</v>
       </c>
       <c r="N13" s="51">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O13" s="60" t="s">
         <v>435</v>
@@ -13836,7 +13842,7 @@
       </c>
       <c r="Q13" s="52">
         <f t="shared" ref="Q13" si="3">P13*N13</f>
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
@@ -13882,17 +13888,17 @@
         <v>150</v>
       </c>
       <c r="N14" s="37">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="O14" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P14" s="38">
-        <v>4.9099999999999998E-2</v>
+        <v>4.4299999999999999E-2</v>
       </c>
       <c r="Q14" s="38">
         <f>P14*N14</f>
-        <v>0.98199999999999998</v>
+        <v>7.0880000000000001</v>
       </c>
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
@@ -13938,17 +13944,17 @@
         <v>100</v>
       </c>
       <c r="N15" s="51">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="O15" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P15" s="52">
-        <v>0.25940000000000002</v>
+        <v>0.24660000000000001</v>
       </c>
       <c r="Q15" s="52">
         <f t="shared" ref="Q15" si="4">P15*N15</f>
-        <v>2.8534000000000002</v>
+        <v>24.906600000000001</v>
       </c>
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
@@ -13994,17 +14000,17 @@
         <v>50</v>
       </c>
       <c r="N16" s="37">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="O16" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P16" s="38">
-        <v>7.0900000000000005E-2</v>
+        <v>6.3799999999999996E-2</v>
       </c>
       <c r="Q16" s="38">
         <f>P16*N16</f>
-        <v>1.0635000000000001</v>
+        <v>3.5089999999999999</v>
       </c>
       <c r="R16" s="37"/>
       <c r="S16" s="59"/>
@@ -14050,17 +14056,17 @@
         <v>50</v>
       </c>
       <c r="N17" s="51">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="O17" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P17" s="52">
-        <v>6.3E-2</v>
+        <v>4.41E-2</v>
       </c>
       <c r="Q17" s="52">
         <f t="shared" ref="Q17" si="5">P17*N17</f>
-        <v>0.63</v>
+        <v>2.4255</v>
       </c>
       <c r="R17" s="51"/>
       <c r="S17" s="59"/>
@@ -14106,17 +14112,17 @@
         <v>50</v>
       </c>
       <c r="N18" s="37">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="O18" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P18" s="38">
-        <v>1.7373000000000001</v>
+        <v>1.478</v>
       </c>
       <c r="Q18" s="38">
         <f>P18*N18</f>
-        <v>10.4238</v>
+        <v>75.378</v>
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
@@ -14162,17 +14168,17 @@
         <v>50</v>
       </c>
       <c r="N19" s="51">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="O19" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P19" s="52">
-        <v>0.26129999999999998</v>
+        <v>0.2016</v>
       </c>
       <c r="Q19" s="52">
         <f t="shared" ref="Q19" si="6">P19*N19</f>
-        <v>2.6129999999999995</v>
+        <v>11.088000000000001</v>
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
@@ -14218,17 +14224,17 @@
         <v>200</v>
       </c>
       <c r="N20" s="37">
-        <v>30</v>
+        <v>220</v>
       </c>
       <c r="O20" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P20" s="38">
-        <v>4.2000000000000003E-2</v>
+        <v>2.92E-2</v>
       </c>
       <c r="Q20" s="38">
         <f>P20*N20</f>
-        <v>1.26</v>
+        <v>6.4240000000000004</v>
       </c>
       <c r="R20" s="37"/>
       <c r="S20" s="59"/>
@@ -14274,17 +14280,17 @@
         <v>100</v>
       </c>
       <c r="N21" s="51">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="O21" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P21" s="52">
-        <v>1.0800000000000001E-2</v>
+        <v>1.09E-2</v>
       </c>
       <c r="Q21" s="52">
         <f t="shared" ref="Q21" si="7">P21*N21</f>
-        <v>0.54</v>
+        <v>1.635</v>
       </c>
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
@@ -14330,7 +14336,7 @@
         <v>100</v>
       </c>
       <c r="N22" s="37">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O22" s="60" t="s">
         <v>435</v>
@@ -14340,7 +14346,7 @@
       </c>
       <c r="Q22" s="38">
         <f>P22*N22</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="R22" s="37"/>
       <c r="S22" s="59"/>
@@ -14386,7 +14392,7 @@
         <v>150</v>
       </c>
       <c r="N23" s="51">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O23" s="60" t="s">
         <v>435</v>
@@ -14396,7 +14402,7 @@
       </c>
       <c r="Q23" s="52">
         <f t="shared" ref="Q23" si="8">P23*N23</f>
-        <v>0.38999999999999996</v>
+        <v>0.77999999999999992</v>
       </c>
       <c r="R23" s="51"/>
       <c r="S23" s="59"/>
@@ -14442,7 +14448,7 @@
         <v>50</v>
       </c>
       <c r="N24" s="37">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O24" s="60" t="s">
         <v>435</v>
@@ -14452,7 +14458,7 @@
       </c>
       <c r="Q24" s="38">
         <f>P24*N24</f>
-        <v>0.55599999999999994</v>
+        <v>3.3359999999999999</v>
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="59"/>
@@ -14498,17 +14504,17 @@
         <v>50</v>
       </c>
       <c r="N25" s="51">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O25" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P25" s="52">
-        <v>4.4600000000000001E-2</v>
+        <v>4.48E-2</v>
       </c>
       <c r="Q25" s="52">
         <f t="shared" ref="Q25" si="9">P25*N25</f>
-        <v>0.44600000000000001</v>
+        <v>2.6880000000000002</v>
       </c>
       <c r="R25" s="51"/>
       <c r="S25" s="59"/>
@@ -14554,17 +14560,17 @@
         <v>50</v>
       </c>
       <c r="N26" s="37">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="O26" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P26" s="38">
-        <v>0.46939999999999998</v>
+        <v>0.3548</v>
       </c>
       <c r="Q26" s="38">
         <f>P26*N26</f>
-        <v>2.8163999999999998</v>
+        <v>18.094799999999999</v>
       </c>
       <c r="R26" s="37"/>
       <c r="S26" s="59"/>
@@ -14610,17 +14616,17 @@
         <v>50</v>
       </c>
       <c r="N27" s="51">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O27" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P27" s="52">
-        <v>3.56E-2</v>
+        <v>3.4099999999999998E-2</v>
       </c>
       <c r="Q27" s="52">
         <f t="shared" ref="Q27" si="10">P27*N27</f>
-        <v>0.35599999999999998</v>
+        <v>2.0459999999999998</v>
       </c>
       <c r="R27" s="51"/>
       <c r="S27" s="59"/>
@@ -14666,17 +14672,17 @@
         <v>150</v>
       </c>
       <c r="N28" s="37">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="O28" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P28" s="38">
-        <v>2.46E-2</v>
+        <v>2.7400000000000001E-2</v>
       </c>
       <c r="Q28" s="38">
         <f>P28*N28</f>
-        <v>0.49199999999999999</v>
+        <v>4.3840000000000003</v>
       </c>
       <c r="R28" s="37"/>
       <c r="S28" s="59"/>
@@ -14722,17 +14728,17 @@
         <v>100</v>
       </c>
       <c r="N29" s="51">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="O29" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P29" s="52">
-        <v>2.3400000000000001E-2</v>
+        <v>2.1700000000000001E-2</v>
       </c>
       <c r="Q29" s="52">
         <f t="shared" ref="Q29" si="11">P29*N29</f>
-        <v>0.46800000000000003</v>
+        <v>2.6040000000000001</v>
       </c>
       <c r="R29" s="51"/>
       <c r="S29" s="59"/>
@@ -14778,17 +14784,17 @@
         <v>200</v>
       </c>
       <c r="N30" s="37">
-        <v>25</v>
+        <v>205</v>
       </c>
       <c r="O30" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P30" s="38">
-        <v>0.1351</v>
+        <v>9.8599999999999993E-2</v>
       </c>
       <c r="Q30" s="38">
         <f>P30*N30</f>
-        <v>3.3774999999999999</v>
+        <v>20.212999999999997</v>
       </c>
       <c r="R30" s="37"/>
       <c r="S30" s="59"/>
@@ -14834,17 +14840,17 @@
         <v>200</v>
       </c>
       <c r="N31" s="51">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="O31" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P31" s="52">
-        <v>4.7500000000000001E-2</v>
+        <v>3.8399999999999997E-2</v>
       </c>
       <c r="Q31" s="52">
         <f t="shared" ref="Q31" si="12">P31*N31</f>
-        <v>1.425</v>
+        <v>8.0640000000000001</v>
       </c>
       <c r="R31" s="51"/>
       <c r="S31" s="59"/>
@@ -14890,17 +14896,17 @@
         <v>50</v>
       </c>
       <c r="N32" s="37">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="O32" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P32" s="38">
-        <v>0.2286</v>
+        <v>0.18679999999999999</v>
       </c>
       <c r="Q32" s="38">
         <f>P32*N32</f>
-        <v>2.286</v>
+        <v>10.273999999999999</v>
       </c>
       <c r="R32" s="37"/>
       <c r="S32" s="59"/>
@@ -14946,17 +14952,17 @@
         <v>50</v>
       </c>
       <c r="N33" s="51">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="O33" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P33" s="52">
-        <v>1.1482000000000001</v>
+        <v>0.89410000000000001</v>
       </c>
       <c r="Q33" s="52">
         <f t="shared" ref="Q33" si="13">P33*N33</f>
-        <v>6.8892000000000007</v>
+        <v>50.069600000000001</v>
       </c>
       <c r="R33" s="51"/>
       <c r="S33" s="59"/>
@@ -15002,17 +15008,17 @@
         <v>200</v>
       </c>
       <c r="N34" s="37">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="O34" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P34" s="38">
-        <v>5.6099999999999997E-2</v>
+        <v>4.7600000000000003E-2</v>
       </c>
       <c r="Q34" s="38">
         <f>P34*N34</f>
-        <v>1.6829999999999998</v>
+        <v>9.9960000000000004</v>
       </c>
       <c r="R34" s="37"/>
       <c r="S34" s="59"/>
@@ -15058,17 +15064,17 @@
         <v>50</v>
       </c>
       <c r="N35" s="51">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="O35" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P35" s="52">
-        <v>8.8300000000000003E-2</v>
+        <v>7.2900000000000006E-2</v>
       </c>
       <c r="Q35" s="52">
         <f t="shared" ref="Q35" si="14">P35*N35</f>
-        <v>0.88300000000000001</v>
+        <v>4.0095000000000001</v>
       </c>
       <c r="R35" s="51"/>
       <c r="S35" s="59"/>
@@ -15114,17 +15120,17 @@
         <v>400</v>
       </c>
       <c r="N36" s="37">
-        <v>45</v>
+        <v>405</v>
       </c>
       <c r="O36" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P36" s="38">
-        <v>0.2316</v>
+        <v>0.159</v>
       </c>
       <c r="Q36" s="38">
         <f>P36*N36</f>
-        <v>10.422000000000001</v>
+        <v>64.394999999999996</v>
       </c>
       <c r="R36" s="37"/>
       <c r="S36" s="59"/>
@@ -15170,17 +15176,17 @@
         <v>50</v>
       </c>
       <c r="N37" s="51">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O37" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P37" s="52">
-        <v>0.21590000000000001</v>
+        <v>0.17929999999999999</v>
       </c>
       <c r="Q37" s="52">
         <f t="shared" ref="Q37" si="15">P37*N37</f>
-        <v>2.1590000000000003</v>
+        <v>10.757999999999999</v>
       </c>
       <c r="R37" s="51"/>
       <c r="S37" s="59"/>
@@ -15226,17 +15232,17 @@
         <v>200</v>
       </c>
       <c r="N38" s="37">
-        <v>25</v>
+        <v>205</v>
       </c>
       <c r="O38" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P38" s="38">
-        <v>0.17299999999999999</v>
+        <v>0.1149</v>
       </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>4.3249999999999993</v>
+        <v>23.554500000000001</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="59"/>
@@ -15282,17 +15288,17 @@
         <v>50</v>
       </c>
       <c r="N39" s="51">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="O39" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P39" s="52">
-        <v>0.14860000000000001</v>
+        <v>0.11849999999999999</v>
       </c>
       <c r="Q39" s="52">
         <f t="shared" ref="Q39" si="16">P39*N39</f>
-        <v>1.4860000000000002</v>
+        <v>6.5175000000000001</v>
       </c>
       <c r="R39" s="51"/>
       <c r="S39" s="59"/>
@@ -15338,17 +15344,17 @@
         <v>50</v>
       </c>
       <c r="N40" s="37">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="O40" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P40" s="38">
-        <v>7.0400000000000004E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="Q40" s="38">
         <f>P40*N40</f>
-        <v>0.8448</v>
+        <v>4.08</v>
       </c>
       <c r="R40" s="37"/>
       <c r="S40" s="59"/>
@@ -15377,11 +15383,15 @@
       <c r="H41" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="I41" s="51"/>
+      <c r="I41" s="51" t="s">
+        <v>429</v>
+      </c>
       <c r="J41" s="51" t="s">
         <v>505</v>
       </c>
-      <c r="K41" s="51"/>
+      <c r="K41" s="51" t="s">
+        <v>429</v>
+      </c>
       <c r="L41" s="51">
         <v>1</v>
       </c>
@@ -15389,12 +15399,18 @@
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="N41" s="51"/>
-      <c r="O41" s="51"/>
-      <c r="P41" s="52"/>
+      <c r="N41" s="51">
+        <v>51</v>
+      </c>
+      <c r="O41" s="60" t="s">
+        <v>435</v>
+      </c>
+      <c r="P41" s="52">
+        <v>0.53280000000000005</v>
+      </c>
       <c r="Q41" s="52">
         <f t="shared" ref="Q41" si="17">P41*N41</f>
-        <v>0</v>
+        <v>27.172800000000002</v>
       </c>
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
@@ -15440,17 +15456,17 @@
         <v>100</v>
       </c>
       <c r="N42" s="37">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="O42" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P42" s="38">
-        <v>0.81459999999999999</v>
+        <v>0.66510000000000002</v>
       </c>
       <c r="Q42" s="38">
         <f>P42*N42</f>
-        <v>8.9605999999999995</v>
+        <v>67.1751</v>
       </c>
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
@@ -15496,7 +15512,7 @@
         <v>150</v>
       </c>
       <c r="N43" s="51">
-        <v>16</v>
+        <v>151</v>
       </c>
       <c r="O43" s="60" t="s">
         <v>480</v>
@@ -15506,7 +15522,7 @@
       </c>
       <c r="Q43" s="52">
         <f t="shared" ref="Q43" si="18">P43*N43</f>
-        <v>16.16</v>
+        <v>152.51</v>
       </c>
       <c r="R43" s="51"/>
       <c r="S43" s="59"/>
@@ -15552,17 +15568,17 @@
         <v>50</v>
       </c>
       <c r="N44" s="37">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="O44" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P44" s="38">
-        <v>0.2137</v>
+        <v>0.1724</v>
       </c>
       <c r="Q44" s="38">
         <f>P44*N44</f>
-        <v>2.137</v>
+        <v>9.4819999999999993</v>
       </c>
       <c r="R44" s="37"/>
       <c r="S44" s="59"/>
@@ -15608,7 +15624,7 @@
         <v>50</v>
       </c>
       <c r="N45" s="51">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O45" s="60" t="s">
         <v>435</v>
@@ -15618,7 +15634,7 @@
       </c>
       <c r="Q45" s="52">
         <f t="shared" ref="Q45" si="19">P45*N45</f>
-        <v>0.41499999999999998</v>
+        <v>0.83</v>
       </c>
       <c r="R45" s="51"/>
       <c r="S45" s="59"/>
@@ -15664,17 +15680,17 @@
         <v>100</v>
       </c>
       <c r="N46" s="37">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="O46" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P46" s="38">
-        <v>5.7599999999999998E-2</v>
+        <v>4.6300000000000001E-2</v>
       </c>
       <c r="Q46" s="38">
         <f>P46*N46</f>
-        <v>1.1519999999999999</v>
+        <v>5.093</v>
       </c>
       <c r="R46" s="37"/>
       <c r="S46" s="59"/>
@@ -15720,7 +15736,7 @@
         <v>50</v>
       </c>
       <c r="N47" s="51">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O47" s="60" t="s">
         <v>435</v>
@@ -15730,7 +15746,7 @@
       </c>
       <c r="Q47" s="52">
         <f t="shared" ref="Q47" si="20">P47*N47</f>
-        <v>0.51500000000000001</v>
+        <v>3.09</v>
       </c>
       <c r="R47" s="51"/>
       <c r="S47" s="59"/>
@@ -15771,7 +15787,7 @@
       <c r="L48" s="62">
         <v>9</v>
       </c>
-      <c r="M48" s="51">
+      <c r="M48" s="62">
         <f t="shared" si="2"/>
         <v>450</v>
       </c>
@@ -15831,7 +15847,7 @@
         <v>50</v>
       </c>
       <c r="N49" s="51">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="O49" s="60" t="s">
         <v>435</v>
@@ -15841,7 +15857,7 @@
       </c>
       <c r="Q49" s="52">
         <f t="shared" ref="Q49" si="21">P49*N49</f>
-        <v>0.42000000000000004</v>
+        <v>1.26</v>
       </c>
       <c r="R49" s="51"/>
       <c r="S49" s="59"/>
@@ -15887,7 +15903,7 @@
         <v>100</v>
       </c>
       <c r="N50" s="37">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="O50" s="60" t="s">
         <v>435</v>
@@ -15897,7 +15913,7 @@
       </c>
       <c r="Q50" s="38">
         <f>P50*N50</f>
-        <v>0.434</v>
+        <v>2.6040000000000001</v>
       </c>
       <c r="R50" s="37"/>
       <c r="S50" s="59"/>
@@ -16056,7 +16072,7 @@
         <v>600</v>
       </c>
       <c r="N53" s="51">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="O53" s="60" t="s">
         <v>435</v>
@@ -16066,7 +16082,7 @@
       </c>
       <c r="Q53" s="52">
         <f t="shared" ref="Q53" si="22">P53*N53</f>
-        <v>0.09</v>
+        <v>0.63</v>
       </c>
       <c r="R53" s="51"/>
       <c r="S53" s="59"/>
@@ -16112,7 +16128,7 @@
         <v>400</v>
       </c>
       <c r="N54" s="37">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="O54" s="60" t="s">
         <v>435</v>
@@ -16122,7 +16138,7 @@
       </c>
       <c r="Q54" s="38">
         <f>P54*N54</f>
-        <v>0.09</v>
+        <v>0.45</v>
       </c>
       <c r="R54" s="37"/>
       <c r="S54" s="59"/>
@@ -16224,7 +16240,7 @@
         <v>100</v>
       </c>
       <c r="N56" s="37">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O56" s="60" t="s">
         <v>435</v>
@@ -16234,7 +16250,7 @@
       </c>
       <c r="Q56" s="38">
         <f>P56*N56</f>
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="R56" s="37"/>
       <c r="S56" s="59"/>
@@ -16280,7 +16296,7 @@
         <v>100</v>
       </c>
       <c r="N57" s="51">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O57" s="60" t="s">
         <v>435</v>
@@ -16290,7 +16306,7 @@
       </c>
       <c r="Q57" s="52">
         <f t="shared" ref="Q57" si="24">P57*N57</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="R57" s="51"/>
       <c r="S57" s="59"/>
@@ -16336,7 +16352,7 @@
         <v>100</v>
       </c>
       <c r="N58" s="37">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O58" s="60" t="s">
         <v>435</v>
@@ -16346,7 +16362,7 @@
       </c>
       <c r="Q58" s="38">
         <f>P58*N58</f>
-        <v>6.9999999999999993E-2</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="R58" s="37"/>
       <c r="S58" s="59"/>
@@ -16392,17 +16408,17 @@
         <v>1100</v>
       </c>
       <c r="N59" s="51">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="O59" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P59" s="52">
-        <v>6.9999999999999999E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q59" s="52">
         <f t="shared" ref="Q59" si="25">P59*N59</f>
-        <v>0.13999999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="R59" s="51"/>
       <c r="S59" s="59"/>
@@ -16504,7 +16520,7 @@
         <v>550</v>
       </c>
       <c r="N61" s="37">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="O61" s="60" t="s">
         <v>435</v>
@@ -16514,66 +16530,66 @@
       </c>
       <c r="Q61" s="38">
         <f>P61*N61</f>
-        <v>6.9999999999999993E-2</v>
+        <v>0.42</v>
       </c>
       <c r="R61" s="37"/>
       <c r="S61" s="59"/>
     </row>
-    <row r="62" spans="1:19" s="70" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="69"/>
-      <c r="B62" s="46">
+    <row r="62" spans="1:19" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="74"/>
+      <c r="B62" s="75">
         <f>ROW(B62) - ROW($B$9)</f>
         <v>53</v>
       </c>
-      <c r="C62" s="54" t="s">
+      <c r="C62" s="86" t="s">
         <v>473</v>
       </c>
-      <c r="D62" s="67" t="s">
+      <c r="D62" s="83" t="s">
         <v>483</v>
       </c>
-      <c r="E62" s="37" t="s">
+      <c r="E62" s="77" t="s">
         <v>493</v>
       </c>
-      <c r="F62" s="37" t="s">
+      <c r="F62" s="77" t="s">
         <v>494</v>
       </c>
-      <c r="G62" s="37" t="s">
+      <c r="G62" s="77" t="s">
         <v>488</v>
       </c>
-      <c r="H62" s="37" t="s">
+      <c r="H62" s="77" t="s">
         <v>282</v>
       </c>
-      <c r="I62" s="37" t="s">
-        <v>429</v>
-      </c>
-      <c r="J62" s="37" t="s">
+      <c r="I62" s="77" t="s">
+        <v>429</v>
+      </c>
+      <c r="J62" s="77" t="s">
         <v>495</v>
       </c>
-      <c r="K62" s="37" t="s">
+      <c r="K62" s="77" t="s">
         <v>402</v>
       </c>
-      <c r="L62" s="37">
+      <c r="L62" s="77">
         <v>3</v>
       </c>
-      <c r="M62" s="51">
+      <c r="M62" s="87">
         <f t="shared" si="2"/>
         <v>150</v>
       </c>
-      <c r="N62" s="37">
-        <v>100</v>
-      </c>
-      <c r="O62" s="73" t="s">
-        <v>435</v>
-      </c>
-      <c r="P62" s="38">
+      <c r="N62" s="77">
+        <v>200</v>
+      </c>
+      <c r="O62" s="99" t="s">
+        <v>435</v>
+      </c>
+      <c r="P62" s="79">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="Q62" s="38">
+      <c r="Q62" s="79">
         <f>P62*N62</f>
-        <v>0.69</v>
-      </c>
-      <c r="R62" s="37"/>
-      <c r="S62" s="59"/>
+        <v>1.38</v>
+      </c>
+      <c r="R62" s="77"/>
+      <c r="S62" s="84"/>
     </row>
     <row r="63" spans="1:19" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="69"/>
@@ -16616,7 +16632,7 @@
         <v>200</v>
       </c>
       <c r="N63" s="37">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O63" s="60" t="s">
         <v>435</v>
@@ -16626,7 +16642,7 @@
       </c>
       <c r="Q63" s="38">
         <f>P63*N63</f>
-        <v>6.9999999999999993E-2</v>
+        <v>0.21</v>
       </c>
       <c r="R63" s="37"/>
       <c r="S63" s="59"/>
@@ -16784,7 +16800,7 @@
         <v>50</v>
       </c>
       <c r="N66" s="51">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="O66" s="60" t="s">
         <v>435</v>
@@ -16794,7 +16810,7 @@
       </c>
       <c r="Q66" s="52">
         <f t="shared" ref="Q66:Q67" si="27">P66*N66</f>
-        <v>0.52</v>
+        <v>1.5599999999999998</v>
       </c>
       <c r="R66" s="51"/>
       <c r="S66" s="59"/>
@@ -16840,7 +16856,7 @@
         <v>200</v>
       </c>
       <c r="N67" s="51">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O67" s="60" t="s">
         <v>435</v>
@@ -16850,7 +16866,7 @@
       </c>
       <c r="Q67" s="52">
         <f t="shared" si="27"/>
-        <v>0.04</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="R67" s="51"/>
       <c r="S67" s="59"/>
@@ -16948,17 +16964,17 @@
         <v>50</v>
       </c>
       <c r="N69" s="51">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="O69" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P69" s="52">
-        <v>5.3600000000000002E-2</v>
+        <v>4.7E-2</v>
       </c>
       <c r="Q69" s="52">
         <f t="shared" ref="Q69" si="28">P69*N69</f>
-        <v>0.53600000000000003</v>
+        <v>2.585</v>
       </c>
       <c r="R69" s="51"/>
       <c r="S69" s="59"/>
@@ -17002,7 +17018,7 @@
         <v>100</v>
       </c>
       <c r="N70" s="37">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O70" s="60" t="s">
         <v>435</v>
@@ -17012,7 +17028,7 @@
       </c>
       <c r="Q70" s="38">
         <f>P70*N70</f>
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="R70" s="37"/>
       <c r="S70" s="59"/>
@@ -17071,63 +17087,63 @@
       <c r="R71" s="51"/>
       <c r="S71" s="59"/>
     </row>
-    <row r="72" spans="1:19" s="70" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A72" s="69"/>
-      <c r="B72" s="47">
+    <row r="72" spans="1:19" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="74"/>
+      <c r="B72" s="85">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="C72" s="54" t="s">
+      <c r="C72" s="86" t="s">
         <v>473</v>
       </c>
-      <c r="D72" s="67" t="s">
+      <c r="D72" s="83" t="s">
         <v>484</v>
       </c>
-      <c r="E72" s="51" t="s">
+      <c r="E72" s="87" t="s">
         <v>474</v>
       </c>
-      <c r="F72" s="51" t="s">
+      <c r="F72" s="87" t="s">
         <v>434</v>
       </c>
-      <c r="G72" s="51" t="s">
+      <c r="G72" s="87" t="s">
         <v>475</v>
       </c>
-      <c r="H72" s="51" t="s">
+      <c r="H72" s="87" t="s">
         <v>282</v>
       </c>
-      <c r="I72" s="51" t="s">
-        <v>429</v>
-      </c>
-      <c r="J72" s="51" t="s">
+      <c r="I72" s="87" t="s">
+        <v>429</v>
+      </c>
+      <c r="J72" s="87" t="s">
         <v>476</v>
       </c>
-      <c r="K72" s="51" t="s">
+      <c r="K72" s="87" t="s">
         <v>399</v>
       </c>
-      <c r="L72" s="51">
+      <c r="L72" s="87">
         <v>2</v>
       </c>
-      <c r="M72" s="51">
+      <c r="M72" s="87">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N72" s="51">
-        <v>50</v>
-      </c>
-      <c r="O72" s="60" t="s">
-        <v>435</v>
-      </c>
-      <c r="P72" s="52">
+      <c r="N72" s="87">
+        <v>150</v>
+      </c>
+      <c r="O72" s="78" t="s">
+        <v>435</v>
+      </c>
+      <c r="P72" s="88">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="Q72" s="52">
+      <c r="Q72" s="88">
         <f t="shared" si="29"/>
-        <v>0.43499999999999994</v>
-      </c>
-      <c r="R72" s="51"/>
-      <c r="S72" s="59"/>
-    </row>
-    <row r="73" spans="1:19" s="70" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+        <v>1.3049999999999999</v>
+      </c>
+      <c r="R72" s="87"/>
+      <c r="S72" s="84"/>
+    </row>
+    <row r="73" spans="1:19" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A73" s="69"/>
       <c r="B73" s="46">
         <f>ROW(B73) - ROW($B$9)</f>
@@ -17184,7 +17200,7 @@
       </c>
       <c r="S73" s="59"/>
     </row>
-    <row r="74" spans="1:19" s="70" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A74" s="69"/>
       <c r="B74" s="47">
         <f t="shared" si="0"/>
@@ -17225,17 +17241,17 @@
         <v>50</v>
       </c>
       <c r="N74" s="51">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="O74" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P74" s="52">
-        <v>0.1275</v>
+        <v>0.1022</v>
       </c>
       <c r="Q74" s="52">
         <f t="shared" ref="Q74" si="30">P74*N74</f>
-        <v>1.2749999999999999</v>
+        <v>5.6209999999999996</v>
       </c>
       <c r="R74" s="51"/>
       <c r="S74" s="59"/>
@@ -17281,17 +17297,17 @@
         <v>50</v>
       </c>
       <c r="N75" s="37">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="O75" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P75" s="38">
-        <v>0.82569999999999999</v>
+        <v>0.52980000000000005</v>
       </c>
       <c r="Q75" s="38">
         <f>P75*N75</f>
-        <v>4.9542000000000002</v>
+        <v>27.019800000000004</v>
       </c>
       <c r="R75" s="37"/>
       <c r="S75" s="59"/>
@@ -17337,17 +17353,17 @@
         <v>50</v>
       </c>
       <c r="N76" s="51">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="O76" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P76" s="52">
-        <v>0.70009999999999994</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="Q76" s="52">
         <f t="shared" ref="Q76" si="32">P76*N76</f>
-        <v>4.2005999999999997</v>
+        <v>26.775000000000002</v>
       </c>
       <c r="R76" s="51"/>
       <c r="S76" s="59"/>
@@ -17393,17 +17409,17 @@
         <v>50</v>
       </c>
       <c r="N77" s="37">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="O77" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P77" s="38">
-        <v>0.32279999999999998</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="Q77" s="38">
         <f>P77*N77</f>
-        <v>3.2279999999999998</v>
+        <v>13.145</v>
       </c>
       <c r="R77" s="37"/>
       <c r="S77" s="59"/>
@@ -17449,17 +17465,17 @@
         <v>50</v>
       </c>
       <c r="N78" s="51">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="O78" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P78" s="52">
-        <v>1.3062</v>
+        <v>0.96730000000000005</v>
       </c>
       <c r="Q78" s="52">
         <f t="shared" ref="Q78" si="33">P78*N78</f>
-        <v>7.8372000000000002</v>
+        <v>49.332300000000004</v>
       </c>
       <c r="R78" s="51"/>
       <c r="S78" s="59"/>
@@ -17503,17 +17519,17 @@
         <v>50</v>
       </c>
       <c r="N79" s="37">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="O79" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P79" s="38">
-        <v>0.3644</v>
+        <v>0.253</v>
       </c>
       <c r="Q79" s="38">
         <f>P79*N79</f>
-        <v>2.1863999999999999</v>
+        <v>12.903</v>
       </c>
       <c r="R79" s="37"/>
       <c r="S79" s="59"/>
@@ -17559,7 +17575,7 @@
         <v>50</v>
       </c>
       <c r="N80" s="51">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="O80" s="60" t="s">
         <v>452</v>
@@ -17569,7 +17585,7 @@
       </c>
       <c r="Q80" s="52">
         <f t="shared" ref="Q80" si="34">P80*N80</f>
-        <v>15.059999999999999</v>
+        <v>128.01</v>
       </c>
       <c r="R80" s="51"/>
       <c r="S80" s="59"/>
@@ -17615,17 +17631,17 @@
         <v>50</v>
       </c>
       <c r="N81" s="37">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="O81" s="60" t="s">
         <v>452</v>
       </c>
       <c r="P81" s="38">
-        <v>3.4329999999999998</v>
+        <v>2.4030999999999998</v>
       </c>
       <c r="Q81" s="38">
         <f>P81*N81</f>
-        <v>20.597999999999999</v>
+        <v>122.5581</v>
       </c>
       <c r="R81" s="37"/>
       <c r="S81" s="59"/>
@@ -17669,76 +17685,76 @@
         <v>50</v>
       </c>
       <c r="N82" s="51">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="O82" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P82" s="52">
-        <v>4.6247999999999996</v>
+        <v>3.6749999999999998</v>
       </c>
       <c r="Q82" s="52">
         <f t="shared" ref="Q82" si="35">P82*N82</f>
-        <v>27.748799999999996</v>
+        <v>187.42499999999998</v>
       </c>
       <c r="R82" s="51"/>
       <c r="S82" s="59"/>
     </row>
-    <row r="83" spans="1:19" s="70" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A83" s="69"/>
-      <c r="B83" s="46">
+    <row r="83" spans="1:19" s="81" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="74"/>
+      <c r="B83" s="75">
         <f>ROW(B83) - ROW($B$9)</f>
         <v>74</v>
       </c>
-      <c r="C83" s="53" t="s">
+      <c r="C83" s="76" t="s">
         <v>24</v>
       </c>
-      <c r="D83" s="37" t="s">
+      <c r="D83" s="77" t="s">
         <v>92</v>
       </c>
-      <c r="E83" s="37" t="s">
+      <c r="E83" s="77" t="s">
         <v>166</v>
       </c>
-      <c r="F83" s="37" t="s">
+      <c r="F83" s="77" t="s">
         <v>213</v>
       </c>
-      <c r="G83" s="37" t="s">
+      <c r="G83" s="77" t="s">
         <v>273</v>
       </c>
-      <c r="H83" s="37" t="s">
+      <c r="H83" s="77" t="s">
         <v>319</v>
       </c>
-      <c r="I83" s="37" t="s">
-        <v>429</v>
-      </c>
-      <c r="J83" s="37" t="s">
-        <v>429</v>
-      </c>
-      <c r="K83" s="37" t="s">
-        <v>429</v>
-      </c>
-      <c r="L83" s="37">
+      <c r="I83" s="77" t="s">
+        <v>429</v>
+      </c>
+      <c r="J83" s="77" t="s">
+        <v>429</v>
+      </c>
+      <c r="K83" s="77" t="s">
+        <v>429</v>
+      </c>
+      <c r="L83" s="77">
         <v>1</v>
       </c>
-      <c r="M83" s="51">
+      <c r="M83" s="87">
         <f t="shared" si="31"/>
         <v>50</v>
       </c>
-      <c r="N83" s="37">
-        <v>6</v>
-      </c>
-      <c r="O83" s="60" t="s">
+      <c r="N83" s="77">
+        <v>51</v>
+      </c>
+      <c r="O83" s="78" t="s">
         <v>452</v>
       </c>
-      <c r="P83" s="38">
+      <c r="P83" s="79">
         <v>7.9</v>
       </c>
-      <c r="Q83" s="38">
+      <c r="Q83" s="79">
         <f>P83*N83</f>
-        <v>47.400000000000006</v>
-      </c>
-      <c r="R83" s="63"/>
-      <c r="S83" s="59"/>
+        <v>402.90000000000003</v>
+      </c>
+      <c r="R83" s="100"/>
+      <c r="S83" s="84"/>
     </row>
     <row r="84" spans="1:19" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="69"/>
@@ -17781,17 +17797,17 @@
         <v>150</v>
       </c>
       <c r="N84" s="51">
-        <v>16</v>
+        <v>151</v>
       </c>
       <c r="O84" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P84" s="52">
-        <v>1.7437</v>
+        <v>1.2091000000000001</v>
       </c>
       <c r="Q84" s="52">
         <f t="shared" ref="Q84" si="36">P84*N84</f>
-        <v>27.8992</v>
+        <v>182.57410000000002</v>
       </c>
       <c r="R84" s="51"/>
       <c r="S84" s="59"/>
@@ -17837,17 +17853,17 @@
         <v>50</v>
       </c>
       <c r="N85" s="37">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="O85" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P85" s="38">
-        <v>7.7799999999999994E-2</v>
+        <v>6.3399999999999998E-2</v>
       </c>
       <c r="Q85" s="38">
         <f>P85*N85</f>
-        <v>0.77799999999999991</v>
+        <v>3.4870000000000001</v>
       </c>
       <c r="R85" s="37"/>
       <c r="S85" s="59"/>
@@ -17893,17 +17909,17 @@
         <v>50</v>
       </c>
       <c r="N86" s="51">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="O86" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P86" s="52">
-        <v>0.77800000000000002</v>
+        <v>0.60619999999999996</v>
       </c>
       <c r="Q86" s="52">
         <f t="shared" ref="Q86" si="37">P86*N86</f>
-        <v>4.6680000000000001</v>
+        <v>30.916199999999996</v>
       </c>
       <c r="R86" s="51"/>
       <c r="S86" s="59"/>
@@ -17949,17 +17965,17 @@
         <v>50</v>
       </c>
       <c r="N87" s="37">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="O87" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P87" s="38">
-        <v>0.41049999999999998</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="Q87" s="38">
         <f>P87*N87</f>
-        <v>2.4630000000000001</v>
+        <v>14.685</v>
       </c>
       <c r="R87" s="37"/>
       <c r="S87" s="59"/>
@@ -18005,17 +18021,17 @@
         <v>50</v>
       </c>
       <c r="N88" s="51">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="O88" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P88" s="52">
-        <v>1.1837</v>
+        <v>0.89549999999999996</v>
       </c>
       <c r="Q88" s="52">
         <f t="shared" ref="Q88" si="38">P88*N88</f>
-        <v>7.1021999999999998</v>
+        <v>45.670499999999997</v>
       </c>
       <c r="R88" s="51"/>
       <c r="S88" s="59"/>
@@ -18061,17 +18077,17 @@
         <v>50</v>
       </c>
       <c r="N89" s="37">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="O89" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P89" s="38">
-        <v>1.2107000000000001</v>
+        <v>0.93389999999999995</v>
       </c>
       <c r="Q89" s="38">
         <f>P89*N89</f>
-        <v>7.2642000000000007</v>
+        <v>47.628899999999994</v>
       </c>
       <c r="R89" s="37"/>
       <c r="S89" s="59"/>
@@ -18117,17 +18133,17 @@
         <v>50</v>
       </c>
       <c r="N90" s="51">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="O90" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P90" s="52">
-        <v>0.08</v>
+        <v>6.6299999999999998E-2</v>
       </c>
       <c r="Q90" s="52">
         <f t="shared" ref="Q90" si="39">P90*N90</f>
-        <v>0.8</v>
+        <v>3.6465000000000001</v>
       </c>
       <c r="R90" s="51"/>
       <c r="S90" s="59"/>
@@ -18173,17 +18189,17 @@
         <v>50</v>
       </c>
       <c r="N91" s="37">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="O91" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P91" s="38">
-        <v>0.1065</v>
+        <v>7.6799999999999993E-2</v>
       </c>
       <c r="Q91" s="38">
         <f>P91*N91</f>
-        <v>1.0649999999999999</v>
+        <v>4.2239999999999993</v>
       </c>
       <c r="R91" s="37"/>
       <c r="S91" s="39"/>
@@ -18229,17 +18245,17 @@
         <v>50</v>
       </c>
       <c r="N92" s="37">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="O92" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P92" s="38">
-        <v>1.1609</v>
+        <v>1.0126999999999999</v>
       </c>
       <c r="Q92" s="38">
         <f>P92*N92</f>
-        <v>5.8045</v>
+        <v>50.634999999999998</v>
       </c>
       <c r="R92" s="37"/>
       <c r="S92" s="39"/>
@@ -18258,17 +18274,17 @@
       <c r="K93" s="45"/>
       <c r="L93" s="45"/>
       <c r="M93" s="45"/>
-      <c r="N93" s="90" t="s">
+      <c r="N93" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="O93" s="91"/>
-      <c r="P93" s="91"/>
+      <c r="O93" s="98"/>
+      <c r="P93" s="98"/>
       <c r="Q93" s="48">
         <f>SUM(Q10:Q92)</f>
-        <v>290.3445000000001</v>
-      </c>
-      <c r="R93" s="86"/>
-      <c r="S93" s="87"/>
+        <v>2030.8572999999999</v>
+      </c>
+      <c r="R93" s="93"/>
+      <c r="S93" s="94"/>
     </row>
     <row r="94" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
@@ -18284,17 +18300,17 @@
       <c r="K94" s="10"/>
       <c r="L94" s="10"/>
       <c r="M94" s="10"/>
-      <c r="N94" s="90" t="s">
+      <c r="N94" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="O94" s="91"/>
-      <c r="P94" s="91"/>
+      <c r="O94" s="98"/>
+      <c r="P94" s="98"/>
       <c r="Q94" s="49">
         <f>Q93/50</f>
-        <v>5.8068900000000019</v>
-      </c>
-      <c r="R94" s="88"/>
-      <c r="S94" s="89"/>
+        <v>40.617145999999998</v>
+      </c>
+      <c r="R94" s="95"/>
+      <c r="S94" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -18308,83 +18324,83 @@
     <hyperlink ref="O43" r:id="rId1"/>
     <hyperlink ref="O72" r:id="rId2"/>
     <hyperlink ref="O91" r:id="rId3"/>
-    <hyperlink ref="O41" r:id="rId4" display="LCSC"/>
-    <hyperlink ref="O18" r:id="rId5"/>
-    <hyperlink ref="O16" r:id="rId6"/>
-    <hyperlink ref="O83" r:id="rId7"/>
-    <hyperlink ref="O81" r:id="rId8"/>
-    <hyperlink ref="O80" r:id="rId9"/>
-    <hyperlink ref="O67" r:id="rId10"/>
-    <hyperlink ref="O57" r:id="rId11"/>
-    <hyperlink ref="O54" r:id="rId12"/>
-    <hyperlink ref="O50" r:id="rId13"/>
-    <hyperlink ref="O27" r:id="rId14"/>
-    <hyperlink ref="O26" r:id="rId15"/>
-    <hyperlink ref="O20" r:id="rId16"/>
-    <hyperlink ref="O74" r:id="rId17"/>
-    <hyperlink ref="O90" r:id="rId18"/>
-    <hyperlink ref="O89" r:id="rId19"/>
-    <hyperlink ref="O88" r:id="rId20"/>
-    <hyperlink ref="O87" r:id="rId21"/>
-    <hyperlink ref="O86" r:id="rId22"/>
-    <hyperlink ref="O85" r:id="rId23"/>
-    <hyperlink ref="O84" r:id="rId24"/>
-    <hyperlink ref="O82" r:id="rId25"/>
-    <hyperlink ref="O79" r:id="rId26"/>
-    <hyperlink ref="O78" r:id="rId27"/>
-    <hyperlink ref="O77" r:id="rId28"/>
-    <hyperlink ref="O76" r:id="rId29"/>
-    <hyperlink ref="O75" r:id="rId30"/>
-    <hyperlink ref="O71" r:id="rId31"/>
-    <hyperlink ref="O70" r:id="rId32"/>
-    <hyperlink ref="O69" r:id="rId33"/>
-    <hyperlink ref="O68" r:id="rId34"/>
-    <hyperlink ref="O61" r:id="rId35"/>
-    <hyperlink ref="O66" r:id="rId36"/>
-    <hyperlink ref="O65" r:id="rId37"/>
-    <hyperlink ref="O64" r:id="rId38"/>
-    <hyperlink ref="O63" r:id="rId39"/>
-    <hyperlink ref="O60" r:id="rId40"/>
-    <hyperlink ref="O59" r:id="rId41"/>
-    <hyperlink ref="O58" r:id="rId42"/>
-    <hyperlink ref="O56" r:id="rId43"/>
-    <hyperlink ref="O55" r:id="rId44"/>
-    <hyperlink ref="O53" r:id="rId45"/>
-    <hyperlink ref="O52" r:id="rId46"/>
-    <hyperlink ref="O51" r:id="rId47"/>
-    <hyperlink ref="O49" r:id="rId48"/>
-    <hyperlink ref="O47" r:id="rId49"/>
-    <hyperlink ref="O46" r:id="rId50"/>
-    <hyperlink ref="O45" r:id="rId51"/>
-    <hyperlink ref="O44" r:id="rId52"/>
-    <hyperlink ref="O42" r:id="rId53"/>
-    <hyperlink ref="O40" r:id="rId54"/>
-    <hyperlink ref="O38" r:id="rId55"/>
-    <hyperlink ref="O37" r:id="rId56"/>
-    <hyperlink ref="O36" r:id="rId57"/>
-    <hyperlink ref="O35" r:id="rId58"/>
-    <hyperlink ref="O34" r:id="rId59"/>
-    <hyperlink ref="O33" r:id="rId60"/>
-    <hyperlink ref="O32" r:id="rId61"/>
-    <hyperlink ref="O31" r:id="rId62"/>
-    <hyperlink ref="O30" r:id="rId63"/>
-    <hyperlink ref="O29" r:id="rId64"/>
-    <hyperlink ref="O28" r:id="rId65"/>
-    <hyperlink ref="O25" r:id="rId66"/>
-    <hyperlink ref="O24" r:id="rId67"/>
-    <hyperlink ref="O23" r:id="rId68"/>
-    <hyperlink ref="O21" r:id="rId69"/>
-    <hyperlink ref="O22" r:id="rId70"/>
-    <hyperlink ref="O19" r:id="rId71"/>
-    <hyperlink ref="O17" r:id="rId72"/>
-    <hyperlink ref="O14" r:id="rId73"/>
-    <hyperlink ref="O13" r:id="rId74"/>
-    <hyperlink ref="O12" r:id="rId75"/>
-    <hyperlink ref="O11" r:id="rId76"/>
-    <hyperlink ref="O15" r:id="rId77"/>
-    <hyperlink ref="O39" r:id="rId78"/>
-    <hyperlink ref="O62" r:id="rId79"/>
-    <hyperlink ref="O92" r:id="rId80"/>
+    <hyperlink ref="O18" r:id="rId4"/>
+    <hyperlink ref="O16" r:id="rId5"/>
+    <hyperlink ref="O83" r:id="rId6"/>
+    <hyperlink ref="O81" r:id="rId7"/>
+    <hyperlink ref="O80" r:id="rId8"/>
+    <hyperlink ref="O67" r:id="rId9"/>
+    <hyperlink ref="O57" r:id="rId10"/>
+    <hyperlink ref="O54" r:id="rId11"/>
+    <hyperlink ref="O50" r:id="rId12"/>
+    <hyperlink ref="O27" r:id="rId13"/>
+    <hyperlink ref="O26" r:id="rId14"/>
+    <hyperlink ref="O20" r:id="rId15"/>
+    <hyperlink ref="O74" r:id="rId16"/>
+    <hyperlink ref="O90" r:id="rId17"/>
+    <hyperlink ref="O89" r:id="rId18"/>
+    <hyperlink ref="O88" r:id="rId19"/>
+    <hyperlink ref="O87" r:id="rId20"/>
+    <hyperlink ref="O86" r:id="rId21"/>
+    <hyperlink ref="O85" r:id="rId22"/>
+    <hyperlink ref="O84" r:id="rId23"/>
+    <hyperlink ref="O82" r:id="rId24"/>
+    <hyperlink ref="O79" r:id="rId25"/>
+    <hyperlink ref="O78" r:id="rId26"/>
+    <hyperlink ref="O77" r:id="rId27"/>
+    <hyperlink ref="O76" r:id="rId28"/>
+    <hyperlink ref="O75" r:id="rId29"/>
+    <hyperlink ref="O71" r:id="rId30"/>
+    <hyperlink ref="O70" r:id="rId31"/>
+    <hyperlink ref="O69" r:id="rId32"/>
+    <hyperlink ref="O68" r:id="rId33"/>
+    <hyperlink ref="O61" r:id="rId34"/>
+    <hyperlink ref="O66" r:id="rId35"/>
+    <hyperlink ref="O65" r:id="rId36"/>
+    <hyperlink ref="O64" r:id="rId37"/>
+    <hyperlink ref="O63" r:id="rId38"/>
+    <hyperlink ref="O60" r:id="rId39"/>
+    <hyperlink ref="O59" r:id="rId40"/>
+    <hyperlink ref="O58" r:id="rId41"/>
+    <hyperlink ref="O56" r:id="rId42"/>
+    <hyperlink ref="O55" r:id="rId43"/>
+    <hyperlink ref="O53" r:id="rId44"/>
+    <hyperlink ref="O52" r:id="rId45"/>
+    <hyperlink ref="O51" r:id="rId46"/>
+    <hyperlink ref="O49" r:id="rId47"/>
+    <hyperlink ref="O47" r:id="rId48"/>
+    <hyperlink ref="O46" r:id="rId49"/>
+    <hyperlink ref="O45" r:id="rId50"/>
+    <hyperlink ref="O44" r:id="rId51"/>
+    <hyperlink ref="O42" r:id="rId52"/>
+    <hyperlink ref="O40" r:id="rId53"/>
+    <hyperlink ref="O38" r:id="rId54"/>
+    <hyperlink ref="O37" r:id="rId55"/>
+    <hyperlink ref="O36" r:id="rId56"/>
+    <hyperlink ref="O35" r:id="rId57"/>
+    <hyperlink ref="O34" r:id="rId58"/>
+    <hyperlink ref="O33" r:id="rId59"/>
+    <hyperlink ref="O32" r:id="rId60"/>
+    <hyperlink ref="O31" r:id="rId61"/>
+    <hyperlink ref="O30" r:id="rId62"/>
+    <hyperlink ref="O29" r:id="rId63"/>
+    <hyperlink ref="O28" r:id="rId64"/>
+    <hyperlink ref="O25" r:id="rId65"/>
+    <hyperlink ref="O24" r:id="rId66"/>
+    <hyperlink ref="O23" r:id="rId67"/>
+    <hyperlink ref="O21" r:id="rId68"/>
+    <hyperlink ref="O22" r:id="rId69"/>
+    <hyperlink ref="O19" r:id="rId70"/>
+    <hyperlink ref="O17" r:id="rId71"/>
+    <hyperlink ref="O14" r:id="rId72"/>
+    <hyperlink ref="O13" r:id="rId73"/>
+    <hyperlink ref="O12" r:id="rId74"/>
+    <hyperlink ref="O11" r:id="rId75"/>
+    <hyperlink ref="O15" r:id="rId76"/>
+    <hyperlink ref="O39" r:id="rId77"/>
+    <hyperlink ref="O62" r:id="rId78"/>
+    <hyperlink ref="O92" r:id="rId79"/>
+    <hyperlink ref="O41" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId81"/>
@@ -18426,15 +18442,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="83"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="89"/>
+      <c r="Q1" s="89"/>
+      <c r="R1" s="89"/>
+      <c r="S1" s="90"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -18484,7 +18500,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="84"/>
+      <c r="S3" s="91"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -18509,7 +18525,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="85"/>
+      <c r="S4" s="92"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -18534,7 +18550,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="85"/>
+      <c r="S5" s="92"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -18555,7 +18571,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="85"/>
+      <c r="S6" s="92"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -18576,7 +18592,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="85"/>
+      <c r="S7" s="92"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -18597,7 +18613,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="85"/>
+      <c r="S8" s="92"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -18711,7 +18727,7 @@
       <c r="R10" s="63" t="s">
         <v>439</v>
       </c>
-      <c r="S10" s="92"/>
+      <c r="S10" s="82"/>
     </row>
     <row r="11" spans="1:19" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="69"/>
@@ -18754,7 +18770,7 @@
         <v>100</v>
       </c>
       <c r="N11" s="51">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="O11" s="60" t="s">
         <v>435</v>
@@ -18764,7 +18780,7 @@
       </c>
       <c r="Q11" s="52">
         <f t="shared" ref="Q11" si="1">P11*N11</f>
-        <v>0.40200000000000002</v>
+        <v>2.4119999999999999</v>
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
@@ -18810,17 +18826,17 @@
         <v>2500</v>
       </c>
       <c r="N12" s="37">
-        <v>150</v>
+        <v>2550</v>
       </c>
       <c r="O12" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P12" s="38">
-        <v>1.0500000000000001E-2</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="Q12" s="38">
         <f>P12*N12</f>
-        <v>1.5750000000000002</v>
+        <v>19.89</v>
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="59"/>
@@ -18866,7 +18882,7 @@
         <v>300</v>
       </c>
       <c r="N13" s="51">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="O13" s="60" t="s">
         <v>435</v>
@@ -18876,7 +18892,7 @@
       </c>
       <c r="Q13" s="52">
         <f t="shared" ref="Q13" si="3">P13*N13</f>
-        <v>0.09</v>
+        <v>0.36</v>
       </c>
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
@@ -18922,17 +18938,17 @@
         <v>300</v>
       </c>
       <c r="N14" s="37">
-        <v>20</v>
+        <v>310</v>
       </c>
       <c r="O14" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P14" s="38">
-        <v>4.9099999999999998E-2</v>
+        <v>3.9300000000000002E-2</v>
       </c>
       <c r="Q14" s="38">
         <f>P14*N14</f>
-        <v>0.98199999999999998</v>
+        <v>12.183</v>
       </c>
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
@@ -18978,17 +18994,17 @@
         <v>200</v>
       </c>
       <c r="N15" s="51">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="O15" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P15" s="52">
-        <v>0.25940000000000002</v>
+        <v>0.24660000000000001</v>
       </c>
       <c r="Q15" s="52">
         <f t="shared" ref="Q15" si="4">P15*N15</f>
-        <v>2.8534000000000002</v>
+        <v>49.566600000000001</v>
       </c>
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
@@ -19034,17 +19050,17 @@
         <v>100</v>
       </c>
       <c r="N16" s="37">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="O16" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P16" s="38">
-        <v>7.0900000000000005E-2</v>
+        <v>6.3799999999999996E-2</v>
       </c>
       <c r="Q16" s="38">
         <f>P16*N16</f>
-        <v>1.0635000000000001</v>
+        <v>6.6989999999999998</v>
       </c>
       <c r="R16" s="37"/>
       <c r="S16" s="59"/>
@@ -19090,17 +19106,17 @@
         <v>100</v>
       </c>
       <c r="N17" s="51">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="O17" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P17" s="52">
-        <v>6.3E-2</v>
+        <v>4.41E-2</v>
       </c>
       <c r="Q17" s="52">
         <f t="shared" ref="Q17" si="5">P17*N17</f>
-        <v>0.63</v>
+        <v>4.6304999999999996</v>
       </c>
       <c r="R17" s="51"/>
       <c r="S17" s="59"/>
@@ -19146,17 +19162,17 @@
         <v>100</v>
       </c>
       <c r="N18" s="37">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="O18" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P18" s="38">
-        <v>1.7373000000000001</v>
+        <v>1.4430000000000001</v>
       </c>
       <c r="Q18" s="38">
         <f>P18*N18</f>
-        <v>10.4238</v>
+        <v>145.74299999999999</v>
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
@@ -19202,17 +19218,17 @@
         <v>100</v>
       </c>
       <c r="N19" s="51">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="O19" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P19" s="52">
-        <v>0.26129999999999998</v>
+        <v>0.2016</v>
       </c>
       <c r="Q19" s="52">
         <f t="shared" ref="Q19" si="6">P19*N19</f>
-        <v>2.6129999999999995</v>
+        <v>21.167999999999999</v>
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
@@ -19258,17 +19274,17 @@
         <v>400</v>
       </c>
       <c r="N20" s="37">
-        <v>30</v>
+        <v>420</v>
       </c>
       <c r="O20" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P20" s="38">
-        <v>4.2000000000000003E-2</v>
+        <v>2.92E-2</v>
       </c>
       <c r="Q20" s="38">
         <f>P20*N20</f>
-        <v>1.26</v>
+        <v>12.263999999999999</v>
       </c>
       <c r="R20" s="37"/>
       <c r="S20" s="59"/>
@@ -19314,7 +19330,7 @@
         <v>200</v>
       </c>
       <c r="N21" s="51">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="O21" s="60" t="s">
         <v>435</v>
@@ -19324,7 +19340,7 @@
       </c>
       <c r="Q21" s="52">
         <f t="shared" ref="Q21" si="7">P21*N21</f>
-        <v>0.54</v>
+        <v>3.24</v>
       </c>
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
@@ -19370,7 +19386,7 @@
         <v>200</v>
       </c>
       <c r="N22" s="37">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O22" s="60" t="s">
         <v>435</v>
@@ -19380,7 +19396,7 @@
       </c>
       <c r="Q22" s="38">
         <f>P22*N22</f>
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="R22" s="37"/>
       <c r="S22" s="59"/>
@@ -19426,7 +19442,7 @@
         <v>300</v>
       </c>
       <c r="N23" s="51">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="O23" s="60" t="s">
         <v>435</v>
@@ -19436,7 +19452,7 @@
       </c>
       <c r="Q23" s="52">
         <f t="shared" ref="Q23" si="8">P23*N23</f>
-        <v>0.38999999999999996</v>
+        <v>1.5599999999999998</v>
       </c>
       <c r="R23" s="51"/>
       <c r="S23" s="59"/>
@@ -19482,17 +19498,17 @@
         <v>100</v>
       </c>
       <c r="N24" s="37">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="O24" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P24" s="38">
-        <v>5.5599999999999997E-2</v>
+        <v>4.3900000000000002E-2</v>
       </c>
       <c r="Q24" s="38">
         <f>P24*N24</f>
-        <v>0.55599999999999994</v>
+        <v>4.8289999999999997</v>
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="59"/>
@@ -19538,17 +19554,17 @@
         <v>100</v>
       </c>
       <c r="N25" s="51">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="O25" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P25" s="52">
-        <v>4.4600000000000001E-2</v>
+        <v>3.6499999999999998E-2</v>
       </c>
       <c r="Q25" s="52">
         <f t="shared" ref="Q25" si="9">P25*N25</f>
-        <v>0.44600000000000001</v>
+        <v>4.0149999999999997</v>
       </c>
       <c r="R25" s="51"/>
       <c r="S25" s="59"/>
@@ -19594,17 +19610,17 @@
         <v>100</v>
       </c>
       <c r="N26" s="37">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="O26" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P26" s="38">
-        <v>0.46939999999999998</v>
+        <v>0.31190000000000001</v>
       </c>
       <c r="Q26" s="38">
         <f>P26*N26</f>
-        <v>2.8163999999999998</v>
+        <v>31.501900000000003</v>
       </c>
       <c r="R26" s="37"/>
       <c r="S26" s="59"/>
@@ -19650,17 +19666,17 @@
         <v>100</v>
       </c>
       <c r="N27" s="51">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="O27" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P27" s="52">
-        <v>3.56E-2</v>
+        <v>2.81E-2</v>
       </c>
       <c r="Q27" s="52">
         <f t="shared" ref="Q27" si="10">P27*N27</f>
-        <v>0.35599999999999998</v>
+        <v>3.0910000000000002</v>
       </c>
       <c r="R27" s="51"/>
       <c r="S27" s="59"/>
@@ -19706,17 +19722,17 @@
         <v>300</v>
       </c>
       <c r="N28" s="37">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="O28" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P28" s="38">
-        <v>2.46E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="Q28" s="38">
         <f>P28*N28</f>
-        <v>0.49199999999999999</v>
+        <v>7.0399999999999991</v>
       </c>
       <c r="R28" s="37"/>
       <c r="S28" s="59"/>
@@ -19762,17 +19778,17 @@
         <v>200</v>
       </c>
       <c r="N29" s="51">
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="O29" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P29" s="52">
-        <v>2.3400000000000001E-2</v>
+        <v>1.7600000000000001E-2</v>
       </c>
       <c r="Q29" s="52">
         <f t="shared" ref="Q29" si="11">P29*N29</f>
-        <v>0.46800000000000003</v>
+        <v>3.8720000000000003</v>
       </c>
       <c r="R29" s="51"/>
       <c r="S29" s="59"/>
@@ -19818,17 +19834,17 @@
         <v>400</v>
       </c>
       <c r="N30" s="37">
-        <v>25</v>
+        <v>405</v>
       </c>
       <c r="O30" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P30" s="38">
-        <v>0.1351</v>
+        <v>9.8599999999999993E-2</v>
       </c>
       <c r="Q30" s="38">
         <f>P30*N30</f>
-        <v>3.3774999999999999</v>
+        <v>39.933</v>
       </c>
       <c r="R30" s="37"/>
       <c r="S30" s="59"/>
@@ -19874,17 +19890,17 @@
         <v>400</v>
       </c>
       <c r="N31" s="51">
-        <v>30</v>
+        <v>410</v>
       </c>
       <c r="O31" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P31" s="52">
-        <v>4.7500000000000001E-2</v>
+        <v>3.3799999999999997E-2</v>
       </c>
       <c r="Q31" s="52">
         <f t="shared" ref="Q31" si="12">P31*N31</f>
-        <v>1.425</v>
+        <v>13.857999999999999</v>
       </c>
       <c r="R31" s="51"/>
       <c r="S31" s="59"/>
@@ -19930,17 +19946,17 @@
         <v>100</v>
       </c>
       <c r="N32" s="37">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="O32" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P32" s="38">
-        <v>0.2286</v>
+        <v>0.18679999999999999</v>
       </c>
       <c r="Q32" s="38">
         <f>P32*N32</f>
-        <v>2.286</v>
+        <v>19.614000000000001</v>
       </c>
       <c r="R32" s="37"/>
       <c r="S32" s="59"/>
@@ -19986,17 +20002,17 @@
         <v>100</v>
       </c>
       <c r="N33" s="51">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="O33" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P33" s="52">
-        <v>1.1482000000000001</v>
+        <v>0.78600000000000003</v>
       </c>
       <c r="Q33" s="52">
         <f t="shared" ref="Q33" si="13">P33*N33</f>
-        <v>6.8892000000000007</v>
+        <v>79.38600000000001</v>
       </c>
       <c r="R33" s="51"/>
       <c r="S33" s="59"/>
@@ -20042,17 +20058,17 @@
         <v>400</v>
       </c>
       <c r="N34" s="37">
-        <v>30</v>
+        <v>410</v>
       </c>
       <c r="O34" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P34" s="38">
-        <v>5.6099999999999997E-2</v>
+        <v>4.19E-2</v>
       </c>
       <c r="Q34" s="38">
         <f>P34*N34</f>
-        <v>1.6829999999999998</v>
+        <v>17.178999999999998</v>
       </c>
       <c r="R34" s="37"/>
       <c r="S34" s="59"/>
@@ -20098,17 +20114,17 @@
         <v>100</v>
       </c>
       <c r="N35" s="51">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="O35" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P35" s="52">
-        <v>8.8300000000000003E-2</v>
+        <v>7.2900000000000006E-2</v>
       </c>
       <c r="Q35" s="52">
         <f t="shared" ref="Q35" si="14">P35*N35</f>
-        <v>0.88300000000000001</v>
+        <v>7.6545000000000005</v>
       </c>
       <c r="R35" s="51"/>
       <c r="S35" s="59"/>
@@ -20154,17 +20170,17 @@
         <v>800</v>
       </c>
       <c r="N36" s="37">
-        <v>45</v>
+        <v>805</v>
       </c>
       <c r="O36" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P36" s="38">
-        <v>0.2316</v>
+        <v>0.1244</v>
       </c>
       <c r="Q36" s="38">
         <f>P36*N36</f>
-        <v>10.422000000000001</v>
+        <v>100.142</v>
       </c>
       <c r="R36" s="37"/>
       <c r="S36" s="59"/>
@@ -20210,17 +20226,17 @@
         <v>100</v>
       </c>
       <c r="N37" s="51">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="O37" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P37" s="52">
-        <v>0.21590000000000001</v>
+        <v>0.17929999999999999</v>
       </c>
       <c r="Q37" s="52">
         <f t="shared" ref="Q37" si="15">P37*N37</f>
-        <v>2.1590000000000003</v>
+        <v>18.826499999999999</v>
       </c>
       <c r="R37" s="51"/>
       <c r="S37" s="59"/>
@@ -20266,17 +20282,17 @@
         <v>400</v>
       </c>
       <c r="N38" s="37">
-        <v>25</v>
+        <v>405</v>
       </c>
       <c r="O38" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P38" s="38">
-        <v>0.17299999999999999</v>
+        <v>0.1149</v>
       </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>4.3249999999999993</v>
+        <v>46.534500000000001</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="59"/>
@@ -20322,17 +20338,17 @@
         <v>100</v>
       </c>
       <c r="N39" s="51">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="O39" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P39" s="52">
-        <v>0.14860000000000001</v>
+        <v>0.11849999999999999</v>
       </c>
       <c r="Q39" s="52">
         <f t="shared" ref="Q39" si="16">P39*N39</f>
-        <v>1.4860000000000002</v>
+        <v>12.442499999999999</v>
       </c>
       <c r="R39" s="51"/>
       <c r="S39" s="59"/>
@@ -20378,17 +20394,17 @@
         <v>100</v>
       </c>
       <c r="N40" s="37">
-        <v>12</v>
+        <v>108</v>
       </c>
       <c r="O40" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P40" s="38">
-        <v>7.0400000000000004E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="Q40" s="38">
         <f>P40*N40</f>
-        <v>0.8448</v>
+        <v>7.3440000000000003</v>
       </c>
       <c r="R40" s="37"/>
       <c r="S40" s="59"/>
@@ -20417,11 +20433,15 @@
       <c r="H41" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="I41" s="51"/>
+      <c r="I41" s="51" t="s">
+        <v>429</v>
+      </c>
       <c r="J41" s="51" t="s">
         <v>505</v>
       </c>
-      <c r="K41" s="51"/>
+      <c r="K41" s="51" t="s">
+        <v>429</v>
+      </c>
       <c r="L41" s="51">
         <v>1</v>
       </c>
@@ -20429,12 +20449,18 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N41" s="51"/>
-      <c r="O41" s="51"/>
-      <c r="P41" s="52"/>
+      <c r="N41" s="51">
+        <v>101</v>
+      </c>
+      <c r="O41" s="60" t="s">
+        <v>435</v>
+      </c>
+      <c r="P41" s="52">
+        <v>0.46689999999999998</v>
+      </c>
       <c r="Q41" s="52">
         <f t="shared" ref="Q41" si="17">P41*N41</f>
-        <v>0</v>
+        <v>47.1569</v>
       </c>
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
@@ -20480,17 +20506,17 @@
         <v>200</v>
       </c>
       <c r="N42" s="37">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="O42" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P42" s="38">
-        <v>0.81459999999999999</v>
+        <v>0.66510000000000002</v>
       </c>
       <c r="Q42" s="38">
         <f>P42*N42</f>
-        <v>8.9605999999999995</v>
+        <v>133.68510000000001</v>
       </c>
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
@@ -20536,7 +20562,7 @@
         <v>300</v>
       </c>
       <c r="N43" s="51">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c r="O43" s="60" t="s">
         <v>480</v>
@@ -20546,7 +20572,7 @@
       </c>
       <c r="Q43" s="52">
         <f t="shared" ref="Q43" si="18">P43*N43</f>
-        <v>16.16</v>
+        <v>304.01</v>
       </c>
       <c r="R43" s="51"/>
       <c r="S43" s="59"/>
@@ -20592,17 +20618,17 @@
         <v>100</v>
       </c>
       <c r="N44" s="37">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="O44" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P44" s="38">
-        <v>0.2137</v>
+        <v>0.1724</v>
       </c>
       <c r="Q44" s="38">
         <f>P44*N44</f>
-        <v>2.137</v>
+        <v>18.102</v>
       </c>
       <c r="R44" s="37"/>
       <c r="S44" s="59"/>
@@ -20648,7 +20674,7 @@
         <v>100</v>
       </c>
       <c r="N45" s="51">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="O45" s="60" t="s">
         <v>435</v>
@@ -20658,7 +20684,7 @@
       </c>
       <c r="Q45" s="52">
         <f t="shared" ref="Q45" si="19">P45*N45</f>
-        <v>0.41499999999999998</v>
+        <v>1.2450000000000001</v>
       </c>
       <c r="R45" s="51"/>
       <c r="S45" s="59"/>
@@ -20704,17 +20730,17 @@
         <v>200</v>
       </c>
       <c r="N46" s="37">
-        <v>20</v>
+        <v>210</v>
       </c>
       <c r="O46" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P46" s="38">
-        <v>5.7599999999999998E-2</v>
+        <v>4.6300000000000001E-2</v>
       </c>
       <c r="Q46" s="38">
         <f>P46*N46</f>
-        <v>1.1519999999999999</v>
+        <v>9.7230000000000008</v>
       </c>
       <c r="R46" s="37"/>
       <c r="S46" s="59"/>
@@ -20760,17 +20786,17 @@
         <v>100</v>
       </c>
       <c r="N47" s="51">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="O47" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P47" s="52">
-        <v>5.1499999999999997E-2</v>
+        <v>4.2599999999999999E-2</v>
       </c>
       <c r="Q47" s="52">
         <f t="shared" ref="Q47" si="20">P47*N47</f>
-        <v>0.51500000000000001</v>
+        <v>4.6859999999999999</v>
       </c>
       <c r="R47" s="51"/>
       <c r="S47" s="59"/>
@@ -20871,17 +20897,17 @@
         <v>100</v>
       </c>
       <c r="N49" s="51">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="O49" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P49" s="52">
-        <v>2.1000000000000001E-2</v>
+        <v>2.0299999999999999E-2</v>
       </c>
       <c r="Q49" s="52">
         <f t="shared" ref="Q49" si="21">P49*N49</f>
-        <v>0.42000000000000004</v>
+        <v>2.4359999999999999</v>
       </c>
       <c r="R49" s="51"/>
       <c r="S49" s="59"/>
@@ -20927,17 +20953,17 @@
         <v>200</v>
       </c>
       <c r="N50" s="37">
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="O50" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P50" s="38">
-        <v>2.1700000000000001E-2</v>
+        <v>1.9400000000000001E-2</v>
       </c>
       <c r="Q50" s="38">
         <f>P50*N50</f>
-        <v>0.434</v>
+        <v>4.2679999999999998</v>
       </c>
       <c r="R50" s="37"/>
       <c r="S50" s="59"/>
@@ -21040,7 +21066,7 @@
         <v>100</v>
       </c>
       <c r="N52" s="37">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O52" s="60" t="s">
         <v>435</v>
@@ -21050,7 +21076,7 @@
       </c>
       <c r="Q52" s="38">
         <f>P52*N52</f>
-        <v>0.26</v>
+        <v>0.52</v>
       </c>
       <c r="R52" s="37"/>
       <c r="S52" s="59"/>
@@ -21096,17 +21122,17 @@
         <v>1200</v>
       </c>
       <c r="N53" s="51">
-        <v>100</v>
+        <v>1300</v>
       </c>
       <c r="O53" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P53" s="52">
-        <v>8.9999999999999998E-4</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="Q53" s="52">
         <f t="shared" ref="Q53" si="22">P53*N53</f>
-        <v>0.09</v>
+        <v>0.91</v>
       </c>
       <c r="R53" s="51"/>
       <c r="S53" s="59"/>
@@ -21152,7 +21178,7 @@
         <v>800</v>
       </c>
       <c r="N54" s="37">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="O54" s="60" t="s">
         <v>435</v>
@@ -21162,7 +21188,7 @@
       </c>
       <c r="Q54" s="38">
         <f>P54*N54</f>
-        <v>0.09</v>
+        <v>0.80999999999999994</v>
       </c>
       <c r="R54" s="37"/>
       <c r="S54" s="59"/>
@@ -21208,7 +21234,7 @@
         <v>100</v>
       </c>
       <c r="N55" s="51">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O55" s="60" t="s">
         <v>435</v>
@@ -21218,7 +21244,7 @@
       </c>
       <c r="Q55" s="52">
         <f t="shared" ref="Q55" si="23">P55*N55</f>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="R55" s="51"/>
       <c r="S55" s="59"/>
@@ -21264,7 +21290,7 @@
         <v>200</v>
       </c>
       <c r="N56" s="37">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O56" s="60" t="s">
         <v>435</v>
@@ -21274,7 +21300,7 @@
       </c>
       <c r="Q56" s="38">
         <f>P56*N56</f>
-        <v>0.08</v>
+        <v>0.24000000000000002</v>
       </c>
       <c r="R56" s="37"/>
       <c r="S56" s="59"/>
@@ -21320,7 +21346,7 @@
         <v>200</v>
       </c>
       <c r="N57" s="51">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O57" s="60" t="s">
         <v>435</v>
@@ -21330,7 +21356,7 @@
       </c>
       <c r="Q57" s="52">
         <f t="shared" ref="Q57" si="24">P57*N57</f>
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="R57" s="51"/>
       <c r="S57" s="59"/>
@@ -21376,7 +21402,7 @@
         <v>200</v>
       </c>
       <c r="N58" s="37">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O58" s="60" t="s">
         <v>435</v>
@@ -21386,7 +21412,7 @@
       </c>
       <c r="Q58" s="38">
         <f>P58*N58</f>
-        <v>6.9999999999999993E-2</v>
+        <v>0.21</v>
       </c>
       <c r="R58" s="37"/>
       <c r="S58" s="59"/>
@@ -21432,17 +21458,17 @@
         <v>2200</v>
       </c>
       <c r="N59" s="51">
-        <v>200</v>
+        <v>2300</v>
       </c>
       <c r="O59" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P59" s="52">
-        <v>6.9999999999999999E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q59" s="52">
         <f t="shared" ref="Q59" si="25">P59*N59</f>
-        <v>0.13999999999999999</v>
+        <v>1.1500000000000001</v>
       </c>
       <c r="R59" s="51"/>
       <c r="S59" s="59"/>
@@ -21488,7 +21514,7 @@
         <v>100</v>
       </c>
       <c r="N60" s="37">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O60" s="60" t="s">
         <v>435</v>
@@ -21498,7 +21524,7 @@
       </c>
       <c r="Q60" s="38">
         <f>P60*N60</f>
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="R60" s="37"/>
       <c r="S60" s="59"/>
@@ -21544,17 +21570,17 @@
         <v>1100</v>
       </c>
       <c r="N61" s="37">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="O61" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P61" s="38">
-        <v>6.9999999999999999E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="Q61" s="38">
         <f>P61*N61</f>
-        <v>6.9999999999999993E-2</v>
+        <v>0.72</v>
       </c>
       <c r="R61" s="37"/>
       <c r="S61" s="59"/>
@@ -21600,17 +21626,17 @@
         <v>300</v>
       </c>
       <c r="N62" s="37">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="O62" s="73" t="s">
         <v>435</v>
       </c>
       <c r="P62" s="38">
-        <v>6.8999999999999999E-3</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="Q62" s="38">
         <f>P62*N62</f>
-        <v>0.69</v>
+        <v>3.1199999999999997</v>
       </c>
       <c r="R62" s="37"/>
       <c r="S62" s="59"/>
@@ -21656,7 +21682,7 @@
         <v>400</v>
       </c>
       <c r="N63" s="37">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="O63" s="60" t="s">
         <v>435</v>
@@ -21666,7 +21692,7 @@
       </c>
       <c r="Q63" s="38">
         <f>P63*N63</f>
-        <v>6.9999999999999993E-2</v>
+        <v>0.35</v>
       </c>
       <c r="R63" s="37"/>
       <c r="S63" s="59"/>
@@ -21712,7 +21738,7 @@
         <v>100</v>
       </c>
       <c r="N64" s="51">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O64" s="60" t="s">
         <v>435</v>
@@ -21722,7 +21748,7 @@
       </c>
       <c r="Q64" s="52">
         <f t="shared" ref="Q64" si="26">P64*N64</f>
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="R64" s="51"/>
       <c r="S64" s="59"/>
@@ -21768,7 +21794,7 @@
         <v>100</v>
       </c>
       <c r="N65" s="37">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O65" s="60" t="s">
         <v>435</v>
@@ -21778,7 +21804,7 @@
       </c>
       <c r="Q65" s="38">
         <f>P65*N65</f>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R65" s="37"/>
       <c r="S65" s="59"/>
@@ -21824,7 +21850,7 @@
         <v>100</v>
       </c>
       <c r="N66" s="51">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="O66" s="60" t="s">
         <v>435</v>
@@ -21834,7 +21860,7 @@
       </c>
       <c r="Q66" s="52">
         <f t="shared" ref="Q66:Q67" si="27">P66*N66</f>
-        <v>0.52</v>
+        <v>3.1199999999999997</v>
       </c>
       <c r="R66" s="51"/>
       <c r="S66" s="59"/>
@@ -21880,7 +21906,7 @@
         <v>400</v>
       </c>
       <c r="N67" s="51">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="O67" s="60" t="s">
         <v>435</v>
@@ -21890,7 +21916,7 @@
       </c>
       <c r="Q67" s="52">
         <f t="shared" si="27"/>
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="R67" s="51"/>
       <c r="S67" s="59"/>
@@ -21934,7 +21960,7 @@
         <v>100</v>
       </c>
       <c r="N68" s="37">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O68" s="60" t="s">
         <v>435</v>
@@ -21944,7 +21970,7 @@
       </c>
       <c r="Q68" s="38">
         <f>P68*N68</f>
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="R68" s="37"/>
       <c r="S68" s="59"/>
@@ -21988,17 +22014,17 @@
         <v>100</v>
       </c>
       <c r="N69" s="51">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="O69" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P69" s="52">
-        <v>5.3600000000000002E-2</v>
+        <v>4.7E-2</v>
       </c>
       <c r="Q69" s="52">
         <f t="shared" ref="Q69" si="28">P69*N69</f>
-        <v>0.53600000000000003</v>
+        <v>4.9349999999999996</v>
       </c>
       <c r="R69" s="51"/>
       <c r="S69" s="59"/>
@@ -22042,7 +22068,7 @@
         <v>200</v>
       </c>
       <c r="N70" s="37">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O70" s="60" t="s">
         <v>435</v>
@@ -22052,7 +22078,7 @@
       </c>
       <c r="Q70" s="38">
         <f>P70*N70</f>
-        <v>0.12</v>
+        <v>0.36</v>
       </c>
       <c r="R70" s="37"/>
       <c r="S70" s="59"/>
@@ -22096,7 +22122,7 @@
         <v>100</v>
       </c>
       <c r="N71" s="51">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O71" s="60" t="s">
         <v>435</v>
@@ -22106,7 +22132,7 @@
       </c>
       <c r="Q71" s="52">
         <f t="shared" ref="Q71:Q72" si="29">P71*N71</f>
-        <v>6.9999999999999993E-2</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="R71" s="51"/>
       <c r="S71" s="59"/>
@@ -22152,7 +22178,7 @@
         <v>200</v>
       </c>
       <c r="N72" s="51">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="O72" s="60" t="s">
         <v>435</v>
@@ -22162,7 +22188,7 @@
       </c>
       <c r="Q72" s="52">
         <f t="shared" si="29"/>
-        <v>0.43499999999999994</v>
+        <v>2.1749999999999998</v>
       </c>
       <c r="R72" s="51"/>
       <c r="S72" s="59"/>
@@ -22265,7 +22291,7 @@
         <v>100</v>
       </c>
       <c r="N74" s="51">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="O74" s="60" t="s">
         <v>435</v>
@@ -22275,7 +22301,7 @@
       </c>
       <c r="Q74" s="52">
         <f t="shared" ref="Q74" si="30">P74*N74</f>
-        <v>1.2749999999999999</v>
+        <v>14.025</v>
       </c>
       <c r="R74" s="51"/>
       <c r="S74" s="59"/>
@@ -22321,17 +22347,17 @@
         <v>100</v>
       </c>
       <c r="N75" s="37">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="O75" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P75" s="38">
-        <v>0.82569999999999999</v>
+        <v>0.46300000000000002</v>
       </c>
       <c r="Q75" s="38">
         <f>P75*N75</f>
-        <v>4.9542000000000002</v>
+        <v>46.763000000000005</v>
       </c>
       <c r="R75" s="37"/>
       <c r="S75" s="59"/>
@@ -22377,17 +22403,17 @@
         <v>100</v>
       </c>
       <c r="N76" s="51">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="O76" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P76" s="52">
-        <v>0.70009999999999994</v>
+        <v>0.45029999999999998</v>
       </c>
       <c r="Q76" s="52">
         <f t="shared" ref="Q76" si="32">P76*N76</f>
-        <v>4.2005999999999997</v>
+        <v>47.281500000000001</v>
       </c>
       <c r="R76" s="51"/>
       <c r="S76" s="59"/>
@@ -22433,17 +22459,17 @@
         <v>100</v>
       </c>
       <c r="N77" s="37">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="O77" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P77" s="38">
-        <v>0.32279999999999998</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="Q77" s="38">
         <f>P77*N77</f>
-        <v>3.2279999999999998</v>
+        <v>25.094999999999999</v>
       </c>
       <c r="R77" s="37"/>
       <c r="S77" s="59"/>
@@ -22489,17 +22515,17 @@
         <v>100</v>
       </c>
       <c r="N78" s="51">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="O78" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P78" s="52">
-        <v>1.3062</v>
+        <v>0.83320000000000005</v>
       </c>
       <c r="Q78" s="52">
         <f t="shared" ref="Q78" si="33">P78*N78</f>
-        <v>7.8372000000000002</v>
+        <v>84.153199999999998</v>
       </c>
       <c r="R78" s="51"/>
       <c r="S78" s="59"/>
@@ -22543,17 +22569,17 @@
         <v>100</v>
       </c>
       <c r="N79" s="37">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="O79" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P79" s="38">
-        <v>0.3644</v>
+        <v>0.218</v>
       </c>
       <c r="Q79" s="38">
         <f>P79*N79</f>
-        <v>2.1863999999999999</v>
+        <v>22.018000000000001</v>
       </c>
       <c r="R79" s="37"/>
       <c r="S79" s="59"/>
@@ -22599,7 +22625,7 @@
         <v>100</v>
       </c>
       <c r="N80" s="51">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="O80" s="60" t="s">
         <v>452</v>
@@ -22609,7 +22635,7 @@
       </c>
       <c r="Q80" s="52">
         <f t="shared" ref="Q80" si="34">P80*N80</f>
-        <v>15.059999999999999</v>
+        <v>253.51</v>
       </c>
       <c r="R80" s="51"/>
       <c r="S80" s="59"/>
@@ -22655,17 +22681,17 @@
         <v>100</v>
       </c>
       <c r="N81" s="37">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="O81" s="60" t="s">
         <v>452</v>
       </c>
       <c r="P81" s="38">
-        <v>3.4329999999999998</v>
+        <v>1.97397</v>
       </c>
       <c r="Q81" s="38">
         <f>P81*N81</f>
-        <v>20.597999999999999</v>
+        <v>199.37097</v>
       </c>
       <c r="R81" s="37"/>
       <c r="S81" s="59"/>
@@ -22709,17 +22735,17 @@
         <v>100</v>
       </c>
       <c r="N82" s="51">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="O82" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P82" s="52">
-        <v>4.6247999999999996</v>
+        <v>3.0834999999999999</v>
       </c>
       <c r="Q82" s="52">
         <f t="shared" ref="Q82" si="35">P82*N82</f>
-        <v>27.748799999999996</v>
+        <v>311.43349999999998</v>
       </c>
       <c r="R82" s="51"/>
       <c r="S82" s="59"/>
@@ -22765,7 +22791,7 @@
         <v>100</v>
       </c>
       <c r="N83" s="37">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="O83" s="60" t="s">
         <v>452</v>
@@ -22775,7 +22801,7 @@
       </c>
       <c r="Q83" s="38">
         <f>P83*N83</f>
-        <v>47.400000000000006</v>
+        <v>797.90000000000009</v>
       </c>
       <c r="R83" s="63"/>
       <c r="S83" s="59"/>
@@ -22821,17 +22847,17 @@
         <v>300</v>
       </c>
       <c r="N84" s="51">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c r="O84" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P84" s="52">
-        <v>1.7437</v>
+        <v>1.2091000000000001</v>
       </c>
       <c r="Q84" s="52">
         <f t="shared" ref="Q84" si="36">P84*N84</f>
-        <v>27.8992</v>
+        <v>363.9391</v>
       </c>
       <c r="R84" s="51"/>
       <c r="S84" s="59"/>
@@ -22877,17 +22903,17 @@
         <v>100</v>
       </c>
       <c r="N85" s="37">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="O85" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P85" s="38">
-        <v>7.7799999999999994E-2</v>
+        <v>6.3399999999999998E-2</v>
       </c>
       <c r="Q85" s="38">
         <f>P85*N85</f>
-        <v>0.77799999999999991</v>
+        <v>6.657</v>
       </c>
       <c r="R85" s="37"/>
       <c r="S85" s="59"/>
@@ -22933,17 +22959,17 @@
         <v>100</v>
       </c>
       <c r="N86" s="51">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="O86" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P86" s="52">
-        <v>0.77800000000000002</v>
+        <v>0.53459999999999996</v>
       </c>
       <c r="Q86" s="52">
         <f t="shared" ref="Q86" si="37">P86*N86</f>
-        <v>4.6680000000000001</v>
+        <v>53.994599999999998</v>
       </c>
       <c r="R86" s="51"/>
       <c r="S86" s="59"/>
@@ -22989,17 +23015,17 @@
         <v>100</v>
       </c>
       <c r="N87" s="37">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="O87" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P87" s="38">
-        <v>0.41049999999999998</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="Q87" s="38">
         <f>P87*N87</f>
-        <v>2.4630000000000001</v>
+        <v>28.035</v>
       </c>
       <c r="R87" s="37"/>
       <c r="S87" s="59"/>
@@ -23045,17 +23071,17 @@
         <v>100</v>
       </c>
       <c r="N88" s="51">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="O88" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P88" s="52">
-        <v>1.1837</v>
+        <v>0.77129999999999999</v>
       </c>
       <c r="Q88" s="52">
         <f t="shared" ref="Q88" si="38">P88*N88</f>
-        <v>7.1021999999999998</v>
+        <v>77.901299999999992</v>
       </c>
       <c r="R88" s="51"/>
       <c r="S88" s="59"/>
@@ -23101,17 +23127,17 @@
         <v>100</v>
       </c>
       <c r="N89" s="37">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="O89" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P89" s="38">
-        <v>1.2107000000000001</v>
+        <v>0.8337</v>
       </c>
       <c r="Q89" s="38">
         <f>P89*N89</f>
-        <v>7.2642000000000007</v>
+        <v>84.203699999999998</v>
       </c>
       <c r="R89" s="37"/>
       <c r="S89" s="59"/>
@@ -23157,17 +23183,17 @@
         <v>100</v>
       </c>
       <c r="N90" s="51">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="O90" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P90" s="52">
-        <v>0.08</v>
+        <v>6.6299999999999998E-2</v>
       </c>
       <c r="Q90" s="52">
         <f t="shared" ref="Q90" si="39">P90*N90</f>
-        <v>0.8</v>
+        <v>6.9615</v>
       </c>
       <c r="R90" s="51"/>
       <c r="S90" s="59"/>
@@ -23213,17 +23239,17 @@
         <v>100</v>
       </c>
       <c r="N91" s="37">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="O91" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P91" s="38">
-        <v>0.1065</v>
+        <v>7.6799999999999993E-2</v>
       </c>
       <c r="Q91" s="38">
         <f>P91*N91</f>
-        <v>1.0649999999999999</v>
+        <v>8.0640000000000001</v>
       </c>
       <c r="R91" s="37"/>
       <c r="S91" s="39"/>
@@ -23269,17 +23295,17 @@
         <v>100</v>
       </c>
       <c r="N92" s="37">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="O92" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P92" s="38">
-        <v>1.1609</v>
+        <v>0.89639999999999997</v>
       </c>
       <c r="Q92" s="38">
         <f>P92*N92</f>
-        <v>5.8045</v>
+        <v>89.64</v>
       </c>
       <c r="R92" s="37"/>
       <c r="S92" s="39"/>
@@ -23298,17 +23324,17 @@
       <c r="K93" s="45"/>
       <c r="L93" s="45"/>
       <c r="M93" s="45"/>
-      <c r="N93" s="90" t="s">
+      <c r="N93" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="O93" s="91"/>
-      <c r="P93" s="91"/>
+      <c r="O93" s="98"/>
+      <c r="P93" s="98"/>
       <c r="Q93" s="48">
         <f>SUM(Q10:Q92)</f>
-        <v>290.3445000000001</v>
-      </c>
-      <c r="R93" s="86"/>
-      <c r="S93" s="87"/>
+        <v>3763.9473699999994</v>
+      </c>
+      <c r="R93" s="93"/>
+      <c r="S93" s="94"/>
     </row>
     <row r="94" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
@@ -23324,17 +23350,17 @@
       <c r="K94" s="10"/>
       <c r="L94" s="10"/>
       <c r="M94" s="10"/>
-      <c r="N94" s="90" t="s">
+      <c r="N94" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="O94" s="91"/>
-      <c r="P94" s="91"/>
+      <c r="O94" s="98"/>
+      <c r="P94" s="98"/>
       <c r="Q94" s="49">
         <f>Q93/100</f>
-        <v>2.9034450000000009</v>
-      </c>
-      <c r="R94" s="88"/>
-      <c r="S94" s="89"/>
+        <v>37.639473699999996</v>
+      </c>
+      <c r="R94" s="95"/>
+      <c r="S94" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -23348,83 +23374,83 @@
     <hyperlink ref="O43" r:id="rId1"/>
     <hyperlink ref="O72" r:id="rId2"/>
     <hyperlink ref="O91" r:id="rId3"/>
-    <hyperlink ref="O41" r:id="rId4" display="LCSC"/>
-    <hyperlink ref="O18" r:id="rId5"/>
-    <hyperlink ref="O16" r:id="rId6"/>
-    <hyperlink ref="O83" r:id="rId7"/>
-    <hyperlink ref="O81" r:id="rId8"/>
-    <hyperlink ref="O80" r:id="rId9"/>
-    <hyperlink ref="O67" r:id="rId10"/>
-    <hyperlink ref="O57" r:id="rId11"/>
-    <hyperlink ref="O54" r:id="rId12"/>
-    <hyperlink ref="O50" r:id="rId13"/>
-    <hyperlink ref="O27" r:id="rId14"/>
-    <hyperlink ref="O26" r:id="rId15"/>
-    <hyperlink ref="O20" r:id="rId16"/>
-    <hyperlink ref="O74" r:id="rId17"/>
-    <hyperlink ref="O90" r:id="rId18"/>
-    <hyperlink ref="O89" r:id="rId19"/>
-    <hyperlink ref="O88" r:id="rId20"/>
-    <hyperlink ref="O87" r:id="rId21"/>
-    <hyperlink ref="O86" r:id="rId22"/>
-    <hyperlink ref="O85" r:id="rId23"/>
-    <hyperlink ref="O84" r:id="rId24"/>
-    <hyperlink ref="O82" r:id="rId25"/>
-    <hyperlink ref="O79" r:id="rId26"/>
-    <hyperlink ref="O78" r:id="rId27"/>
-    <hyperlink ref="O77" r:id="rId28"/>
-    <hyperlink ref="O76" r:id="rId29"/>
-    <hyperlink ref="O75" r:id="rId30"/>
-    <hyperlink ref="O71" r:id="rId31"/>
-    <hyperlink ref="O70" r:id="rId32"/>
-    <hyperlink ref="O69" r:id="rId33"/>
-    <hyperlink ref="O68" r:id="rId34"/>
-    <hyperlink ref="O61" r:id="rId35"/>
-    <hyperlink ref="O66" r:id="rId36"/>
-    <hyperlink ref="O65" r:id="rId37"/>
-    <hyperlink ref="O64" r:id="rId38"/>
-    <hyperlink ref="O63" r:id="rId39"/>
-    <hyperlink ref="O60" r:id="rId40"/>
-    <hyperlink ref="O59" r:id="rId41"/>
-    <hyperlink ref="O58" r:id="rId42"/>
-    <hyperlink ref="O56" r:id="rId43"/>
-    <hyperlink ref="O55" r:id="rId44"/>
-    <hyperlink ref="O53" r:id="rId45"/>
-    <hyperlink ref="O52" r:id="rId46"/>
-    <hyperlink ref="O51" r:id="rId47"/>
-    <hyperlink ref="O49" r:id="rId48"/>
-    <hyperlink ref="O47" r:id="rId49"/>
-    <hyperlink ref="O46" r:id="rId50"/>
-    <hyperlink ref="O45" r:id="rId51"/>
-    <hyperlink ref="O44" r:id="rId52"/>
-    <hyperlink ref="O42" r:id="rId53"/>
-    <hyperlink ref="O40" r:id="rId54"/>
-    <hyperlink ref="O38" r:id="rId55"/>
-    <hyperlink ref="O37" r:id="rId56"/>
-    <hyperlink ref="O36" r:id="rId57"/>
-    <hyperlink ref="O35" r:id="rId58"/>
-    <hyperlink ref="O34" r:id="rId59"/>
-    <hyperlink ref="O33" r:id="rId60"/>
-    <hyperlink ref="O32" r:id="rId61"/>
-    <hyperlink ref="O31" r:id="rId62"/>
-    <hyperlink ref="O30" r:id="rId63"/>
-    <hyperlink ref="O29" r:id="rId64"/>
-    <hyperlink ref="O28" r:id="rId65"/>
-    <hyperlink ref="O25" r:id="rId66"/>
-    <hyperlink ref="O24" r:id="rId67"/>
-    <hyperlink ref="O23" r:id="rId68"/>
-    <hyperlink ref="O21" r:id="rId69"/>
-    <hyperlink ref="O22" r:id="rId70"/>
-    <hyperlink ref="O19" r:id="rId71"/>
-    <hyperlink ref="O17" r:id="rId72"/>
-    <hyperlink ref="O14" r:id="rId73"/>
-    <hyperlink ref="O13" r:id="rId74"/>
-    <hyperlink ref="O12" r:id="rId75"/>
-    <hyperlink ref="O11" r:id="rId76"/>
-    <hyperlink ref="O15" r:id="rId77"/>
-    <hyperlink ref="O39" r:id="rId78"/>
-    <hyperlink ref="O62" r:id="rId79"/>
-    <hyperlink ref="O92" r:id="rId80"/>
+    <hyperlink ref="O18" r:id="rId4"/>
+    <hyperlink ref="O16" r:id="rId5"/>
+    <hyperlink ref="O83" r:id="rId6"/>
+    <hyperlink ref="O81" r:id="rId7"/>
+    <hyperlink ref="O80" r:id="rId8"/>
+    <hyperlink ref="O67" r:id="rId9"/>
+    <hyperlink ref="O57" r:id="rId10"/>
+    <hyperlink ref="O54" r:id="rId11"/>
+    <hyperlink ref="O50" r:id="rId12"/>
+    <hyperlink ref="O27" r:id="rId13"/>
+    <hyperlink ref="O26" r:id="rId14"/>
+    <hyperlink ref="O20" r:id="rId15"/>
+    <hyperlink ref="O74" r:id="rId16"/>
+    <hyperlink ref="O90" r:id="rId17"/>
+    <hyperlink ref="O89" r:id="rId18"/>
+    <hyperlink ref="O88" r:id="rId19"/>
+    <hyperlink ref="O87" r:id="rId20"/>
+    <hyperlink ref="O86" r:id="rId21"/>
+    <hyperlink ref="O85" r:id="rId22"/>
+    <hyperlink ref="O84" r:id="rId23"/>
+    <hyperlink ref="O82" r:id="rId24"/>
+    <hyperlink ref="O79" r:id="rId25"/>
+    <hyperlink ref="O78" r:id="rId26"/>
+    <hyperlink ref="O77" r:id="rId27"/>
+    <hyperlink ref="O76" r:id="rId28"/>
+    <hyperlink ref="O75" r:id="rId29"/>
+    <hyperlink ref="O71" r:id="rId30"/>
+    <hyperlink ref="O70" r:id="rId31"/>
+    <hyperlink ref="O69" r:id="rId32"/>
+    <hyperlink ref="O68" r:id="rId33"/>
+    <hyperlink ref="O61" r:id="rId34"/>
+    <hyperlink ref="O66" r:id="rId35"/>
+    <hyperlink ref="O65" r:id="rId36"/>
+    <hyperlink ref="O64" r:id="rId37"/>
+    <hyperlink ref="O63" r:id="rId38"/>
+    <hyperlink ref="O60" r:id="rId39"/>
+    <hyperlink ref="O59" r:id="rId40"/>
+    <hyperlink ref="O58" r:id="rId41"/>
+    <hyperlink ref="O56" r:id="rId42"/>
+    <hyperlink ref="O55" r:id="rId43"/>
+    <hyperlink ref="O53" r:id="rId44"/>
+    <hyperlink ref="O52" r:id="rId45"/>
+    <hyperlink ref="O51" r:id="rId46"/>
+    <hyperlink ref="O49" r:id="rId47"/>
+    <hyperlink ref="O47" r:id="rId48"/>
+    <hyperlink ref="O46" r:id="rId49"/>
+    <hyperlink ref="O45" r:id="rId50"/>
+    <hyperlink ref="O44" r:id="rId51"/>
+    <hyperlink ref="O42" r:id="rId52"/>
+    <hyperlink ref="O40" r:id="rId53"/>
+    <hyperlink ref="O38" r:id="rId54"/>
+    <hyperlink ref="O37" r:id="rId55"/>
+    <hyperlink ref="O36" r:id="rId56"/>
+    <hyperlink ref="O35" r:id="rId57"/>
+    <hyperlink ref="O34" r:id="rId58"/>
+    <hyperlink ref="O33" r:id="rId59"/>
+    <hyperlink ref="O32" r:id="rId60"/>
+    <hyperlink ref="O31" r:id="rId61"/>
+    <hyperlink ref="O30" r:id="rId62"/>
+    <hyperlink ref="O29" r:id="rId63"/>
+    <hyperlink ref="O28" r:id="rId64"/>
+    <hyperlink ref="O25" r:id="rId65"/>
+    <hyperlink ref="O24" r:id="rId66"/>
+    <hyperlink ref="O23" r:id="rId67"/>
+    <hyperlink ref="O21" r:id="rId68"/>
+    <hyperlink ref="O22" r:id="rId69"/>
+    <hyperlink ref="O19" r:id="rId70"/>
+    <hyperlink ref="O17" r:id="rId71"/>
+    <hyperlink ref="O14" r:id="rId72"/>
+    <hyperlink ref="O13" r:id="rId73"/>
+    <hyperlink ref="O12" r:id="rId74"/>
+    <hyperlink ref="O11" r:id="rId75"/>
+    <hyperlink ref="O15" r:id="rId76"/>
+    <hyperlink ref="O39" r:id="rId77"/>
+    <hyperlink ref="O62" r:id="rId78"/>
+    <hyperlink ref="O92" r:id="rId79"/>
+    <hyperlink ref="O41" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId81"/>
@@ -23466,15 +23492,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="83"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="89"/>
+      <c r="Q1" s="89"/>
+      <c r="R1" s="89"/>
+      <c r="S1" s="90"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -23524,7 +23550,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="84"/>
+      <c r="S3" s="91"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -23549,7 +23575,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="85"/>
+      <c r="S4" s="92"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -23574,7 +23600,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="85"/>
+      <c r="S5" s="92"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -23595,7 +23621,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="85"/>
+      <c r="S6" s="92"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -23616,7 +23642,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="85"/>
+      <c r="S7" s="92"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -23637,7 +23663,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="85"/>
+      <c r="S8" s="92"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -23751,7 +23777,7 @@
       <c r="R10" s="63" t="s">
         <v>439</v>
       </c>
-      <c r="S10" s="92"/>
+      <c r="S10" s="82"/>
     </row>
     <row r="11" spans="1:19" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="69"/>
@@ -23794,17 +23820,17 @@
         <v>500</v>
       </c>
       <c r="N11" s="51">
-        <v>20</v>
+        <v>520</v>
       </c>
       <c r="O11" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P11" s="52">
-        <v>2.01E-2</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="Q11" s="52">
         <f t="shared" ref="Q11" si="1">P11*N11</f>
-        <v>0.40200000000000002</v>
+        <v>8.58</v>
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
@@ -23850,17 +23876,17 @@
         <v>12500</v>
       </c>
       <c r="N12" s="37">
-        <v>150</v>
+        <v>12600</v>
       </c>
       <c r="O12" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P12" s="38">
-        <v>1.0500000000000001E-2</v>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="Q12" s="38">
         <f>P12*N12</f>
-        <v>1.5750000000000002</v>
+        <v>74.34</v>
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="59"/>
@@ -23906,17 +23932,17 @@
         <v>1500</v>
       </c>
       <c r="N13" s="51">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="O13" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P13" s="52">
-        <v>8.9999999999999998E-4</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="Q13" s="52">
         <f t="shared" ref="Q13" si="3">P13*N13</f>
-        <v>0.09</v>
+        <v>1.1199999999999999</v>
       </c>
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
@@ -23962,17 +23988,17 @@
         <v>1500</v>
       </c>
       <c r="N14" s="37">
-        <v>20</v>
+        <v>1510</v>
       </c>
       <c r="O14" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P14" s="38">
-        <v>4.9099999999999998E-2</v>
+        <v>3.39E-2</v>
       </c>
       <c r="Q14" s="38">
         <f>P14*N14</f>
-        <v>0.98199999999999998</v>
+        <v>51.189</v>
       </c>
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
@@ -24018,17 +24044,17 @@
         <v>1000</v>
       </c>
       <c r="N15" s="51">
-        <v>11</v>
+        <v>1002</v>
       </c>
       <c r="O15" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P15" s="52">
-        <v>0.25940000000000002</v>
+        <v>0.24660000000000001</v>
       </c>
       <c r="Q15" s="52">
         <f t="shared" ref="Q15" si="4">P15*N15</f>
-        <v>2.8534000000000002</v>
+        <v>247.09320000000002</v>
       </c>
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
@@ -24074,17 +24100,17 @@
         <v>500</v>
       </c>
       <c r="N16" s="37">
-        <v>15</v>
+        <v>505</v>
       </c>
       <c r="O16" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P16" s="38">
-        <v>7.0900000000000005E-2</v>
+        <v>5.0099999999999999E-2</v>
       </c>
       <c r="Q16" s="38">
         <f>P16*N16</f>
-        <v>1.0635000000000001</v>
+        <v>25.3005</v>
       </c>
       <c r="R16" s="37"/>
       <c r="S16" s="59"/>
@@ -24130,17 +24156,17 @@
         <v>500</v>
       </c>
       <c r="N17" s="51">
-        <v>10</v>
+        <v>505</v>
       </c>
       <c r="O17" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P17" s="52">
-        <v>6.3E-2</v>
+        <v>4.19E-2</v>
       </c>
       <c r="Q17" s="52">
         <f t="shared" ref="Q17" si="5">P17*N17</f>
-        <v>0.63</v>
+        <v>21.159500000000001</v>
       </c>
       <c r="R17" s="51"/>
       <c r="S17" s="59"/>
@@ -24186,17 +24212,17 @@
         <v>500</v>
       </c>
       <c r="N18" s="37">
-        <v>6</v>
+        <v>501</v>
       </c>
       <c r="O18" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P18" s="38">
-        <v>1.7373000000000001</v>
+        <v>1.4430000000000001</v>
       </c>
       <c r="Q18" s="38">
         <f>P18*N18</f>
-        <v>10.4238</v>
+        <v>722.94299999999998</v>
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
@@ -24242,17 +24268,17 @@
         <v>500</v>
       </c>
       <c r="N19" s="51">
-        <v>10</v>
+        <v>505</v>
       </c>
       <c r="O19" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P19" s="52">
-        <v>0.26129999999999998</v>
+        <v>0.15129999999999999</v>
       </c>
       <c r="Q19" s="52">
         <f t="shared" ref="Q19" si="6">P19*N19</f>
-        <v>2.6129999999999995</v>
+        <v>76.406499999999994</v>
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
@@ -24298,17 +24324,17 @@
         <v>2000</v>
       </c>
       <c r="N20" s="37">
-        <v>30</v>
+        <v>2020</v>
       </c>
       <c r="O20" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P20" s="38">
-        <v>4.2000000000000003E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="Q20" s="38">
         <f>P20*N20</f>
-        <v>1.26</v>
+        <v>46.46</v>
       </c>
       <c r="R20" s="37"/>
       <c r="S20" s="59"/>
@@ -24354,17 +24380,17 @@
         <v>1000</v>
       </c>
       <c r="N21" s="51">
-        <v>50</v>
+        <v>1050</v>
       </c>
       <c r="O21" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P21" s="52">
-        <v>1.0800000000000001E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="Q21" s="52">
         <f t="shared" ref="Q21" si="7">P21*N21</f>
-        <v>0.54</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
@@ -24410,17 +24436,17 @@
         <v>1000</v>
       </c>
       <c r="N22" s="37">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="O22" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P22" s="38">
-        <v>1E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="Q22" s="38">
         <f>P22*N22</f>
-        <v>0.1</v>
+        <v>0.88</v>
       </c>
       <c r="R22" s="37"/>
       <c r="S22" s="59"/>
@@ -24466,17 +24492,17 @@
         <v>1500</v>
       </c>
       <c r="N23" s="51">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="O23" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P23" s="52">
-        <v>3.8999999999999998E-3</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="Q23" s="52">
         <f t="shared" ref="Q23" si="8">P23*N23</f>
-        <v>0.38999999999999996</v>
+        <v>4.96</v>
       </c>
       <c r="R23" s="51"/>
       <c r="S23" s="59"/>
@@ -24522,17 +24548,17 @@
         <v>500</v>
       </c>
       <c r="N24" s="37">
-        <v>10</v>
+        <v>510</v>
       </c>
       <c r="O24" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P24" s="38">
-        <v>5.5599999999999997E-2</v>
+        <v>3.8699999999999998E-2</v>
       </c>
       <c r="Q24" s="38">
         <f>P24*N24</f>
-        <v>0.55599999999999994</v>
+        <v>19.736999999999998</v>
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="59"/>
@@ -24578,17 +24604,17 @@
         <v>500</v>
       </c>
       <c r="N25" s="51">
-        <v>10</v>
+        <v>510</v>
       </c>
       <c r="O25" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P25" s="52">
-        <v>4.4600000000000001E-2</v>
+        <v>3.2399999999999998E-2</v>
       </c>
       <c r="Q25" s="52">
         <f t="shared" ref="Q25" si="9">P25*N25</f>
-        <v>0.44600000000000001</v>
+        <v>16.523999999999997</v>
       </c>
       <c r="R25" s="51"/>
       <c r="S25" s="59"/>
@@ -24634,17 +24660,17 @@
         <v>500</v>
       </c>
       <c r="N26" s="37">
-        <v>6</v>
+        <v>501</v>
       </c>
       <c r="O26" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P26" s="38">
-        <v>0.46939999999999998</v>
+        <v>0.2928</v>
       </c>
       <c r="Q26" s="38">
         <f>P26*N26</f>
-        <v>2.8163999999999998</v>
+        <v>146.69280000000001</v>
       </c>
       <c r="R26" s="37"/>
       <c r="S26" s="59"/>
@@ -24690,17 +24716,17 @@
         <v>500</v>
       </c>
       <c r="N27" s="51">
-        <v>10</v>
+        <v>510</v>
       </c>
       <c r="O27" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P27" s="52">
-        <v>3.56E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q27" s="52">
         <f t="shared" ref="Q27" si="10">P27*N27</f>
-        <v>0.35599999999999998</v>
+        <v>12.75</v>
       </c>
       <c r="R27" s="51"/>
       <c r="S27" s="59"/>
@@ -24746,17 +24772,17 @@
         <v>1500</v>
       </c>
       <c r="N28" s="37">
-        <v>20</v>
+        <v>1520</v>
       </c>
       <c r="O28" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P28" s="38">
-        <v>2.46E-2</v>
+        <v>1.9099999999999999E-2</v>
       </c>
       <c r="Q28" s="38">
         <f>P28*N28</f>
-        <v>0.49199999999999999</v>
+        <v>29.032</v>
       </c>
       <c r="R28" s="37"/>
       <c r="S28" s="59"/>
@@ -24802,17 +24828,17 @@
         <v>1000</v>
       </c>
       <c r="N29" s="51">
-        <v>20</v>
+        <v>1020</v>
       </c>
       <c r="O29" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P29" s="52">
-        <v>2.3400000000000001E-2</v>
+        <v>1.5299999999999999E-2</v>
       </c>
       <c r="Q29" s="52">
         <f t="shared" ref="Q29" si="11">P29*N29</f>
-        <v>0.46800000000000003</v>
+        <v>15.606</v>
       </c>
       <c r="R29" s="51"/>
       <c r="S29" s="59"/>
@@ -24858,17 +24884,17 @@
         <v>2000</v>
       </c>
       <c r="N30" s="37">
-        <v>25</v>
+        <v>2005</v>
       </c>
       <c r="O30" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P30" s="38">
-        <v>0.1351</v>
+        <v>8.9399999999999993E-2</v>
       </c>
       <c r="Q30" s="38">
         <f>P30*N30</f>
-        <v>3.3774999999999999</v>
+        <v>179.24699999999999</v>
       </c>
       <c r="R30" s="37"/>
       <c r="S30" s="59"/>
@@ -24914,17 +24940,17 @@
         <v>2000</v>
       </c>
       <c r="N31" s="51">
-        <v>30</v>
+        <v>2010</v>
       </c>
       <c r="O31" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P31" s="52">
-        <v>4.7500000000000001E-2</v>
+        <v>3.3799999999999997E-2</v>
       </c>
       <c r="Q31" s="52">
         <f t="shared" ref="Q31" si="12">P31*N31</f>
-        <v>1.425</v>
+        <v>67.937999999999988</v>
       </c>
       <c r="R31" s="51"/>
       <c r="S31" s="59"/>
@@ -24970,17 +24996,17 @@
         <v>500</v>
       </c>
       <c r="N32" s="37">
-        <v>10</v>
+        <v>505</v>
       </c>
       <c r="O32" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P32" s="38">
-        <v>0.2286</v>
+        <v>0.14649999999999999</v>
       </c>
       <c r="Q32" s="38">
         <f>P32*N32</f>
-        <v>2.286</v>
+        <v>73.982500000000002</v>
       </c>
       <c r="R32" s="37"/>
       <c r="S32" s="59"/>
@@ -25026,17 +25052,17 @@
         <v>500</v>
       </c>
       <c r="N33" s="51">
-        <v>6</v>
+        <v>501</v>
       </c>
       <c r="O33" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P33" s="52">
-        <v>1.1482000000000001</v>
+        <v>0.63639999999999997</v>
       </c>
       <c r="Q33" s="52">
         <f t="shared" ref="Q33" si="13">P33*N33</f>
-        <v>6.8892000000000007</v>
+        <v>318.83639999999997</v>
       </c>
       <c r="R33" s="51"/>
       <c r="S33" s="59"/>
@@ -25082,17 +25108,17 @@
         <v>2000</v>
       </c>
       <c r="N34" s="37">
-        <v>30</v>
+        <v>2010</v>
       </c>
       <c r="O34" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P34" s="38">
-        <v>5.6099999999999997E-2</v>
+        <v>3.7600000000000001E-2</v>
       </c>
       <c r="Q34" s="38">
         <f>P34*N34</f>
-        <v>1.6829999999999998</v>
+        <v>75.576000000000008</v>
       </c>
       <c r="R34" s="37"/>
       <c r="S34" s="59"/>
@@ -25138,17 +25164,17 @@
         <v>500</v>
       </c>
       <c r="N35" s="51">
-        <v>10</v>
+        <v>505</v>
       </c>
       <c r="O35" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P35" s="52">
-        <v>8.8300000000000003E-2</v>
+        <v>4.3900000000000002E-2</v>
       </c>
       <c r="Q35" s="52">
         <f t="shared" ref="Q35" si="14">P35*N35</f>
-        <v>0.88300000000000001</v>
+        <v>22.169499999999999</v>
       </c>
       <c r="R35" s="51"/>
       <c r="S35" s="59"/>
@@ -25194,17 +25220,17 @@
         <v>4000</v>
       </c>
       <c r="N36" s="37">
-        <v>45</v>
+        <v>4005</v>
       </c>
       <c r="O36" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P36" s="38">
-        <v>0.2316</v>
+        <v>0.1145</v>
       </c>
       <c r="Q36" s="38">
         <f>P36*N36</f>
-        <v>10.422000000000001</v>
+        <v>458.57249999999999</v>
       </c>
       <c r="R36" s="37"/>
       <c r="S36" s="59"/>
@@ -25250,17 +25276,17 @@
         <v>500</v>
       </c>
       <c r="N37" s="51">
-        <v>10</v>
+        <v>505</v>
       </c>
       <c r="O37" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P37" s="52">
-        <v>0.21590000000000001</v>
+        <v>0.1615</v>
       </c>
       <c r="Q37" s="52">
         <f t="shared" ref="Q37" si="15">P37*N37</f>
-        <v>2.1590000000000003</v>
+        <v>81.557500000000005</v>
       </c>
       <c r="R37" s="51"/>
       <c r="S37" s="59"/>
@@ -25306,17 +25332,17 @@
         <v>2000</v>
       </c>
       <c r="N38" s="37">
-        <v>25</v>
+        <v>2005</v>
       </c>
       <c r="O38" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P38" s="38">
-        <v>0.17299999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>4.3249999999999993</v>
+        <v>180.45</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="59"/>
@@ -25362,17 +25388,17 @@
         <v>500</v>
       </c>
       <c r="N39" s="51">
-        <v>10</v>
+        <v>505</v>
       </c>
       <c r="O39" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P39" s="52">
-        <v>0.14860000000000001</v>
+        <v>0.1056</v>
       </c>
       <c r="Q39" s="52">
         <f t="shared" ref="Q39" si="16">P39*N39</f>
-        <v>1.4860000000000002</v>
+        <v>53.328000000000003</v>
       </c>
       <c r="R39" s="51"/>
       <c r="S39" s="59"/>
@@ -25418,17 +25444,17 @@
         <v>500</v>
       </c>
       <c r="N40" s="37">
-        <v>12</v>
+        <v>504</v>
       </c>
       <c r="O40" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P40" s="38">
-        <v>7.0400000000000004E-2</v>
+        <v>4.7300000000000002E-2</v>
       </c>
       <c r="Q40" s="38">
         <f>P40*N40</f>
-        <v>0.8448</v>
+        <v>23.839200000000002</v>
       </c>
       <c r="R40" s="37"/>
       <c r="S40" s="59"/>
@@ -25457,11 +25483,15 @@
       <c r="H41" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="I41" s="51"/>
+      <c r="I41" s="51" t="s">
+        <v>429</v>
+      </c>
       <c r="J41" s="51" t="s">
         <v>505</v>
       </c>
-      <c r="K41" s="51"/>
+      <c r="K41" s="51" t="s">
+        <v>429</v>
+      </c>
       <c r="L41" s="51">
         <v>1</v>
       </c>
@@ -25469,12 +25499,18 @@
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="N41" s="51"/>
-      <c r="O41" s="51"/>
-      <c r="P41" s="52"/>
+      <c r="N41" s="51">
+        <v>501</v>
+      </c>
+      <c r="O41" s="60" t="s">
+        <v>435</v>
+      </c>
+      <c r="P41" s="52">
+        <v>0.42670000000000002</v>
+      </c>
       <c r="Q41" s="52">
         <f t="shared" ref="Q41" si="17">P41*N41</f>
-        <v>0</v>
+        <v>213.77670000000001</v>
       </c>
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
@@ -25520,17 +25556,17 @@
         <v>1000</v>
       </c>
       <c r="N42" s="37">
-        <v>11</v>
+        <v>1002</v>
       </c>
       <c r="O42" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P42" s="38">
-        <v>0.81459999999999999</v>
+        <v>0.61570000000000003</v>
       </c>
       <c r="Q42" s="38">
         <f>P42*N42</f>
-        <v>8.9605999999999995</v>
+        <v>616.93140000000005</v>
       </c>
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
@@ -25576,7 +25612,7 @@
         <v>1500</v>
       </c>
       <c r="N43" s="51">
-        <v>16</v>
+        <v>1502</v>
       </c>
       <c r="O43" s="60" t="s">
         <v>480</v>
@@ -25586,7 +25622,7 @@
       </c>
       <c r="Q43" s="52">
         <f t="shared" ref="Q43" si="18">P43*N43</f>
-        <v>16.16</v>
+        <v>1517.02</v>
       </c>
       <c r="R43" s="51"/>
       <c r="S43" s="59"/>
@@ -25632,17 +25668,17 @@
         <v>500</v>
       </c>
       <c r="N44" s="37">
-        <v>10</v>
+        <v>505</v>
       </c>
       <c r="O44" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P44" s="38">
-        <v>0.2137</v>
+        <v>0.1547</v>
       </c>
       <c r="Q44" s="38">
         <f>P44*N44</f>
-        <v>2.137</v>
+        <v>78.123500000000007</v>
       </c>
       <c r="R44" s="37"/>
       <c r="S44" s="59"/>
@@ -25688,17 +25724,17 @@
         <v>500</v>
       </c>
       <c r="N45" s="51">
-        <v>50</v>
+        <v>550</v>
       </c>
       <c r="O45" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P45" s="52">
-        <v>8.3000000000000001E-3</v>
+        <v>6.7999999999999996E-3</v>
       </c>
       <c r="Q45" s="52">
         <f t="shared" ref="Q45" si="19">P45*N45</f>
-        <v>0.41499999999999998</v>
+        <v>3.7399999999999998</v>
       </c>
       <c r="R45" s="51"/>
       <c r="S45" s="59"/>
@@ -25744,17 +25780,17 @@
         <v>1000</v>
       </c>
       <c r="N46" s="37">
-        <v>20</v>
+        <v>1020</v>
       </c>
       <c r="O46" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P46" s="38">
-        <v>5.7599999999999998E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="Q46" s="38">
         <f>P46*N46</f>
-        <v>1.1519999999999999</v>
+        <v>41.616</v>
       </c>
       <c r="R46" s="37"/>
       <c r="S46" s="59"/>
@@ -25800,17 +25836,17 @@
         <v>500</v>
       </c>
       <c r="N47" s="51">
-        <v>10</v>
+        <v>510</v>
       </c>
       <c r="O47" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P47" s="52">
-        <v>5.1499999999999997E-2</v>
+        <v>3.8100000000000002E-2</v>
       </c>
       <c r="Q47" s="52">
         <f t="shared" ref="Q47" si="20">P47*N47</f>
-        <v>0.51500000000000001</v>
+        <v>19.431000000000001</v>
       </c>
       <c r="R47" s="51"/>
       <c r="S47" s="59"/>
@@ -25851,7 +25887,7 @@
       <c r="L48" s="62">
         <v>9</v>
       </c>
-      <c r="M48" s="51">
+      <c r="M48" s="62">
         <f t="shared" si="2"/>
         <v>4500</v>
       </c>
@@ -25911,17 +25947,17 @@
         <v>500</v>
       </c>
       <c r="N49" s="51">
-        <v>20</v>
+        <v>520</v>
       </c>
       <c r="O49" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P49" s="52">
-        <v>2.1000000000000001E-2</v>
+        <v>1.6299999999999999E-2</v>
       </c>
       <c r="Q49" s="52">
         <f t="shared" ref="Q49" si="21">P49*N49</f>
-        <v>0.42000000000000004</v>
+        <v>8.4759999999999991</v>
       </c>
       <c r="R49" s="51"/>
       <c r="S49" s="59"/>
@@ -25967,17 +26003,17 @@
         <v>1000</v>
       </c>
       <c r="N50" s="37">
-        <v>20</v>
+        <v>1020</v>
       </c>
       <c r="O50" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P50" s="38">
-        <v>2.1700000000000001E-2</v>
+        <v>1.7100000000000001E-2</v>
       </c>
       <c r="Q50" s="38">
         <f>P50*N50</f>
-        <v>0.434</v>
+        <v>17.442</v>
       </c>
       <c r="R50" s="37"/>
       <c r="S50" s="59"/>
@@ -26080,7 +26116,7 @@
         <v>500</v>
       </c>
       <c r="N52" s="37">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="O52" s="60" t="s">
         <v>435</v>
@@ -26090,7 +26126,7 @@
       </c>
       <c r="Q52" s="38">
         <f>P52*N52</f>
-        <v>0.26</v>
+        <v>1.5599999999999998</v>
       </c>
       <c r="R52" s="37"/>
       <c r="S52" s="59"/>
@@ -26136,17 +26172,17 @@
         <v>6000</v>
       </c>
       <c r="N53" s="51">
-        <v>100</v>
+        <v>6100</v>
       </c>
       <c r="O53" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P53" s="52">
-        <v>8.9999999999999998E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="Q53" s="52">
         <f t="shared" ref="Q53" si="22">P53*N53</f>
-        <v>0.09</v>
+        <v>3.6599999999999997</v>
       </c>
       <c r="R53" s="51"/>
       <c r="S53" s="59"/>
@@ -26192,17 +26228,17 @@
         <v>4000</v>
       </c>
       <c r="N54" s="37">
-        <v>100</v>
+        <v>4100</v>
       </c>
       <c r="O54" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P54" s="38">
-        <v>8.9999999999999998E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="Q54" s="38">
         <f>P54*N54</f>
-        <v>0.09</v>
+        <v>2.46</v>
       </c>
       <c r="R54" s="37"/>
       <c r="S54" s="59"/>
@@ -26248,7 +26284,7 @@
         <v>500</v>
       </c>
       <c r="N55" s="51">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="O55" s="60" t="s">
         <v>435</v>
@@ -26258,7 +26294,7 @@
       </c>
       <c r="Q55" s="52">
         <f t="shared" ref="Q55" si="23">P55*N55</f>
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="R55" s="51"/>
       <c r="S55" s="59"/>
@@ -26304,17 +26340,17 @@
         <v>1000</v>
       </c>
       <c r="N56" s="37">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="O56" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P56" s="38">
-        <v>8.0000000000000004E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="Q56" s="38">
         <f>P56*N56</f>
-        <v>0.08</v>
+        <v>0.65999999999999992</v>
       </c>
       <c r="R56" s="37"/>
       <c r="S56" s="59"/>
@@ -26360,7 +26396,7 @@
         <v>1000</v>
       </c>
       <c r="N57" s="51">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="O57" s="60" t="s">
         <v>435</v>
@@ -26370,7 +26406,7 @@
       </c>
       <c r="Q57" s="52">
         <f t="shared" ref="Q57" si="24">P57*N57</f>
-        <v>0.05</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="R57" s="51"/>
       <c r="S57" s="59"/>
@@ -26416,17 +26452,17 @@
         <v>1000</v>
       </c>
       <c r="N58" s="37">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="O58" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P58" s="38">
-        <v>6.9999999999999999E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q58" s="38">
         <f>P58*N58</f>
-        <v>6.9999999999999993E-2</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="R58" s="37"/>
       <c r="S58" s="59"/>
@@ -26472,17 +26508,17 @@
         <v>11000</v>
       </c>
       <c r="N59" s="51">
-        <v>200</v>
+        <v>11100</v>
       </c>
       <c r="O59" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P59" s="52">
-        <v>6.9999999999999999E-4</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="Q59" s="52">
         <f t="shared" ref="Q59" si="25">P59*N59</f>
-        <v>0.13999999999999999</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="R59" s="51"/>
       <c r="S59" s="59"/>
@@ -26528,7 +26564,7 @@
         <v>500</v>
       </c>
       <c r="N60" s="37">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="O60" s="60" t="s">
         <v>435</v>
@@ -26538,7 +26574,7 @@
       </c>
       <c r="Q60" s="38">
         <f>P60*N60</f>
-        <v>0.06</v>
+        <v>0.36</v>
       </c>
       <c r="R60" s="37"/>
       <c r="S60" s="59"/>
@@ -26584,17 +26620,17 @@
         <v>5500</v>
       </c>
       <c r="N61" s="37">
-        <v>100</v>
+        <v>5600</v>
       </c>
       <c r="O61" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P61" s="38">
-        <v>6.9999999999999999E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q61" s="38">
         <f>P61*N61</f>
-        <v>6.9999999999999993E-2</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="R61" s="37"/>
       <c r="S61" s="59"/>
@@ -26640,17 +26676,17 @@
         <v>1500</v>
       </c>
       <c r="N62" s="37">
-        <v>100</v>
+        <v>1600</v>
       </c>
       <c r="O62" s="73" t="s">
         <v>435</v>
       </c>
       <c r="P62" s="38">
-        <v>6.8999999999999999E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="Q62" s="38">
         <f>P62*N62</f>
-        <v>0.69</v>
+        <v>10.24</v>
       </c>
       <c r="R62" s="37"/>
       <c r="S62" s="59"/>
@@ -26696,17 +26732,17 @@
         <v>2000</v>
       </c>
       <c r="N63" s="37">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="O63" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P63" s="38">
-        <v>6.9999999999999999E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q63" s="38">
         <f>P63*N63</f>
-        <v>6.9999999999999993E-2</v>
+        <v>1.05</v>
       </c>
       <c r="R63" s="37"/>
       <c r="S63" s="59"/>
@@ -26752,7 +26788,7 @@
         <v>500</v>
       </c>
       <c r="N64" s="51">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="O64" s="60" t="s">
         <v>435</v>
@@ -26762,7 +26798,7 @@
       </c>
       <c r="Q64" s="52">
         <f t="shared" ref="Q64" si="26">P64*N64</f>
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="R64" s="51"/>
       <c r="S64" s="59"/>
@@ -26808,7 +26844,7 @@
         <v>500</v>
       </c>
       <c r="N65" s="37">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="O65" s="60" t="s">
         <v>435</v>
@@ -26818,7 +26854,7 @@
       </c>
       <c r="Q65" s="38">
         <f>P65*N65</f>
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="R65" s="37"/>
       <c r="S65" s="59"/>
@@ -26864,7 +26900,7 @@
         <v>500</v>
       </c>
       <c r="N66" s="51">
-        <v>20</v>
+        <v>600</v>
       </c>
       <c r="O66" s="60" t="s">
         <v>435</v>
@@ -26874,7 +26910,7 @@
       </c>
       <c r="Q66" s="52">
         <f t="shared" ref="Q66:Q67" si="27">P66*N66</f>
-        <v>0.52</v>
+        <v>15.6</v>
       </c>
       <c r="R66" s="51"/>
       <c r="S66" s="59"/>
@@ -26920,7 +26956,7 @@
         <v>2000</v>
       </c>
       <c r="N67" s="51">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="O67" s="60" t="s">
         <v>435</v>
@@ -26930,7 +26966,7 @@
       </c>
       <c r="Q67" s="52">
         <f t="shared" si="27"/>
-        <v>0.04</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="R67" s="51"/>
       <c r="S67" s="59"/>
@@ -26974,7 +27010,7 @@
         <v>500</v>
       </c>
       <c r="N68" s="37">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="O68" s="60" t="s">
         <v>435</v>
@@ -26984,7 +27020,7 @@
       </c>
       <c r="Q68" s="38">
         <f>P68*N68</f>
-        <v>0.12</v>
+        <v>0.72</v>
       </c>
       <c r="R68" s="37"/>
       <c r="S68" s="59"/>
@@ -27028,17 +27064,17 @@
         <v>500</v>
       </c>
       <c r="N69" s="51">
-        <v>10</v>
+        <v>505</v>
       </c>
       <c r="O69" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P69" s="52">
-        <v>5.3600000000000002E-2</v>
+        <v>4.3099999999999999E-2</v>
       </c>
       <c r="Q69" s="52">
         <f t="shared" ref="Q69" si="28">P69*N69</f>
-        <v>0.53600000000000003</v>
+        <v>21.765499999999999</v>
       </c>
       <c r="R69" s="51"/>
       <c r="S69" s="59"/>
@@ -27082,17 +27118,17 @@
         <v>1000</v>
       </c>
       <c r="N70" s="37">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="O70" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P70" s="38">
-        <v>1.1999999999999999E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="Q70" s="38">
         <f>P70*N70</f>
-        <v>0.12</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="R70" s="37"/>
       <c r="S70" s="59"/>
@@ -27136,7 +27172,7 @@
         <v>500</v>
       </c>
       <c r="N71" s="51">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="O71" s="60" t="s">
         <v>435</v>
@@ -27146,7 +27182,7 @@
       </c>
       <c r="Q71" s="52">
         <f t="shared" ref="Q71:Q72" si="29">P71*N71</f>
-        <v>6.9999999999999993E-2</v>
+        <v>0.42</v>
       </c>
       <c r="R71" s="51"/>
       <c r="S71" s="59"/>
@@ -27192,17 +27228,17 @@
         <v>1000</v>
       </c>
       <c r="N72" s="51">
-        <v>50</v>
+        <v>1050</v>
       </c>
       <c r="O72" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P72" s="52">
-        <v>8.6999999999999994E-3</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="Q72" s="52">
         <f t="shared" si="29"/>
-        <v>0.43499999999999994</v>
+        <v>7.4550000000000001</v>
       </c>
       <c r="R72" s="51"/>
       <c r="S72" s="59"/>
@@ -27305,17 +27341,17 @@
         <v>500</v>
       </c>
       <c r="N74" s="51">
-        <v>10</v>
+        <v>505</v>
       </c>
       <c r="O74" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P74" s="52">
-        <v>0.1275</v>
+        <v>0.09</v>
       </c>
       <c r="Q74" s="52">
         <f t="shared" ref="Q74" si="30">P74*N74</f>
-        <v>1.2749999999999999</v>
+        <v>45.449999999999996</v>
       </c>
       <c r="R74" s="51"/>
       <c r="S74" s="59"/>
@@ -27361,17 +27397,17 @@
         <v>500</v>
       </c>
       <c r="N75" s="37">
-        <v>6</v>
+        <v>501</v>
       </c>
       <c r="O75" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P75" s="38">
-        <v>0.82569999999999999</v>
+        <v>0.44230000000000003</v>
       </c>
       <c r="Q75" s="38">
         <f>P75*N75</f>
-        <v>4.9542000000000002</v>
+        <v>221.59230000000002</v>
       </c>
       <c r="R75" s="37"/>
       <c r="S75" s="59"/>
@@ -27417,17 +27453,17 @@
         <v>500</v>
       </c>
       <c r="N76" s="51">
-        <v>6</v>
+        <v>501</v>
       </c>
       <c r="O76" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P76" s="52">
-        <v>0.70009999999999994</v>
+        <v>0.41370000000000001</v>
       </c>
       <c r="Q76" s="52">
         <f t="shared" ref="Q76" si="32">P76*N76</f>
-        <v>4.2005999999999997</v>
+        <v>207.2637</v>
       </c>
       <c r="R76" s="51"/>
       <c r="S76" s="59"/>
@@ -27473,17 +27509,17 @@
         <v>500</v>
       </c>
       <c r="N77" s="37">
-        <v>10</v>
+        <v>505</v>
       </c>
       <c r="O77" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P77" s="38">
-        <v>0.32279999999999998</v>
+        <v>0.18110000000000001</v>
       </c>
       <c r="Q77" s="38">
         <f>P77*N77</f>
-        <v>3.2279999999999998</v>
+        <v>91.455500000000001</v>
       </c>
       <c r="R77" s="37"/>
       <c r="S77" s="59"/>
@@ -27529,17 +27565,17 @@
         <v>500</v>
       </c>
       <c r="N78" s="51">
-        <v>6</v>
+        <v>501</v>
       </c>
       <c r="O78" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P78" s="52">
-        <v>1.3062</v>
+        <v>0.83320000000000005</v>
       </c>
       <c r="Q78" s="52">
         <f t="shared" ref="Q78" si="33">P78*N78</f>
-        <v>7.8372000000000002</v>
+        <v>417.4332</v>
       </c>
       <c r="R78" s="51"/>
       <c r="S78" s="59"/>
@@ -27583,17 +27619,17 @@
         <v>500</v>
       </c>
       <c r="N79" s="37">
-        <v>6</v>
+        <v>501</v>
       </c>
       <c r="O79" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P79" s="38">
-        <v>0.3644</v>
+        <v>0.21</v>
       </c>
       <c r="Q79" s="38">
         <f>P79*N79</f>
-        <v>2.1863999999999999</v>
+        <v>105.21</v>
       </c>
       <c r="R79" s="37"/>
       <c r="S79" s="59"/>
@@ -27639,7 +27675,7 @@
         <v>500</v>
       </c>
       <c r="N80" s="51">
-        <v>6</v>
+        <v>501</v>
       </c>
       <c r="O80" s="60" t="s">
         <v>452</v>
@@ -27649,7 +27685,7 @@
       </c>
       <c r="Q80" s="52">
         <f t="shared" ref="Q80" si="34">P80*N80</f>
-        <v>15.059999999999999</v>
+        <v>1257.51</v>
       </c>
       <c r="R80" s="51"/>
       <c r="S80" s="59"/>
@@ -27695,17 +27731,17 @@
         <v>500</v>
       </c>
       <c r="N81" s="37">
-        <v>6</v>
+        <v>501</v>
       </c>
       <c r="O81" s="60" t="s">
         <v>452</v>
       </c>
       <c r="P81" s="38">
-        <v>3.4329999999999998</v>
+        <v>1.88815</v>
       </c>
       <c r="Q81" s="38">
         <f>P81*N81</f>
-        <v>20.597999999999999</v>
+        <v>945.96315000000004</v>
       </c>
       <c r="R81" s="37"/>
       <c r="S81" s="59"/>
@@ -27749,17 +27785,17 @@
         <v>500</v>
       </c>
       <c r="N82" s="51">
-        <v>6</v>
+        <v>501</v>
       </c>
       <c r="O82" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P82" s="52">
-        <v>4.6247999999999996</v>
+        <v>2.9295</v>
       </c>
       <c r="Q82" s="52">
         <f t="shared" ref="Q82" si="35">P82*N82</f>
-        <v>27.748799999999996</v>
+        <v>1467.6795</v>
       </c>
       <c r="R82" s="51"/>
       <c r="S82" s="59"/>
@@ -27805,7 +27841,7 @@
         <v>500</v>
       </c>
       <c r="N83" s="37">
-        <v>6</v>
+        <v>501</v>
       </c>
       <c r="O83" s="60" t="s">
         <v>452</v>
@@ -27815,7 +27851,7 @@
       </c>
       <c r="Q83" s="38">
         <f>P83*N83</f>
-        <v>47.400000000000006</v>
+        <v>3957.9</v>
       </c>
       <c r="R83" s="63"/>
       <c r="S83" s="59"/>
@@ -27861,17 +27897,17 @@
         <v>1500</v>
       </c>
       <c r="N84" s="51">
-        <v>16</v>
+        <v>1502</v>
       </c>
       <c r="O84" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P84" s="52">
-        <v>1.7437</v>
+        <v>1.0834999999999999</v>
       </c>
       <c r="Q84" s="52">
         <f t="shared" ref="Q84" si="36">P84*N84</f>
-        <v>27.8992</v>
+        <v>1627.4169999999999</v>
       </c>
       <c r="R84" s="51"/>
       <c r="S84" s="59"/>
@@ -27917,17 +27953,17 @@
         <v>500</v>
       </c>
       <c r="N85" s="37">
-        <v>10</v>
+        <v>505</v>
       </c>
       <c r="O85" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P85" s="38">
-        <v>7.7799999999999994E-2</v>
+        <v>4.9299999999999997E-2</v>
       </c>
       <c r="Q85" s="38">
         <f>P85*N85</f>
-        <v>0.77799999999999991</v>
+        <v>24.8965</v>
       </c>
       <c r="R85" s="37"/>
       <c r="S85" s="59"/>
@@ -27973,17 +28009,17 @@
         <v>500</v>
       </c>
       <c r="N86" s="51">
-        <v>6</v>
+        <v>501</v>
       </c>
       <c r="O86" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P86" s="52">
-        <v>0.77800000000000002</v>
+        <v>0.51229999999999998</v>
       </c>
       <c r="Q86" s="52">
         <f t="shared" ref="Q86" si="37">P86*N86</f>
-        <v>4.6680000000000001</v>
+        <v>256.66230000000002</v>
       </c>
       <c r="R86" s="51"/>
       <c r="S86" s="59"/>
@@ -28029,17 +28065,17 @@
         <v>500</v>
       </c>
       <c r="N87" s="37">
-        <v>6</v>
+        <v>505</v>
       </c>
       <c r="O87" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P87" s="38">
-        <v>0.41049999999999998</v>
+        <v>0.2026</v>
       </c>
       <c r="Q87" s="38">
         <f>P87*N87</f>
-        <v>2.4630000000000001</v>
+        <v>102.313</v>
       </c>
       <c r="R87" s="37"/>
       <c r="S87" s="59"/>
@@ -28085,17 +28121,17 @@
         <v>500</v>
       </c>
       <c r="N88" s="51">
-        <v>6</v>
+        <v>501</v>
       </c>
       <c r="O88" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P88" s="52">
-        <v>1.1837</v>
+        <v>0.73709999999999998</v>
       </c>
       <c r="Q88" s="52">
         <f t="shared" ref="Q88" si="38">P88*N88</f>
-        <v>7.1021999999999998</v>
+        <v>369.28710000000001</v>
       </c>
       <c r="R88" s="51"/>
       <c r="S88" s="59"/>
@@ -28141,17 +28177,17 @@
         <v>500</v>
       </c>
       <c r="N89" s="37">
-        <v>6</v>
+        <v>501</v>
       </c>
       <c r="O89" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P89" s="38">
-        <v>1.2107000000000001</v>
+        <v>0.7923</v>
       </c>
       <c r="Q89" s="38">
         <f>P89*N89</f>
-        <v>7.2642000000000007</v>
+        <v>396.94229999999999</v>
       </c>
       <c r="R89" s="37"/>
       <c r="S89" s="59"/>
@@ -28197,17 +28233,17 @@
         <v>500</v>
       </c>
       <c r="N90" s="51">
-        <v>10</v>
+        <v>505</v>
       </c>
       <c r="O90" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P90" s="52">
-        <v>0.08</v>
+        <v>5.3699999999999998E-2</v>
       </c>
       <c r="Q90" s="52">
         <f t="shared" ref="Q90" si="39">P90*N90</f>
-        <v>0.8</v>
+        <v>27.118499999999997</v>
       </c>
       <c r="R90" s="51"/>
       <c r="S90" s="59"/>
@@ -28253,17 +28289,17 @@
         <v>500</v>
       </c>
       <c r="N91" s="37">
-        <v>10</v>
+        <v>505</v>
       </c>
       <c r="O91" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P91" s="38">
-        <v>0.1065</v>
+        <v>6.7900000000000002E-2</v>
       </c>
       <c r="Q91" s="38">
         <f>P91*N91</f>
-        <v>1.0649999999999999</v>
+        <v>34.289500000000004</v>
       </c>
       <c r="R91" s="37"/>
       <c r="S91" s="39"/>
@@ -28309,17 +28345,17 @@
         <v>500</v>
       </c>
       <c r="N92" s="37">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="O92" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P92" s="38">
-        <v>1.1609</v>
+        <v>0.89639999999999997</v>
       </c>
       <c r="Q92" s="38">
         <f>P92*N92</f>
-        <v>5.8045</v>
+        <v>448.2</v>
       </c>
       <c r="R92" s="37"/>
       <c r="S92" s="39"/>
@@ -28338,17 +28374,17 @@
       <c r="K93" s="45"/>
       <c r="L93" s="45"/>
       <c r="M93" s="45"/>
-      <c r="N93" s="90" t="s">
+      <c r="N93" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="O93" s="91"/>
-      <c r="P93" s="91"/>
+      <c r="O93" s="98"/>
+      <c r="P93" s="98"/>
       <c r="Q93" s="48">
         <f>SUM(Q10:Q92)</f>
-        <v>290.3445000000001</v>
-      </c>
-      <c r="R93" s="86"/>
-      <c r="S93" s="87"/>
+        <v>17665.910750000003</v>
+      </c>
+      <c r="R93" s="93"/>
+      <c r="S93" s="94"/>
     </row>
     <row r="94" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
@@ -28364,17 +28400,17 @@
       <c r="K94" s="10"/>
       <c r="L94" s="10"/>
       <c r="M94" s="10"/>
-      <c r="N94" s="90" t="s">
+      <c r="N94" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="O94" s="91"/>
-      <c r="P94" s="91"/>
+      <c r="O94" s="98"/>
+      <c r="P94" s="98"/>
       <c r="Q94" s="49">
         <f>Q93/500</f>
-        <v>0.58068900000000023</v>
-      </c>
-      <c r="R94" s="88"/>
-      <c r="S94" s="89"/>
+        <v>35.331821500000004</v>
+      </c>
+      <c r="R94" s="95"/>
+      <c r="S94" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -28388,83 +28424,83 @@
     <hyperlink ref="O43" r:id="rId1"/>
     <hyperlink ref="O72" r:id="rId2"/>
     <hyperlink ref="O91" r:id="rId3"/>
-    <hyperlink ref="O41" r:id="rId4" display="LCSC"/>
-    <hyperlink ref="O18" r:id="rId5"/>
-    <hyperlink ref="O16" r:id="rId6"/>
-    <hyperlink ref="O83" r:id="rId7"/>
-    <hyperlink ref="O81" r:id="rId8"/>
-    <hyperlink ref="O80" r:id="rId9"/>
-    <hyperlink ref="O67" r:id="rId10"/>
-    <hyperlink ref="O57" r:id="rId11"/>
-    <hyperlink ref="O54" r:id="rId12"/>
-    <hyperlink ref="O50" r:id="rId13"/>
-    <hyperlink ref="O27" r:id="rId14"/>
-    <hyperlink ref="O26" r:id="rId15"/>
-    <hyperlink ref="O20" r:id="rId16"/>
-    <hyperlink ref="O74" r:id="rId17"/>
-    <hyperlink ref="O90" r:id="rId18"/>
-    <hyperlink ref="O89" r:id="rId19"/>
-    <hyperlink ref="O88" r:id="rId20"/>
-    <hyperlink ref="O87" r:id="rId21"/>
-    <hyperlink ref="O86" r:id="rId22"/>
-    <hyperlink ref="O85" r:id="rId23"/>
-    <hyperlink ref="O84" r:id="rId24"/>
-    <hyperlink ref="O82" r:id="rId25"/>
-    <hyperlink ref="O79" r:id="rId26"/>
-    <hyperlink ref="O78" r:id="rId27"/>
-    <hyperlink ref="O77" r:id="rId28"/>
-    <hyperlink ref="O76" r:id="rId29"/>
-    <hyperlink ref="O75" r:id="rId30"/>
-    <hyperlink ref="O71" r:id="rId31"/>
-    <hyperlink ref="O70" r:id="rId32"/>
-    <hyperlink ref="O69" r:id="rId33"/>
-    <hyperlink ref="O68" r:id="rId34"/>
-    <hyperlink ref="O61" r:id="rId35"/>
-    <hyperlink ref="O66" r:id="rId36"/>
-    <hyperlink ref="O65" r:id="rId37"/>
-    <hyperlink ref="O64" r:id="rId38"/>
-    <hyperlink ref="O63" r:id="rId39"/>
-    <hyperlink ref="O60" r:id="rId40"/>
-    <hyperlink ref="O59" r:id="rId41"/>
-    <hyperlink ref="O58" r:id="rId42"/>
-    <hyperlink ref="O56" r:id="rId43"/>
-    <hyperlink ref="O55" r:id="rId44"/>
-    <hyperlink ref="O53" r:id="rId45"/>
-    <hyperlink ref="O52" r:id="rId46"/>
-    <hyperlink ref="O51" r:id="rId47"/>
-    <hyperlink ref="O49" r:id="rId48"/>
-    <hyperlink ref="O47" r:id="rId49"/>
-    <hyperlink ref="O46" r:id="rId50"/>
-    <hyperlink ref="O45" r:id="rId51"/>
-    <hyperlink ref="O44" r:id="rId52"/>
-    <hyperlink ref="O42" r:id="rId53"/>
-    <hyperlink ref="O40" r:id="rId54"/>
-    <hyperlink ref="O38" r:id="rId55"/>
-    <hyperlink ref="O37" r:id="rId56"/>
-    <hyperlink ref="O36" r:id="rId57"/>
-    <hyperlink ref="O35" r:id="rId58"/>
-    <hyperlink ref="O34" r:id="rId59"/>
-    <hyperlink ref="O33" r:id="rId60"/>
-    <hyperlink ref="O32" r:id="rId61"/>
-    <hyperlink ref="O31" r:id="rId62"/>
-    <hyperlink ref="O30" r:id="rId63"/>
-    <hyperlink ref="O29" r:id="rId64"/>
-    <hyperlink ref="O28" r:id="rId65"/>
-    <hyperlink ref="O25" r:id="rId66"/>
-    <hyperlink ref="O24" r:id="rId67"/>
-    <hyperlink ref="O23" r:id="rId68"/>
-    <hyperlink ref="O21" r:id="rId69"/>
-    <hyperlink ref="O22" r:id="rId70"/>
-    <hyperlink ref="O19" r:id="rId71"/>
-    <hyperlink ref="O17" r:id="rId72"/>
-    <hyperlink ref="O14" r:id="rId73"/>
-    <hyperlink ref="O13" r:id="rId74"/>
-    <hyperlink ref="O12" r:id="rId75"/>
-    <hyperlink ref="O11" r:id="rId76"/>
-    <hyperlink ref="O15" r:id="rId77"/>
-    <hyperlink ref="O39" r:id="rId78"/>
-    <hyperlink ref="O62" r:id="rId79"/>
-    <hyperlink ref="O92" r:id="rId80"/>
+    <hyperlink ref="O18" r:id="rId4"/>
+    <hyperlink ref="O16" r:id="rId5"/>
+    <hyperlink ref="O83" r:id="rId6"/>
+    <hyperlink ref="O81" r:id="rId7"/>
+    <hyperlink ref="O80" r:id="rId8"/>
+    <hyperlink ref="O67" r:id="rId9"/>
+    <hyperlink ref="O57" r:id="rId10"/>
+    <hyperlink ref="O54" r:id="rId11"/>
+    <hyperlink ref="O50" r:id="rId12"/>
+    <hyperlink ref="O27" r:id="rId13"/>
+    <hyperlink ref="O26" r:id="rId14"/>
+    <hyperlink ref="O20" r:id="rId15"/>
+    <hyperlink ref="O74" r:id="rId16"/>
+    <hyperlink ref="O90" r:id="rId17"/>
+    <hyperlink ref="O89" r:id="rId18"/>
+    <hyperlink ref="O88" r:id="rId19"/>
+    <hyperlink ref="O87" r:id="rId20"/>
+    <hyperlink ref="O86" r:id="rId21"/>
+    <hyperlink ref="O85" r:id="rId22"/>
+    <hyperlink ref="O84" r:id="rId23"/>
+    <hyperlink ref="O82" r:id="rId24"/>
+    <hyperlink ref="O79" r:id="rId25"/>
+    <hyperlink ref="O78" r:id="rId26"/>
+    <hyperlink ref="O77" r:id="rId27"/>
+    <hyperlink ref="O76" r:id="rId28"/>
+    <hyperlink ref="O75" r:id="rId29"/>
+    <hyperlink ref="O71" r:id="rId30"/>
+    <hyperlink ref="O70" r:id="rId31"/>
+    <hyperlink ref="O69" r:id="rId32"/>
+    <hyperlink ref="O68" r:id="rId33"/>
+    <hyperlink ref="O61" r:id="rId34"/>
+    <hyperlink ref="O66" r:id="rId35"/>
+    <hyperlink ref="O65" r:id="rId36"/>
+    <hyperlink ref="O64" r:id="rId37"/>
+    <hyperlink ref="O63" r:id="rId38"/>
+    <hyperlink ref="O60" r:id="rId39"/>
+    <hyperlink ref="O59" r:id="rId40"/>
+    <hyperlink ref="O58" r:id="rId41"/>
+    <hyperlink ref="O56" r:id="rId42"/>
+    <hyperlink ref="O55" r:id="rId43"/>
+    <hyperlink ref="O53" r:id="rId44"/>
+    <hyperlink ref="O52" r:id="rId45"/>
+    <hyperlink ref="O51" r:id="rId46"/>
+    <hyperlink ref="O49" r:id="rId47"/>
+    <hyperlink ref="O47" r:id="rId48"/>
+    <hyperlink ref="O46" r:id="rId49"/>
+    <hyperlink ref="O45" r:id="rId50"/>
+    <hyperlink ref="O44" r:id="rId51"/>
+    <hyperlink ref="O42" r:id="rId52"/>
+    <hyperlink ref="O40" r:id="rId53"/>
+    <hyperlink ref="O38" r:id="rId54"/>
+    <hyperlink ref="O37" r:id="rId55"/>
+    <hyperlink ref="O36" r:id="rId56"/>
+    <hyperlink ref="O35" r:id="rId57"/>
+    <hyperlink ref="O34" r:id="rId58"/>
+    <hyperlink ref="O33" r:id="rId59"/>
+    <hyperlink ref="O32" r:id="rId60"/>
+    <hyperlink ref="O31" r:id="rId61"/>
+    <hyperlink ref="O30" r:id="rId62"/>
+    <hyperlink ref="O29" r:id="rId63"/>
+    <hyperlink ref="O28" r:id="rId64"/>
+    <hyperlink ref="O25" r:id="rId65"/>
+    <hyperlink ref="O24" r:id="rId66"/>
+    <hyperlink ref="O23" r:id="rId67"/>
+    <hyperlink ref="O21" r:id="rId68"/>
+    <hyperlink ref="O22" r:id="rId69"/>
+    <hyperlink ref="O19" r:id="rId70"/>
+    <hyperlink ref="O17" r:id="rId71"/>
+    <hyperlink ref="O14" r:id="rId72"/>
+    <hyperlink ref="O13" r:id="rId73"/>
+    <hyperlink ref="O12" r:id="rId74"/>
+    <hyperlink ref="O11" r:id="rId75"/>
+    <hyperlink ref="O15" r:id="rId76"/>
+    <hyperlink ref="O39" r:id="rId77"/>
+    <hyperlink ref="O62" r:id="rId78"/>
+    <hyperlink ref="O92" r:id="rId79"/>
+    <hyperlink ref="O41" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId81"/>
@@ -28507,15 +28543,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="83"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="89"/>
+      <c r="Q1" s="89"/>
+      <c r="R1" s="89"/>
+      <c r="S1" s="90"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -28565,7 +28601,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="84"/>
+      <c r="S3" s="91"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -28590,7 +28626,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="85"/>
+      <c r="S4" s="92"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -28615,7 +28651,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="85"/>
+      <c r="S5" s="92"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -28636,7 +28672,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="85"/>
+      <c r="S6" s="92"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -28657,7 +28693,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="85"/>
+      <c r="S7" s="92"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -28678,7 +28714,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="85"/>
+      <c r="S8" s="92"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -28792,7 +28828,7 @@
       <c r="R10" s="63" t="s">
         <v>439</v>
       </c>
-      <c r="S10" s="92"/>
+      <c r="S10" s="82"/>
     </row>
     <row r="11" spans="1:19" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="69"/>
@@ -28835,17 +28871,17 @@
         <v>1000</v>
       </c>
       <c r="N11" s="51">
-        <v>20</v>
+        <v>1020</v>
       </c>
       <c r="O11" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P11" s="52">
-        <v>2.01E-2</v>
+        <v>1.44E-2</v>
       </c>
       <c r="Q11" s="52">
         <f t="shared" ref="Q11" si="1">P11*N11</f>
-        <v>0.40200000000000002</v>
+        <v>14.687999999999999</v>
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
@@ -28891,17 +28927,17 @@
         <v>25000</v>
       </c>
       <c r="N12" s="37">
-        <v>150</v>
+        <v>25050</v>
       </c>
       <c r="O12" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P12" s="38">
-        <v>1.0500000000000001E-2</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="Q12" s="38">
         <f>P12*N12</f>
-        <v>1.5750000000000002</v>
+        <v>137.77500000000001</v>
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="59"/>
@@ -28947,17 +28983,17 @@
         <v>3000</v>
       </c>
       <c r="N13" s="51">
-        <v>100</v>
+        <v>3100</v>
       </c>
       <c r="O13" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P13" s="52">
-        <v>8.9999999999999998E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="Q13" s="52">
         <f t="shared" ref="Q13" si="3">P13*N13</f>
-        <v>0.09</v>
+        <v>1.8599999999999999</v>
       </c>
       <c r="R13" s="51"/>
       <c r="S13" s="59"/>
@@ -29003,17 +29039,17 @@
         <v>3000</v>
       </c>
       <c r="N14" s="37">
-        <v>20</v>
+        <v>3010</v>
       </c>
       <c r="O14" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P14" s="38">
-        <v>4.9099999999999998E-2</v>
+        <v>3.39E-2</v>
       </c>
       <c r="Q14" s="38">
         <f>P14*N14</f>
-        <v>0.98199999999999998</v>
+        <v>102.039</v>
       </c>
       <c r="R14" s="37"/>
       <c r="S14" s="59"/>
@@ -29059,17 +29095,17 @@
         <v>2000</v>
       </c>
       <c r="N15" s="51">
-        <v>11</v>
+        <v>2002</v>
       </c>
       <c r="O15" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P15" s="52">
-        <v>0.25940000000000002</v>
+        <v>0.24660000000000001</v>
       </c>
       <c r="Q15" s="52">
         <f t="shared" ref="Q15" si="4">P15*N15</f>
-        <v>2.8534000000000002</v>
+        <v>493.69320000000005</v>
       </c>
       <c r="R15" s="51"/>
       <c r="S15" s="59"/>
@@ -29115,17 +29151,17 @@
         <v>1000</v>
       </c>
       <c r="N16" s="37">
-        <v>15</v>
+        <v>1005</v>
       </c>
       <c r="O16" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P16" s="38">
-        <v>7.0900000000000005E-2</v>
+        <v>5.0099999999999999E-2</v>
       </c>
       <c r="Q16" s="38">
         <f>P16*N16</f>
-        <v>1.0635000000000001</v>
+        <v>50.350499999999997</v>
       </c>
       <c r="R16" s="37"/>
       <c r="S16" s="59"/>
@@ -29171,17 +29207,17 @@
         <v>1000</v>
       </c>
       <c r="N17" s="51">
-        <v>10</v>
+        <v>1005</v>
       </c>
       <c r="O17" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P17" s="52">
-        <v>6.3E-2</v>
+        <v>4.19E-2</v>
       </c>
       <c r="Q17" s="52">
         <f t="shared" ref="Q17" si="5">P17*N17</f>
-        <v>0.63</v>
+        <v>42.109499999999997</v>
       </c>
       <c r="R17" s="51"/>
       <c r="S17" s="59"/>
@@ -29227,17 +29263,17 @@
         <v>1000</v>
       </c>
       <c r="N18" s="37">
-        <v>6</v>
+        <v>1001</v>
       </c>
       <c r="O18" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P18" s="38">
-        <v>1.7373000000000001</v>
+        <v>1.4430000000000001</v>
       </c>
       <c r="Q18" s="38">
         <f>P18*N18</f>
-        <v>10.4238</v>
+        <v>1444.443</v>
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="59"/>
@@ -29283,17 +29319,17 @@
         <v>1000</v>
       </c>
       <c r="N19" s="51">
-        <v>10</v>
+        <v>1005</v>
       </c>
       <c r="O19" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P19" s="52">
-        <v>0.26129999999999998</v>
+        <v>0.15129999999999999</v>
       </c>
       <c r="Q19" s="52">
         <f t="shared" ref="Q19" si="6">P19*N19</f>
-        <v>2.6129999999999995</v>
+        <v>152.0565</v>
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="59"/>
@@ -29339,17 +29375,17 @@
         <v>4000</v>
       </c>
       <c r="N20" s="37">
-        <v>30</v>
+        <v>4020</v>
       </c>
       <c r="O20" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P20" s="38">
-        <v>4.2000000000000003E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="Q20" s="38">
         <f>P20*N20</f>
-        <v>1.26</v>
+        <v>92.46</v>
       </c>
       <c r="R20" s="37"/>
       <c r="S20" s="59"/>
@@ -29395,17 +29431,17 @@
         <v>2000</v>
       </c>
       <c r="N21" s="51">
-        <v>50</v>
+        <v>2050</v>
       </c>
       <c r="O21" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P21" s="52">
-        <v>1.0800000000000001E-2</v>
+        <v>7.9000000000000008E-3</v>
       </c>
       <c r="Q21" s="52">
         <f t="shared" ref="Q21" si="7">P21*N21</f>
-        <v>0.54</v>
+        <v>16.195</v>
       </c>
       <c r="R21" s="51"/>
       <c r="S21" s="59"/>
@@ -29451,17 +29487,17 @@
         <v>2000</v>
       </c>
       <c r="N22" s="37">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="O22" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P22" s="38">
-        <v>1E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="Q22" s="38">
         <f>P22*N22</f>
-        <v>0.1</v>
+        <v>1.6800000000000002</v>
       </c>
       <c r="R22" s="37"/>
       <c r="S22" s="59"/>
@@ -29507,17 +29543,17 @@
         <v>3000</v>
       </c>
       <c r="N23" s="51">
-        <v>100</v>
+        <v>3100</v>
       </c>
       <c r="O23" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P23" s="52">
-        <v>3.8999999999999998E-3</v>
+        <v>3.0999999999999999E-3</v>
       </c>
       <c r="Q23" s="52">
         <f t="shared" ref="Q23" si="8">P23*N23</f>
-        <v>0.38999999999999996</v>
+        <v>9.61</v>
       </c>
       <c r="R23" s="51"/>
       <c r="S23" s="59"/>
@@ -29563,17 +29599,17 @@
         <v>1000</v>
       </c>
       <c r="N24" s="37">
-        <v>10</v>
+        <v>1010</v>
       </c>
       <c r="O24" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P24" s="38">
-        <v>5.5599999999999997E-2</v>
+        <v>3.4700000000000002E-2</v>
       </c>
       <c r="Q24" s="38">
         <f>P24*N24</f>
-        <v>0.55599999999999994</v>
+        <v>35.047000000000004</v>
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="59"/>
@@ -29619,17 +29655,17 @@
         <v>1000</v>
       </c>
       <c r="N25" s="51">
-        <v>10</v>
+        <v>1010</v>
       </c>
       <c r="O25" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P25" s="52">
-        <v>4.4600000000000001E-2</v>
+        <v>2.5700000000000001E-2</v>
       </c>
       <c r="Q25" s="52">
         <f t="shared" ref="Q25" si="9">P25*N25</f>
-        <v>0.44600000000000001</v>
+        <v>25.957000000000001</v>
       </c>
       <c r="R25" s="51"/>
       <c r="S25" s="59"/>
@@ -29675,17 +29711,17 @@
         <v>1000</v>
       </c>
       <c r="N26" s="37">
-        <v>6</v>
+        <v>1002</v>
       </c>
       <c r="O26" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P26" s="38">
-        <v>0.46939999999999998</v>
+        <v>0.28010000000000002</v>
       </c>
       <c r="Q26" s="38">
         <f>P26*N26</f>
-        <v>2.8163999999999998</v>
+        <v>280.66020000000003</v>
       </c>
       <c r="R26" s="37"/>
       <c r="S26" s="59"/>
@@ -29731,17 +29767,17 @@
         <v>1000</v>
       </c>
       <c r="N27" s="51">
-        <v>10</v>
+        <v>1010</v>
       </c>
       <c r="O27" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P27" s="52">
-        <v>3.56E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q27" s="52">
         <f t="shared" ref="Q27" si="10">P27*N27</f>
-        <v>0.35599999999999998</v>
+        <v>25.25</v>
       </c>
       <c r="R27" s="51"/>
       <c r="S27" s="59"/>
@@ -29787,17 +29823,17 @@
         <v>3000</v>
       </c>
       <c r="N28" s="37">
-        <v>20</v>
+        <v>3020</v>
       </c>
       <c r="O28" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P28" s="38">
-        <v>2.46E-2</v>
+        <v>1.72E-2</v>
       </c>
       <c r="Q28" s="38">
         <f>P28*N28</f>
-        <v>0.49199999999999999</v>
+        <v>51.944000000000003</v>
       </c>
       <c r="R28" s="37"/>
       <c r="S28" s="59"/>
@@ -29843,17 +29879,17 @@
         <v>2000</v>
       </c>
       <c r="N29" s="51">
-        <v>20</v>
+        <v>2020</v>
       </c>
       <c r="O29" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P29" s="52">
-        <v>2.3400000000000001E-2</v>
+        <v>1.5299999999999999E-2</v>
       </c>
       <c r="Q29" s="52">
         <f t="shared" ref="Q29" si="11">P29*N29</f>
-        <v>0.46800000000000003</v>
+        <v>30.905999999999999</v>
       </c>
       <c r="R29" s="51"/>
       <c r="S29" s="59"/>
@@ -29899,17 +29935,17 @@
         <v>4000</v>
       </c>
       <c r="N30" s="37">
-        <v>25</v>
+        <v>4005</v>
       </c>
       <c r="O30" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P30" s="38">
-        <v>0.1351</v>
+        <v>8.2100000000000006E-2</v>
       </c>
       <c r="Q30" s="38">
         <f>P30*N30</f>
-        <v>3.3774999999999999</v>
+        <v>328.81050000000005</v>
       </c>
       <c r="R30" s="37"/>
       <c r="S30" s="59"/>
@@ -29955,17 +29991,17 @@
         <v>4000</v>
       </c>
       <c r="N31" s="51">
-        <v>30</v>
+        <v>4010</v>
       </c>
       <c r="O31" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P31" s="52">
-        <v>4.7500000000000001E-2</v>
+        <v>2.8899999999999999E-2</v>
       </c>
       <c r="Q31" s="52">
         <f t="shared" ref="Q31" si="12">P31*N31</f>
-        <v>1.425</v>
+        <v>115.889</v>
       </c>
       <c r="R31" s="51"/>
       <c r="S31" s="59"/>
@@ -30011,17 +30047,17 @@
         <v>1000</v>
       </c>
       <c r="N32" s="37">
-        <v>10</v>
+        <v>1005</v>
       </c>
       <c r="O32" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P32" s="38">
-        <v>0.2286</v>
+        <v>0.14649999999999999</v>
       </c>
       <c r="Q32" s="38">
         <f>P32*N32</f>
-        <v>2.286</v>
+        <v>147.23249999999999</v>
       </c>
       <c r="R32" s="37"/>
       <c r="S32" s="59"/>
@@ -30067,17 +30103,17 @@
         <v>1000</v>
       </c>
       <c r="N33" s="51">
-        <v>6</v>
+        <v>1002</v>
       </c>
       <c r="O33" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P33" s="52">
-        <v>1.1482000000000001</v>
+        <v>0.61570000000000003</v>
       </c>
       <c r="Q33" s="52">
         <f t="shared" ref="Q33" si="13">P33*N33</f>
-        <v>6.8892000000000007</v>
+        <v>616.93140000000005</v>
       </c>
       <c r="R33" s="51"/>
       <c r="S33" s="59"/>
@@ -30123,22 +30159,22 @@
         <v>4000</v>
       </c>
       <c r="N34" s="37">
-        <v>30</v>
+        <v>4010</v>
       </c>
       <c r="O34" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P34" s="38">
-        <v>5.6099999999999997E-2</v>
+        <v>3.7600000000000001E-2</v>
       </c>
       <c r="Q34" s="38">
         <f>P34*N34</f>
-        <v>1.6829999999999998</v>
+        <v>150.77600000000001</v>
       </c>
       <c r="R34" s="37"/>
       <c r="S34" s="59"/>
     </row>
-    <row r="35" spans="1:19" s="70" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="69"/>
       <c r="B35" s="47">
         <f t="shared" si="0"/>
@@ -30179,17 +30215,17 @@
         <v>1000</v>
       </c>
       <c r="N35" s="51">
-        <v>10</v>
+        <v>1005</v>
       </c>
       <c r="O35" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P35" s="52">
-        <v>8.8300000000000003E-2</v>
+        <v>4.3900000000000002E-2</v>
       </c>
       <c r="Q35" s="52">
         <f t="shared" ref="Q35" si="14">P35*N35</f>
-        <v>0.88300000000000001</v>
+        <v>44.119500000000002</v>
       </c>
       <c r="R35" s="51"/>
       <c r="S35" s="59"/>
@@ -30235,17 +30271,17 @@
         <v>8000</v>
       </c>
       <c r="N36" s="37">
-        <v>45</v>
+        <v>8005</v>
       </c>
       <c r="O36" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P36" s="38">
-        <v>0.2316</v>
+        <v>0.1085</v>
       </c>
       <c r="Q36" s="38">
         <f>P36*N36</f>
-        <v>10.422000000000001</v>
+        <v>868.54250000000002</v>
       </c>
       <c r="R36" s="37"/>
       <c r="S36" s="59"/>
@@ -30291,17 +30327,17 @@
         <v>1000</v>
       </c>
       <c r="N37" s="51">
-        <v>10</v>
+        <v>1005</v>
       </c>
       <c r="O37" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P37" s="52">
-        <v>0.21590000000000001</v>
+        <v>0.14549999999999999</v>
       </c>
       <c r="Q37" s="52">
         <f t="shared" ref="Q37" si="15">P37*N37</f>
-        <v>2.1590000000000003</v>
+        <v>146.22749999999999</v>
       </c>
       <c r="R37" s="51"/>
       <c r="S37" s="59"/>
@@ -30347,17 +30383,17 @@
         <v>4000</v>
       </c>
       <c r="N38" s="37">
-        <v>25</v>
+        <v>4005</v>
       </c>
       <c r="O38" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P38" s="38">
-        <v>0.17299999999999999</v>
+        <v>8.2799999999999999E-2</v>
       </c>
       <c r="Q38" s="38">
         <f>P38*N38</f>
-        <v>4.3249999999999993</v>
+        <v>331.61399999999998</v>
       </c>
       <c r="R38" s="37"/>
       <c r="S38" s="59"/>
@@ -30403,17 +30439,17 @@
         <v>1000</v>
       </c>
       <c r="N39" s="51">
-        <v>10</v>
+        <v>1005</v>
       </c>
       <c r="O39" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P39" s="52">
-        <v>0.14860000000000001</v>
+        <v>8.9499999999999996E-2</v>
       </c>
       <c r="Q39" s="52">
         <f t="shared" ref="Q39" si="16">P39*N39</f>
-        <v>1.4860000000000002</v>
+        <v>89.947499999999991</v>
       </c>
       <c r="R39" s="51"/>
       <c r="S39" s="59"/>
@@ -30459,17 +30495,17 @@
         <v>1000</v>
       </c>
       <c r="N40" s="37">
-        <v>12</v>
+        <v>1008</v>
       </c>
       <c r="O40" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P40" s="38">
-        <v>7.0400000000000004E-2</v>
+        <v>4.7300000000000002E-2</v>
       </c>
       <c r="Q40" s="38">
         <f>P40*N40</f>
-        <v>0.8448</v>
+        <v>47.678400000000003</v>
       </c>
       <c r="R40" s="37"/>
       <c r="S40" s="59"/>
@@ -30498,11 +30534,15 @@
       <c r="H41" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="I41" s="51"/>
+      <c r="I41" s="51" t="s">
+        <v>429</v>
+      </c>
       <c r="J41" s="51" t="s">
         <v>505</v>
       </c>
-      <c r="K41" s="51"/>
+      <c r="K41" s="51" t="s">
+        <v>429</v>
+      </c>
       <c r="L41" s="51">
         <v>1</v>
       </c>
@@ -30510,12 +30550,18 @@
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="N41" s="51"/>
-      <c r="O41" s="51"/>
-      <c r="P41" s="52"/>
+      <c r="N41" s="51">
+        <v>1001</v>
+      </c>
+      <c r="O41" s="60" t="s">
+        <v>435</v>
+      </c>
+      <c r="P41" s="52">
+        <v>0.40679999999999999</v>
+      </c>
       <c r="Q41" s="52">
         <f t="shared" ref="Q41" si="17">P41*N41</f>
-        <v>0</v>
+        <v>407.20679999999999</v>
       </c>
       <c r="R41" s="51"/>
       <c r="S41" s="59"/>
@@ -30561,22 +30607,22 @@
         <v>2000</v>
       </c>
       <c r="N42" s="37">
-        <v>11</v>
+        <v>2002</v>
       </c>
       <c r="O42" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P42" s="38">
-        <v>0.81459999999999999</v>
+        <v>0.59030000000000005</v>
       </c>
       <c r="Q42" s="38">
         <f>P42*N42</f>
-        <v>8.9605999999999995</v>
+        <v>1181.7806</v>
       </c>
       <c r="R42" s="37"/>
       <c r="S42" s="59"/>
     </row>
-    <row r="43" spans="1:19" s="70" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A43" s="69"/>
       <c r="B43" s="47">
         <f t="shared" si="0"/>
@@ -30617,7 +30663,7 @@
         <v>3000</v>
       </c>
       <c r="N43" s="51">
-        <v>16</v>
+        <v>3001</v>
       </c>
       <c r="O43" s="60" t="s">
         <v>480</v>
@@ -30627,7 +30673,7 @@
       </c>
       <c r="Q43" s="52">
         <f t="shared" ref="Q43" si="18">P43*N43</f>
-        <v>16.16</v>
+        <v>3031.01</v>
       </c>
       <c r="R43" s="51"/>
       <c r="S43" s="59"/>
@@ -30673,17 +30719,17 @@
         <v>1000</v>
       </c>
       <c r="N44" s="37">
-        <v>10</v>
+        <v>1005</v>
       </c>
       <c r="O44" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P44" s="38">
-        <v>0.2137</v>
+        <v>0.1288</v>
       </c>
       <c r="Q44" s="38">
         <f>P44*N44</f>
-        <v>2.137</v>
+        <v>129.44399999999999</v>
       </c>
       <c r="R44" s="37"/>
       <c r="S44" s="59"/>
@@ -30729,17 +30775,17 @@
         <v>1000</v>
       </c>
       <c r="N45" s="51">
-        <v>50</v>
+        <v>1050</v>
       </c>
       <c r="O45" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P45" s="52">
-        <v>8.3000000000000001E-3</v>
+        <v>6.7999999999999996E-3</v>
       </c>
       <c r="Q45" s="52">
         <f t="shared" ref="Q45" si="19">P45*N45</f>
-        <v>0.41499999999999998</v>
+        <v>7.14</v>
       </c>
       <c r="R45" s="51"/>
       <c r="S45" s="59"/>
@@ -30785,17 +30831,17 @@
         <v>2000</v>
       </c>
       <c r="N46" s="37">
-        <v>20</v>
+        <v>2020</v>
       </c>
       <c r="O46" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P46" s="38">
-        <v>5.7599999999999998E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="Q46" s="38">
         <f>P46*N46</f>
-        <v>1.1519999999999999</v>
+        <v>82.416000000000011</v>
       </c>
       <c r="R46" s="37"/>
       <c r="S46" s="59"/>
@@ -30841,17 +30887,17 @@
         <v>1000</v>
       </c>
       <c r="N47" s="51">
-        <v>10</v>
+        <v>1010</v>
       </c>
       <c r="O47" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P47" s="52">
-        <v>5.1499999999999997E-2</v>
+        <v>3.8100000000000002E-2</v>
       </c>
       <c r="Q47" s="52">
         <f t="shared" ref="Q47" si="20">P47*N47</f>
-        <v>0.51500000000000001</v>
+        <v>38.481000000000002</v>
       </c>
       <c r="R47" s="51"/>
       <c r="S47" s="59"/>
@@ -30892,7 +30938,7 @@
       <c r="L48" s="62">
         <v>9</v>
       </c>
-      <c r="M48" s="51">
+      <c r="M48" s="62">
         <f t="shared" si="2"/>
         <v>9000</v>
       </c>
@@ -30952,17 +30998,17 @@
         <v>1000</v>
       </c>
       <c r="N49" s="51">
-        <v>20</v>
+        <v>1020</v>
       </c>
       <c r="O49" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P49" s="52">
-        <v>2.1000000000000001E-2</v>
+        <v>1.41E-2</v>
       </c>
       <c r="Q49" s="52">
         <f t="shared" ref="Q49" si="21">P49*N49</f>
-        <v>0.42000000000000004</v>
+        <v>14.382</v>
       </c>
       <c r="R49" s="51"/>
       <c r="S49" s="59"/>
@@ -31008,17 +31054,17 @@
         <v>2000</v>
       </c>
       <c r="N50" s="37">
-        <v>20</v>
+        <v>2020</v>
       </c>
       <c r="O50" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P50" s="38">
-        <v>2.1700000000000001E-2</v>
+        <v>1.5699999999999999E-2</v>
       </c>
       <c r="Q50" s="38">
         <f>P50*N50</f>
-        <v>0.434</v>
+        <v>31.713999999999999</v>
       </c>
       <c r="R50" s="37"/>
       <c r="S50" s="59"/>
@@ -31121,17 +31167,17 @@
         <v>1000</v>
       </c>
       <c r="N52" s="37">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="O52" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P52" s="38">
-        <v>2.5999999999999999E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="Q52" s="38">
         <f>P52*N52</f>
-        <v>0.26</v>
+        <v>2.75</v>
       </c>
       <c r="R52" s="37"/>
       <c r="S52" s="59"/>
@@ -31177,17 +31223,17 @@
         <v>12000</v>
       </c>
       <c r="N53" s="51">
-        <v>100</v>
+        <v>12100</v>
       </c>
       <c r="O53" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P53" s="52">
-        <v>8.9999999999999998E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="Q53" s="52">
         <f t="shared" ref="Q53" si="22">P53*N53</f>
-        <v>0.09</v>
+        <v>7.26</v>
       </c>
       <c r="R53" s="51"/>
       <c r="S53" s="59"/>
@@ -31233,17 +31279,17 @@
         <v>8000</v>
       </c>
       <c r="N54" s="37">
-        <v>100</v>
+        <v>8100</v>
       </c>
       <c r="O54" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P54" s="38">
-        <v>8.9999999999999998E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="Q54" s="38">
         <f>P54*N54</f>
-        <v>0.09</v>
+        <v>4.8599999999999994</v>
       </c>
       <c r="R54" s="37"/>
       <c r="S54" s="59"/>
@@ -31289,17 +31335,17 @@
         <v>1000</v>
       </c>
       <c r="N55" s="51">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="O55" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P55" s="52">
-        <v>1E-3</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="Q55" s="52">
         <f t="shared" ref="Q55" si="23">P55*N55</f>
-        <v>0.1</v>
+        <v>0.88</v>
       </c>
       <c r="R55" s="51"/>
       <c r="S55" s="59"/>
@@ -31345,17 +31391,17 @@
         <v>2000</v>
       </c>
       <c r="N56" s="37">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="O56" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P56" s="38">
-        <v>8.0000000000000004E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="Q56" s="38">
         <f>P56*N56</f>
-        <v>0.08</v>
+        <v>1.2599999999999998</v>
       </c>
       <c r="R56" s="37"/>
       <c r="S56" s="59"/>
@@ -31401,7 +31447,7 @@
         <v>2000</v>
       </c>
       <c r="N57" s="51">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="O57" s="60" t="s">
         <v>435</v>
@@ -31411,7 +31457,7 @@
       </c>
       <c r="Q57" s="52">
         <f t="shared" ref="Q57" si="24">P57*N57</f>
-        <v>0.05</v>
+        <v>1.05</v>
       </c>
       <c r="R57" s="51"/>
       <c r="S57" s="59"/>
@@ -31457,17 +31503,17 @@
         <v>2000</v>
       </c>
       <c r="N58" s="37">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="O58" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P58" s="38">
-        <v>6.9999999999999999E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q58" s="38">
         <f>P58*N58</f>
-        <v>6.9999999999999993E-2</v>
+        <v>1.05</v>
       </c>
       <c r="R58" s="37"/>
       <c r="S58" s="59"/>
@@ -31513,17 +31559,17 @@
         <v>22000</v>
       </c>
       <c r="N59" s="51">
-        <v>200</v>
+        <v>22100</v>
       </c>
       <c r="O59" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P59" s="52">
-        <v>6.9999999999999999E-4</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="Q59" s="52">
         <f t="shared" ref="Q59" si="25">P59*N59</f>
-        <v>0.13999999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="R59" s="51"/>
       <c r="S59" s="59"/>
@@ -31569,17 +31615,17 @@
         <v>1000</v>
       </c>
       <c r="N60" s="37">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="O60" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P60" s="38">
-        <v>5.9999999999999995E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q60" s="38">
         <f>P60*N60</f>
-        <v>0.06</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="R60" s="37"/>
       <c r="S60" s="59"/>
@@ -31625,17 +31671,17 @@
         <v>11000</v>
       </c>
       <c r="N61" s="37">
-        <v>100</v>
+        <v>11100</v>
       </c>
       <c r="O61" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P61" s="38">
-        <v>6.9999999999999999E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q61" s="38">
         <f>P61*N61</f>
-        <v>6.9999999999999993E-2</v>
+        <v>5.55</v>
       </c>
       <c r="R61" s="37"/>
       <c r="S61" s="59"/>
@@ -31681,17 +31727,17 @@
         <v>3000</v>
       </c>
       <c r="N62" s="37">
-        <v>100</v>
+        <v>3100</v>
       </c>
       <c r="O62" s="73" t="s">
         <v>435</v>
       </c>
       <c r="P62" s="38">
-        <v>6.8999999999999999E-3</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="Q62" s="38">
         <f>P62*N62</f>
-        <v>0.69</v>
+        <v>19.84</v>
       </c>
       <c r="R62" s="37"/>
       <c r="S62" s="59"/>
@@ -31737,17 +31783,17 @@
         <v>4000</v>
       </c>
       <c r="N63" s="37">
-        <v>100</v>
+        <v>4100</v>
       </c>
       <c r="O63" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P63" s="38">
-        <v>6.9999999999999999E-4</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="Q63" s="38">
         <f>P63*N63</f>
-        <v>6.9999999999999993E-2</v>
+        <v>1.6400000000000001</v>
       </c>
       <c r="R63" s="37"/>
       <c r="S63" s="59"/>
@@ -31793,17 +31839,17 @@
         <v>1000</v>
       </c>
       <c r="N64" s="51">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="O64" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P64" s="52">
-        <v>1.1999999999999999E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="Q64" s="52">
         <f t="shared" ref="Q64" si="26">P64*N64</f>
-        <v>0.12</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="R64" s="51"/>
       <c r="S64" s="59"/>
@@ -31849,17 +31895,17 @@
         <v>1000</v>
       </c>
       <c r="N65" s="37">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="O65" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P65" s="38">
-        <v>2.5000000000000001E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="Q65" s="38">
         <f>P65*N65</f>
-        <v>0.25</v>
+        <v>2.09</v>
       </c>
       <c r="R65" s="37"/>
       <c r="S65" s="59"/>
@@ -31905,17 +31951,17 @@
         <v>1000</v>
       </c>
       <c r="N66" s="51">
-        <v>20</v>
+        <v>1020</v>
       </c>
       <c r="O66" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P66" s="52">
-        <v>2.5999999999999999E-2</v>
+        <v>1.8800000000000001E-2</v>
       </c>
       <c r="Q66" s="52">
         <f t="shared" ref="Q66:Q67" si="27">P66*N66</f>
-        <v>0.52</v>
+        <v>19.176000000000002</v>
       </c>
       <c r="R66" s="51"/>
       <c r="S66" s="59"/>
@@ -31961,17 +32007,17 @@
         <v>4000</v>
       </c>
       <c r="N67" s="51">
-        <v>100</v>
+        <v>4100</v>
       </c>
       <c r="O67" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P67" s="52">
-        <v>4.0000000000000002E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="Q67" s="52">
         <f t="shared" si="27"/>
-        <v>0.04</v>
+        <v>1.23</v>
       </c>
       <c r="R67" s="51"/>
       <c r="S67" s="59"/>
@@ -32015,17 +32061,17 @@
         <v>1000</v>
       </c>
       <c r="N68" s="37">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="O68" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P68" s="38">
-        <v>1.1999999999999999E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="Q68" s="38">
         <f>P68*N68</f>
-        <v>0.12</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="R68" s="37"/>
       <c r="S68" s="59"/>
@@ -32069,17 +32115,17 @@
         <v>1000</v>
       </c>
       <c r="N69" s="51">
-        <v>10</v>
+        <v>1005</v>
       </c>
       <c r="O69" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P69" s="52">
-        <v>5.3600000000000002E-2</v>
+        <v>4.3099999999999999E-2</v>
       </c>
       <c r="Q69" s="52">
         <f t="shared" ref="Q69" si="28">P69*N69</f>
-        <v>0.53600000000000003</v>
+        <v>43.3155</v>
       </c>
       <c r="R69" s="51"/>
       <c r="S69" s="59"/>
@@ -32123,17 +32169,17 @@
         <v>2000</v>
       </c>
       <c r="N70" s="37">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="O70" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P70" s="38">
-        <v>1.1999999999999999E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="Q70" s="38">
         <f>P70*N70</f>
-        <v>0.12</v>
+        <v>2.1</v>
       </c>
       <c r="R70" s="37"/>
       <c r="S70" s="59"/>
@@ -32177,17 +32223,17 @@
         <v>1000</v>
       </c>
       <c r="N71" s="51">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="O71" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P71" s="52">
-        <v>6.9999999999999999E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q71" s="52">
         <f t="shared" ref="Q71:Q72" si="29">P71*N71</f>
-        <v>6.9999999999999993E-2</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="R71" s="51"/>
       <c r="S71" s="59"/>
@@ -32233,17 +32279,17 @@
         <v>2000</v>
       </c>
       <c r="N72" s="51">
-        <v>50</v>
+        <v>2050</v>
       </c>
       <c r="O72" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P72" s="52">
-        <v>8.6999999999999994E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="Q72" s="52">
         <f t="shared" si="29"/>
-        <v>0.43499999999999994</v>
+        <v>12.709999999999999</v>
       </c>
       <c r="R72" s="51"/>
       <c r="S72" s="59"/>
@@ -32284,7 +32330,7 @@
       <c r="L73" s="64">
         <v>3</v>
       </c>
-      <c r="M73" s="51">
+      <c r="M73" s="64">
         <f t="shared" si="2"/>
         <v>3000</v>
       </c>
@@ -32346,17 +32392,17 @@
         <v>1000</v>
       </c>
       <c r="N74" s="51">
-        <v>10</v>
+        <v>1005</v>
       </c>
       <c r="O74" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P74" s="52">
-        <v>0.1275</v>
+        <v>8.09E-2</v>
       </c>
       <c r="Q74" s="52">
         <f t="shared" ref="Q74" si="30">P74*N74</f>
-        <v>1.2749999999999999</v>
+        <v>81.304500000000004</v>
       </c>
       <c r="R74" s="51"/>
       <c r="S74" s="59"/>
@@ -32402,17 +32448,17 @@
         <v>1000</v>
       </c>
       <c r="N75" s="37">
-        <v>6</v>
+        <v>1001</v>
       </c>
       <c r="O75" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P75" s="38">
-        <v>0.82569999999999999</v>
+        <v>0.42959999999999998</v>
       </c>
       <c r="Q75" s="38">
         <f>P75*N75</f>
-        <v>4.9542000000000002</v>
+        <v>430.02959999999996</v>
       </c>
       <c r="R75" s="37"/>
       <c r="S75" s="59"/>
@@ -32458,17 +32504,17 @@
         <v>1000</v>
       </c>
       <c r="N76" s="51">
-        <v>6</v>
+        <v>1001</v>
       </c>
       <c r="O76" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P76" s="52">
-        <v>0.70009999999999994</v>
+        <v>0.39460000000000001</v>
       </c>
       <c r="Q76" s="52">
         <f t="shared" ref="Q76" si="32">P76*N76</f>
-        <v>4.2005999999999997</v>
+        <v>394.99459999999999</v>
       </c>
       <c r="R76" s="51"/>
       <c r="S76" s="59"/>
@@ -32514,17 +32560,17 @@
         <v>1000</v>
       </c>
       <c r="N77" s="37">
-        <v>10</v>
+        <v>1005</v>
       </c>
       <c r="O77" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P77" s="38">
-        <v>0.32279999999999998</v>
+        <v>0.18110000000000001</v>
       </c>
       <c r="Q77" s="38">
         <f>P77*N77</f>
-        <v>3.2279999999999998</v>
+        <v>182.00550000000001</v>
       </c>
       <c r="R77" s="37"/>
       <c r="S77" s="59"/>
@@ -32570,17 +32616,17 @@
         <v>1000</v>
       </c>
       <c r="N78" s="51">
-        <v>6</v>
+        <v>1001</v>
       </c>
       <c r="O78" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P78" s="52">
-        <v>1.3062</v>
+        <v>0.79390000000000005</v>
       </c>
       <c r="Q78" s="52">
         <f t="shared" ref="Q78" si="33">P78*N78</f>
-        <v>7.8372000000000002</v>
+        <v>794.6939000000001</v>
       </c>
       <c r="R78" s="51"/>
       <c r="S78" s="59"/>
@@ -32624,22 +32670,22 @@
         <v>1000</v>
       </c>
       <c r="N79" s="37">
-        <v>6</v>
+        <v>1001</v>
       </c>
       <c r="O79" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P79" s="38">
-        <v>0.3644</v>
+        <v>0.20369999999999999</v>
       </c>
       <c r="Q79" s="38">
         <f>P79*N79</f>
-        <v>2.1863999999999999</v>
+        <v>203.90369999999999</v>
       </c>
       <c r="R79" s="37"/>
       <c r="S79" s="59"/>
     </row>
-    <row r="80" spans="1:19" s="70" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" s="70" customFormat="1" ht="24" x14ac:dyDescent="0.25">
       <c r="A80" s="69"/>
       <c r="B80" s="47">
         <f t="shared" si="0"/>
@@ -32680,7 +32726,7 @@
         <v>1000</v>
       </c>
       <c r="N80" s="51">
-        <v>6</v>
+        <v>1001</v>
       </c>
       <c r="O80" s="60" t="s">
         <v>452</v>
@@ -32690,12 +32736,12 @@
       </c>
       <c r="Q80" s="52">
         <f t="shared" ref="Q80" si="34">P80*N80</f>
-        <v>15.059999999999999</v>
+        <v>2512.5099999999998</v>
       </c>
       <c r="R80" s="51"/>
       <c r="S80" s="59"/>
     </row>
-    <row r="81" spans="1:19" s="70" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="69"/>
       <c r="B81" s="46">
         <f>ROW(B81) - ROW($B$9)</f>
@@ -32736,17 +32782,17 @@
         <v>1000</v>
       </c>
       <c r="N81" s="37">
-        <v>6</v>
+        <v>1001</v>
       </c>
       <c r="O81" s="60" t="s">
         <v>452</v>
       </c>
       <c r="P81" s="38">
-        <v>3.4329999999999998</v>
+        <v>1.7164999999999999</v>
       </c>
       <c r="Q81" s="38">
         <f>P81*N81</f>
-        <v>20.597999999999999</v>
+        <v>1718.2165</v>
       </c>
       <c r="R81" s="37"/>
       <c r="S81" s="59"/>
@@ -32790,22 +32836,22 @@
         <v>1000</v>
       </c>
       <c r="N82" s="51">
-        <v>6</v>
+        <v>1001</v>
       </c>
       <c r="O82" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P82" s="52">
-        <v>4.6247999999999996</v>
+        <v>2.8616000000000001</v>
       </c>
       <c r="Q82" s="52">
         <f t="shared" ref="Q82" si="35">P82*N82</f>
-        <v>27.748799999999996</v>
+        <v>2864.4616000000001</v>
       </c>
       <c r="R82" s="51"/>
       <c r="S82" s="59"/>
     </row>
-    <row r="83" spans="1:19" s="70" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="69"/>
       <c r="B83" s="46">
         <f>ROW(B83) - ROW($B$9)</f>
@@ -32846,7 +32892,7 @@
         <v>1000</v>
       </c>
       <c r="N83" s="37">
-        <v>6</v>
+        <v>1001</v>
       </c>
       <c r="O83" s="60" t="s">
         <v>452</v>
@@ -32856,7 +32902,7 @@
       </c>
       <c r="Q83" s="38">
         <f>P83*N83</f>
-        <v>47.400000000000006</v>
+        <v>7907.9000000000005</v>
       </c>
       <c r="R83" s="63"/>
       <c r="S83" s="59"/>
@@ -32902,17 +32948,17 @@
         <v>3000</v>
       </c>
       <c r="N84" s="51">
-        <v>16</v>
+        <v>3002</v>
       </c>
       <c r="O84" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P84" s="52">
-        <v>1.7437</v>
+        <v>1.0834999999999999</v>
       </c>
       <c r="Q84" s="52">
         <f t="shared" ref="Q84" si="36">P84*N84</f>
-        <v>27.8992</v>
+        <v>3252.6669999999999</v>
       </c>
       <c r="R84" s="51"/>
       <c r="S84" s="59"/>
@@ -32958,17 +33004,17 @@
         <v>1000</v>
       </c>
       <c r="N85" s="37">
-        <v>10</v>
+        <v>1005</v>
       </c>
       <c r="O85" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P85" s="38">
-        <v>7.7799999999999994E-2</v>
+        <v>4.9299999999999997E-2</v>
       </c>
       <c r="Q85" s="38">
         <f>P85*N85</f>
-        <v>0.77799999999999991</v>
+        <v>49.546499999999995</v>
       </c>
       <c r="R85" s="37"/>
       <c r="S85" s="59"/>
@@ -33014,17 +33060,17 @@
         <v>1000</v>
       </c>
       <c r="N86" s="51">
-        <v>6</v>
+        <v>1001</v>
       </c>
       <c r="O86" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P86" s="52">
-        <v>0.77800000000000002</v>
+        <v>0.49959999999999999</v>
       </c>
       <c r="Q86" s="52">
         <f t="shared" ref="Q86" si="37">P86*N86</f>
-        <v>4.6680000000000001</v>
+        <v>500.09960000000001</v>
       </c>
       <c r="R86" s="51"/>
       <c r="S86" s="59"/>
@@ -33070,17 +33116,17 @@
         <v>1000</v>
       </c>
       <c r="N87" s="37">
-        <v>6</v>
+        <v>1005</v>
       </c>
       <c r="O87" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P87" s="38">
-        <v>0.41049999999999998</v>
+        <v>0.2026</v>
       </c>
       <c r="Q87" s="38">
         <f>P87*N87</f>
-        <v>2.4630000000000001</v>
+        <v>203.613</v>
       </c>
       <c r="R87" s="37"/>
       <c r="S87" s="59"/>
@@ -33126,17 +33172,17 @@
         <v>1000</v>
       </c>
       <c r="N88" s="51">
-        <v>6</v>
+        <v>1001</v>
       </c>
       <c r="O88" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P88" s="52">
-        <v>1.1837</v>
+        <v>0.7167</v>
       </c>
       <c r="Q88" s="52">
         <f t="shared" ref="Q88" si="38">P88*N88</f>
-        <v>7.1021999999999998</v>
+        <v>717.41669999999999</v>
       </c>
       <c r="R88" s="51"/>
       <c r="S88" s="59"/>
@@ -33182,17 +33228,17 @@
         <v>1000</v>
       </c>
       <c r="N89" s="37">
-        <v>6</v>
+        <v>1001</v>
       </c>
       <c r="O89" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P89" s="38">
-        <v>1.2107000000000001</v>
+        <v>0.77159999999999995</v>
       </c>
       <c r="Q89" s="38">
         <f>P89*N89</f>
-        <v>7.2642000000000007</v>
+        <v>772.37159999999994</v>
       </c>
       <c r="R89" s="37"/>
       <c r="S89" s="59"/>
@@ -33238,17 +33284,17 @@
         <v>1000</v>
       </c>
       <c r="N90" s="51">
-        <v>10</v>
+        <v>1005</v>
       </c>
       <c r="O90" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P90" s="52">
-        <v>0.08</v>
+        <v>5.3699999999999998E-2</v>
       </c>
       <c r="Q90" s="52">
         <f t="shared" ref="Q90" si="39">P90*N90</f>
-        <v>0.8</v>
+        <v>53.968499999999999</v>
       </c>
       <c r="R90" s="51"/>
       <c r="S90" s="59"/>
@@ -33294,17 +33340,17 @@
         <v>1000</v>
       </c>
       <c r="N91" s="37">
-        <v>10</v>
+        <v>1005</v>
       </c>
       <c r="O91" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P91" s="38">
-        <v>0.1065</v>
+        <v>5.7099999999999998E-2</v>
       </c>
       <c r="Q91" s="38">
         <f>P91*N91</f>
-        <v>1.0649999999999999</v>
+        <v>57.3855</v>
       </c>
       <c r="R91" s="37"/>
       <c r="S91" s="39"/>
@@ -33350,17 +33396,17 @@
         <v>1000</v>
       </c>
       <c r="N92" s="37">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="O92" s="60" t="s">
         <v>435</v>
       </c>
       <c r="P92" s="38">
-        <v>1.1609</v>
+        <v>0.89639999999999997</v>
       </c>
       <c r="Q92" s="38">
         <f>P92*N92</f>
-        <v>5.8045</v>
+        <v>896.4</v>
       </c>
       <c r="R92" s="37"/>
       <c r="S92" s="39"/>
@@ -33379,17 +33425,17 @@
       <c r="K93" s="45"/>
       <c r="L93" s="45"/>
       <c r="M93" s="45"/>
-      <c r="N93" s="90" t="s">
+      <c r="N93" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="O93" s="91"/>
-      <c r="P93" s="91"/>
+      <c r="O93" s="98"/>
+      <c r="P93" s="98"/>
       <c r="Q93" s="48">
         <f>SUM(Q10:Q92)</f>
-        <v>290.3445000000001</v>
-      </c>
-      <c r="R93" s="86"/>
-      <c r="S93" s="87"/>
+        <v>34552.456899999997</v>
+      </c>
+      <c r="R93" s="93"/>
+      <c r="S93" s="94"/>
     </row>
     <row r="94" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
@@ -33405,17 +33451,17 @@
       <c r="K94" s="10"/>
       <c r="L94" s="10"/>
       <c r="M94" s="10"/>
-      <c r="N94" s="90" t="s">
+      <c r="N94" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="O94" s="91"/>
-      <c r="P94" s="91"/>
+      <c r="O94" s="98"/>
+      <c r="P94" s="98"/>
       <c r="Q94" s="49">
         <f>Q93/1000</f>
-        <v>0.29034450000000012</v>
-      </c>
-      <c r="R94" s="88"/>
-      <c r="S94" s="89"/>
+        <v>34.552456899999996</v>
+      </c>
+      <c r="R94" s="95"/>
+      <c r="S94" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -33429,83 +33475,83 @@
     <hyperlink ref="O43" r:id="rId1"/>
     <hyperlink ref="O72" r:id="rId2"/>
     <hyperlink ref="O91" r:id="rId3"/>
-    <hyperlink ref="O41" r:id="rId4" display="LCSC"/>
-    <hyperlink ref="O18" r:id="rId5"/>
-    <hyperlink ref="O16" r:id="rId6"/>
-    <hyperlink ref="O83" r:id="rId7"/>
-    <hyperlink ref="O81" r:id="rId8"/>
-    <hyperlink ref="O80" r:id="rId9"/>
-    <hyperlink ref="O67" r:id="rId10"/>
-    <hyperlink ref="O57" r:id="rId11"/>
-    <hyperlink ref="O54" r:id="rId12"/>
-    <hyperlink ref="O50" r:id="rId13"/>
-    <hyperlink ref="O27" r:id="rId14"/>
-    <hyperlink ref="O26" r:id="rId15"/>
-    <hyperlink ref="O20" r:id="rId16"/>
-    <hyperlink ref="O74" r:id="rId17"/>
-    <hyperlink ref="O90" r:id="rId18"/>
-    <hyperlink ref="O89" r:id="rId19"/>
-    <hyperlink ref="O88" r:id="rId20"/>
-    <hyperlink ref="O87" r:id="rId21"/>
-    <hyperlink ref="O86" r:id="rId22"/>
-    <hyperlink ref="O85" r:id="rId23"/>
-    <hyperlink ref="O84" r:id="rId24"/>
-    <hyperlink ref="O82" r:id="rId25"/>
-    <hyperlink ref="O79" r:id="rId26"/>
-    <hyperlink ref="O78" r:id="rId27"/>
-    <hyperlink ref="O77" r:id="rId28"/>
-    <hyperlink ref="O76" r:id="rId29"/>
-    <hyperlink ref="O75" r:id="rId30"/>
-    <hyperlink ref="O71" r:id="rId31"/>
-    <hyperlink ref="O70" r:id="rId32"/>
-    <hyperlink ref="O69" r:id="rId33"/>
-    <hyperlink ref="O68" r:id="rId34"/>
-    <hyperlink ref="O61" r:id="rId35"/>
-    <hyperlink ref="O66" r:id="rId36"/>
-    <hyperlink ref="O65" r:id="rId37"/>
-    <hyperlink ref="O64" r:id="rId38"/>
-    <hyperlink ref="O63" r:id="rId39"/>
-    <hyperlink ref="O60" r:id="rId40"/>
-    <hyperlink ref="O59" r:id="rId41"/>
-    <hyperlink ref="O58" r:id="rId42"/>
-    <hyperlink ref="O56" r:id="rId43"/>
-    <hyperlink ref="O55" r:id="rId44"/>
-    <hyperlink ref="O53" r:id="rId45"/>
-    <hyperlink ref="O52" r:id="rId46"/>
-    <hyperlink ref="O51" r:id="rId47"/>
-    <hyperlink ref="O49" r:id="rId48"/>
-    <hyperlink ref="O47" r:id="rId49"/>
-    <hyperlink ref="O46" r:id="rId50"/>
-    <hyperlink ref="O45" r:id="rId51"/>
-    <hyperlink ref="O44" r:id="rId52"/>
-    <hyperlink ref="O42" r:id="rId53"/>
-    <hyperlink ref="O40" r:id="rId54"/>
-    <hyperlink ref="O38" r:id="rId55"/>
-    <hyperlink ref="O37" r:id="rId56"/>
-    <hyperlink ref="O36" r:id="rId57"/>
-    <hyperlink ref="O35" r:id="rId58"/>
-    <hyperlink ref="O34" r:id="rId59"/>
-    <hyperlink ref="O33" r:id="rId60"/>
-    <hyperlink ref="O32" r:id="rId61"/>
-    <hyperlink ref="O31" r:id="rId62"/>
-    <hyperlink ref="O30" r:id="rId63"/>
-    <hyperlink ref="O29" r:id="rId64"/>
-    <hyperlink ref="O28" r:id="rId65"/>
-    <hyperlink ref="O25" r:id="rId66"/>
-    <hyperlink ref="O24" r:id="rId67"/>
-    <hyperlink ref="O23" r:id="rId68"/>
-    <hyperlink ref="O21" r:id="rId69"/>
-    <hyperlink ref="O22" r:id="rId70"/>
-    <hyperlink ref="O19" r:id="rId71"/>
-    <hyperlink ref="O17" r:id="rId72"/>
-    <hyperlink ref="O14" r:id="rId73"/>
-    <hyperlink ref="O13" r:id="rId74"/>
-    <hyperlink ref="O12" r:id="rId75"/>
-    <hyperlink ref="O11" r:id="rId76"/>
-    <hyperlink ref="O15" r:id="rId77"/>
-    <hyperlink ref="O39" r:id="rId78"/>
-    <hyperlink ref="O62" r:id="rId79"/>
-    <hyperlink ref="O92" r:id="rId80"/>
+    <hyperlink ref="O18" r:id="rId4"/>
+    <hyperlink ref="O16" r:id="rId5"/>
+    <hyperlink ref="O83" r:id="rId6"/>
+    <hyperlink ref="O81" r:id="rId7"/>
+    <hyperlink ref="O80" r:id="rId8"/>
+    <hyperlink ref="O67" r:id="rId9"/>
+    <hyperlink ref="O57" r:id="rId10"/>
+    <hyperlink ref="O54" r:id="rId11"/>
+    <hyperlink ref="O50" r:id="rId12"/>
+    <hyperlink ref="O27" r:id="rId13"/>
+    <hyperlink ref="O26" r:id="rId14"/>
+    <hyperlink ref="O20" r:id="rId15"/>
+    <hyperlink ref="O74" r:id="rId16"/>
+    <hyperlink ref="O90" r:id="rId17"/>
+    <hyperlink ref="O89" r:id="rId18"/>
+    <hyperlink ref="O88" r:id="rId19"/>
+    <hyperlink ref="O87" r:id="rId20"/>
+    <hyperlink ref="O86" r:id="rId21"/>
+    <hyperlink ref="O85" r:id="rId22"/>
+    <hyperlink ref="O84" r:id="rId23"/>
+    <hyperlink ref="O82" r:id="rId24"/>
+    <hyperlink ref="O79" r:id="rId25"/>
+    <hyperlink ref="O78" r:id="rId26"/>
+    <hyperlink ref="O77" r:id="rId27"/>
+    <hyperlink ref="O76" r:id="rId28"/>
+    <hyperlink ref="O75" r:id="rId29"/>
+    <hyperlink ref="O71" r:id="rId30"/>
+    <hyperlink ref="O70" r:id="rId31"/>
+    <hyperlink ref="O69" r:id="rId32"/>
+    <hyperlink ref="O68" r:id="rId33"/>
+    <hyperlink ref="O61" r:id="rId34"/>
+    <hyperlink ref="O66" r:id="rId35"/>
+    <hyperlink ref="O65" r:id="rId36"/>
+    <hyperlink ref="O64" r:id="rId37"/>
+    <hyperlink ref="O63" r:id="rId38"/>
+    <hyperlink ref="O60" r:id="rId39"/>
+    <hyperlink ref="O59" r:id="rId40"/>
+    <hyperlink ref="O58" r:id="rId41"/>
+    <hyperlink ref="O56" r:id="rId42"/>
+    <hyperlink ref="O55" r:id="rId43"/>
+    <hyperlink ref="O53" r:id="rId44"/>
+    <hyperlink ref="O52" r:id="rId45"/>
+    <hyperlink ref="O51" r:id="rId46"/>
+    <hyperlink ref="O49" r:id="rId47"/>
+    <hyperlink ref="O47" r:id="rId48"/>
+    <hyperlink ref="O46" r:id="rId49"/>
+    <hyperlink ref="O45" r:id="rId50"/>
+    <hyperlink ref="O44" r:id="rId51"/>
+    <hyperlink ref="O42" r:id="rId52"/>
+    <hyperlink ref="O40" r:id="rId53"/>
+    <hyperlink ref="O38" r:id="rId54"/>
+    <hyperlink ref="O37" r:id="rId55"/>
+    <hyperlink ref="O36" r:id="rId56"/>
+    <hyperlink ref="O35" r:id="rId57"/>
+    <hyperlink ref="O34" r:id="rId58"/>
+    <hyperlink ref="O33" r:id="rId59"/>
+    <hyperlink ref="O32" r:id="rId60"/>
+    <hyperlink ref="O31" r:id="rId61"/>
+    <hyperlink ref="O30" r:id="rId62"/>
+    <hyperlink ref="O29" r:id="rId63"/>
+    <hyperlink ref="O28" r:id="rId64"/>
+    <hyperlink ref="O25" r:id="rId65"/>
+    <hyperlink ref="O24" r:id="rId66"/>
+    <hyperlink ref="O23" r:id="rId67"/>
+    <hyperlink ref="O21" r:id="rId68"/>
+    <hyperlink ref="O22" r:id="rId69"/>
+    <hyperlink ref="O19" r:id="rId70"/>
+    <hyperlink ref="O17" r:id="rId71"/>
+    <hyperlink ref="O14" r:id="rId72"/>
+    <hyperlink ref="O13" r:id="rId73"/>
+    <hyperlink ref="O12" r:id="rId74"/>
+    <hyperlink ref="O11" r:id="rId75"/>
+    <hyperlink ref="O15" r:id="rId76"/>
+    <hyperlink ref="O39" r:id="rId77"/>
+    <hyperlink ref="O62" r:id="rId78"/>
+    <hyperlink ref="O92" r:id="rId79"/>
+    <hyperlink ref="O41" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId81"/>

--- a/Design Files/Baseboard-v2.0/BOM/eSpark_BOM_Baseboard-v2.0.xlsx
+++ b/Design Files/Baseboard-v2.0/BOM/eSpark_BOM_Baseboard-v2.0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5194" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5248" uniqueCount="530">
   <si>
     <t>Component list</t>
   </si>
@@ -1605,6 +1605,27 @@
   </si>
   <si>
     <t>C20, C25, C48</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">DIA 2mm Light Pipe Plastic LED Light Pipe RoHS Light Pipe Guide PDPLC-2.0-Series </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(PDPLC-2.0-2.54)</t>
+    </r>
+  </si>
+  <si>
+    <t>PDPLC-2.0-2.54</t>
   </si>
 </sst>
 </file>
@@ -1616,7 +1637,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1811,6 +1832,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2997,7 +3025,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA94"/>
+  <dimension ref="A1:AA95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -3013,7 +3041,7 @@
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.28515625" customWidth="1"/>
+    <col min="15" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -8218,73 +8246,127 @@
       <c r="R92" s="77"/>
       <c r="S92" s="80"/>
     </row>
-    <row r="93" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="1"/>
-      <c r="B93" s="40"/>
-      <c r="C93" s="41"/>
-      <c r="D93" s="42"/>
-      <c r="E93" s="43"/>
-      <c r="F93" s="44"/>
-      <c r="G93" s="45"/>
-      <c r="H93" s="44"/>
-      <c r="I93" s="45"/>
-      <c r="J93" s="44"/>
-      <c r="K93" s="45"/>
-      <c r="L93" s="45"/>
-      <c r="M93" s="45"/>
-      <c r="N93" s="99" t="s">
+    <row r="93" spans="1:27" s="81" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="74"/>
+      <c r="B93" s="75">
+        <f>ROW(B93) - ROW($B$9)</f>
+        <v>84</v>
+      </c>
+      <c r="C93" s="76" t="s">
+        <v>495</v>
+      </c>
+      <c r="D93" s="77"/>
+      <c r="E93" s="37" t="s">
+        <v>528</v>
+      </c>
+      <c r="F93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="G93" s="77" t="s">
+        <v>529</v>
+      </c>
+      <c r="H93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="I93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="J93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="K93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="L93" s="77">
+        <v>1</v>
+      </c>
+      <c r="M93" s="77">
+        <f>L93*5</f>
         <v>5</v>
       </c>
-      <c r="O93" s="100"/>
-      <c r="P93" s="100"/>
-      <c r="Q93" s="48">
-        <f>SUM(Q10:Q92)</f>
-        <v>290.3445000000001</v>
-      </c>
-      <c r="R93" s="95"/>
-      <c r="S93" s="96"/>
-      <c r="U93" s="70"/>
-      <c r="V93" s="70"/>
-      <c r="W93" s="70"/>
-      <c r="X93" s="70"/>
+      <c r="N93" s="77">
+        <v>50</v>
+      </c>
+      <c r="O93" s="78" t="s">
+        <v>527</v>
+      </c>
+      <c r="P93" s="79">
+        <v>10.98</v>
+      </c>
+      <c r="Q93" s="79">
+        <f>P93*N93</f>
+        <v>549</v>
+      </c>
+      <c r="R93" s="77"/>
+      <c r="S93" s="80"/>
     </row>
     <row r="94" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
-      <c r="B94" s="25"/>
-      <c r="C94" s="36"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="10"/>
-      <c r="I94" s="10"/>
-      <c r="J94" s="10"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="10"/>
+      <c r="B94" s="40"/>
+      <c r="C94" s="41"/>
+      <c r="D94" s="42"/>
+      <c r="E94" s="43"/>
+      <c r="F94" s="44"/>
+      <c r="G94" s="45"/>
+      <c r="H94" s="44"/>
+      <c r="I94" s="45"/>
+      <c r="J94" s="44"/>
+      <c r="K94" s="45"/>
+      <c r="L94" s="45"/>
+      <c r="M94" s="45"/>
       <c r="N94" s="99" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O94" s="100"/>
       <c r="P94" s="100"/>
-      <c r="Q94" s="49">
-        <f>Q93/5</f>
-        <v>58.068900000000021</v>
-      </c>
-      <c r="R94" s="97"/>
-      <c r="S94" s="98"/>
+      <c r="Q94" s="48">
+        <f>SUM(Q10:Q93)</f>
+        <v>839.34450000000015</v>
+      </c>
+      <c r="R94" s="95"/>
+      <c r="S94" s="96"/>
       <c r="U94" s="70"/>
       <c r="V94" s="70"/>
       <c r="W94" s="70"/>
       <c r="X94" s="70"/>
     </row>
+    <row r="95" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="1"/>
+      <c r="B95" s="25"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="10"/>
+      <c r="F95" s="10"/>
+      <c r="G95" s="10"/>
+      <c r="H95" s="10"/>
+      <c r="I95" s="10"/>
+      <c r="J95" s="10"/>
+      <c r="K95" s="10"/>
+      <c r="L95" s="10"/>
+      <c r="M95" s="10"/>
+      <c r="N95" s="99" t="s">
+        <v>6</v>
+      </c>
+      <c r="O95" s="100"/>
+      <c r="P95" s="100"/>
+      <c r="Q95" s="49">
+        <f>Q94/5</f>
+        <v>167.86890000000002</v>
+      </c>
+      <c r="R95" s="97"/>
+      <c r="S95" s="98"/>
+      <c r="U95" s="70"/>
+      <c r="V95" s="70"/>
+      <c r="W95" s="70"/>
+      <c r="X95" s="70"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R93:S94"/>
-    <mergeCell ref="N93:P93"/>
+    <mergeCell ref="R94:S95"/>
     <mergeCell ref="N94:P94"/>
+    <mergeCell ref="N95:P95"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O43" r:id="rId1"/>
@@ -8367,16 +8449,17 @@
     <hyperlink ref="O39" r:id="rId78"/>
     <hyperlink ref="O62" r:id="rId79"/>
     <hyperlink ref="O92" r:id="rId80"/>
+    <hyperlink ref="O93" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId81"/>
-  <drawing r:id="rId82"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId82"/>
+  <drawing r:id="rId83"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S94"/>
+  <dimension ref="A1:S95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -12313,7 +12396,7 @@
         <v>1</v>
       </c>
       <c r="M75" s="67">
-        <f t="shared" ref="M75:M92" si="31">L75*20</f>
+        <f t="shared" ref="M75:M93" si="31">L75*20</f>
         <v>20</v>
       </c>
       <c r="N75" s="37">
@@ -13280,65 +13363,119 @@
       <c r="R92" s="37"/>
       <c r="S92" s="39"/>
     </row>
-    <row r="93" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="1"/>
-      <c r="B93" s="40"/>
-      <c r="C93" s="41"/>
-      <c r="D93" s="42"/>
-      <c r="E93" s="43"/>
-      <c r="F93" s="44"/>
-      <c r="G93" s="45"/>
-      <c r="H93" s="44"/>
-      <c r="I93" s="45"/>
-      <c r="J93" s="44"/>
-      <c r="K93" s="45"/>
-      <c r="L93" s="45"/>
-      <c r="M93" s="45"/>
-      <c r="N93" s="99" t="s">
-        <v>5</v>
-      </c>
-      <c r="O93" s="100"/>
-      <c r="P93" s="100"/>
-      <c r="Q93" s="48">
-        <f>SUM(Q10:Q92)</f>
-        <v>921.62700000000007</v>
-      </c>
-      <c r="R93" s="95"/>
-      <c r="S93" s="96"/>
+    <row r="93" spans="1:19" s="81" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="74"/>
+      <c r="B93" s="75">
+        <f>ROW(B93) - ROW($B$9)</f>
+        <v>84</v>
+      </c>
+      <c r="C93" s="76" t="s">
+        <v>495</v>
+      </c>
+      <c r="D93" s="77"/>
+      <c r="E93" s="37" t="s">
+        <v>528</v>
+      </c>
+      <c r="F93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="G93" s="77" t="s">
+        <v>529</v>
+      </c>
+      <c r="H93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="I93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="J93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="K93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="L93" s="77">
+        <v>1</v>
+      </c>
+      <c r="M93" s="67">
+        <f t="shared" si="31"/>
+        <v>20</v>
+      </c>
+      <c r="N93" s="77">
+        <v>50</v>
+      </c>
+      <c r="O93" s="78" t="s">
+        <v>527</v>
+      </c>
+      <c r="P93" s="79">
+        <v>10.98</v>
+      </c>
+      <c r="Q93" s="79">
+        <f>P93*N93</f>
+        <v>549</v>
+      </c>
+      <c r="R93" s="77"/>
+      <c r="S93" s="80"/>
     </row>
     <row r="94" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
-      <c r="B94" s="25"/>
-      <c r="C94" s="36"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="10"/>
-      <c r="I94" s="10"/>
-      <c r="J94" s="10"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="10"/>
+      <c r="B94" s="40"/>
+      <c r="C94" s="41"/>
+      <c r="D94" s="42"/>
+      <c r="E94" s="43"/>
+      <c r="F94" s="44"/>
+      <c r="G94" s="45"/>
+      <c r="H94" s="44"/>
+      <c r="I94" s="45"/>
+      <c r="J94" s="44"/>
+      <c r="K94" s="45"/>
+      <c r="L94" s="45"/>
+      <c r="M94" s="45"/>
       <c r="N94" s="99" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O94" s="100"/>
       <c r="P94" s="100"/>
-      <c r="Q94" s="49">
-        <f>Q93/20</f>
-        <v>46.08135</v>
-      </c>
-      <c r="R94" s="97"/>
-      <c r="S94" s="98"/>
+      <c r="Q94" s="48">
+        <f>SUM(Q10:Q93)</f>
+        <v>1470.627</v>
+      </c>
+      <c r="R94" s="95"/>
+      <c r="S94" s="96"/>
+    </row>
+    <row r="95" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="1"/>
+      <c r="B95" s="25"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="10"/>
+      <c r="F95" s="10"/>
+      <c r="G95" s="10"/>
+      <c r="H95" s="10"/>
+      <c r="I95" s="10"/>
+      <c r="J95" s="10"/>
+      <c r="K95" s="10"/>
+      <c r="L95" s="10"/>
+      <c r="M95" s="10"/>
+      <c r="N95" s="99" t="s">
+        <v>6</v>
+      </c>
+      <c r="O95" s="100"/>
+      <c r="P95" s="100"/>
+      <c r="Q95" s="49">
+        <f>Q94/20</f>
+        <v>73.531350000000003</v>
+      </c>
+      <c r="R95" s="97"/>
+      <c r="S95" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N93:P93"/>
-    <mergeCell ref="R93:S94"/>
     <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R94:S95"/>
+    <mergeCell ref="N95:P95"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O43" r:id="rId1"/>
@@ -13421,16 +13558,17 @@
     <hyperlink ref="O62" r:id="rId78"/>
     <hyperlink ref="O92" r:id="rId79"/>
     <hyperlink ref="O41" r:id="rId80"/>
+    <hyperlink ref="O93" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId81"/>
-  <drawing r:id="rId82"/>
+  <pageSetup orientation="portrait" r:id="rId82"/>
+  <drawing r:id="rId83"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S94"/>
+  <dimension ref="A1:S95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -17420,7 +17558,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="51">
-        <f t="shared" ref="M76:M92" si="31">L76*50</f>
+        <f t="shared" ref="M76:M93" si="31">L76*50</f>
         <v>50</v>
       </c>
       <c r="N76" s="51">
@@ -18331,65 +18469,119 @@
       <c r="R92" s="37"/>
       <c r="S92" s="39"/>
     </row>
-    <row r="93" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="1"/>
-      <c r="B93" s="40"/>
-      <c r="C93" s="41"/>
-      <c r="D93" s="42"/>
-      <c r="E93" s="43"/>
-      <c r="F93" s="44"/>
-      <c r="G93" s="45"/>
-      <c r="H93" s="44"/>
-      <c r="I93" s="45"/>
-      <c r="J93" s="44"/>
-      <c r="K93" s="45"/>
-      <c r="L93" s="45"/>
-      <c r="M93" s="45"/>
-      <c r="N93" s="99" t="s">
-        <v>5</v>
-      </c>
-      <c r="O93" s="100"/>
-      <c r="P93" s="100"/>
-      <c r="Q93" s="48">
-        <f>SUM(Q10:Q92)</f>
-        <v>2031.4022999999997</v>
-      </c>
-      <c r="R93" s="95"/>
-      <c r="S93" s="96"/>
+    <row r="93" spans="1:19" s="81" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="74"/>
+      <c r="B93" s="75">
+        <f>ROW(B93) - ROW($B$9)</f>
+        <v>84</v>
+      </c>
+      <c r="C93" s="76" t="s">
+        <v>495</v>
+      </c>
+      <c r="D93" s="77"/>
+      <c r="E93" s="37" t="s">
+        <v>528</v>
+      </c>
+      <c r="F93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="G93" s="77" t="s">
+        <v>529</v>
+      </c>
+      <c r="H93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="I93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="J93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="K93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="L93" s="77">
+        <v>1</v>
+      </c>
+      <c r="M93" s="51">
+        <f t="shared" si="31"/>
+        <v>50</v>
+      </c>
+      <c r="N93" s="77">
+        <v>50</v>
+      </c>
+      <c r="O93" s="78" t="s">
+        <v>527</v>
+      </c>
+      <c r="P93" s="79">
+        <v>10.98</v>
+      </c>
+      <c r="Q93" s="79">
+        <f>P93*N93</f>
+        <v>549</v>
+      </c>
+      <c r="R93" s="77"/>
+      <c r="S93" s="80"/>
     </row>
     <row r="94" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
-      <c r="B94" s="25"/>
-      <c r="C94" s="36"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="10"/>
-      <c r="I94" s="10"/>
-      <c r="J94" s="10"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="10"/>
+      <c r="B94" s="40"/>
+      <c r="C94" s="41"/>
+      <c r="D94" s="42"/>
+      <c r="E94" s="43"/>
+      <c r="F94" s="44"/>
+      <c r="G94" s="45"/>
+      <c r="H94" s="44"/>
+      <c r="I94" s="45"/>
+      <c r="J94" s="44"/>
+      <c r="K94" s="45"/>
+      <c r="L94" s="45"/>
+      <c r="M94" s="45"/>
       <c r="N94" s="99" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O94" s="100"/>
       <c r="P94" s="100"/>
-      <c r="Q94" s="49">
-        <f>Q93/50</f>
-        <v>40.628045999999998</v>
-      </c>
-      <c r="R94" s="97"/>
-      <c r="S94" s="98"/>
+      <c r="Q94" s="48">
+        <f>SUM(Q10:Q93)</f>
+        <v>2580.4022999999997</v>
+      </c>
+      <c r="R94" s="95"/>
+      <c r="S94" s="96"/>
+    </row>
+    <row r="95" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="1"/>
+      <c r="B95" s="25"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="10"/>
+      <c r="F95" s="10"/>
+      <c r="G95" s="10"/>
+      <c r="H95" s="10"/>
+      <c r="I95" s="10"/>
+      <c r="J95" s="10"/>
+      <c r="K95" s="10"/>
+      <c r="L95" s="10"/>
+      <c r="M95" s="10"/>
+      <c r="N95" s="99" t="s">
+        <v>6</v>
+      </c>
+      <c r="O95" s="100"/>
+      <c r="P95" s="100"/>
+      <c r="Q95" s="49">
+        <f>Q94/50</f>
+        <v>51.608045999999995</v>
+      </c>
+      <c r="R95" s="97"/>
+      <c r="S95" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N93:P93"/>
-    <mergeCell ref="R93:S94"/>
     <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R94:S95"/>
+    <mergeCell ref="N95:P95"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O43" r:id="rId1"/>
@@ -18472,15 +18664,16 @@
     <hyperlink ref="O62" r:id="rId78"/>
     <hyperlink ref="O92" r:id="rId79"/>
     <hyperlink ref="O41" r:id="rId80"/>
+    <hyperlink ref="O93" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId81"/>
+  <drawing r:id="rId82"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S94"/>
+  <dimension ref="A1:S95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -22470,7 +22663,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="51">
-        <f t="shared" ref="M76:M92" si="31">L76*100</f>
+        <f t="shared" ref="M76:M93" si="31">L76*100</f>
         <v>100</v>
       </c>
       <c r="N76" s="51">
@@ -23381,65 +23574,119 @@
       <c r="R92" s="37"/>
       <c r="S92" s="39"/>
     </row>
-    <row r="93" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="1"/>
-      <c r="B93" s="40"/>
-      <c r="C93" s="41"/>
-      <c r="D93" s="42"/>
-      <c r="E93" s="43"/>
-      <c r="F93" s="44"/>
-      <c r="G93" s="45"/>
-      <c r="H93" s="44"/>
-      <c r="I93" s="45"/>
-      <c r="J93" s="44"/>
-      <c r="K93" s="45"/>
-      <c r="L93" s="45"/>
-      <c r="M93" s="45"/>
-      <c r="N93" s="99" t="s">
-        <v>5</v>
-      </c>
-      <c r="O93" s="100"/>
-      <c r="P93" s="100"/>
-      <c r="Q93" s="48">
-        <f>SUM(Q10:Q92)</f>
-        <v>3764.3973699999997</v>
-      </c>
-      <c r="R93" s="95"/>
-      <c r="S93" s="96"/>
+    <row r="93" spans="1:19" s="81" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="74"/>
+      <c r="B93" s="75">
+        <f>ROW(B93) - ROW($B$9)</f>
+        <v>84</v>
+      </c>
+      <c r="C93" s="76" t="s">
+        <v>495</v>
+      </c>
+      <c r="D93" s="77"/>
+      <c r="E93" s="37" t="s">
+        <v>528</v>
+      </c>
+      <c r="F93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="G93" s="77" t="s">
+        <v>529</v>
+      </c>
+      <c r="H93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="I93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="J93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="K93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="L93" s="77">
+        <v>1</v>
+      </c>
+      <c r="M93" s="51">
+        <f t="shared" si="31"/>
+        <v>100</v>
+      </c>
+      <c r="N93" s="77">
+        <v>100</v>
+      </c>
+      <c r="O93" s="78" t="s">
+        <v>527</v>
+      </c>
+      <c r="P93" s="79">
+        <v>10.98</v>
+      </c>
+      <c r="Q93" s="79">
+        <f>P93*N93</f>
+        <v>1098</v>
+      </c>
+      <c r="R93" s="77"/>
+      <c r="S93" s="80"/>
     </row>
     <row r="94" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
-      <c r="B94" s="25"/>
-      <c r="C94" s="36"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="10"/>
-      <c r="I94" s="10"/>
-      <c r="J94" s="10"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="10"/>
+      <c r="B94" s="40"/>
+      <c r="C94" s="41"/>
+      <c r="D94" s="42"/>
+      <c r="E94" s="43"/>
+      <c r="F94" s="44"/>
+      <c r="G94" s="45"/>
+      <c r="H94" s="44"/>
+      <c r="I94" s="45"/>
+      <c r="J94" s="44"/>
+      <c r="K94" s="45"/>
+      <c r="L94" s="45"/>
+      <c r="M94" s="45"/>
       <c r="N94" s="99" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O94" s="100"/>
       <c r="P94" s="100"/>
-      <c r="Q94" s="49">
-        <f>Q93/100</f>
-        <v>37.643973699999997</v>
-      </c>
-      <c r="R94" s="97"/>
-      <c r="S94" s="98"/>
+      <c r="Q94" s="48">
+        <f>SUM(Q10:Q93)</f>
+        <v>4862.3973699999997</v>
+      </c>
+      <c r="R94" s="95"/>
+      <c r="S94" s="96"/>
+    </row>
+    <row r="95" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="1"/>
+      <c r="B95" s="25"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="10"/>
+      <c r="F95" s="10"/>
+      <c r="G95" s="10"/>
+      <c r="H95" s="10"/>
+      <c r="I95" s="10"/>
+      <c r="J95" s="10"/>
+      <c r="K95" s="10"/>
+      <c r="L95" s="10"/>
+      <c r="M95" s="10"/>
+      <c r="N95" s="99" t="s">
+        <v>6</v>
+      </c>
+      <c r="O95" s="100"/>
+      <c r="P95" s="100"/>
+      <c r="Q95" s="49">
+        <f>Q94/100</f>
+        <v>48.623973699999993</v>
+      </c>
+      <c r="R95" s="97"/>
+      <c r="S95" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N93:P93"/>
-    <mergeCell ref="R93:S94"/>
     <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R94:S95"/>
+    <mergeCell ref="N95:P95"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O43" r:id="rId1"/>
@@ -23522,15 +23769,16 @@
     <hyperlink ref="O62" r:id="rId78"/>
     <hyperlink ref="O92" r:id="rId79"/>
     <hyperlink ref="O41" r:id="rId80"/>
+    <hyperlink ref="O93" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId81"/>
+  <drawing r:id="rId82"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S94"/>
+  <dimension ref="A1:S95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -27520,7 +27768,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="51">
-        <f t="shared" ref="M76:M92" si="31">L76*500</f>
+        <f t="shared" ref="M76:M93" si="31">L76*500</f>
         <v>500</v>
       </c>
       <c r="N76" s="51">
@@ -28431,65 +28679,119 @@
       <c r="R92" s="37"/>
       <c r="S92" s="39"/>
     </row>
-    <row r="93" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="1"/>
-      <c r="B93" s="40"/>
-      <c r="C93" s="41"/>
-      <c r="D93" s="42"/>
-      <c r="E93" s="43"/>
-      <c r="F93" s="44"/>
-      <c r="G93" s="45"/>
-      <c r="H93" s="44"/>
-      <c r="I93" s="45"/>
-      <c r="J93" s="44"/>
-      <c r="K93" s="45"/>
-      <c r="L93" s="45"/>
-      <c r="M93" s="45"/>
-      <c r="N93" s="99" t="s">
-        <v>5</v>
-      </c>
-      <c r="O93" s="100"/>
-      <c r="P93" s="100"/>
-      <c r="Q93" s="48">
-        <f>SUM(Q10:Q92)</f>
-        <v>17670.060750000001</v>
-      </c>
-      <c r="R93" s="95"/>
-      <c r="S93" s="96"/>
+    <row r="93" spans="1:19" s="81" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="74"/>
+      <c r="B93" s="75">
+        <f>ROW(B93) - ROW($B$9)</f>
+        <v>84</v>
+      </c>
+      <c r="C93" s="76" t="s">
+        <v>495</v>
+      </c>
+      <c r="D93" s="77"/>
+      <c r="E93" s="37" t="s">
+        <v>528</v>
+      </c>
+      <c r="F93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="G93" s="77" t="s">
+        <v>529</v>
+      </c>
+      <c r="H93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="I93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="J93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="K93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="L93" s="77">
+        <v>1</v>
+      </c>
+      <c r="M93" s="51">
+        <f t="shared" si="31"/>
+        <v>500</v>
+      </c>
+      <c r="N93" s="77">
+        <v>500</v>
+      </c>
+      <c r="O93" s="78" t="s">
+        <v>527</v>
+      </c>
+      <c r="P93" s="79">
+        <v>10.98</v>
+      </c>
+      <c r="Q93" s="79">
+        <f>P93*N93</f>
+        <v>5490</v>
+      </c>
+      <c r="R93" s="77"/>
+      <c r="S93" s="80"/>
     </row>
     <row r="94" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
-      <c r="B94" s="25"/>
-      <c r="C94" s="36"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="10"/>
-      <c r="I94" s="10"/>
-      <c r="J94" s="10"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="10"/>
+      <c r="B94" s="40"/>
+      <c r="C94" s="41"/>
+      <c r="D94" s="42"/>
+      <c r="E94" s="43"/>
+      <c r="F94" s="44"/>
+      <c r="G94" s="45"/>
+      <c r="H94" s="44"/>
+      <c r="I94" s="45"/>
+      <c r="J94" s="44"/>
+      <c r="K94" s="45"/>
+      <c r="L94" s="45"/>
+      <c r="M94" s="45"/>
       <c r="N94" s="99" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O94" s="100"/>
       <c r="P94" s="100"/>
-      <c r="Q94" s="49">
-        <f>Q93/500</f>
-        <v>35.340121500000002</v>
-      </c>
-      <c r="R94" s="97"/>
-      <c r="S94" s="98"/>
+      <c r="Q94" s="48">
+        <f>SUM(Q10:Q93)</f>
+        <v>23160.060750000001</v>
+      </c>
+      <c r="R94" s="95"/>
+      <c r="S94" s="96"/>
+    </row>
+    <row r="95" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="1"/>
+      <c r="B95" s="25"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="10"/>
+      <c r="F95" s="10"/>
+      <c r="G95" s="10"/>
+      <c r="H95" s="10"/>
+      <c r="I95" s="10"/>
+      <c r="J95" s="10"/>
+      <c r="K95" s="10"/>
+      <c r="L95" s="10"/>
+      <c r="M95" s="10"/>
+      <c r="N95" s="99" t="s">
+        <v>6</v>
+      </c>
+      <c r="O95" s="100"/>
+      <c r="P95" s="100"/>
+      <c r="Q95" s="49">
+        <f>Q94/500</f>
+        <v>46.320121499999999</v>
+      </c>
+      <c r="R95" s="97"/>
+      <c r="S95" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N93:P93"/>
-    <mergeCell ref="R93:S94"/>
     <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R94:S95"/>
+    <mergeCell ref="N95:P95"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O43" r:id="rId1"/>
@@ -28572,15 +28874,16 @@
     <hyperlink ref="O62" r:id="rId78"/>
     <hyperlink ref="O92" r:id="rId79"/>
     <hyperlink ref="O41" r:id="rId80"/>
+    <hyperlink ref="O93" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId81"/>
+  <drawing r:id="rId82"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S94"/>
+  <dimension ref="A1:S95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -32571,7 +32874,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="51">
-        <f t="shared" ref="M76:M92" si="31">L76*1000</f>
+        <f t="shared" ref="M76:M93" si="31">L76*1000</f>
         <v>1000</v>
       </c>
       <c r="N76" s="51">
@@ -33482,65 +33785,119 @@
       <c r="R92" s="37"/>
       <c r="S92" s="39"/>
     </row>
-    <row r="93" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="1"/>
-      <c r="B93" s="40"/>
-      <c r="C93" s="41"/>
-      <c r="D93" s="42"/>
-      <c r="E93" s="43"/>
-      <c r="F93" s="44"/>
-      <c r="G93" s="45"/>
-      <c r="H93" s="44"/>
-      <c r="I93" s="45"/>
-      <c r="J93" s="44"/>
-      <c r="K93" s="45"/>
-      <c r="L93" s="45"/>
-      <c r="M93" s="45"/>
-      <c r="N93" s="99" t="s">
-        <v>5</v>
-      </c>
-      <c r="O93" s="100"/>
-      <c r="P93" s="100"/>
-      <c r="Q93" s="48">
-        <f>SUM(Q10:Q92)</f>
-        <v>34559.7569</v>
-      </c>
-      <c r="R93" s="95"/>
-      <c r="S93" s="96"/>
+    <row r="93" spans="1:19" s="81" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="74"/>
+      <c r="B93" s="75">
+        <f>ROW(B93) - ROW($B$9)</f>
+        <v>84</v>
+      </c>
+      <c r="C93" s="76" t="s">
+        <v>495</v>
+      </c>
+      <c r="D93" s="77"/>
+      <c r="E93" s="37" t="s">
+        <v>528</v>
+      </c>
+      <c r="F93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="G93" s="77" t="s">
+        <v>529</v>
+      </c>
+      <c r="H93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="I93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="J93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="K93" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="L93" s="77">
+        <v>1</v>
+      </c>
+      <c r="M93" s="51">
+        <f t="shared" si="31"/>
+        <v>1000</v>
+      </c>
+      <c r="N93" s="77">
+        <v>1000</v>
+      </c>
+      <c r="O93" s="78" t="s">
+        <v>527</v>
+      </c>
+      <c r="P93" s="79">
+        <v>10.98</v>
+      </c>
+      <c r="Q93" s="79">
+        <f>P93*N93</f>
+        <v>10980</v>
+      </c>
+      <c r="R93" s="77"/>
+      <c r="S93" s="80"/>
     </row>
     <row r="94" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
-      <c r="B94" s="25"/>
-      <c r="C94" s="36"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="10"/>
-      <c r="H94" s="10"/>
-      <c r="I94" s="10"/>
-      <c r="J94" s="10"/>
-      <c r="K94" s="10"/>
-      <c r="L94" s="10"/>
-      <c r="M94" s="10"/>
+      <c r="B94" s="40"/>
+      <c r="C94" s="41"/>
+      <c r="D94" s="42"/>
+      <c r="E94" s="43"/>
+      <c r="F94" s="44"/>
+      <c r="G94" s="45"/>
+      <c r="H94" s="44"/>
+      <c r="I94" s="45"/>
+      <c r="J94" s="44"/>
+      <c r="K94" s="45"/>
+      <c r="L94" s="45"/>
+      <c r="M94" s="45"/>
       <c r="N94" s="99" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O94" s="100"/>
       <c r="P94" s="100"/>
-      <c r="Q94" s="49">
-        <f>Q93/1000</f>
-        <v>34.559756900000004</v>
-      </c>
-      <c r="R94" s="97"/>
-      <c r="S94" s="98"/>
+      <c r="Q94" s="48">
+        <f>SUM(Q10:Q93)</f>
+        <v>45539.7569</v>
+      </c>
+      <c r="R94" s="95"/>
+      <c r="S94" s="96"/>
+    </row>
+    <row r="95" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="1"/>
+      <c r="B95" s="25"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="10"/>
+      <c r="F95" s="10"/>
+      <c r="G95" s="10"/>
+      <c r="H95" s="10"/>
+      <c r="I95" s="10"/>
+      <c r="J95" s="10"/>
+      <c r="K95" s="10"/>
+      <c r="L95" s="10"/>
+      <c r="M95" s="10"/>
+      <c r="N95" s="99" t="s">
+        <v>6</v>
+      </c>
+      <c r="O95" s="100"/>
+      <c r="P95" s="100"/>
+      <c r="Q95" s="49">
+        <f>Q94/1000</f>
+        <v>45.5397569</v>
+      </c>
+      <c r="R95" s="97"/>
+      <c r="S95" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="N93:P93"/>
-    <mergeCell ref="R93:S94"/>
     <mergeCell ref="N94:P94"/>
+    <mergeCell ref="R94:S95"/>
+    <mergeCell ref="N95:P95"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O43" r:id="rId1"/>
@@ -33623,8 +33980,9 @@
     <hyperlink ref="O62" r:id="rId78"/>
     <hyperlink ref="O92" r:id="rId79"/>
     <hyperlink ref="O41" r:id="rId80"/>
+    <hyperlink ref="O93" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId81"/>
+  <drawing r:id="rId82"/>
 </worksheet>
 </file>